--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -527,13 +527,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Validator</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B12" t="str">
-        <v>Validador de perfis ICC</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C12" t="str">
-        <v>Validador de perfis ICC</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="13">
@@ -714,13 +714,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Validator · powered by IccProfLib</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B29" t="str">
-        <v>Validador de perfis ICC · com IccProfLib</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C29" t="str">
-        <v>Validador de perfis ICC · com IccProfLib</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="30">

--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C69"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -734,9 +734,438 @@
         <v>Erro:</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Converter para XML</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Converter para XML</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Converter para JSON</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Converter para JSON</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Converter para ICC</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Converter para ICC</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B34" t="str">
+        <v>A converter para XML…</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Convertendo para XML…</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B35" t="str">
+        <v>A converter para JSON…</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Convertendo para JSON…</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B36" t="str">
+        <v>A converter para ICC…</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Convertendo para ICC…</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Carregar perfil ICC</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Carregar perfil ICC</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Zona de largada para ficheiros de perfil ICC</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Área de soltar para arquivos de perfil ICC</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B39" t="str">
+        <v>ID do perfil</v>
+      </c>
+      <c r="C39" t="str">
+        <v>ID do perfil</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Nenhuma etiqueta encontrada.</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Nenhuma tag encontrada.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Nome da etiqueta</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Nome da tag</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B42" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C42" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Deslocamento</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Deslocamento</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Tamanho</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Tamanho</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Preenchimento</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Preenchimento</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Bytes alterados desde o carregamento</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Bytes alterados desde o carregamento</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Vetor de {type}</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Array de {type}</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B49" t="str">
+        <v>(Sem conteúdo)</v>
+      </c>
+      <c r="C49" t="str">
+        <v>(Sem conteúdo)</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B50" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="C50" t="str">
+        <v>bytes</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B51" t="str">
+        <v>A carregar descrição completa…</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Carregando descrição completa…</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Não foi possível carregar a descrição completa:</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Não foi possível carregar a descrição completa:</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Sem avisos nem erros encontrados.</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Nenhum aviso ou erro encontrado.</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Válido</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Aviso</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Aviso</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Erro</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Erro</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Desconhecido</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Desconhecido</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B59" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B60" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B63" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C63" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B64" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C64" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B67" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C67" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B68" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C68" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Profile written from edits, but re-validation failed:</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C69"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C79"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1044,128 +1044,238 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B59" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C59" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B60" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C60" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B61" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Acionado por</v>
       </c>
       <c r="C61" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B62" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Campo</v>
       </c>
       <c r="C62" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B63" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Valor atual</v>
       </c>
       <c r="C63" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B64" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C64" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B65" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C65" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B66" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Inválido</v>
       </c>
       <c r="C66" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B67" t="str">
-        <v>indentação</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C67" t="str">
-        <v>indentação</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B68" t="str">
-        <v>ordenar chaves</v>
+        <v>Fechar</v>
       </c>
       <c r="C68" t="str">
-        <v>ordenar chaves</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B69" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B70" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B73" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C73" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B74" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C74" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B77" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C77" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B78" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C78" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B79" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C69" t="str">
+      <c r="C79" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C69"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C81"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -978,304 +978,326 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B53" t="str">
-        <v>Sem saída de validação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C53" t="str">
-        <v>Sem saída de validação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B54" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C54" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B55" t="str">
-        <v>Válido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C55" t="str">
-        <v>Válido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B56" t="str">
-        <v>Aviso</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C56" t="str">
-        <v>Aviso</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B57" t="str">
-        <v>Erro</v>
+        <v>Válido</v>
       </c>
       <c r="C57" t="str">
-        <v>Erro</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B58" t="str">
-        <v>Desconhecido</v>
+        <v>Aviso</v>
       </c>
       <c r="C58" t="str">
-        <v>Desconhecido</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B59" t="str">
-        <v>Ver no contexto</v>
+        <v>Erro</v>
       </c>
       <c r="C59" t="str">
-        <v>Ver no contexto</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B60" t="str">
-        <v>Detalhe de validação</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C60" t="str">
-        <v>Detalhe de validação</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B61" t="str">
-        <v>Acionado por</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C61" t="str">
-        <v>Acionado por</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B62" t="str">
-        <v>Campo</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C62" t="str">
-        <v>Campo</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B63" t="str">
-        <v>Valor atual</v>
+        <v>Acionado por</v>
       </c>
       <c r="C63" t="str">
-        <v>Valor atual</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B64" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Campo</v>
       </c>
       <c r="C64" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B65" t="str">
-        <v>Esperado: {value}</v>
+        <v>Valor atual</v>
       </c>
       <c r="C65" t="str">
-        <v>Esperado: {value}</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B66" t="str">
-        <v>Inválido</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C66" t="str">
-        <v>Inválido</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B67" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C67" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B68" t="str">
-        <v>Fechar</v>
+        <v>Inválido</v>
       </c>
       <c r="C68" t="str">
-        <v>Fechar</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B69" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C69" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B70" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Fechar</v>
       </c>
       <c r="C70" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B71" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C71" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B72" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C72" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B73" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C73" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B74" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C74" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B75" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C75" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B76" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C76" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B77" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C77" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B78" t="str">
-        <v>ordenar chaves</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C78" t="str">
-        <v>ordenar chaves</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B79" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C79" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B80" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C80" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B81" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C79" t="str">
+      <c r="C81" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C81"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C87"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1011,293 +1011,359 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B56" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C56" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B57" t="str">
-        <v>Válido</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C57" t="str">
-        <v>Válido</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Warning</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B58" t="str">
-        <v>Aviso</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C58" t="str">
-        <v>Aviso</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Error</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B59" t="str">
-        <v>Erro</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C59" t="str">
-        <v>Erro</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B60" t="str">
-        <v>Desconhecido</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C60" t="str">
-        <v>Desconhecido</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>View in context</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B61" t="str">
-        <v>Ver no contexto</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C61" t="str">
-        <v>Ver no contexto</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Validation detail</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B62" t="str">
-        <v>Detalhe de validação</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C62" t="str">
-        <v>Detalhe de validação</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Triggered by</v>
+        <v>Valid</v>
       </c>
       <c r="B63" t="str">
-        <v>Acionado por</v>
+        <v>Válido</v>
       </c>
       <c r="C63" t="str">
-        <v>Acionado por</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Field</v>
+        <v>Warning</v>
       </c>
       <c r="B64" t="str">
-        <v>Campo</v>
+        <v>Aviso</v>
       </c>
       <c r="C64" t="str">
-        <v>Campo</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Current value</v>
+        <v>Error</v>
       </c>
       <c r="B65" t="str">
-        <v>Valor atual</v>
+        <v>Erro</v>
       </c>
       <c r="C65" t="str">
-        <v>Valor atual</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Required: 0</v>
+        <v>Unknown</v>
       </c>
       <c r="B66" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C66" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Expected: {value}</v>
+        <v>View in context</v>
       </c>
       <c r="B67" t="str">
-        <v>Esperado: {value}</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C67" t="str">
-        <v>Esperado: {value}</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Invalid</v>
+        <v>Validation detail</v>
       </c>
       <c r="B68" t="str">
-        <v>Inválido</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C68" t="str">
-        <v>Inválido</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Triggered by</v>
       </c>
       <c r="B69" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Acionado por</v>
       </c>
       <c r="C69" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Close</v>
+        <v>Field</v>
       </c>
       <c r="B70" t="str">
-        <v>Fechar</v>
+        <v>Campo</v>
       </c>
       <c r="C70" t="str">
-        <v>Fechar</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Loading XML editor…</v>
+        <v>Current value</v>
       </c>
       <c r="B71" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Valor atual</v>
       </c>
       <c r="C71" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Required: 0</v>
       </c>
       <c r="B72" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C72" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B73" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C73" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Invalid</v>
       </c>
       <c r="B74" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Inválido</v>
       </c>
       <c r="C74" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>● unsaved XML edits</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B75" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C75" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Close</v>
       </c>
       <c r="B76" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Fechar</v>
       </c>
       <c r="C76" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B77" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C77" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B78" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C78" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>indent</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B79" t="str">
-        <v>indentação</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C79" t="str">
-        <v>indentação</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>sort keys</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B80" t="str">
-        <v>ordenar chaves</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C80" t="str">
-        <v>ordenar chaves</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B81" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C81" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B82" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C82" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B85" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C85" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B86" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C86" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B87" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C81" t="str">
+      <c r="C87" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C87"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C98"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -681,689 +681,810 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Raw Output</v>
+        <v>Profile Assessment WG</v>
       </c>
       <c r="B26" t="str">
-        <v>Saída em bruto</v>
+        <v/>
       </c>
       <c r="C26" t="str">
-        <v>Saída bruta</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B27" t="str">
-        <v>XML</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C27" t="str">
-        <v>XML</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="C28" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>JSON</v>
       </c>
       <c r="B29" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>JSON</v>
       </c>
       <c r="C29" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Error:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B30" t="str">
-        <v>Erro:</v>
+        <v/>
       </c>
       <c r="C30" t="str">
-        <v>Erro:</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Convert to XML</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B31" t="str">
-        <v>Converter para XML</v>
+        <v/>
       </c>
       <c r="C31" t="str">
-        <v>Converter para XML</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Convert to JSON</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B32" t="str">
-        <v>Converter para JSON</v>
+        <v/>
       </c>
       <c r="C32" t="str">
-        <v>Converter para JSON</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Convert to ICC</v>
+        <v>Security</v>
       </c>
       <c r="B33" t="str">
-        <v>Converter para ICC</v>
+        <v/>
       </c>
       <c r="C33" t="str">
-        <v>Converter para ICC</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Converting to XML…</v>
+        <v>Conformance</v>
       </c>
       <c r="B34" t="str">
-        <v>A converter para XML…</v>
+        <v/>
       </c>
       <c r="C34" t="str">
-        <v>Convertendo para XML…</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Converting to JSON…</v>
+        <v>Quality</v>
       </c>
       <c r="B35" t="str">
-        <v>A converter para JSON…</v>
+        <v/>
       </c>
       <c r="C35" t="str">
-        <v>Convertendo para JSON…</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Converting to ICC…</v>
+        <v>REPORT</v>
       </c>
       <c r="B36" t="str">
-        <v>A converter para ICC…</v>
+        <v/>
       </c>
       <c r="C36" t="str">
-        <v>Convertendo para ICC…</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Load ICC profile</v>
+        <v>FAIL</v>
       </c>
       <c r="B37" t="str">
-        <v>Carregar perfil ICC</v>
+        <v/>
       </c>
       <c r="C37" t="str">
-        <v>Carregar perfil ICC</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>checks</v>
       </c>
       <c r="B38" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v/>
       </c>
       <c r="C38" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Profile ID</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B39" t="str">
-        <v>ID do perfil</v>
+        <v/>
       </c>
       <c r="C39" t="str">
-        <v>ID do perfil</v>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B40" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C40" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tag Name</v>
+        <v>Error:</v>
       </c>
       <c r="B41" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Erro:</v>
       </c>
       <c r="C41" t="str">
-        <v>Nome da tag</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ID</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B42" t="str">
-        <v>ID</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C42" t="str">
-        <v>ID</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Offset</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B43" t="str">
-        <v>Deslocamento</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C43" t="str">
-        <v>Deslocamento</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Size</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B44" t="str">
-        <v>Tamanho</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C44" t="str">
-        <v>Tamanho</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Pad</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B45" t="str">
-        <v>Preenchimento</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C45" t="str">
-        <v>Preenchimento</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B46" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C46" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Type</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B47" t="str">
-        <v>Tipo</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C47" t="str">
-        <v>Tipo</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Array of {type}</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B48" t="str">
-        <v>Vetor de {type}</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C48" t="str">
-        <v>Array de {type}</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>(No content)</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B49" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C49" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>bytes</v>
+        <v>Profile ID</v>
       </c>
       <c r="B50" t="str">
-        <v>bytes</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C50" t="str">
-        <v>bytes</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Loading full description…</v>
+        <v>No tags found.</v>
       </c>
       <c r="B51" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C51" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Could not load full description:</v>
+        <v>Tag Name</v>
       </c>
       <c r="B52" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C52" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ID</v>
       </c>
       <c r="B53" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>ID</v>
       </c>
       <c r="C53" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Offset</v>
       </c>
       <c r="B54" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C54" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>No validation output</v>
+        <v>Size</v>
       </c>
       <c r="B55" t="str">
-        <v>Sem saída de validação</v>
+        <v>Tamanho</v>
       </c>
       <c r="C55" t="str">
-        <v>Sem saída de validação</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Profile is valid</v>
+        <v>Pad</v>
       </c>
       <c r="B56" t="str">
-        <v>O perfil é válido</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C56" t="str">
-        <v>O perfil é válido</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B57" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C57" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Type</v>
       </c>
       <c r="B58" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Tipo</v>
       </c>
       <c r="C58" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Critical validation error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B59" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C59" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Unknown validation status</v>
+        <v>(No content)</v>
       </c>
       <c r="B60" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C60" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>bytes</v>
       </c>
       <c r="B61" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>bytes</v>
       </c>
       <c r="C61" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B62" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C62" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B63" t="str">
-        <v>Válido</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C63" t="str">
-        <v>Válido</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Warning</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B64" t="str">
-        <v>Aviso</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C64" t="str">
-        <v>Aviso</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Error</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B65" t="str">
-        <v>Erro</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C65" t="str">
-        <v>Erro</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Unknown</v>
+        <v>No validation output</v>
       </c>
       <c r="B66" t="str">
-        <v>Desconhecido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C66" t="str">
-        <v>Desconhecido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>View in context</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B67" t="str">
-        <v>Ver no contexto</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C67" t="str">
-        <v>Ver no contexto</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Validation detail</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B68" t="str">
-        <v>Detalhe de validação</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C68" t="str">
-        <v>Detalhe de validação</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Triggered by</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B69" t="str">
-        <v>Acionado por</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C69" t="str">
-        <v>Acionado por</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Field</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B70" t="str">
-        <v>Campo</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C70" t="str">
-        <v>Campo</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Current value</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B71" t="str">
-        <v>Valor atual</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C71" t="str">
-        <v>Valor atual</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Required: 0</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B72" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C72" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Expected: {value}</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B73" t="str">
-        <v>Esperado: {value}</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C73" t="str">
-        <v>Esperado: {value}</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Invalid</v>
+        <v>Valid</v>
       </c>
       <c r="B74" t="str">
-        <v>Inválido</v>
+        <v>Válido</v>
       </c>
       <c r="C74" t="str">
-        <v>Inválido</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Warning</v>
       </c>
       <c r="B75" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Aviso</v>
       </c>
       <c r="C75" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Close</v>
+        <v>Error</v>
       </c>
       <c r="B76" t="str">
-        <v>Fechar</v>
+        <v>Erro</v>
       </c>
       <c r="C76" t="str">
-        <v>Fechar</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Loading XML editor…</v>
+        <v>Unknown</v>
       </c>
       <c r="B77" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C77" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading JSON editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B78" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C78" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Validation detail</v>
       </c>
       <c r="B79" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C79" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B80" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Acionado por</v>
       </c>
       <c r="C80" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Field</v>
       </c>
       <c r="B81" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Campo</v>
       </c>
       <c r="C81" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Current value</v>
       </c>
       <c r="B82" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Valor atual</v>
       </c>
       <c r="C82" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B83" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C83" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B84" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C84" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>indent</v>
+        <v>Invalid</v>
       </c>
       <c r="B85" t="str">
-        <v>indentação</v>
+        <v>Inválido</v>
       </c>
       <c r="C85" t="str">
-        <v>indentação</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>sort keys</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B86" t="str">
-        <v>ordenar chaves</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C86" t="str">
-        <v>ordenar chaves</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B88" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B89" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B92" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C92" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B93" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C93" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B96" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C96" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B97" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C97" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B98" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C87" t="str">
+      <c r="C98" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C98"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C100"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -725,29 +725,29 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C30" t="str">
-        <v/>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -758,7 +758,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Security</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -769,7 +769,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Conformance</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -780,7 +780,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Quality</v>
+        <v>Security</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -791,7 +791,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>REPORT</v>
+        <v>Conformance</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -802,7 +802,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>FAIL</v>
+        <v>Quality</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -813,7 +813,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>checks</v>
+        <v>REPORT</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -824,7 +824,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>FAIL</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -835,656 +835,678 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>checks</v>
       </c>
       <c r="B40" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v/>
       </c>
       <c r="C40" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Error:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B41" t="str">
-        <v>Erro:</v>
+        <v/>
       </c>
       <c r="C41" t="str">
-        <v>Erro:</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Convert to XML</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B42" t="str">
-        <v>Converter para XML</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C42" t="str">
-        <v>Converter para XML</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Convert to JSON</v>
+        <v>Error:</v>
       </c>
       <c r="B43" t="str">
-        <v>Converter para JSON</v>
+        <v>Erro:</v>
       </c>
       <c r="C43" t="str">
-        <v>Converter para JSON</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B44" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C44" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B45" t="str">
-        <v>A converter para XML…</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C45" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B46" t="str">
-        <v>A converter para JSON…</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C46" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B47" t="str">
-        <v>A converter para ICC…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C47" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B48" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C48" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B49" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C49" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Profile ID</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B50" t="str">
-        <v>ID do perfil</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C50" t="str">
-        <v>ID do perfil</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>No tags found.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B51" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C51" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tag Name</v>
+        <v>Profile ID</v>
       </c>
       <c r="B52" t="str">
-        <v>Nome da etiqueta</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C52" t="str">
-        <v>Nome da tag</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B53" t="str">
-        <v>ID</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C53" t="str">
-        <v>ID</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Offset</v>
+        <v>Tag Name</v>
       </c>
       <c r="B54" t="str">
-        <v>Deslocamento</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C54" t="str">
-        <v>Deslocamento</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Size</v>
+        <v>ID</v>
       </c>
       <c r="B55" t="str">
-        <v>Tamanho</v>
+        <v>ID</v>
       </c>
       <c r="C55" t="str">
-        <v>Tamanho</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Pad</v>
+        <v>Offset</v>
       </c>
       <c r="B56" t="str">
-        <v>Preenchimento</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C56" t="str">
-        <v>Preenchimento</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bytes changed since load</v>
+        <v>Size</v>
       </c>
       <c r="B57" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Tamanho</v>
       </c>
       <c r="C57" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Type</v>
+        <v>Pad</v>
       </c>
       <c r="B58" t="str">
-        <v>Tipo</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C58" t="str">
-        <v>Tipo</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Array of {type}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B59" t="str">
-        <v>Vetor de {type}</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C59" t="str">
-        <v>Array de {type}</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>(No content)</v>
+        <v>Type</v>
       </c>
       <c r="B60" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Tipo</v>
       </c>
       <c r="C60" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>bytes</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B61" t="str">
-        <v>bytes</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C61" t="str">
-        <v>bytes</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading full description…</v>
+        <v>(No content)</v>
       </c>
       <c r="B62" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C62" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Could not load full description:</v>
+        <v>bytes</v>
       </c>
       <c r="B63" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>bytes</v>
       </c>
       <c r="C63" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B64" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C64" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B65" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C65" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>No validation output</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B66" t="str">
-        <v>Sem saída de validação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C66" t="str">
-        <v>Sem saída de validação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Profile is valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B67" t="str">
-        <v>O perfil é válido</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C67" t="str">
-        <v>O perfil é válido</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No validation output</v>
       </c>
       <c r="B68" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C68" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B69" t="str">
-        <v>O perfil não é conforme</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C69" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Critical validation error</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B70" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C70" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B71" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C71" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B72" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C72" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B73" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C73" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Valid</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B74" t="str">
-        <v>Válido</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C74" t="str">
-        <v>Válido</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Warning</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B75" t="str">
-        <v>Aviso</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C75" t="str">
-        <v>Aviso</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Error</v>
+        <v>Valid</v>
       </c>
       <c r="B76" t="str">
-        <v>Erro</v>
+        <v>Válido</v>
       </c>
       <c r="C76" t="str">
-        <v>Erro</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Unknown</v>
+        <v>Warning</v>
       </c>
       <c r="B77" t="str">
-        <v>Desconhecido</v>
+        <v>Aviso</v>
       </c>
       <c r="C77" t="str">
-        <v>Desconhecido</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B78" t="str">
-        <v>Ver no contexto</v>
+        <v>Erro</v>
       </c>
       <c r="C78" t="str">
-        <v>Ver no contexto</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B79" t="str">
-        <v>Detalhe de validação</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C79" t="str">
-        <v>Detalhe de validação</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Triggered by</v>
+        <v>View in context</v>
       </c>
       <c r="B80" t="str">
-        <v>Acionado por</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C80" t="str">
-        <v>Acionado por</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Field</v>
+        <v>Validation detail</v>
       </c>
       <c r="B81" t="str">
-        <v>Campo</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C81" t="str">
-        <v>Campo</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Current value</v>
+        <v>Triggered by</v>
       </c>
       <c r="B82" t="str">
-        <v>Valor atual</v>
+        <v>Acionado por</v>
       </c>
       <c r="C82" t="str">
-        <v>Valor atual</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Required: 0</v>
+        <v>Field</v>
       </c>
       <c r="B83" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Campo</v>
       </c>
       <c r="C83" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Expected: {value}</v>
+        <v>Current value</v>
       </c>
       <c r="B84" t="str">
-        <v>Esperado: {value}</v>
+        <v>Valor atual</v>
       </c>
       <c r="C84" t="str">
-        <v>Esperado: {value}</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Invalid</v>
+        <v>Required: 0</v>
       </c>
       <c r="B85" t="str">
-        <v>Inválido</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C85" t="str">
-        <v>Inválido</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B86" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C86" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Close</v>
+        <v>Invalid</v>
       </c>
       <c r="B87" t="str">
-        <v>Fechar</v>
+        <v>Inválido</v>
       </c>
       <c r="C87" t="str">
-        <v>Fechar</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Loading XML editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B88" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C88" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Close</v>
       </c>
       <c r="B89" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Fechar</v>
       </c>
       <c r="C89" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B90" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C90" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B91" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C91" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B92" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C92" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B93" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C93" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B94" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C94" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B95" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C95" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B96" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C96" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B97" t="str">
-        <v>ordenar chaves</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C97" t="str">
-        <v>ordenar chaves</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B98" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C98" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B99" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C99" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B100" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C98" t="str">
+      <c r="C100" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C129"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -552,15 +552,15 @@
         <v>specification using the</v>
       </c>
       <c r="B14" t="str">
-        <v>através da implementação de referência</v>
+        <v>através da implementação de demonstração</v>
       </c>
       <c r="C14" t="str">
-        <v>usando a implementação de referência</v>
+        <v>usando a implementação de demonstração</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>reference implementation.</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B15" t="str">
         <v>.</v>
@@ -571,942 +571,1261 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Validating…</v>
+        <v>Based on</v>
       </c>
       <c r="B16" t="str">
-        <v>A validar…</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
       <c r="C16" t="str">
-        <v>Validando…</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Save ICC profile</v>
+        <v>demo implementation</v>
       </c>
       <c r="B17" t="str">
-        <v>Guardar perfil ICC</v>
+        <v/>
       </c>
       <c r="C17" t="str">
-        <v>Salvar perfil ICC</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Validating…</v>
       </c>
       <c r="B18" t="str">
-        <v>● Modificado — não guardado</v>
+        <v>A validar…</v>
       </c>
       <c r="C18" t="str">
-        <v>● Modificado — não salvo</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B19" t="str">
-        <v>Largue um perfil ICC aqui</v>
+        <v>Guardar perfil ICC</v>
       </c>
       <c r="C19" t="str">
-        <v>Solte um perfil ICC aqui</v>
+        <v>Salvar perfil ICC</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>or</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B20" t="str">
-        <v>ou</v>
+        <v>● Modificado — não guardado</v>
       </c>
       <c r="C20" t="str">
-        <v>ou</v>
+        <v>● Modificado — não salvo</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Choose file</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B21" t="str">
-        <v>Escolher ficheiro</v>
+        <v>Largue um perfil ICC aqui</v>
       </c>
       <c r="C21" t="str">
-        <v>Escolher arquivo</v>
+        <v>Solte um perfil ICC aqui</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>.icc and .icm files</v>
+        <v>or</v>
       </c>
       <c r="B22" t="str">
-        <v>Ficheiros .icc e .icm</v>
+        <v>ou</v>
       </c>
       <c r="C22" t="str">
-        <v>Arquivos .icc e .icm</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Header</v>
+        <v>Choose file</v>
       </c>
       <c r="B23" t="str">
-        <v>Cabeçalho</v>
+        <v>Escolher ficheiro</v>
       </c>
       <c r="C23" t="str">
-        <v>Cabeçalho</v>
+        <v>Escolher arquivo</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Tags</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B24" t="str">
-        <v>Etiquetas</v>
+        <v>Ficheiros .icc e .icm</v>
       </c>
       <c r="C24" t="str">
-        <v>Tags</v>
+        <v>Arquivos .icc e .icm</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Validation</v>
+        <v>Header</v>
       </c>
       <c r="B25" t="str">
-        <v>Validação</v>
+        <v>Cabeçalho</v>
       </c>
       <c r="C25" t="str">
-        <v>Validação</v>
+        <v>Cabeçalho</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Profile Assessment WG</v>
+        <v>Tags</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>Etiquetas</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>Tags</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Raw Output</v>
+        <v>Validation</v>
       </c>
       <c r="B27" t="str">
-        <v>Saída em bruto</v>
+        <v>Validação</v>
       </c>
       <c r="C27" t="str">
-        <v>Saída bruta</v>
+        <v>Validação</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>XML</v>
+        <v>Plot</v>
       </c>
       <c r="B28" t="str">
-        <v>XML</v>
+        <v>Gráfico</v>
       </c>
       <c r="C28" t="str">
-        <v>XML</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>JSON</v>
+        <v>Raw Output</v>
       </c>
       <c r="B29" t="str">
-        <v>JSON</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C29" t="str">
-        <v>JSON</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Invalid profile URL:</v>
+        <v>XML</v>
       </c>
       <c r="B30" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>XML</v>
       </c>
       <c r="C30" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>JSON</v>
       </c>
       <c r="B31" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>JSON</v>
       </c>
       <c r="C31" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Curves</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Curvas</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Input curves</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Output curves</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Curvas de saída</v>
       </c>
       <c r="C34" t="str">
-        <v/>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Security</v>
+        <v>CLUT image</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C35" t="str">
-        <v/>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Conformance</v>
+        <v>Gamut image</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C36" t="str">
-        <v/>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Quality</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Cromaticidade</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>REPORT</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C38" t="str">
-        <v/>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>FAIL</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C39" t="str">
-        <v/>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>checks</v>
+        <v>Curve table</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Tabela da curva</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Tables</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>Tabelas</v>
       </c>
       <c r="C41" t="str">
-        <v/>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Data</v>
       </c>
       <c r="B42" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Dados</v>
       </c>
       <c r="C42" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Error:</v>
+        <v>Evaluate</v>
       </c>
       <c r="B43" t="str">
-        <v>Erro:</v>
+        <v>Avaliar</v>
       </c>
       <c r="C43" t="str">
-        <v>Erro:</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Convert to XML</v>
+        <v>Loading…</v>
       </c>
       <c r="B44" t="str">
-        <v>Converter para XML</v>
+        <v>A carregar…</v>
       </c>
       <c r="C44" t="str">
-        <v>Converter para XML</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Convert to JSON</v>
+        <v>Input</v>
       </c>
       <c r="B45" t="str">
-        <v>Converter para JSON</v>
+        <v>Entrada</v>
       </c>
       <c r="C45" t="str">
-        <v>Converter para JSON</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Convert to ICC</v>
+        <v>Output</v>
       </c>
       <c r="B46" t="str">
-        <v>Converter para ICC</v>
+        <v>Saída</v>
       </c>
       <c r="C46" t="str">
-        <v>Converter para ICC</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Converting to XML…</v>
+        <v>Floating point</v>
       </c>
       <c r="B47" t="str">
-        <v>A converter para XML…</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C47" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Converting to JSON…</v>
+        <v>Grid point</v>
       </c>
       <c r="B48" t="str">
-        <v>A converter para JSON…</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C48" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Converting to ICC…</v>
+        <v>Normalized</v>
       </c>
       <c r="B49" t="str">
-        <v>A converter para ICC…</v>
+        <v>Normalizado</v>
       </c>
       <c r="C49" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Load ICC profile</v>
+        <v>Human</v>
       </c>
       <c r="B50" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Legível</v>
       </c>
       <c r="C50" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B51" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C51" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Profile ID</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B52" t="str">
-        <v>ID do perfil</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C52" t="str">
-        <v>ID do perfil</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No tags found.</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B53" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C53" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Tag Name</v>
+        <v>Loading…</v>
       </c>
       <c r="B54" t="str">
-        <v>Nome da etiqueta</v>
+        <v>A carregar…</v>
       </c>
       <c r="C54" t="str">
-        <v>Nome da tag</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ID</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B55" t="str">
-        <v>ID</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C55" t="str">
-        <v>ID</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Offset</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B56" t="str">
-        <v>Deslocamento</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C56" t="str">
-        <v>Deslocamento</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Size</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B57" t="str">
-        <v>Tamanho</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C57" t="str">
-        <v>Tamanho</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Pad</v>
+        <v>Loading plot module…</v>
       </c>
       <c r="B58" t="str">
-        <v>Preenchimento</v>
+        <v/>
       </c>
       <c r="C58" t="str">
-        <v>Preenchimento</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Bytes changed since load</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B59" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v/>
       </c>
       <c r="C59" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Type</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B60" t="str">
-        <v>Tipo</v>
+        <v/>
       </c>
       <c r="C60" t="str">
-        <v>Tipo</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Array of {type}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B61" t="str">
-        <v>Vetor de {type}</v>
+        <v/>
       </c>
       <c r="C61" t="str">
-        <v>Array de {type}</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>(No content)</v>
+        <v>Security</v>
       </c>
       <c r="B62" t="str">
-        <v>(Sem conteúdo)</v>
+        <v/>
       </c>
       <c r="C62" t="str">
-        <v>(Sem conteúdo)</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>bytes</v>
+        <v>Conformance</v>
       </c>
       <c r="B63" t="str">
-        <v>bytes</v>
+        <v/>
       </c>
       <c r="C63" t="str">
-        <v>bytes</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Loading full description…</v>
+        <v>Quality</v>
       </c>
       <c r="B64" t="str">
-        <v>A carregar descrição completa…</v>
+        <v/>
       </c>
       <c r="C64" t="str">
-        <v>Carregando descrição completa…</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Could not load full description:</v>
+        <v>REPORT</v>
       </c>
       <c r="B65" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v/>
       </c>
       <c r="C65" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>FAIL</v>
       </c>
       <c r="B66" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v/>
       </c>
       <c r="C66" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>checks</v>
       </c>
       <c r="B67" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v/>
       </c>
       <c r="C67" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No validation output</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B68" t="str">
-        <v>Sem saída de validação</v>
+        <v/>
       </c>
       <c r="C68" t="str">
-        <v>Sem saída de validação</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Profile is valid</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B69" t="str">
-        <v>O perfil é válido</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C69" t="str">
-        <v>O perfil é válido</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Error:</v>
       </c>
       <c r="B70" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Erro:</v>
       </c>
       <c r="C70" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B71" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C71" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Critical validation error</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B72" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C72" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Unknown validation status</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B73" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C73" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B74" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C74" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B75" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C75" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Valid</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B76" t="str">
-        <v>Válido</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C76" t="str">
-        <v>Válido</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Warning</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B77" t="str">
-        <v>Aviso</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C77" t="str">
-        <v>Aviso</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Error</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B78" t="str">
-        <v>Erro</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C78" t="str">
-        <v>Erro</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Unknown</v>
+        <v>Profile ID</v>
       </c>
       <c r="B79" t="str">
-        <v>Desconhecido</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C79" t="str">
-        <v>Desconhecido</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>View in context</v>
+        <v>No tags found.</v>
       </c>
       <c r="B80" t="str">
-        <v>Ver no contexto</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C80" t="str">
-        <v>Ver no contexto</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Validation detail</v>
+        <v>Tag Name</v>
       </c>
       <c r="B81" t="str">
-        <v>Detalhe de validação</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C81" t="str">
-        <v>Detalhe de validação</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Triggered by</v>
+        <v>ID</v>
       </c>
       <c r="B82" t="str">
-        <v>Acionado por</v>
+        <v>ID</v>
       </c>
       <c r="C82" t="str">
-        <v>Acionado por</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Field</v>
+        <v>Offset</v>
       </c>
       <c r="B83" t="str">
-        <v>Campo</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C83" t="str">
-        <v>Campo</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Current value</v>
+        <v>Size</v>
       </c>
       <c r="B84" t="str">
-        <v>Valor atual</v>
+        <v>Tamanho</v>
       </c>
       <c r="C84" t="str">
-        <v>Valor atual</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Required: 0</v>
+        <v>Pad</v>
       </c>
       <c r="B85" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C85" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Expected: {value}</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B86" t="str">
-        <v>Esperado: {value}</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C86" t="str">
-        <v>Esperado: {value}</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Invalid</v>
+        <v>Type</v>
       </c>
       <c r="B87" t="str">
-        <v>Inválido</v>
+        <v>Tipo</v>
       </c>
       <c r="C87" t="str">
-        <v>Inválido</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B88" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C88" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Close</v>
+        <v>(No content)</v>
       </c>
       <c r="B89" t="str">
-        <v>Fechar</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C89" t="str">
-        <v>Fechar</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading XML editor…</v>
+        <v>bytes</v>
       </c>
       <c r="B90" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>bytes</v>
       </c>
       <c r="C90" t="str">
-        <v>Carregando editor XML…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B91" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C91" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B92" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C92" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B93" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C93" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B94" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C94" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>No validation output</v>
       </c>
       <c r="B95" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C95" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B96" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C96" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B97" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C97" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>indent</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B98" t="str">
-        <v>indentação</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C98" t="str">
-        <v>indentação</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>sort keys</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B99" t="str">
-        <v>ordenar chaves</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C99" t="str">
-        <v>ordenar chaves</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Estado de validação desconhecido</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Status de validação desconhecido</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Crítico — apresentado apenas para inspeção</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Crítico — exibido apenas para inspeção</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Sem avisos nem erros encontrados.</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Nenhum aviso ou erro encontrado.</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Válido</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Aviso</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Aviso</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Erro</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Erro</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Desconhecido</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Desconhecido</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Aprovado</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Reprovado</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Reprovado</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Ver no contexto</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Ver no contexto</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Acionado por</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Acionado por</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B119" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B120" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B123" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C123" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B124" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C124" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B127" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C127" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B128" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C128" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B129" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C100" t="str">
+      <c r="C129" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C128"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1033,799 +1033,788 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading plot module…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Security</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Segurança</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Security</v>
+        <v>Conformance</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Conformidade</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Conformance</v>
+        <v>Quality</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Qualidade</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Quality</v>
+        <v>REPORT</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>REPORT</v>
+        <v>FAIL</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>REPROVADO</v>
       </c>
       <c r="C65" t="str">
-        <v/>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>FAIL</v>
+        <v>checks</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>verificações</v>
       </c>
       <c r="C66" t="str">
-        <v/>
+        <v>verificações</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>checks</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C68" t="str">
-        <v/>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Error:</v>
       </c>
       <c r="B69" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Erro:</v>
       </c>
       <c r="C69" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Error:</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B70" t="str">
-        <v>Erro:</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C70" t="str">
-        <v>Erro:</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to XML</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B71" t="str">
-        <v>Converter para XML</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C71" t="str">
-        <v>Converter para XML</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B72" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C72" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B73" t="str">
-        <v>Converter para ICC</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C73" t="str">
-        <v>Converter para ICC</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to XML…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B74" t="str">
-        <v>A converter para XML…</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C74" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B75" t="str">
-        <v>A converter para JSON…</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C75" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to ICC…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B76" t="str">
-        <v>A converter para ICC…</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C76" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Load ICC profile</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B77" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C77" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Profile ID</v>
       </c>
       <c r="B78" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C78" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Profile ID</v>
+        <v>No tags found.</v>
       </c>
       <c r="B79" t="str">
-        <v>ID do perfil</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C79" t="str">
-        <v>ID do perfil</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>No tags found.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B80" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C80" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Tag Name</v>
+        <v>ID</v>
       </c>
       <c r="B81" t="str">
-        <v>Nome da etiqueta</v>
+        <v>ID</v>
       </c>
       <c r="C81" t="str">
-        <v>Nome da tag</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ID</v>
+        <v>Offset</v>
       </c>
       <c r="B82" t="str">
-        <v>ID</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C82" t="str">
-        <v>ID</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Offset</v>
+        <v>Size</v>
       </c>
       <c r="B83" t="str">
-        <v>Deslocamento</v>
+        <v>Tamanho</v>
       </c>
       <c r="C83" t="str">
-        <v>Deslocamento</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Size</v>
+        <v>Pad</v>
       </c>
       <c r="B84" t="str">
-        <v>Tamanho</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C84" t="str">
-        <v>Tamanho</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Pad</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B85" t="str">
-        <v>Preenchimento</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C85" t="str">
-        <v>Preenchimento</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bytes changed since load</v>
+        <v>Type</v>
       </c>
       <c r="B86" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Tipo</v>
       </c>
       <c r="C86" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Type</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B87" t="str">
-        <v>Tipo</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C87" t="str">
-        <v>Tipo</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Array of {type}</v>
+        <v>(No content)</v>
       </c>
       <c r="B88" t="str">
-        <v>Vetor de {type}</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C88" t="str">
-        <v>Array de {type}</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>(No content)</v>
+        <v>bytes</v>
       </c>
       <c r="B89" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>bytes</v>
       </c>
       <c r="C89" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>bytes</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B90" t="str">
-        <v>bytes</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C90" t="str">
-        <v>bytes</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading full description…</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B91" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C91" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not load full description:</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B92" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C92" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B93" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C93" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>No validation output</v>
       </c>
       <c r="B94" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C94" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>No validation output</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B95" t="str">
-        <v>Sem saída de validação</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C95" t="str">
-        <v>Sem saída de validação</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile is valid</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B96" t="str">
-        <v>O perfil é válido</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C96" t="str">
-        <v>O perfil é válido</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B97" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C97" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B98" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C98" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Critical validation error</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B99" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C99" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B100" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C100" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B101" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C101" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Valid</v>
       </c>
       <c r="B102" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Válido</v>
       </c>
       <c r="C102" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Valid</v>
+        <v>Warning</v>
       </c>
       <c r="B103" t="str">
-        <v>Válido</v>
+        <v>Aviso</v>
       </c>
       <c r="C103" t="str">
-        <v>Válido</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Warning</v>
+        <v>Error</v>
       </c>
       <c r="B104" t="str">
-        <v>Aviso</v>
+        <v>Erro</v>
       </c>
       <c r="C104" t="str">
-        <v>Aviso</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Error</v>
+        <v>Unknown</v>
       </c>
       <c r="B105" t="str">
-        <v>Erro</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C105" t="str">
-        <v>Erro</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Unknown</v>
+        <v>Pass</v>
       </c>
       <c r="B106" t="str">
-        <v>Desconhecido</v>
+        <v>Aprovado</v>
       </c>
       <c r="C106" t="str">
-        <v>Desconhecido</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Pass</v>
+        <v>Fail</v>
       </c>
       <c r="B107" t="str">
-        <v>Aprovado</v>
+        <v>Reprovado</v>
       </c>
       <c r="C107" t="str">
-        <v>Aprovado</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Fail</v>
+        <v>View in context</v>
       </c>
       <c r="B108" t="str">
-        <v>Reprovado</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C108" t="str">
-        <v>Reprovado</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>View in context</v>
+        <v>Validation detail</v>
       </c>
       <c r="B109" t="str">
-        <v>Ver no contexto</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C109" t="str">
-        <v>Ver no contexto</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Validation detail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B110" t="str">
-        <v>Detalhe de validação</v>
+        <v>Acionado por</v>
       </c>
       <c r="C110" t="str">
-        <v>Detalhe de validação</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Triggered by</v>
+        <v>Field</v>
       </c>
       <c r="B111" t="str">
-        <v>Acionado por</v>
+        <v>Campo</v>
       </c>
       <c r="C111" t="str">
-        <v>Acionado por</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Field</v>
+        <v>Current value</v>
       </c>
       <c r="B112" t="str">
-        <v>Campo</v>
+        <v>Valor atual</v>
       </c>
       <c r="C112" t="str">
-        <v>Campo</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Current value</v>
+        <v>Required: 0</v>
       </c>
       <c r="B113" t="str">
-        <v>Valor atual</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C113" t="str">
-        <v>Valor atual</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Required: 0</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B114" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C114" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid</v>
       </c>
       <c r="B115" t="str">
-        <v>Esperado: {value}</v>
+        <v>Inválido</v>
       </c>
       <c r="C115" t="str">
-        <v>Esperado: {value}</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Invalid</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B116" t="str">
-        <v>Inválido</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C116" t="str">
-        <v>Inválido</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Close</v>
       </c>
       <c r="B117" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Fechar</v>
       </c>
       <c r="C117" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Close</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B118" t="str">
-        <v>Fechar</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C118" t="str">
-        <v>Fechar</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading XML editor…</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B119" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C119" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Loading JSON editor…</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B120" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C120" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B121" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C121" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B122" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C122" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved XML edits</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B123" t="str">
-        <v>● edições XML por guardar</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C123" t="str">
-        <v>● edições XML não salvas</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B124" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C124" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B125" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C125" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>indent</v>
       </c>
       <c r="B126" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>indentação</v>
       </c>
       <c r="C126" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>indentação</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>indent</v>
+        <v>sort keys</v>
       </c>
       <c r="B127" t="str">
-        <v>indentação</v>
+        <v>ordenar chaves</v>
       </c>
       <c r="C127" t="str">
-        <v>indentação</v>
+        <v>ordenar chaves</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>sort keys</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B128" t="str">
-        <v>ordenar chaves</v>
+        <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
       <c r="C128" t="str">
-        <v>ordenar chaves</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B129" t="str">
-        <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
-      </c>
-      <c r="C129" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C128"/>
+  <dimension ref="A1:C131"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -505,1316 +505,1349 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Help</v>
+        <v>Number format</v>
       </c>
       <c r="B10" t="str">
-        <v>Ajuda</v>
+        <v>Formato numérico</v>
       </c>
       <c r="C10" t="str">
-        <v>Ajuda</v>
+        <v>Formato numérico</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Contact</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B11" t="str">
-        <v>Contacto</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="C11" t="str">
-        <v>Contato</v>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Decimal</v>
       </c>
       <c r="B12" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Decimal</v>
       </c>
       <c r="C12" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Help</v>
       </c>
       <c r="B13" t="str">
-        <v>Carregue um perfil ICC para o validar segundo a especificação</v>
+        <v>Ajuda</v>
       </c>
       <c r="C13" t="str">
-        <v>Envie um perfil ICC para validá-lo conforme a especificação</v>
+        <v>Ajuda</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>specification using the</v>
+        <v>Contact</v>
       </c>
       <c r="B14" t="str">
-        <v>através da implementação de demonstração</v>
+        <v>Contacto</v>
       </c>
       <c r="C14" t="str">
-        <v>usando a implementação de demonstração</v>
+        <v>Contato</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>demo implementation.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B15" t="str">
-        <v>.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C15" t="str">
-        <v>.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Based on</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B16" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Carregue um perfil ICC para o validar segundo a especificação</v>
       </c>
       <c r="C16" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Envie um perfil ICC para validá-lo conforme a especificação</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>demo implementation</v>
+        <v>specification using the</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>através da implementação de demonstração</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>usando a implementação de demonstração</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Validating…</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B18" t="str">
-        <v>A validar…</v>
+        <v>.</v>
       </c>
       <c r="C18" t="str">
-        <v>Validando…</v>
+        <v>.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Save ICC profile</v>
+        <v>Based on</v>
       </c>
       <c r="B19" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
       <c r="C19" t="str">
-        <v>Salvar perfil ICC</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>demo implementation</v>
       </c>
       <c r="B20" t="str">
-        <v>● Modificado — não guardado</v>
+        <v/>
       </c>
       <c r="C20" t="str">
-        <v>● Modificado — não salvo</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Validating…</v>
       </c>
       <c r="B21" t="str">
-        <v>Largue um perfil ICC aqui</v>
+        <v>A validar…</v>
       </c>
       <c r="C21" t="str">
-        <v>Solte um perfil ICC aqui</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>or</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B22" t="str">
-        <v>ou</v>
+        <v>Guardar perfil ICC</v>
       </c>
       <c r="C22" t="str">
-        <v>ou</v>
+        <v>Salvar perfil ICC</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Choose file</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B23" t="str">
-        <v>Escolher ficheiro</v>
+        <v>● Modificado — não guardado</v>
       </c>
       <c r="C23" t="str">
-        <v>Escolher arquivo</v>
+        <v>● Modificado — não salvo</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>.icc and .icm files</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B24" t="str">
-        <v>Ficheiros .icc e .icm</v>
+        <v>Largue um perfil ICC aqui</v>
       </c>
       <c r="C24" t="str">
-        <v>Arquivos .icc e .icm</v>
+        <v>Solte um perfil ICC aqui</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Header</v>
+        <v>or</v>
       </c>
       <c r="B25" t="str">
-        <v>Cabeçalho</v>
+        <v>ou</v>
       </c>
       <c r="C25" t="str">
-        <v>Cabeçalho</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Tags</v>
+        <v>Choose file</v>
       </c>
       <c r="B26" t="str">
-        <v>Etiquetas</v>
+        <v>Escolher ficheiro</v>
       </c>
       <c r="C26" t="str">
-        <v>Tags</v>
+        <v>Escolher arquivo</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Validation</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B27" t="str">
-        <v>Validação</v>
+        <v>Ficheiros .icc e .icm</v>
       </c>
       <c r="C27" t="str">
-        <v>Validação</v>
+        <v>Arquivos .icc e .icm</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Plot</v>
+        <v>Header</v>
       </c>
       <c r="B28" t="str">
-        <v>Gráfico</v>
+        <v>Cabeçalho</v>
       </c>
       <c r="C28" t="str">
-        <v>Gráfico</v>
+        <v>Cabeçalho</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Raw Output</v>
+        <v>Tags</v>
       </c>
       <c r="B29" t="str">
-        <v>Saída em bruto</v>
+        <v>Etiquetas</v>
       </c>
       <c r="C29" t="str">
-        <v>Saída bruta</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>XML</v>
+        <v>Validation</v>
       </c>
       <c r="B30" t="str">
-        <v>XML</v>
+        <v>Validação</v>
       </c>
       <c r="C30" t="str">
-        <v>XML</v>
+        <v>Validação</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>JSON</v>
+        <v>Plot</v>
       </c>
       <c r="B31" t="str">
-        <v>JSON</v>
+        <v>Gráfico</v>
       </c>
       <c r="C31" t="str">
-        <v>JSON</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B32" t="str">
-        <v>Curvas</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C32" t="str">
-        <v>Curvas</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Input curves</v>
+        <v>XML</v>
       </c>
       <c r="B33" t="str">
-        <v>Curvas de entrada</v>
+        <v>XML</v>
       </c>
       <c r="C33" t="str">
-        <v>Curvas de entrada</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Output curves</v>
+        <v>JSON</v>
       </c>
       <c r="B34" t="str">
-        <v>Curvas de saída</v>
+        <v>JSON</v>
       </c>
       <c r="C34" t="str">
-        <v>Curvas de saída</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CLUT image</v>
+        <v>Curves</v>
       </c>
       <c r="B35" t="str">
-        <v>Imagem CLUT</v>
+        <v>Curvas</v>
       </c>
       <c r="C35" t="str">
-        <v>Imagem CLUT</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Gamut image</v>
+        <v>Input curves</v>
       </c>
       <c r="B36" t="str">
-        <v>Imagem de gamut</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C36" t="str">
-        <v>Imagem de gamut</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Chromaticity</v>
+        <v>Output curves</v>
       </c>
       <c r="B37" t="str">
-        <v>Cromaticidade</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C37" t="str">
-        <v>Cromaticidade</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Scatter plot</v>
+        <v>CLUT image</v>
       </c>
       <c r="B38" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C38" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Tone response curve</v>
+        <v>Gamut image</v>
       </c>
       <c r="B39" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C39" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Curve table</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B40" t="str">
-        <v>Tabela da curva</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C40" t="str">
-        <v>Tabela da curva</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tables</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B41" t="str">
-        <v>Tabelas</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C41" t="str">
-        <v>Tabelas</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Data</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B42" t="str">
-        <v>Dados</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C42" t="str">
-        <v>Dados</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Evaluate</v>
+        <v>Curve table</v>
       </c>
       <c r="B43" t="str">
-        <v>Avaliar</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C43" t="str">
-        <v>Avaliar</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Loading…</v>
+        <v>Tables</v>
       </c>
       <c r="B44" t="str">
-        <v>A carregar…</v>
+        <v>Tabelas</v>
       </c>
       <c r="C44" t="str">
-        <v>Carregando…</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Input</v>
+        <v>Data</v>
       </c>
       <c r="B45" t="str">
-        <v>Entrada</v>
+        <v>Dados</v>
       </c>
       <c r="C45" t="str">
-        <v>Entrada</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Output</v>
+        <v>Evaluate</v>
       </c>
       <c r="B46" t="str">
-        <v>Saída</v>
+        <v>Avaliar</v>
       </c>
       <c r="C46" t="str">
-        <v>Saída</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Floating point</v>
+        <v>Loading…</v>
       </c>
       <c r="B47" t="str">
-        <v>Vírgula flutuante</v>
+        <v>A carregar…</v>
       </c>
       <c r="C47" t="str">
-        <v>Ponto flutuante</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Grid point</v>
+        <v>Input</v>
       </c>
       <c r="B48" t="str">
-        <v>Ponto da grelha</v>
+        <v>Entrada</v>
       </c>
       <c r="C48" t="str">
-        <v>Ponto da grade</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Normalized</v>
+        <v>Output</v>
       </c>
       <c r="B49" t="str">
-        <v>Normalizado</v>
+        <v>Saída</v>
       </c>
       <c r="C49" t="str">
-        <v>Normalizado</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Human</v>
+        <v>Floating point</v>
       </c>
       <c r="B50" t="str">
-        <v>Legível</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C50" t="str">
-        <v>Legível</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Device → PCS</v>
+        <v>Grid point</v>
       </c>
       <c r="B51" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C51" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>PCS → Device</v>
+        <v>Normalized</v>
       </c>
       <c r="B52" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Normalizado</v>
       </c>
       <c r="C52" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No CLUT grid</v>
+        <v>Human</v>
       </c>
       <c r="B53" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>Legível</v>
       </c>
       <c r="C53" t="str">
-        <v>Sem grade CLUT</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Loading…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B54" t="str">
-        <v>A carregar…</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C54" t="str">
-        <v>Carregando…</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B55" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C55" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Invalid profile URL:</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B56" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C56" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Loading…</v>
       </c>
       <c r="B57" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>A carregar…</v>
       </c>
       <c r="C57" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B58" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C58" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B59" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C59" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B60" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C60" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Security</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B61" t="str">
-        <v>Segurança</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C61" t="str">
-        <v>Segurança</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Conformance</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B62" t="str">
-        <v>Conformidade</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C62" t="str">
-        <v>Conformidade</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Quality</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B63" t="str">
-        <v>Qualidade</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C63" t="str">
-        <v>Qualidade</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>REPORT</v>
+        <v>Security</v>
       </c>
       <c r="B64" t="str">
-        <v>RELATÓRIO</v>
+        <v>Segurança</v>
       </c>
       <c r="C64" t="str">
-        <v>RELATÓRIO</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>FAIL</v>
+        <v>Conformance</v>
       </c>
       <c r="B65" t="str">
-        <v>REPROVADO</v>
+        <v>Conformidade</v>
       </c>
       <c r="C65" t="str">
-        <v>REPROVADO</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>checks</v>
+        <v>Quality</v>
       </c>
       <c r="B66" t="str">
-        <v>verificações</v>
+        <v>Qualidade</v>
       </c>
       <c r="C66" t="str">
-        <v>verificações</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>REPORT</v>
       </c>
       <c r="B67" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C67" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>FAIL</v>
       </c>
       <c r="B68" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C68" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Error:</v>
+        <v>checks</v>
       </c>
       <c r="B69" t="str">
-        <v>Erro:</v>
+        <v>verificações</v>
       </c>
       <c r="C69" t="str">
-        <v>Erro:</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Convert to XML</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B70" t="str">
-        <v>Converter para XML</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C70" t="str">
-        <v>Converter para XML</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Convert to JSON</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B71" t="str">
-        <v>Converter para JSON</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C71" t="str">
-        <v>Converter para JSON</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Convert to ICC</v>
+        <v>Error:</v>
       </c>
       <c r="B72" t="str">
-        <v>Converter para ICC</v>
+        <v>Erro:</v>
       </c>
       <c r="C72" t="str">
-        <v>Converter para ICC</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B73" t="str">
-        <v>A converter para XML…</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C73" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B74" t="str">
-        <v>A converter para JSON…</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C74" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B75" t="str">
-        <v>A converter para ICC…</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C75" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B76" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C76" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B77" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C77" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Profile ID</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B78" t="str">
-        <v>ID do perfil</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C78" t="str">
-        <v>ID do perfil</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>No tags found.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B79" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C79" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Tag Name</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B80" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C80" t="str">
-        <v>Nome da tag</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ID</v>
+        <v>Profile ID</v>
       </c>
       <c r="B81" t="str">
-        <v>ID</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C81" t="str">
-        <v>ID</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Offset</v>
+        <v>No tags found.</v>
       </c>
       <c r="B82" t="str">
-        <v>Deslocamento</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C82" t="str">
-        <v>Deslocamento</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Size</v>
+        <v>Tag Name</v>
       </c>
       <c r="B83" t="str">
-        <v>Tamanho</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C83" t="str">
-        <v>Tamanho</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Pad</v>
+        <v>ID</v>
       </c>
       <c r="B84" t="str">
-        <v>Preenchimento</v>
+        <v>ID</v>
       </c>
       <c r="C84" t="str">
-        <v>Preenchimento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Bytes changed since load</v>
+        <v>Offset</v>
       </c>
       <c r="B85" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C85" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Type</v>
+        <v>Size</v>
       </c>
       <c r="B86" t="str">
-        <v>Tipo</v>
+        <v>Tamanho</v>
       </c>
       <c r="C86" t="str">
-        <v>Tipo</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Array of {type}</v>
+        <v>Pad</v>
       </c>
       <c r="B87" t="str">
-        <v>Vetor de {type}</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C87" t="str">
-        <v>Array de {type}</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>(No content)</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B88" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C88" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>bytes</v>
+        <v>Type</v>
       </c>
       <c r="B89" t="str">
-        <v>bytes</v>
+        <v>Tipo</v>
       </c>
       <c r="C89" t="str">
-        <v>bytes</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading full description…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B90" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C90" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Could not load full description:</v>
+        <v>(No content)</v>
       </c>
       <c r="B91" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C91" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>bytes</v>
       </c>
       <c r="B92" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>bytes</v>
       </c>
       <c r="C92" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B93" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C93" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>No validation output</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B94" t="str">
-        <v>Sem saída de validação</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C94" t="str">
-        <v>Sem saída de validação</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Profile is valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B95" t="str">
-        <v>O perfil é válido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C95" t="str">
-        <v>O perfil é válido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B96" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C96" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile is non-compliant</v>
+        <v>No validation output</v>
       </c>
       <c r="B97" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C97" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B98" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C98" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B99" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C99" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B100" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C100" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B101" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C101" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Valid</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B102" t="str">
-        <v>Válido</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C102" t="str">
-        <v>Válido</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Warning</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B103" t="str">
-        <v>Aviso</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C103" t="str">
-        <v>Aviso</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B104" t="str">
-        <v>Erro</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C104" t="str">
-        <v>Erro</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Unknown</v>
+        <v>Valid</v>
       </c>
       <c r="B105" t="str">
-        <v>Desconhecido</v>
+        <v>Válido</v>
       </c>
       <c r="C105" t="str">
-        <v>Desconhecido</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Pass</v>
+        <v>Warning</v>
       </c>
       <c r="B106" t="str">
-        <v>Aprovado</v>
+        <v>Aviso</v>
       </c>
       <c r="C106" t="str">
-        <v>Aprovado</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Fail</v>
+        <v>Error</v>
       </c>
       <c r="B107" t="str">
-        <v>Reprovado</v>
+        <v>Erro</v>
       </c>
       <c r="C107" t="str">
-        <v>Reprovado</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>View in context</v>
+        <v>Unknown</v>
       </c>
       <c r="B108" t="str">
-        <v>Ver no contexto</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C108" t="str">
-        <v>Ver no contexto</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Validation detail</v>
+        <v>Pass</v>
       </c>
       <c r="B109" t="str">
-        <v>Detalhe de validação</v>
+        <v>Aprovado</v>
       </c>
       <c r="C109" t="str">
-        <v>Detalhe de validação</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Triggered by</v>
+        <v>Fail</v>
       </c>
       <c r="B110" t="str">
-        <v>Acionado por</v>
+        <v>Reprovado</v>
       </c>
       <c r="C110" t="str">
-        <v>Acionado por</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Field</v>
+        <v>View in context</v>
       </c>
       <c r="B111" t="str">
-        <v>Campo</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C111" t="str">
-        <v>Campo</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Current value</v>
+        <v>Validation detail</v>
       </c>
       <c r="B112" t="str">
-        <v>Valor atual</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C112" t="str">
-        <v>Valor atual</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Required: 0</v>
+        <v>Triggered by</v>
       </c>
       <c r="B113" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Acionado por</v>
       </c>
       <c r="C113" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Expected: {value}</v>
+        <v>Field</v>
       </c>
       <c r="B114" t="str">
-        <v>Esperado: {value}</v>
+        <v>Campo</v>
       </c>
       <c r="C114" t="str">
-        <v>Esperado: {value}</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Invalid</v>
+        <v>Current value</v>
       </c>
       <c r="B115" t="str">
-        <v>Inválido</v>
+        <v>Valor atual</v>
       </c>
       <c r="C115" t="str">
-        <v>Inválido</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B116" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C116" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Close</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B117" t="str">
-        <v>Fechar</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C117" t="str">
-        <v>Fechar</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Loading XML editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B118" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Inválido</v>
       </c>
       <c r="C118" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Loading JSON editor…</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B119" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C119" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B120" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Fechar</v>
       </c>
       <c r="C120" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B121" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C121" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>● edições XML por guardar</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C122" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B123" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C123" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C124" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B125" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C125" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>indent</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B126" t="str">
-        <v>indentação</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C126" t="str">
-        <v>indentação</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>sort keys</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B127" t="str">
-        <v>ordenar chaves</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C127" t="str">
-        <v>ordenar chaves</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B129" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C129" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B130" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C130" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B128" t="str">
+      <c r="B131" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C128" t="str">
+      <c r="C131" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C131"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C132"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1066,788 +1066,799 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B61" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C61" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B62" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C62" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B63" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C63" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B64" t="str">
-        <v>Segurança</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C64" t="str">
-        <v>Segurança</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B65" t="str">
-        <v>Conformidade</v>
+        <v>Segurança</v>
       </c>
       <c r="C65" t="str">
-        <v>Conformidade</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B66" t="str">
-        <v>Qualidade</v>
+        <v>Conformidade</v>
       </c>
       <c r="C66" t="str">
-        <v>Qualidade</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B67" t="str">
-        <v>RELATÓRIO</v>
+        <v>Qualidade</v>
       </c>
       <c r="C67" t="str">
-        <v>RELATÓRIO</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B68" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C68" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B69" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C69" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B70" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
       <c r="C70" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B71" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C71" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Error:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B72" t="str">
-        <v>Erro:</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C72" t="str">
-        <v>Erro:</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B73" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
       <c r="C73" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B74" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C74" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B75" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C75" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B76" t="str">
-        <v>A converter para XML…</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C76" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B77" t="str">
-        <v>A converter para JSON…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C77" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B78" t="str">
-        <v>A converter para ICC…</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C78" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B79" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C79" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B80" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C80" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B81" t="str">
-        <v>ID do perfil</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C81" t="str">
-        <v>ID do perfil</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B82" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C82" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B83" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C83" t="str">
-        <v>Nome da tag</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B84" t="str">
-        <v>ID</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C84" t="str">
-        <v>ID</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B85" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
       <c r="C85" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B86" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C86" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B87" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
       <c r="C87" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B88" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C88" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B89" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C89" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B90" t="str">
-        <v>Vetor de {type}</v>
+        <v>Tipo</v>
       </c>
       <c r="C90" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B91" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C91" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B92" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C92" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B93" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>bytes</v>
       </c>
       <c r="C93" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B94" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C94" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B95" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C95" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B96" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C96" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B97" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C97" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B98" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C98" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B99" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C99" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B100" t="str">
-        <v>O perfil não é conforme</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C100" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B101" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C101" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B102" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C102" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B103" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C103" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B104" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C104" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B105" t="str">
-        <v>Válido</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C105" t="str">
-        <v>Válido</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B106" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
       <c r="C106" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B107" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
       <c r="C107" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B108" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
       <c r="C108" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B109" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C109" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B110" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
       <c r="C110" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B111" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
       <c r="C111" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B112" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C112" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B113" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C113" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B114" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
       <c r="C114" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B115" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
       <c r="C115" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B116" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
       <c r="C116" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B117" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C117" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B118" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C118" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B119" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
       <c r="C119" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B120" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C120" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B121" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Fechar</v>
       </c>
       <c r="C121" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B122" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C122" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B123" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C123" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B124" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C124" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B125" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C125" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B126" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C126" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B127" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C127" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B128" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C128" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B129" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C129" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B130" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
       <c r="C130" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B131" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C131" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B131" t="str">
+      <c r="B132" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C131" t="str">
+      <c r="C132" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C132"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C132"/>
+  <dimension ref="A1:C181"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -736,1129 +736,1668 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Plot</v>
+        <v>Analysis</v>
       </c>
       <c r="B31" t="str">
-        <v>Gráfico</v>
+        <v>Análise</v>
       </c>
       <c r="C31" t="str">
-        <v>Gráfico</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Raw Output</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B32" t="str">
-        <v>Saída em bruto</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
       <c r="C32" t="str">
-        <v>Saída bruta</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>XML</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B33" t="str">
-        <v>XML</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
       </c>
       <c r="C33" t="str">
-        <v>XML</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>JSON</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B34" t="str">
-        <v>JSON</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C34" t="str">
-        <v>JSON</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Curves</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B35" t="str">
-        <v>Curvas</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
       <c r="C35" t="str">
-        <v>Curvas</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Input curves</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B36" t="str">
-        <v>Curvas de entrada</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C36" t="str">
-        <v>Curvas de entrada</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Output curves</v>
+        <v>% ink</v>
       </c>
       <c r="B37" t="str">
-        <v>Curvas de saída</v>
+        <v>% tinta</v>
       </c>
       <c r="C37" t="str">
-        <v>Curvas de saída</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CLUT image</v>
+        <v>Perceptual</v>
       </c>
       <c r="B38" t="str">
-        <v>Imagem CLUT</v>
+        <v>Perceptual</v>
       </c>
       <c r="C38" t="str">
-        <v>Imagem CLUT</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Gamut image</v>
+        <v>Relative colorimetric</v>
       </c>
       <c r="B39" t="str">
-        <v>Imagem de gamut</v>
+        <v>Colorimétrico relativo</v>
       </c>
       <c r="C39" t="str">
-        <v>Imagem de gamut</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Chromaticity</v>
+        <v>Saturation</v>
       </c>
       <c r="B40" t="str">
-        <v>Cromaticidade</v>
+        <v>Saturação</v>
       </c>
       <c r="C40" t="str">
-        <v>Cromaticidade</v>
+        <v>Saturação</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Scatter plot</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B41" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Os canais com muitas inversões mostram apenas as {shown} maiores por ΔL*.</v>
       </c>
       <c r="C41" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Os canais com muitas inversões mostram apenas as {shown} maiores por ΔL*.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Tone response curve</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B42" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Mostrar mais ({n})</v>
       </c>
       <c r="C42" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Mostrar mais ({n})</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Curve table</v>
+        <v>All</v>
       </c>
       <c r="B43" t="str">
-        <v>Tabela da curva</v>
+        <v>Todos</v>
       </c>
       <c r="C43" t="str">
-        <v>Tabela da curva</v>
+        <v>Todos</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Tables</v>
+        <v>Analysing…</v>
       </c>
       <c r="B44" t="str">
-        <v>Tabelas</v>
+        <v>A analisar…</v>
       </c>
       <c r="C44" t="str">
-        <v>Tabelas</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Data</v>
+        <v>Analysis</v>
       </c>
       <c r="B45" t="str">
-        <v>Dados</v>
+        <v>Análise</v>
       </c>
       <c r="C45" t="str">
-        <v>Dados</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Evaluate</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B46" t="str">
-        <v>Avaliar</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C46" t="str">
-        <v>Avaliar</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Loading…</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B47" t="str">
-        <v>A carregar…</v>
+        <v>Inversão de tom L*</v>
       </c>
       <c r="C47" t="str">
-        <v>Carregando…</v>
+        <v>Inversão de tom L*</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Input</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B48" t="str">
-        <v>Entrada</v>
+        <v>Adicionar tinta nunca deveria tornar uma cor mais clara. Cada canal é percorrido mantendo os outros fixos; qualquer passo em que L* sobe é assinalado. Algoritmo originalmente de Harold Boll.</v>
       </c>
       <c r="C48" t="str">
-        <v>Entrada</v>
+        <v>Adicionar tinta nunca deveria deixar uma cor mais clara. Cada canal é percorrido mantendo os outros fixos; qualquer passo em que L* sobe é sinalizado. Algoritmo originalmente de Harold Boll.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Output</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B49" t="str">
-        <v>Saída</v>
+        <v>Este perfil não tem uma CLUT dispositivo→PCS, pelo que a análise de inversão L* não se aplica (por exemplo, um perfil de ecrã de matriz/TRC).</v>
       </c>
       <c r="C49" t="str">
-        <v>Saída</v>
+        <v>Este perfil não tem uma CLUT dispositivo→PCS, então a análise de inversão L* não se aplica (por exemplo, um perfil de tela de matriz/TRC).</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Floating point</v>
+        <v>LUT table</v>
       </c>
       <c r="B50" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Tabela LUT</v>
       </c>
       <c r="C50" t="str">
-        <v>Ponto flutuante</v>
+        <v>Tabela LUT</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Grid point</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B51" t="str">
-        <v>Ponto da grelha</v>
+        <v>Limiar ΔL* (ε)</v>
       </c>
       <c r="C51" t="str">
-        <v>Ponto da grade</v>
+        <v>Limiar ΔL* (ε)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Normalized</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B52" t="str">
-        <v>Normalizado</v>
+        <v>{n} inversões acima de ε = {eps}</v>
       </c>
       <c r="C52" t="str">
-        <v>Normalizado</v>
+        <v>{n} inversões acima de ε = {eps}</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Human</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B53" t="str">
-        <v>Legível</v>
+        <v>Sem inversões L* acima de ε = {eps}</v>
       </c>
       <c r="C53" t="str">
-        <v>Legível</v>
+        <v>Sem inversões L* acima de ε = {eps}</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Device → PCS</v>
+        <v>Channel</v>
       </c>
       <c r="B54" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Canal</v>
       </c>
       <c r="C54" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Canal</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PCS → Device</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B55" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Tinta (baixo → alto)</v>
       </c>
       <c r="C55" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Tinta (baixo → alto)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>No CLUT grid</v>
+        <v>Plot</v>
       </c>
       <c r="B56" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>Gráfico</v>
       </c>
       <c r="C56" t="str">
-        <v>Sem grade CLUT</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Loading…</v>
+        <v>Raw Output</v>
       </c>
       <c r="B57" t="str">
-        <v>A carregar…</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C57" t="str">
-        <v>Carregando…</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>XML</v>
       </c>
       <c r="B58" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>XML</v>
       </c>
       <c r="C58" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Invalid profile URL:</v>
+        <v>JSON</v>
       </c>
       <c r="B59" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>JSON</v>
       </c>
       <c r="C59" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curves</v>
       </c>
       <c r="B60" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>Curvas</v>
       </c>
       <c r="C60" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Input curves</v>
       </c>
       <c r="B61" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C61" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Output curves</v>
       </c>
       <c r="B62" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C62" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B63" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C63" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Gamut image</v>
       </c>
       <c r="B64" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C64" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Security</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B65" t="str">
-        <v>Segurança</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C65" t="str">
-        <v>Segurança</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Conformance</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B66" t="str">
-        <v>Conformidade</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C66" t="str">
-        <v>Conformidade</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Quality</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B67" t="str">
-        <v>Qualidade</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C67" t="str">
-        <v>Qualidade</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>REPORT</v>
+        <v>Curve table</v>
       </c>
       <c r="B68" t="str">
-        <v>RELATÓRIO</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C68" t="str">
-        <v>RELATÓRIO</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>FAIL</v>
+        <v>Tables</v>
       </c>
       <c r="B69" t="str">
-        <v>REPROVADO</v>
+        <v>Tabelas</v>
       </c>
       <c r="C69" t="str">
-        <v>REPROVADO</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>checks</v>
+        <v>Data</v>
       </c>
       <c r="B70" t="str">
-        <v>verificações</v>
+        <v>Dados</v>
       </c>
       <c r="C70" t="str">
-        <v>verificações</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B71" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Avaliar</v>
       </c>
       <c r="C71" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading…</v>
       </c>
       <c r="B72" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>A carregar…</v>
       </c>
       <c r="C72" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Error:</v>
+        <v>Input</v>
       </c>
       <c r="B73" t="str">
-        <v>Erro:</v>
+        <v>Entrada</v>
       </c>
       <c r="C73" t="str">
-        <v>Erro:</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Convert to XML</v>
+        <v>Output</v>
       </c>
       <c r="B74" t="str">
-        <v>Converter para XML</v>
+        <v>Saída</v>
       </c>
       <c r="C74" t="str">
-        <v>Converter para XML</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Convert to JSON</v>
+        <v>Floating point</v>
       </c>
       <c r="B75" t="str">
-        <v>Converter para JSON</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C75" t="str">
-        <v>Converter para JSON</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Convert to ICC</v>
+        <v>Grid point</v>
       </c>
       <c r="B76" t="str">
-        <v>Converter para ICC</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C76" t="str">
-        <v>Converter para ICC</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Converting to XML…</v>
+        <v>Normalized</v>
       </c>
       <c r="B77" t="str">
-        <v>A converter para XML…</v>
+        <v>Normalizado</v>
       </c>
       <c r="C77" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Converting to JSON…</v>
+        <v>Human</v>
       </c>
       <c r="B78" t="str">
-        <v>A converter para JSON…</v>
+        <v>Legível</v>
       </c>
       <c r="C78" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B79" t="str">
-        <v>A converter para ICC…</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C79" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Load ICC profile</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B80" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C80" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B81" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C81" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Profile ID</v>
+        <v>Loading…</v>
       </c>
       <c r="B82" t="str">
-        <v>ID do perfil</v>
+        <v>A carregar…</v>
       </c>
       <c r="C82" t="str">
-        <v>ID do perfil</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>No tags found.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B83" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C83" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Tag Name</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B84" t="str">
-        <v>Nome da etiqueta</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C84" t="str">
-        <v>Nome da tag</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ID</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B85" t="str">
-        <v>ID</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C85" t="str">
-        <v>ID</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Offset</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B86" t="str">
-        <v>Deslocamento</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C86" t="str">
-        <v>Deslocamento</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Size</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B87" t="str">
-        <v>Tamanho</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C87" t="str">
-        <v>Tamanho</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Pad</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B88" t="str">
-        <v>Preenchimento</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C88" t="str">
-        <v>Preenchimento</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B89" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C89" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Type</v>
+        <v>Security</v>
       </c>
       <c r="B90" t="str">
-        <v>Tipo</v>
+        <v>Segurança</v>
       </c>
       <c r="C90" t="str">
-        <v>Tipo</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Array of {type}</v>
+        <v>Conformance</v>
       </c>
       <c r="B91" t="str">
-        <v>Vetor de {type}</v>
+        <v>Conformidade</v>
       </c>
       <c r="C91" t="str">
-        <v>Array de {type}</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>(No content)</v>
+        <v>Quality</v>
       </c>
       <c r="B92" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Qualidade</v>
       </c>
       <c r="C92" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>bytes</v>
+        <v>REPORT</v>
       </c>
       <c r="B93" t="str">
-        <v>bytes</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C93" t="str">
-        <v>bytes</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading full description…</v>
+        <v>FAIL</v>
       </c>
       <c r="B94" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C94" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Could not load full description:</v>
+        <v>checks</v>
       </c>
       <c r="B95" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>verificações</v>
       </c>
       <c r="C95" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B96" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C96" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B97" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C97" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>No validation output</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B98" t="str">
-        <v>Sem saída de validação</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C98" t="str">
-        <v>Sem saída de validação</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Profile is valid</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B99" t="str">
-        <v>O perfil é válido</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C99" t="str">
-        <v>O perfil é válido</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Subscribe</v>
       </c>
       <c r="B100" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Subscrever</v>
       </c>
       <c r="C100" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B101" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C101" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Critical validation error</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B102" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C102" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Unknown validation status</v>
+        <v>Close</v>
       </c>
       <c r="B103" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Fechar</v>
       </c>
       <c r="C103" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B104" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C104" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Email address</v>
       </c>
       <c r="B105" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C105" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Valid</v>
+        <v>you@example.com</v>
       </c>
       <c r="B106" t="str">
-        <v>Válido</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C106" t="str">
-        <v>Válido</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Warning</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B107" t="str">
-        <v>Aviso</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C107" t="str">
-        <v>Aviso</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Error</v>
+        <v>(optional)</v>
       </c>
       <c r="B108" t="str">
-        <v>Erro</v>
+        <v>(opcional)</v>
       </c>
       <c r="C108" t="str">
-        <v>Erro</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Unknown</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B109" t="str">
-        <v>Desconhecido</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C109" t="str">
-        <v>Desconhecido</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Pass</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B110" t="str">
-        <v>Aprovado</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C110" t="str">
-        <v>Aprovado</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Fail</v>
+        <v>Cancel</v>
       </c>
       <c r="B111" t="str">
-        <v>Reprovado</v>
+        <v>Cancelar</v>
       </c>
       <c r="C111" t="str">
-        <v>Reprovado</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>View in context</v>
+        <v>Subscribe</v>
       </c>
       <c r="B112" t="str">
-        <v>Ver no contexto</v>
+        <v>Subscrever</v>
       </c>
       <c r="C112" t="str">
-        <v>Ver no contexto</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Validation detail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B113" t="str">
-        <v>Detalhe de validação</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C113" t="str">
-        <v>Detalhe de validação</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Triggered by</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B114" t="str">
-        <v>Acionado por</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C114" t="str">
-        <v>Acionado por</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Field</v>
+        <v>Close</v>
       </c>
       <c r="B115" t="str">
-        <v>Campo</v>
+        <v>Fechar</v>
       </c>
       <c r="C115" t="str">
-        <v>Campo</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Current value</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B116" t="str">
-        <v>Valor atual</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C116" t="str">
-        <v>Valor atual</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Required: 0</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B117" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C117" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Expected: {value}</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B118" t="str">
-        <v>Esperado: {value}</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C118" t="str">
-        <v>Esperado: {value}</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Invalid</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B119" t="str">
-        <v>Inválido</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C119" t="str">
-        <v>Inválido</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B120" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C120" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Close</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B121" t="str">
-        <v>Fechar</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C121" t="str">
-        <v>Fechar</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Loading XML editor…</v>
+        <v>Error:</v>
       </c>
       <c r="B122" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Erro:</v>
       </c>
       <c r="C122" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B123" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C123" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B124" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C124" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B125" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C125" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B126" t="str">
-        <v>● edições XML por guardar</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C126" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B127" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C127" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B128" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C128" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B129" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C129" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>indent</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B130" t="str">
-        <v>indentação</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C130" t="str">
-        <v>indentação</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>sort keys</v>
+        <v>Profile ID</v>
       </c>
       <c r="B131" t="str">
-        <v>ordenar chaves</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C131" t="str">
-        <v>ordenar chaves</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Nenhuma etiqueta encontrada.</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Nenhuma tag encontrada.</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Nome da etiqueta</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Nome da tag</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C134" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Deslocamento</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Deslocamento</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Tamanho</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Tamanho</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Preenchimento</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Preenchimento</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Bytes alterados desde o carregamento</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Bytes alterados desde o carregamento</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Vetor de {type}</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Array de {type}</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B141" t="str">
+        <v>(Sem conteúdo)</v>
+      </c>
+      <c r="C141" t="str">
+        <v>(Sem conteúdo)</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B142" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="C142" t="str">
+        <v>bytes</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B143" t="str">
+        <v>A carregar descrição completa…</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Carregando descrição completa…</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Não foi possível carregar a descrição completa:</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Não foi possível carregar a descrição completa:</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B148" t="str">
+        <v>O perfil é válido</v>
+      </c>
+      <c r="C148" t="str">
+        <v>O perfil é válido</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B149" t="str">
+        <v>O perfil tem avisos</v>
+      </c>
+      <c r="C149" t="str">
+        <v>O perfil tem avisos</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B150" t="str">
+        <v>O perfil não é conforme</v>
+      </c>
+      <c r="C150" t="str">
+        <v>O perfil não está em conformidade</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Erro de validação crítico</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Erro de validação crítico</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Estado de validação desconhecido</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Status de validação desconhecido</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Crítico — apresentado apenas para inspeção</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Crítico — exibido apenas para inspeção</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Sem avisos nem erros encontrados.</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Nenhum aviso ou erro encontrado.</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Válido</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Aviso</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Aviso</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Erro</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Erro</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Desconhecido</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Desconhecido</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Aprovado</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Reprovado</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Reprovado</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Ver no contexto</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Ver no contexto</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Acionado por</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Acionado por</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B171" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B172" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B175" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C175" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B176" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C176" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B179" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C179" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B180" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C180" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B132" t="str">
+      <c r="B181" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C132" t="str">
+      <c r="C181" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C132"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C181"/>
+  <dimension ref="A1:C190"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -560,1844 +560,1943 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ICC Profile Tool</v>
+        <v>User guide</v>
       </c>
       <c r="B15" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Guia do utilizador</v>
       </c>
       <c r="C15" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Guia do usuário</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Search guide</v>
       </c>
       <c r="B16" t="str">
-        <v>Carregue um perfil ICC para o validar segundo a especificação</v>
+        <v>Pesquisar no guia</v>
       </c>
       <c r="C16" t="str">
-        <v>Envie um perfil ICC para validá-lo conforme a especificação</v>
+        <v>Pesquisar no guia</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>specification using the</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B17" t="str">
-        <v>através da implementação de demonstração</v>
+        <v>Pesquisar no guia do utilizador</v>
       </c>
       <c r="C17" t="str">
-        <v>usando a implementação de demonstração</v>
+        <v>Pesquisar no guia do usuário</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>demo implementation.</v>
+        <v>Previous match</v>
       </c>
       <c r="B18" t="str">
-        <v>.</v>
+        <v>Resultado anterior</v>
       </c>
       <c r="C18" t="str">
-        <v>.</v>
+        <v>Resultado anterior</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Based on</v>
+        <v>Next match</v>
       </c>
       <c r="B19" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Resultado seguinte</v>
       </c>
       <c r="C19" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Próximo resultado</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>demo implementation</v>
+        <v>Close user guide</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>Fechar o guia</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>Fechar o guia</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Validating…</v>
+        <v>Loading…</v>
       </c>
       <c r="B21" t="str">
-        <v>A validar…</v>
+        <v>A carregar…</v>
       </c>
       <c r="C21" t="str">
-        <v>Validando…</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Save ICC profile</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B22" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>Não foi possível carregar o guia do utilizador.</v>
       </c>
       <c r="C22" t="str">
-        <v>Salvar perfil ICC</v>
+        <v>Não foi possível carregar o guia do usuário.</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>None</v>
       </c>
       <c r="B23" t="str">
-        <v>● Modificado — não guardado</v>
+        <v>Nenhum</v>
       </c>
       <c r="C23" t="str">
-        <v>● Modificado — não salvo</v>
+        <v>Nenhum</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B24" t="str">
-        <v>Largue um perfil ICC aqui</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C24" t="str">
-        <v>Solte um perfil ICC aqui</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>or</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B25" t="str">
-        <v>ou</v>
+        <v>Carregue um perfil ICC para o validar segundo a especificação</v>
       </c>
       <c r="C25" t="str">
-        <v>ou</v>
+        <v>Envie um perfil ICC para validá-lo conforme a especificação</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Choose file</v>
+        <v>specification using the</v>
       </c>
       <c r="B26" t="str">
-        <v>Escolher ficheiro</v>
+        <v>através da implementação de demonstração</v>
       </c>
       <c r="C26" t="str">
-        <v>Escolher arquivo</v>
+        <v>usando a implementação de demonstração</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>.icc and .icm files</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B27" t="str">
-        <v>Ficheiros .icc e .icm</v>
+        <v>.</v>
       </c>
       <c r="C27" t="str">
-        <v>Arquivos .icc e .icm</v>
+        <v>.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Header</v>
+        <v>Based on</v>
       </c>
       <c r="B28" t="str">
-        <v>Cabeçalho</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
       <c r="C28" t="str">
-        <v>Cabeçalho</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Tags</v>
+        <v>demo implementation</v>
       </c>
       <c r="B29" t="str">
-        <v>Etiquetas</v>
+        <v/>
       </c>
       <c r="C29" t="str">
-        <v>Tags</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validation</v>
+        <v>Validating…</v>
       </c>
       <c r="B30" t="str">
-        <v>Validação</v>
+        <v>A validar…</v>
       </c>
       <c r="C30" t="str">
-        <v>Validação</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Analysis</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B31" t="str">
-        <v>Análise</v>
+        <v>Guardar perfil ICC</v>
       </c>
       <c r="C31" t="str">
-        <v>Análise</v>
+        <v>Salvar perfil ICC</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B32" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>● Modificado — não guardado</v>
       </c>
       <c r="C32" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>● Modificado — não salvo</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B33" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
+        <v>Largue um perfil ICC aqui</v>
       </c>
       <c r="C33" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
+        <v>Solte um perfil ICC aqui</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>or</v>
       </c>
       <c r="B34" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>ou</v>
       </c>
       <c r="C34" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Choose file</v>
       </c>
       <c r="B35" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>Escolher ficheiro</v>
       </c>
       <c r="C35" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>Escolher arquivo</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Rendering intent</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B36" t="str">
-        <v>Intenção de renderização</v>
+        <v>Ficheiros .icc e .icm</v>
       </c>
       <c r="C36" t="str">
-        <v>Intenção de renderização</v>
+        <v>Arquivos .icc e .icm</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>% ink</v>
+        <v>Header</v>
       </c>
       <c r="B37" t="str">
-        <v>% tinta</v>
+        <v>Cabeçalho</v>
       </c>
       <c r="C37" t="str">
-        <v>% tinta</v>
+        <v>Cabeçalho</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Perceptual</v>
+        <v>Tags</v>
       </c>
       <c r="B38" t="str">
-        <v>Perceptual</v>
+        <v>Etiquetas</v>
       </c>
       <c r="C38" t="str">
-        <v>Perceptual</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Relative colorimetric</v>
+        <v>Validation</v>
       </c>
       <c r="B39" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Validação</v>
       </c>
       <c r="C39" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Validação</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Saturation</v>
+        <v>Analysis</v>
       </c>
       <c r="B40" t="str">
-        <v>Saturação</v>
+        <v>Análise</v>
       </c>
       <c r="C40" t="str">
-        <v>Saturação</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B41" t="str">
-        <v>Os canais com muitas inversões mostram apenas as {shown} maiores por ΔL*.</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
       <c r="C41" t="str">
-        <v>Os canais com muitas inversões mostram apenas as {shown} maiores por ΔL*.</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Show more ({n})</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B42" t="str">
-        <v>Mostrar mais ({n})</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
       </c>
       <c r="C42" t="str">
-        <v>Mostrar mais ({n})</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>All</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B43" t="str">
-        <v>Todos</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C43" t="str">
-        <v>Todos</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Analysing…</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B44" t="str">
-        <v>A analisar…</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
       <c r="C44" t="str">
-        <v>Analisando…</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B45" t="str">
-        <v>Análise</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C45" t="str">
-        <v>Análise</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>% ink</v>
       </c>
       <c r="B46" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>% tinta</v>
       </c>
       <c r="C46" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Perceptual</v>
       </c>
       <c r="B47" t="str">
-        <v>Inversão de tom L*</v>
+        <v>Perceptual</v>
       </c>
       <c r="C47" t="str">
-        <v>Inversão de tom L*</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B48" t="str">
-        <v>Adicionar tinta nunca deveria tornar uma cor mais clara. Cada canal é percorrido mantendo os outros fixos; qualquer passo em que L* sobe é assinalado. Algoritmo originalmente de Harold Boll.</v>
+        <v>Colorimétrico relativo</v>
       </c>
       <c r="C48" t="str">
-        <v>Adicionar tinta nunca deveria deixar uma cor mais clara. Cada canal é percorrido mantendo os outros fixos; qualquer passo em que L* sobe é sinalizado. Algoritmo originalmente de Harold Boll.</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B49" t="str">
-        <v>Este perfil não tem uma CLUT dispositivo→PCS, pelo que a análise de inversão L* não se aplica (por exemplo, um perfil de ecrã de matriz/TRC).</v>
+        <v>Saturação</v>
       </c>
       <c r="C49" t="str">
-        <v>Este perfil não tem uma CLUT dispositivo→PCS, então a análise de inversão L* não se aplica (por exemplo, um perfil de tela de matriz/TRC).</v>
+        <v>Saturação</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LUT table</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B50" t="str">
-        <v>Tabela LUT</v>
+        <v>Os canais com muitas inversões mostram apenas as {shown} maiores por ΔL*.</v>
       </c>
       <c r="C50" t="str">
-        <v>Tabela LUT</v>
+        <v>Os canais com muitas inversões mostram apenas as {shown} maiores por ΔL*.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B51" t="str">
-        <v>Limiar ΔL* (ε)</v>
+        <v>Mostrar mais ({n})</v>
       </c>
       <c r="C51" t="str">
-        <v>Limiar ΔL* (ε)</v>
+        <v>Mostrar mais ({n})</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B52" t="str">
-        <v>{n} inversões acima de ε = {eps}</v>
+        <v>Todos</v>
       </c>
       <c r="C52" t="str">
-        <v>{n} inversões acima de ε = {eps}</v>
+        <v>Todos</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Analysing…</v>
       </c>
       <c r="B53" t="str">
-        <v>Sem inversões L* acima de ε = {eps}</v>
+        <v>A analisar…</v>
       </c>
       <c r="C53" t="str">
-        <v>Sem inversões L* acima de ε = {eps}</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Channel</v>
+        <v>Analysis</v>
       </c>
       <c r="B54" t="str">
-        <v>Canal</v>
+        <v>Análise</v>
       </c>
       <c r="C54" t="str">
-        <v>Canal</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Ink (low → high)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B55" t="str">
-        <v>Tinta (baixo → alto)</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C55" t="str">
-        <v>Tinta (baixo → alto)</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Plot</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B56" t="str">
-        <v>Gráfico</v>
+        <v>Inversão de tom L*</v>
       </c>
       <c r="C56" t="str">
-        <v>Gráfico</v>
+        <v>Inversão de tom L*</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Raw Output</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B57" t="str">
-        <v>Saída em bruto</v>
+        <v>Adicionar tinta nunca deveria tornar uma cor mais clara. Cada canal é percorrido mantendo os outros fixos; qualquer passo em que L* sobe é assinalado. Algoritmo originalmente de Harold Boll.</v>
       </c>
       <c r="C57" t="str">
-        <v>Saída bruta</v>
+        <v>Adicionar tinta nunca deveria deixar uma cor mais clara. Cada canal é percorrido mantendo os outros fixos; qualquer passo em que L* sobe é sinalizado. Algoritmo originalmente de Harold Boll.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>XML</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B58" t="str">
-        <v>XML</v>
+        <v>Este perfil não tem uma CLUT dispositivo→PCS, pelo que a análise de inversão L* não se aplica (por exemplo, um perfil de ecrã de matriz/TRC).</v>
       </c>
       <c r="C58" t="str">
-        <v>XML</v>
+        <v>Este perfil não tem uma CLUT dispositivo→PCS, então a análise de inversão L* não se aplica (por exemplo, um perfil de tela de matriz/TRC).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>JSON</v>
+        <v>LUT table</v>
       </c>
       <c r="B59" t="str">
-        <v>JSON</v>
+        <v>Tabela LUT</v>
       </c>
       <c r="C59" t="str">
-        <v>JSON</v>
+        <v>Tabela LUT</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B60" t="str">
-        <v>Curvas</v>
+        <v>Limiar ΔL* (ε)</v>
       </c>
       <c r="C60" t="str">
-        <v>Curvas</v>
+        <v>Limiar ΔL* (ε)</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Input curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B61" t="str">
-        <v>Curvas de entrada</v>
+        <v>{n} inversões acima de ε = {eps}</v>
       </c>
       <c r="C61" t="str">
-        <v>Curvas de entrada</v>
+        <v>{n} inversões acima de ε = {eps}</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Output curves</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B62" t="str">
-        <v>Curvas de saída</v>
+        <v>Sem inversões L* acima de ε = {eps}</v>
       </c>
       <c r="C62" t="str">
-        <v>Curvas de saída</v>
+        <v>Sem inversões L* acima de ε = {eps}</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>CLUT image</v>
+        <v>Channel</v>
       </c>
       <c r="B63" t="str">
-        <v>Imagem CLUT</v>
+        <v>Canal</v>
       </c>
       <c r="C63" t="str">
-        <v>Imagem CLUT</v>
+        <v>Canal</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Gamut image</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B64" t="str">
-        <v>Imagem de gamut</v>
+        <v>Tinta (baixo → alto)</v>
       </c>
       <c r="C64" t="str">
-        <v>Imagem de gamut</v>
+        <v>Tinta (baixo → alto)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Chromaticity</v>
+        <v>Plot</v>
       </c>
       <c r="B65" t="str">
-        <v>Cromaticidade</v>
+        <v>Gráfico</v>
       </c>
       <c r="C65" t="str">
-        <v>Cromaticidade</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Scatter plot</v>
+        <v>Raw Output</v>
       </c>
       <c r="B66" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C66" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Tone response curve</v>
+        <v>XML</v>
       </c>
       <c r="B67" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>XML</v>
       </c>
       <c r="C67" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curve table</v>
+        <v>JSON</v>
       </c>
       <c r="B68" t="str">
-        <v>Tabela da curva</v>
+        <v>JSON</v>
       </c>
       <c r="C68" t="str">
-        <v>Tabela da curva</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Tables</v>
+        <v>Curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Tabelas</v>
+        <v>Curvas</v>
       </c>
       <c r="C69" t="str">
-        <v>Tabelas</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Data</v>
+        <v>Input curves</v>
       </c>
       <c r="B70" t="str">
-        <v>Dados</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C70" t="str">
-        <v>Dados</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Evaluate</v>
+        <v>Output curves</v>
       </c>
       <c r="B71" t="str">
-        <v>Avaliar</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C71" t="str">
-        <v>Avaliar</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Loading…</v>
+        <v>CLUT image</v>
       </c>
       <c r="B72" t="str">
-        <v>A carregar…</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C72" t="str">
-        <v>Carregando…</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Input</v>
+        <v>Gamut image</v>
       </c>
       <c r="B73" t="str">
-        <v>Entrada</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C73" t="str">
-        <v>Entrada</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Output</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B74" t="str">
-        <v>Saída</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C74" t="str">
-        <v>Saída</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Floating point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B75" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C75" t="str">
-        <v>Ponto flutuante</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Grid point</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B76" t="str">
-        <v>Ponto da grelha</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C76" t="str">
-        <v>Ponto da grade</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Normalized</v>
+        <v>Curve table</v>
       </c>
       <c r="B77" t="str">
-        <v>Normalizado</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C77" t="str">
-        <v>Normalizado</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Human</v>
+        <v>Tables</v>
       </c>
       <c r="B78" t="str">
-        <v>Legível</v>
+        <v>Tabelas</v>
       </c>
       <c r="C78" t="str">
-        <v>Legível</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Device → PCS</v>
+        <v>Data</v>
       </c>
       <c r="B79" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Dados</v>
       </c>
       <c r="C79" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>PCS → Device</v>
+        <v>Evaluate</v>
       </c>
       <c r="B80" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Avaliar</v>
       </c>
       <c r="C80" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>No CLUT grid</v>
+        <v>Loading…</v>
       </c>
       <c r="B81" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>A carregar…</v>
       </c>
       <c r="C81" t="str">
-        <v>Sem grade CLUT</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Loading…</v>
+        <v>Input</v>
       </c>
       <c r="B82" t="str">
-        <v>A carregar…</v>
+        <v>Entrada</v>
       </c>
       <c r="C82" t="str">
-        <v>Carregando…</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Output</v>
       </c>
       <c r="B83" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Saída</v>
       </c>
       <c r="C83" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Floating point</v>
       </c>
       <c r="B84" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C84" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Grid point</v>
       </c>
       <c r="B85" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C85" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Normalized</v>
       </c>
       <c r="B86" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>Normalizado</v>
       </c>
       <c r="C86" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Human</v>
       </c>
       <c r="B87" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Legível</v>
       </c>
       <c r="C87" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B88" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C88" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B89" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C89" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Security</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B90" t="str">
-        <v>Segurança</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C90" t="str">
-        <v>Segurança</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Conformance</v>
+        <v>Loading…</v>
       </c>
       <c r="B91" t="str">
-        <v>Conformidade</v>
+        <v>A carregar…</v>
       </c>
       <c r="C91" t="str">
-        <v>Conformidade</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Quality</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B92" t="str">
-        <v>Qualidade</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C92" t="str">
-        <v>Qualidade</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>REPORT</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B93" t="str">
-        <v>RELATÓRIO</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C93" t="str">
-        <v>RELATÓRIO</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>FAIL</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B94" t="str">
-        <v>REPROVADO</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C94" t="str">
-        <v>REPROVADO</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>checks</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B95" t="str">
-        <v>verificações</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C95" t="str">
-        <v>verificações</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B96" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C96" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B97" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C97" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B98" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C98" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Powered by {lib}</v>
+        <v>Security</v>
       </c>
       <c r="B99" t="str">
-        <v>Com {lib}</v>
+        <v>Segurança</v>
       </c>
       <c r="C99" t="str">
-        <v>Com {lib}</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Subscribe</v>
+        <v>Conformance</v>
       </c>
       <c r="B100" t="str">
-        <v>Subscrever</v>
+        <v>Conformidade</v>
       </c>
       <c r="C100" t="str">
-        <v>Inscrever-se</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Quality</v>
       </c>
       <c r="B101" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Qualidade</v>
       </c>
       <c r="C101" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Get notified about new releases</v>
+        <v>REPORT</v>
       </c>
       <c r="B102" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C102" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Close</v>
+        <v>FAIL</v>
       </c>
       <c r="B103" t="str">
-        <v>Fechar</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C103" t="str">
-        <v>Fechar</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>checks</v>
       </c>
       <c r="B104" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>verificações</v>
       </c>
       <c r="C104" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Email address</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B105" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C105" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>you@example.com</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B106" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C106" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B107" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C107" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>(optional)</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B108" t="str">
-        <v>(opcional)</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C108" t="str">
-        <v>(opcional)</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B109" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Subscrever</v>
       </c>
       <c r="C109" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B110" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C110" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B111" t="str">
-        <v>Cancelar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C111" t="str">
-        <v>Cancelar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B112" t="str">
-        <v>Subscrever</v>
+        <v>Fechar</v>
       </c>
       <c r="C112" t="str">
-        <v>Inscrever-se</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B113" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C113" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Email address</v>
       </c>
       <c r="B114" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C114" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B115" t="str">
-        <v>Fechar</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C115" t="str">
-        <v>Fechar</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Privacy notice</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B116" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C116" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>(optional)</v>
       </c>
       <c r="B117" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>(opcional)</v>
       </c>
       <c r="C117" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B118" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C118" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Please check the form and try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B119" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C119" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B120" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Cancelar</v>
       </c>
       <c r="C120" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B121" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C121" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Error:</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B122" t="str">
-        <v>Erro:</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C122" t="str">
-        <v>Erro:</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Convert to XML</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B123" t="str">
-        <v>Converter para XML</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C123" t="str">
-        <v>Converter para XML</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Convert to JSON</v>
+        <v>Close</v>
       </c>
       <c r="B124" t="str">
-        <v>Converter para JSON</v>
+        <v>Fechar</v>
       </c>
       <c r="C124" t="str">
-        <v>Converter para JSON</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Convert to ICC</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B125" t="str">
-        <v>Converter para ICC</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C125" t="str">
-        <v>Converter para ICC</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Converting to XML…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B126" t="str">
-        <v>A converter para XML…</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C126" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Converting to JSON…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B127" t="str">
-        <v>A converter para JSON…</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C127" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Converting to ICC…</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>A converter para ICC…</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C128" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Load ICC profile</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C129" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B130" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C130" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Profile ID</v>
+        <v>Error:</v>
       </c>
       <c r="B131" t="str">
-        <v>ID do perfil</v>
+        <v>Erro:</v>
       </c>
       <c r="C131" t="str">
-        <v>ID do perfil</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>No tags found.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B132" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C132" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Tag Name</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B133" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C133" t="str">
-        <v>Nome da tag</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>ID</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B134" t="str">
-        <v>ID</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C134" t="str">
-        <v>ID</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Offset</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B135" t="str">
-        <v>Deslocamento</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C135" t="str">
-        <v>Deslocamento</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Size</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B136" t="str">
-        <v>Tamanho</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C136" t="str">
-        <v>Tamanho</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Pad</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B137" t="str">
-        <v>Preenchimento</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C137" t="str">
-        <v>Preenchimento</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Bytes changed since load</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B138" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C138" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Type</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B139" t="str">
-        <v>Tipo</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C139" t="str">
-        <v>Tipo</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Array of {type}</v>
+        <v>Profile ID</v>
       </c>
       <c r="B140" t="str">
-        <v>Vetor de {type}</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C140" t="str">
-        <v>Array de {type}</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>(No content)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B141" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C141" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>bytes</v>
+        <v>Tag Name</v>
       </c>
       <c r="B142" t="str">
-        <v>bytes</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C142" t="str">
-        <v>bytes</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Loading full description…</v>
+        <v>ID</v>
       </c>
       <c r="B143" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>ID</v>
       </c>
       <c r="C143" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Could not load full description:</v>
+        <v>Offset</v>
       </c>
       <c r="B144" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C144" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Size</v>
       </c>
       <c r="B145" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Tamanho</v>
       </c>
       <c r="C145" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Pad</v>
       </c>
       <c r="B146" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C146" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>No validation output</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B147" t="str">
-        <v>Sem saída de validação</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C147" t="str">
-        <v>Sem saída de validação</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Profile is valid</v>
+        <v>Type</v>
       </c>
       <c r="B148" t="str">
-        <v>O perfil é válido</v>
+        <v>Tipo</v>
       </c>
       <c r="C148" t="str">
-        <v>O perfil é válido</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B149" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C149" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile is non-compliant</v>
+        <v>(No content)</v>
       </c>
       <c r="B150" t="str">
-        <v>O perfil não é conforme</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C150" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Critical validation error</v>
+        <v>bytes</v>
       </c>
       <c r="B151" t="str">
-        <v>Erro de validação crítico</v>
+        <v>bytes</v>
       </c>
       <c r="C151" t="str">
-        <v>Erro de validação crítico</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Unknown validation status</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B152" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C152" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B153" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C153" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No warnings or errors found.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B154" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C154" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Valid</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B155" t="str">
-        <v>Válido</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C155" t="str">
-        <v>Válido</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Warning</v>
+        <v>No validation output</v>
       </c>
       <c r="B156" t="str">
-        <v>Aviso</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C156" t="str">
-        <v>Aviso</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Error</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B157" t="str">
-        <v>Erro</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C157" t="str">
-        <v>Erro</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Unknown</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B158" t="str">
-        <v>Desconhecido</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C158" t="str">
-        <v>Desconhecido</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Pass</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B159" t="str">
-        <v>Aprovado</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C159" t="str">
-        <v>Aprovado</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Fail</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B160" t="str">
-        <v>Reprovado</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C160" t="str">
-        <v>Reprovado</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>View in context</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B161" t="str">
-        <v>Ver no contexto</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C161" t="str">
-        <v>Ver no contexto</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Validation detail</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B162" t="str">
-        <v>Detalhe de validação</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C162" t="str">
-        <v>Detalhe de validação</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Triggered by</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B163" t="str">
-        <v>Acionado por</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C163" t="str">
-        <v>Acionado por</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Field</v>
+        <v>Valid</v>
       </c>
       <c r="B164" t="str">
-        <v>Campo</v>
+        <v>Válido</v>
       </c>
       <c r="C164" t="str">
-        <v>Campo</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Current value</v>
+        <v>Warning</v>
       </c>
       <c r="B165" t="str">
-        <v>Valor atual</v>
+        <v>Aviso</v>
       </c>
       <c r="C165" t="str">
-        <v>Valor atual</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Required: 0</v>
+        <v>Error</v>
       </c>
       <c r="B166" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Erro</v>
       </c>
       <c r="C166" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Expected: {value}</v>
+        <v>Unknown</v>
       </c>
       <c r="B167" t="str">
-        <v>Esperado: {value}</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C167" t="str">
-        <v>Esperado: {value}</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Invalid</v>
+        <v>Pass</v>
       </c>
       <c r="B168" t="str">
-        <v>Inválido</v>
+        <v>Aprovado</v>
       </c>
       <c r="C168" t="str">
-        <v>Inválido</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Fail</v>
       </c>
       <c r="B169" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Reprovado</v>
       </c>
       <c r="C169" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>View in context</v>
       </c>
       <c r="B170" t="str">
-        <v>Fechar</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C170" t="str">
-        <v>Fechar</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Loading XML editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B171" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C171" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Triggered by</v>
       </c>
       <c r="B172" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Acionado por</v>
       </c>
       <c r="C172" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B173" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Campo</v>
       </c>
       <c r="C173" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Current value</v>
       </c>
       <c r="B174" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Valor atual</v>
       </c>
       <c r="C174" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B175" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C175" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B176" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C176" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B177" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Inválido</v>
       </c>
       <c r="C177" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B178" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C178" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>indent</v>
+        <v>Close</v>
       </c>
       <c r="B179" t="str">
-        <v>indentação</v>
+        <v>Fechar</v>
       </c>
       <c r="C179" t="str">
-        <v>indentação</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>sort keys</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>ordenar chaves</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C180" t="str">
-        <v>ordenar chaves</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B181" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B184" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C184" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B185" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C185" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B188" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C188" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C189" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B181" t="str">
+      <c r="B190" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C181" t="str">
+      <c r="C190" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C190"/>
+  <dimension ref="A1:C200"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -945,453 +945,453 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B50" t="str">
-        <v>Os canais com muitas inversões mostram apenas as {shown} maiores por ΔL*.</v>
+        <v>Colorimétrico absoluto</v>
       </c>
       <c r="C50" t="str">
-        <v>Os canais com muitas inversões mostram apenas as {shown} maiores por ΔL*.</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Show more ({n})</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B51" t="str">
-        <v>Mostrar mais ({n})</v>
+        <v>Estatísticas do perfil</v>
       </c>
       <c r="C51" t="str">
-        <v>Mostrar mais ({n})</v>
+        <v>Estatísticas do perfil</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>All</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B52" t="str">
-        <v>Todos</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
       <c r="C52" t="str">
-        <v>Todos</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Analysing…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B53" t="str">
-        <v>A analisar…</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
       </c>
       <c r="C53" t="str">
-        <v>Analisando…</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Analysis</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B54" t="str">
-        <v>Análise</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C54" t="str">
-        <v>Análise</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B55" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Volume de gamute (ΔE³)</v>
       </c>
       <c r="C55" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>L* Tone Reversal</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B56" t="str">
-        <v>Inversão de tom L*</v>
+        <v>ΔE de percurso</v>
       </c>
       <c r="C56" t="str">
-        <v>Inversão de tom L*</v>
+        <v>ΔE de percurso</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>mean</v>
       </c>
       <c r="B57" t="str">
-        <v>Adicionar tinta nunca deveria tornar uma cor mais clara. Cada canal é percorrido mantendo os outros fixos; qualquer passo em que L* sobe é assinalado. Algoritmo originalmente de Harold Boll.</v>
+        <v>média</v>
       </c>
       <c r="C57" t="str">
-        <v>Adicionar tinta nunca deveria deixar uma cor mais clara. Cada canal é percorrido mantendo os outros fixos; qualquer passo em que L* sobe é sinalizado. Algoritmo originalmente de Harold Boll.</v>
+        <v>média</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>P90</v>
       </c>
       <c r="B58" t="str">
-        <v>Este perfil não tem uma CLUT dispositivo→PCS, pelo que a análise de inversão L* não se aplica (por exemplo, um perfil de ecrã de matriz/TRC).</v>
+        <v>P90</v>
       </c>
       <c r="C58" t="str">
-        <v>Este perfil não tem uma CLUT dispositivo→PCS, então a análise de inversão L* não se aplica (por exemplo, um perfil de tela de matriz/TRC).</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>LUT table</v>
+        <v>max</v>
       </c>
       <c r="B59" t="str">
-        <v>Tabela LUT</v>
+        <v>máx.</v>
       </c>
       <c r="C59" t="str">
-        <v>Tabela LUT</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
       </c>
       <c r="B60" t="str">
-        <v>Limiar ΔL* (ε)</v>
+        <v>Os canais com muitas inversões mostram apenas as {shown} maiores por ΔL*.</v>
       </c>
       <c r="C60" t="str">
-        <v>Limiar ΔL* (ε)</v>
+        <v>Os canais com muitas inversões mostram apenas as {shown} maiores por ΔL*.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Show more ({n})</v>
       </c>
       <c r="B61" t="str">
-        <v>{n} inversões acima de ε = {eps}</v>
+        <v>Mostrar mais ({n})</v>
       </c>
       <c r="C61" t="str">
-        <v>{n} inversões acima de ε = {eps}</v>
+        <v>Mostrar mais ({n})</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>All</v>
       </c>
       <c r="B62" t="str">
-        <v>Sem inversões L* acima de ε = {eps}</v>
+        <v>Todos</v>
       </c>
       <c r="C62" t="str">
-        <v>Sem inversões L* acima de ε = {eps}</v>
+        <v>Todos</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Channel</v>
+        <v>Analysing…</v>
       </c>
       <c r="B63" t="str">
-        <v>Canal</v>
+        <v>A analisar…</v>
       </c>
       <c r="C63" t="str">
-        <v>Canal</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Ink (low → high)</v>
+        <v>Analysis</v>
       </c>
       <c r="B64" t="str">
-        <v>Tinta (baixo → alto)</v>
+        <v>Análise</v>
       </c>
       <c r="C64" t="str">
-        <v>Tinta (baixo → alto)</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B65" t="str">
-        <v>Gráfico</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C65" t="str">
-        <v>Gráfico</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Raw Output</v>
+        <v>L* Tone Reversal</v>
       </c>
       <c r="B66" t="str">
-        <v>Saída em bruto</v>
+        <v>Inversão de tom L*</v>
       </c>
       <c r="C66" t="str">
-        <v>Saída bruta</v>
+        <v>Inversão de tom L*</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>XML</v>
+        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
       </c>
       <c r="B67" t="str">
-        <v>XML</v>
+        <v>Adicionar tinta nunca deveria tornar uma cor mais clara. Cada canal é percorrido mantendo os outros fixos; qualquer passo em que L* sobe é assinalado. Algoritmo originalmente de Harold Boll.</v>
       </c>
       <c r="C67" t="str">
-        <v>XML</v>
+        <v>Adicionar tinta nunca deveria deixar uma cor mais clara. Cada canal é percorrido mantendo os outros fixos; qualquer passo em que L* sobe é sinalizado. Algoritmo originalmente de Harold Boll.</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>JSON</v>
+        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
       </c>
       <c r="B68" t="str">
-        <v>JSON</v>
+        <v>Este perfil não tem uma CLUT dispositivo→PCS, pelo que a análise de inversão L* não se aplica (por exemplo, um perfil de ecrã de matriz/TRC).</v>
       </c>
       <c r="C68" t="str">
-        <v>JSON</v>
+        <v>Este perfil não tem uma CLUT dispositivo→PCS, então a análise de inversão L* não se aplica (por exemplo, um perfil de tela de matriz/TRC).</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Curves</v>
+        <v>LUT table</v>
       </c>
       <c r="B69" t="str">
-        <v>Curvas</v>
+        <v>Tabela LUT</v>
       </c>
       <c r="C69" t="str">
-        <v>Curvas</v>
+        <v>Tabela LUT</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Input curves</v>
+        <v>ΔL* threshold (ε)</v>
       </c>
       <c r="B70" t="str">
-        <v>Curvas de entrada</v>
+        <v>Limiar ΔL* (ε)</v>
       </c>
       <c r="C70" t="str">
-        <v>Curvas de entrada</v>
+        <v>Limiar ΔL* (ε)</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Output curves</v>
+        <v>{n} reversals above ε = {eps}</v>
       </c>
       <c r="B71" t="str">
-        <v>Curvas de saída</v>
+        <v>{n} inversões acima de ε = {eps}</v>
       </c>
       <c r="C71" t="str">
-        <v>Curvas de saída</v>
+        <v>{n} inversões acima de ε = {eps}</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>CLUT image</v>
+        <v>No L* reversals above ε = {eps}</v>
       </c>
       <c r="B72" t="str">
-        <v>Imagem CLUT</v>
+        <v>Sem inversões L* acima de ε = {eps}</v>
       </c>
       <c r="C72" t="str">
-        <v>Imagem CLUT</v>
+        <v>Sem inversões L* acima de ε = {eps}</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut image</v>
+        <v>Channel</v>
       </c>
       <c r="B73" t="str">
-        <v>Imagem de gamut</v>
+        <v>Canal</v>
       </c>
       <c r="C73" t="str">
-        <v>Imagem de gamut</v>
+        <v>Canal</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Chromaticity</v>
+        <v>Ink (low → high)</v>
       </c>
       <c r="B74" t="str">
-        <v>Cromaticidade</v>
+        <v>Tinta (baixo → alto)</v>
       </c>
       <c r="C74" t="str">
-        <v>Cromaticidade</v>
+        <v>Tinta (baixo → alto)</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Scatter plot</v>
+        <v>Plot</v>
       </c>
       <c r="B75" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Gráfico</v>
       </c>
       <c r="C75" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tone response curve</v>
+        <v>Raw Output</v>
       </c>
       <c r="B76" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C76" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Curve table</v>
+        <v>XML</v>
       </c>
       <c r="B77" t="str">
-        <v>Tabela da curva</v>
+        <v>XML</v>
       </c>
       <c r="C77" t="str">
-        <v>Tabela da curva</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tables</v>
+        <v>JSON</v>
       </c>
       <c r="B78" t="str">
-        <v>Tabelas</v>
+        <v>JSON</v>
       </c>
       <c r="C78" t="str">
-        <v>Tabelas</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Data</v>
+        <v>Curves</v>
       </c>
       <c r="B79" t="str">
-        <v>Dados</v>
+        <v>Curvas</v>
       </c>
       <c r="C79" t="str">
-        <v>Dados</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Evaluate</v>
+        <v>Input curves</v>
       </c>
       <c r="B80" t="str">
-        <v>Avaliar</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C80" t="str">
-        <v>Avaliar</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Loading…</v>
+        <v>Output curves</v>
       </c>
       <c r="B81" t="str">
-        <v>A carregar…</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C81" t="str">
-        <v>Carregando…</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Input</v>
+        <v>CLUT image</v>
       </c>
       <c r="B82" t="str">
-        <v>Entrada</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C82" t="str">
-        <v>Entrada</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B83" t="str">
-        <v>Saída</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C83" t="str">
-        <v>Saída</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Floating point</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B84" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C84" t="str">
-        <v>Ponto flutuante</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Grid point</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B85" t="str">
-        <v>Ponto da grelha</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C85" t="str">
-        <v>Ponto da grade</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Normalized</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B86" t="str">
-        <v>Normalizado</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C86" t="str">
-        <v>Normalizado</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Human</v>
+        <v>Curve table</v>
       </c>
       <c r="B87" t="str">
-        <v>Legível</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C87" t="str">
-        <v>Legível</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Device → PCS</v>
+        <v>Tables</v>
       </c>
       <c r="B88" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Tabelas</v>
       </c>
       <c r="C88" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>PCS → Device</v>
+        <v>Data</v>
       </c>
       <c r="B89" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dados</v>
       </c>
       <c r="C89" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>No CLUT grid</v>
+        <v>Evaluate</v>
       </c>
       <c r="B90" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>Avaliar</v>
       </c>
       <c r="C90" t="str">
-        <v>Sem grade CLUT</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="91">
@@ -1407,1096 +1407,1206 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Input</v>
       </c>
       <c r="B92" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Entrada</v>
       </c>
       <c r="C92" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Output</v>
       </c>
       <c r="B93" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Saída</v>
       </c>
       <c r="C93" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Floating point</v>
       </c>
       <c r="B94" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C94" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Grid point</v>
       </c>
       <c r="B95" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C95" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Normalized</v>
       </c>
       <c r="B96" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Normalizado</v>
       </c>
       <c r="C96" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Human</v>
       </c>
       <c r="B97" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>Legível</v>
       </c>
       <c r="C97" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B98" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C98" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Security</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B99" t="str">
-        <v>Segurança</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C99" t="str">
-        <v>Segurança</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Conformance</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B100" t="str">
-        <v>Conformidade</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C100" t="str">
-        <v>Conformidade</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Quality</v>
+        <v>Loading…</v>
       </c>
       <c r="B101" t="str">
-        <v>Qualidade</v>
+        <v>A carregar…</v>
       </c>
       <c r="C101" t="str">
-        <v>Qualidade</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>REPORT</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B102" t="str">
-        <v>RELATÓRIO</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C102" t="str">
-        <v>RELATÓRIO</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>FAIL</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B103" t="str">
-        <v>REPROVADO</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C103" t="str">
-        <v>REPROVADO</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>checks</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B104" t="str">
-        <v>verificações</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C104" t="str">
-        <v>verificações</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B105" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C105" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B106" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C106" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B107" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C107" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Powered by {lib}</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B108" t="str">
-        <v>Com {lib}</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C108" t="str">
-        <v>Com {lib}</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Subscribe</v>
+        <v>Security</v>
       </c>
       <c r="B109" t="str">
-        <v>Subscrever</v>
+        <v>Segurança</v>
       </c>
       <c r="C109" t="str">
-        <v>Inscrever-se</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Conformance</v>
       </c>
       <c r="B110" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Conformidade</v>
       </c>
       <c r="C110" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Get notified about new releases</v>
+        <v>Quality</v>
       </c>
       <c r="B111" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Qualidade</v>
       </c>
       <c r="C111" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Close</v>
+        <v>REPORT</v>
       </c>
       <c r="B112" t="str">
-        <v>Fechar</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C112" t="str">
-        <v>Fechar</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>FAIL</v>
       </c>
       <c r="B113" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C113" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Email address</v>
+        <v>checks</v>
       </c>
       <c r="B114" t="str">
-        <v>Endereço de e-mail</v>
+        <v>verificações</v>
       </c>
       <c r="C114" t="str">
-        <v>Endereço de e-mail</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>you@example.com</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B115" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C115" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>How will you use profiletool?</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B116" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C116" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>(optional)</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B117" t="str">
-        <v>(opcional)</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C117" t="str">
-        <v>(opcional)</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B118" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C118" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B119" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C119" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Cancel</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B120" t="str">
-        <v>Cancelar</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C120" t="str">
-        <v>Cancelar</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Subscribe</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B121" t="str">
-        <v>Subscrever</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C121" t="str">
-        <v>Inscrever-se</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Close</v>
       </c>
       <c r="B122" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Fechar</v>
       </c>
       <c r="C122" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B123" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C123" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Close</v>
+        <v>Email address</v>
       </c>
       <c r="B124" t="str">
-        <v>Fechar</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C124" t="str">
-        <v>Fechar</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Privacy notice</v>
+        <v>you@example.com</v>
       </c>
       <c r="B125" t="str">
-        <v>Aviso de privacidade</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C125" t="str">
-        <v>Aviso de privacidade</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B126" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C126" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>(optional)</v>
       </c>
       <c r="B127" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>(opcional)</v>
       </c>
       <c r="C127" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Please check the form and try again.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B128" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C128" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B129" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C129" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Cancel</v>
       </c>
       <c r="B130" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Cancelar</v>
       </c>
       <c r="C130" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Error:</v>
+        <v>Subscribe</v>
       </c>
       <c r="B131" t="str">
-        <v>Erro:</v>
+        <v>Subscrever</v>
       </c>
       <c r="C131" t="str">
-        <v>Erro:</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to XML</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B132" t="str">
-        <v>Converter para XML</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C132" t="str">
-        <v>Converter para XML</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to JSON</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B133" t="str">
-        <v>Converter para JSON</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C133" t="str">
-        <v>Converter para JSON</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Convert to ICC</v>
+        <v>Close</v>
       </c>
       <c r="B134" t="str">
-        <v>Converter para ICC</v>
+        <v>Fechar</v>
       </c>
       <c r="C134" t="str">
-        <v>Converter para ICC</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to XML…</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B135" t="str">
-        <v>A converter para XML…</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C135" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to JSON…</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B136" t="str">
-        <v>A converter para JSON…</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C136" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Converting to ICC…</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B137" t="str">
-        <v>A converter para ICC…</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C137" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Load ICC profile</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B138" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C138" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B139" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C139" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Profile ID</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B140" t="str">
-        <v>ID do perfil</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C140" t="str">
-        <v>ID do perfil</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>No tags found.</v>
+        <v>Error:</v>
       </c>
       <c r="B141" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Erro:</v>
       </c>
       <c r="C141" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Tag Name</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B142" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C142" t="str">
-        <v>Nome da tag</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ID</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B143" t="str">
-        <v>ID</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C143" t="str">
-        <v>ID</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Offset</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B144" t="str">
-        <v>Deslocamento</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C144" t="str">
-        <v>Deslocamento</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Size</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B145" t="str">
-        <v>Tamanho</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C145" t="str">
-        <v>Tamanho</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Pad</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B146" t="str">
-        <v>Preenchimento</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C146" t="str">
-        <v>Preenchimento</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Bytes changed since load</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B147" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C147" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Type</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B148" t="str">
-        <v>Tipo</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C148" t="str">
-        <v>Tipo</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Array of {type}</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B149" t="str">
-        <v>Vetor de {type}</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C149" t="str">
-        <v>Array de {type}</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>(No content)</v>
+        <v>Profile ID</v>
       </c>
       <c r="B150" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C150" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>bytes</v>
+        <v>No tags found.</v>
       </c>
       <c r="B151" t="str">
-        <v>bytes</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C151" t="str">
-        <v>bytes</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Loading full description…</v>
+        <v>Tag Name</v>
       </c>
       <c r="B152" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C152" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Could not load full description:</v>
+        <v>ID</v>
       </c>
       <c r="B153" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>ID</v>
       </c>
       <c r="C153" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Offset</v>
       </c>
       <c r="B154" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C154" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Size</v>
       </c>
       <c r="B155" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Tamanho</v>
       </c>
       <c r="C155" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>No validation output</v>
+        <v>Pad</v>
       </c>
       <c r="B156" t="str">
-        <v>Sem saída de validação</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C156" t="str">
-        <v>Sem saída de validação</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B157" t="str">
-        <v>O perfil é válido</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C157" t="str">
-        <v>O perfil é válido</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Type</v>
       </c>
       <c r="B158" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Tipo</v>
       </c>
       <c r="C158" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B159" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C159" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical validation error</v>
+        <v>(No content)</v>
       </c>
       <c r="B160" t="str">
-        <v>Erro de validação crítico</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C160" t="str">
-        <v>Erro de validação crítico</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Unknown validation status</v>
+        <v>bytes</v>
       </c>
       <c r="B161" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>bytes</v>
       </c>
       <c r="C161" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B162" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C162" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B163" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C163" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Valid</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B164" t="str">
-        <v>Válido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C164" t="str">
-        <v>Válido</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Warning</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B165" t="str">
-        <v>Aviso</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C165" t="str">
-        <v>Aviso</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Error</v>
+        <v>No validation output</v>
       </c>
       <c r="B166" t="str">
-        <v>Erro</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C166" t="str">
-        <v>Erro</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Unknown</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B167" t="str">
-        <v>Desconhecido</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C167" t="str">
-        <v>Desconhecido</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Pass</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B168" t="str">
-        <v>Aprovado</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C168" t="str">
-        <v>Aprovado</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fail</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B169" t="str">
-        <v>Reprovado</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C169" t="str">
-        <v>Reprovado</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>View in context</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B170" t="str">
-        <v>Ver no contexto</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C170" t="str">
-        <v>Ver no contexto</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Validation detail</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B171" t="str">
-        <v>Detalhe de validação</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C171" t="str">
-        <v>Detalhe de validação</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Triggered by</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B172" t="str">
-        <v>Acionado por</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C172" t="str">
-        <v>Acionado por</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Field</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B173" t="str">
-        <v>Campo</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C173" t="str">
-        <v>Campo</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Current value</v>
+        <v>Valid</v>
       </c>
       <c r="B174" t="str">
-        <v>Valor atual</v>
+        <v>Válido</v>
       </c>
       <c r="C174" t="str">
-        <v>Valor atual</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Required: 0</v>
+        <v>Warning</v>
       </c>
       <c r="B175" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Aviso</v>
       </c>
       <c r="C175" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Expected: {value}</v>
+        <v>Error</v>
       </c>
       <c r="B176" t="str">
-        <v>Esperado: {value}</v>
+        <v>Erro</v>
       </c>
       <c r="C176" t="str">
-        <v>Esperado: {value}</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Invalid</v>
+        <v>Unknown</v>
       </c>
       <c r="B177" t="str">
-        <v>Inválido</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C177" t="str">
-        <v>Inválido</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Pass</v>
       </c>
       <c r="B178" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Aprovado</v>
       </c>
       <c r="C178" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Close</v>
+        <v>Fail</v>
       </c>
       <c r="B179" t="str">
-        <v>Fechar</v>
+        <v>Reprovado</v>
       </c>
       <c r="C179" t="str">
-        <v>Fechar</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading XML editor…</v>
+        <v>View in context</v>
       </c>
       <c r="B180" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C180" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Validation detail</v>
       </c>
       <c r="B181" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C181" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Triggered by</v>
       </c>
       <c r="B182" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Acionado por</v>
       </c>
       <c r="C182" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Field</v>
       </c>
       <c r="B183" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Campo</v>
       </c>
       <c r="C183" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Current value</v>
       </c>
       <c r="B184" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Valor atual</v>
       </c>
       <c r="C184" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Required: 0</v>
       </c>
       <c r="B185" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C185" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B186" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C186" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid</v>
       </c>
       <c r="B187" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Inválido</v>
       </c>
       <c r="C187" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>indent</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B188" t="str">
-        <v>indentação</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C188" t="str">
-        <v>indentação</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>sort keys</v>
+        <v>Close</v>
       </c>
       <c r="B189" t="str">
-        <v>ordenar chaves</v>
+        <v>Fechar</v>
       </c>
       <c r="C189" t="str">
-        <v>ordenar chaves</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B190" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B191" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B194" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C194" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B195" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C195" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B198" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C198" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B199" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C199" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B190" t="str">
+      <c r="B200" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C190" t="str">
+      <c r="C200" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C200"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C200"/>
+  <dimension ref="A1:C188"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1055,651 +1055,651 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Channels with many reversals show only the {shown} largest by ΔL*.</v>
+        <v>Analysing…</v>
       </c>
       <c r="B60" t="str">
-        <v>Os canais com muitas inversões mostram apenas as {shown} maiores por ΔL*.</v>
+        <v>A analisar…</v>
       </c>
       <c r="C60" t="str">
-        <v>Os canais com muitas inversões mostram apenas as {shown} maiores por ΔL*.</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Show more ({n})</v>
+        <v>Analysis</v>
       </c>
       <c r="B61" t="str">
-        <v>Mostrar mais ({n})</v>
+        <v>Análise</v>
       </c>
       <c r="C61" t="str">
-        <v>Mostrar mais ({n})</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>All</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B62" t="str">
-        <v>Todos</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C62" t="str">
-        <v>Todos</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B63" t="str">
-        <v>A analisar…</v>
+        <v>Gráfico</v>
       </c>
       <c r="C63" t="str">
-        <v>Analisando…</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B64" t="str">
-        <v>Análise</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C64" t="str">
-        <v>Análise</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B65" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>XML</v>
       </c>
       <c r="C65" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>L* Tone Reversal</v>
+        <v>JSON</v>
       </c>
       <c r="B66" t="str">
-        <v>Inversão de tom L*</v>
+        <v>JSON</v>
       </c>
       <c r="C66" t="str">
-        <v>Inversão de tom L*</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Adding ink should never make a colour lighter. Each device channel is swept while the others are held fixed; any step where L* rises is flagged. Algorithm originally due to Harold Boll.</v>
+        <v>Curves</v>
       </c>
       <c r="B67" t="str">
-        <v>Adicionar tinta nunca deveria tornar uma cor mais clara. Cada canal é percorrido mantendo os outros fixos; qualquer passo em que L* sobe é assinalado. Algoritmo originalmente de Harold Boll.</v>
+        <v>Curvas</v>
       </c>
       <c r="C67" t="str">
-        <v>Adicionar tinta nunca deveria deixar uma cor mais clara. Cada canal é percorrido mantendo os outros fixos; qualquer passo em que L* sobe é sinalizado. Algoritmo originalmente de Harold Boll.</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No device-to-PCS CLUT in this profile, so the L* reversal scan does not apply (for example, a matrix/TRC display profile).</v>
+        <v>Input curves</v>
       </c>
       <c r="B68" t="str">
-        <v>Este perfil não tem uma CLUT dispositivo→PCS, pelo que a análise de inversão L* não se aplica (por exemplo, um perfil de ecrã de matriz/TRC).</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C68" t="str">
-        <v>Este perfil não tem uma CLUT dispositivo→PCS, então a análise de inversão L* não se aplica (por exemplo, um perfil de tela de matriz/TRC).</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>LUT table</v>
+        <v>Output curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Tabela LUT</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C69" t="str">
-        <v>Tabela LUT</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ΔL* threshold (ε)</v>
+        <v>CLUT image</v>
       </c>
       <c r="B70" t="str">
-        <v>Limiar ΔL* (ε)</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C70" t="str">
-        <v>Limiar ΔL* (ε)</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>{n} reversals above ε = {eps}</v>
+        <v>Gamut image</v>
       </c>
       <c r="B71" t="str">
-        <v>{n} inversões acima de ε = {eps}</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C71" t="str">
-        <v>{n} inversões acima de ε = {eps}</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>No L* reversals above ε = {eps}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B72" t="str">
-        <v>Sem inversões L* acima de ε = {eps}</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C72" t="str">
-        <v>Sem inversões L* acima de ε = {eps}</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Channel</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B73" t="str">
-        <v>Canal</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C73" t="str">
-        <v>Canal</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ink (low → high)</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B74" t="str">
-        <v>Tinta (baixo → alto)</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C74" t="str">
-        <v>Tinta (baixo → alto)</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Plot</v>
+        <v>Curve table</v>
       </c>
       <c r="B75" t="str">
-        <v>Gráfico</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C75" t="str">
-        <v>Gráfico</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Raw Output</v>
+        <v>Tables</v>
       </c>
       <c r="B76" t="str">
-        <v>Saída em bruto</v>
+        <v>Tabelas</v>
       </c>
       <c r="C76" t="str">
-        <v>Saída bruta</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>XML</v>
+        <v>Data</v>
       </c>
       <c r="B77" t="str">
-        <v>XML</v>
+        <v>Dados</v>
       </c>
       <c r="C77" t="str">
-        <v>XML</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>JSON</v>
+        <v>Evaluate</v>
       </c>
       <c r="B78" t="str">
-        <v>JSON</v>
+        <v>Avaliar</v>
       </c>
       <c r="C78" t="str">
-        <v>JSON</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Curves</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>Curvas</v>
+        <v>A carregar…</v>
       </c>
       <c r="C79" t="str">
-        <v>Curvas</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input curves</v>
+        <v>Input</v>
       </c>
       <c r="B80" t="str">
-        <v>Curvas de entrada</v>
+        <v>Entrada</v>
       </c>
       <c r="C80" t="str">
-        <v>Curvas de entrada</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output curves</v>
+        <v>Output</v>
       </c>
       <c r="B81" t="str">
-        <v>Curvas de saída</v>
+        <v>Saída</v>
       </c>
       <c r="C81" t="str">
-        <v>Curvas de saída</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>CLUT image</v>
+        <v>Floating point</v>
       </c>
       <c r="B82" t="str">
-        <v>Imagem CLUT</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C82" t="str">
-        <v>Imagem CLUT</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Gamut image</v>
+        <v>Grid point</v>
       </c>
       <c r="B83" t="str">
-        <v>Imagem de gamut</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C83" t="str">
-        <v>Imagem de gamut</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Chromaticity</v>
+        <v>Normalized</v>
       </c>
       <c r="B84" t="str">
-        <v>Cromaticidade</v>
+        <v>Normalizado</v>
       </c>
       <c r="C84" t="str">
-        <v>Cromaticidade</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Scatter plot</v>
+        <v>Human</v>
       </c>
       <c r="B85" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Legível</v>
       </c>
       <c r="C85" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Tone response curve</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B86" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C86" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Curve table</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B87" t="str">
-        <v>Tabela da curva</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C87" t="str">
-        <v>Tabela da curva</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Tables</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B88" t="str">
-        <v>Tabelas</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C88" t="str">
-        <v>Tabelas</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Data</v>
+        <v>Loading…</v>
       </c>
       <c r="B89" t="str">
-        <v>Dados</v>
+        <v>A carregar…</v>
       </c>
       <c r="C89" t="str">
-        <v>Dados</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Evaluate</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B90" t="str">
-        <v>Avaliar</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C90" t="str">
-        <v>Avaliar</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Loading…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B91" t="str">
-        <v>A carregar…</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C91" t="str">
-        <v>Carregando…</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Input</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B92" t="str">
-        <v>Entrada</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C92" t="str">
-        <v>Entrada</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Output</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B93" t="str">
-        <v>Saída</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C93" t="str">
-        <v>Saída</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Floating point</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B94" t="str">
-        <v>Vírgula flutuante</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C94" t="str">
-        <v>Ponto flutuante</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Grid point</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B95" t="str">
-        <v>Ponto da grelha</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C95" t="str">
-        <v>Ponto da grade</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Normalized</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B96" t="str">
-        <v>Normalizado</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C96" t="str">
-        <v>Normalizado</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Human</v>
+        <v>Security</v>
       </c>
       <c r="B97" t="str">
-        <v>Legível</v>
+        <v>Segurança</v>
       </c>
       <c r="C97" t="str">
-        <v>Legível</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Device → PCS</v>
+        <v>Conformance</v>
       </c>
       <c r="B98" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Conformidade</v>
       </c>
       <c r="C98" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>PCS → Device</v>
+        <v>Quality</v>
       </c>
       <c r="B99" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Qualidade</v>
       </c>
       <c r="C99" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No CLUT grid</v>
+        <v>REPORT</v>
       </c>
       <c r="B100" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C100" t="str">
-        <v>Sem grade CLUT</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Loading…</v>
+        <v>FAIL</v>
       </c>
       <c r="B101" t="str">
-        <v>A carregar…</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C101" t="str">
-        <v>Carregando…</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>checks</v>
       </c>
       <c r="B102" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>verificações</v>
       </c>
       <c r="C102" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B103" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C103" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B104" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C104" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B105" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C105" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B106" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C106" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Subscribe</v>
       </c>
       <c r="B107" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>Subscrever</v>
       </c>
       <c r="C107" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B108" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C108" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Security</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B109" t="str">
-        <v>Segurança</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C109" t="str">
-        <v>Segurança</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Conformance</v>
+        <v>Close</v>
       </c>
       <c r="B110" t="str">
-        <v>Conformidade</v>
+        <v>Fechar</v>
       </c>
       <c r="C110" t="str">
-        <v>Conformidade</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Quality</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B111" t="str">
-        <v>Qualidade</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C111" t="str">
-        <v>Qualidade</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>REPORT</v>
+        <v>Email address</v>
       </c>
       <c r="B112" t="str">
-        <v>RELATÓRIO</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C112" t="str">
-        <v>RELATÓRIO</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>FAIL</v>
+        <v>you@example.com</v>
       </c>
       <c r="B113" t="str">
-        <v>REPROVADO</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C113" t="str">
-        <v>REPROVADO</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>checks</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B114" t="str">
-        <v>verificações</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C114" t="str">
-        <v>verificações</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>(optional)</v>
       </c>
       <c r="B115" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>(opcional)</v>
       </c>
       <c r="C115" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B116" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C116" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>ICC Profile Tool</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B117" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C117" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Powered by {lib}</v>
+        <v>Cancel</v>
       </c>
       <c r="B118" t="str">
-        <v>Com {lib}</v>
+        <v>Cancelar</v>
       </c>
       <c r="C118" t="str">
-        <v>Com {lib}</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="119">
@@ -1715,24 +1715,24 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B120" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C120" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Get notified about new releases</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B121" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C121" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="122">
@@ -1748,865 +1748,733 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B123" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C123" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Email address</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B124" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C124" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>you@example.com</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B125" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C125" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B126" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C126" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>(optional)</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>(opcional)</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C127" t="str">
-        <v>(opcional)</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C128" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Error:</v>
       </c>
       <c r="B129" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Erro:</v>
       </c>
       <c r="C129" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Cancel</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B130" t="str">
-        <v>Cancelar</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C130" t="str">
-        <v>Cancelar</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Subscribe</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B131" t="str">
-        <v>Subscrever</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C131" t="str">
-        <v>Inscrever-se</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B132" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C132" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B133" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C133" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Close</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B134" t="str">
-        <v>Fechar</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C134" t="str">
-        <v>Fechar</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Privacy notice</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B135" t="str">
-        <v>Aviso de privacidade</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C135" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B136" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C136" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B137" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C137" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B138" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C138" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>No tags found.</v>
       </c>
       <c r="B139" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C139" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Tag Name</v>
       </c>
       <c r="B140" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C140" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Error:</v>
+        <v>ID</v>
       </c>
       <c r="B141" t="str">
-        <v>Erro:</v>
+        <v>ID</v>
       </c>
       <c r="C141" t="str">
-        <v>Erro:</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Convert to XML</v>
+        <v>Offset</v>
       </c>
       <c r="B142" t="str">
-        <v>Converter para XML</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C142" t="str">
-        <v>Converter para XML</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Convert to JSON</v>
+        <v>Size</v>
       </c>
       <c r="B143" t="str">
-        <v>Converter para JSON</v>
+        <v>Tamanho</v>
       </c>
       <c r="C143" t="str">
-        <v>Converter para JSON</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Convert to ICC</v>
+        <v>Pad</v>
       </c>
       <c r="B144" t="str">
-        <v>Converter para ICC</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C144" t="str">
-        <v>Converter para ICC</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Converting to XML…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B145" t="str">
-        <v>A converter para XML…</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C145" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Converting to JSON…</v>
+        <v>Type</v>
       </c>
       <c r="B146" t="str">
-        <v>A converter para JSON…</v>
+        <v>Tipo</v>
       </c>
       <c r="C146" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Converting to ICC…</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B147" t="str">
-        <v>A converter para ICC…</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C147" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Load ICC profile</v>
+        <v>(No content)</v>
       </c>
       <c r="B148" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C148" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>bytes</v>
       </c>
       <c r="B149" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>bytes</v>
       </c>
       <c r="C149" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Profile ID</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B150" t="str">
-        <v>ID do perfil</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C150" t="str">
-        <v>ID do perfil</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>No tags found.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B151" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C151" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Tag Name</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B152" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C152" t="str">
-        <v>Nome da tag</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ID</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B153" t="str">
-        <v>ID</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C153" t="str">
-        <v>ID</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Offset</v>
+        <v>No validation output</v>
       </c>
       <c r="B154" t="str">
-        <v>Deslocamento</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C154" t="str">
-        <v>Deslocamento</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Size</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B155" t="str">
-        <v>Tamanho</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C155" t="str">
-        <v>Tamanho</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Pad</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B156" t="str">
-        <v>Preenchimento</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C156" t="str">
-        <v>Preenchimento</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B157" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C157" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Type</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B158" t="str">
-        <v>Tipo</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C158" t="str">
-        <v>Tipo</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Array of {type}</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B159" t="str">
-        <v>Vetor de {type}</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C159" t="str">
-        <v>Array de {type}</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>(No content)</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B160" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C160" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>bytes</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B161" t="str">
-        <v>bytes</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C161" t="str">
-        <v>bytes</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Loading full description…</v>
+        <v>Valid</v>
       </c>
       <c r="B162" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Válido</v>
       </c>
       <c r="C162" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Could not load full description:</v>
+        <v>Warning</v>
       </c>
       <c r="B163" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Aviso</v>
       </c>
       <c r="C163" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Error</v>
       </c>
       <c r="B164" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Erro</v>
       </c>
       <c r="C164" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Unknown</v>
       </c>
       <c r="B165" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C165" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>No validation output</v>
+        <v>Pass</v>
       </c>
       <c r="B166" t="str">
-        <v>Sem saída de validação</v>
+        <v>Aprovado</v>
       </c>
       <c r="C166" t="str">
-        <v>Sem saída de validação</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Profile is valid</v>
+        <v>Fail</v>
       </c>
       <c r="B167" t="str">
-        <v>O perfil é válido</v>
+        <v>Reprovado</v>
       </c>
       <c r="C167" t="str">
-        <v>O perfil é válido</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Profile has warning(s)</v>
+        <v>View in context</v>
       </c>
       <c r="B168" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C168" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Validation detail</v>
       </c>
       <c r="B169" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C169" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Critical validation error</v>
+        <v>Triggered by</v>
       </c>
       <c r="B170" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Acionado por</v>
       </c>
       <c r="C170" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Unknown validation status</v>
+        <v>Field</v>
       </c>
       <c r="B171" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Campo</v>
       </c>
       <c r="C171" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Current value</v>
       </c>
       <c r="B172" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Valor atual</v>
       </c>
       <c r="C172" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Required: 0</v>
       </c>
       <c r="B173" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C173" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Valid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B174" t="str">
-        <v>Válido</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C174" t="str">
-        <v>Válido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Warning</v>
+        <v>Invalid</v>
       </c>
       <c r="B175" t="str">
-        <v>Aviso</v>
+        <v>Inválido</v>
       </c>
       <c r="C175" t="str">
-        <v>Aviso</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Error</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B176" t="str">
-        <v>Erro</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C176" t="str">
-        <v>Erro</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Unknown</v>
+        <v>Close</v>
       </c>
       <c r="B177" t="str">
-        <v>Desconhecido</v>
+        <v>Fechar</v>
       </c>
       <c r="C177" t="str">
-        <v>Desconhecido</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Pass</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B178" t="str">
-        <v>Aprovado</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C178" t="str">
-        <v>Aprovado</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Fail</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>Reprovado</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C179" t="str">
-        <v>Reprovado</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>View in context</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B180" t="str">
-        <v>Ver no contexto</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C180" t="str">
-        <v>Ver no contexto</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Validation detail</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>Detalhe de validação</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C181" t="str">
-        <v>Detalhe de validação</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Triggered by</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B182" t="str">
-        <v>Acionado por</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C182" t="str">
-        <v>Acionado por</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Field</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B183" t="str">
-        <v>Campo</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C183" t="str">
-        <v>Campo</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Current value</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B184" t="str">
-        <v>Valor atual</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C184" t="str">
-        <v>Valor atual</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Required: 0</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C185" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Expected: {value}</v>
+        <v>indent</v>
       </c>
       <c r="B186" t="str">
-        <v>Esperado: {value}</v>
+        <v>indentação</v>
       </c>
       <c r="C186" t="str">
-        <v>Esperado: {value}</v>
+        <v>indentação</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Invalid</v>
+        <v>sort keys</v>
       </c>
       <c r="B187" t="str">
-        <v>Inválido</v>
+        <v>ordenar chaves</v>
       </c>
       <c r="C187" t="str">
-        <v>Inválido</v>
+        <v>ordenar chaves</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B188" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
       <c r="C188" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>Close</v>
-      </c>
-      <c r="B189" t="str">
-        <v>Fechar</v>
-      </c>
-      <c r="C189" t="str">
-        <v>Fechar</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Loading XML editor…</v>
-      </c>
-      <c r="B190" t="str">
-        <v>A carregar o editor XML…</v>
-      </c>
-      <c r="C190" t="str">
-        <v>Carregando editor XML…</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Loading JSON editor…</v>
-      </c>
-      <c r="B191" t="str">
-        <v>A carregar o editor JSON…</v>
-      </c>
-      <c r="C191" t="str">
-        <v>Carregando editor JSON…</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B192" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
-      </c>
-      <c r="C192" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
-      </c>
-      <c r="B193" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
-      </c>
-      <c r="C193" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>● unsaved XML edits</v>
-      </c>
-      <c r="B194" t="str">
-        <v>● edições XML por guardar</v>
-      </c>
-      <c r="C194" t="str">
-        <v>● edições XML não salvas</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>● unsaved JSON edits</v>
-      </c>
-      <c r="B195" t="str">
-        <v>● edições JSON por guardar</v>
-      </c>
-      <c r="C195" t="str">
-        <v>● edições JSON não salvas</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B196" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
-      </c>
-      <c r="C196" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
-      </c>
-      <c r="B197" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
-      </c>
-      <c r="C197" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B198" t="str">
-        <v>indentação</v>
-      </c>
-      <c r="C198" t="str">
-        <v>indentação</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B199" t="str">
-        <v>ordenar chaves</v>
-      </c>
-      <c r="C199" t="str">
-        <v>ordenar chaves</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B200" t="str">
-        <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
-      </c>
-      <c r="C200" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C188"/>
+  <dimension ref="A1:C189"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1022,1459 +1022,1470 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B57" t="str">
-        <v>média</v>
+        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
       </c>
       <c r="C57" t="str">
-        <v>média</v>
+        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B58" t="str">
-        <v>P90</v>
+        <v>média</v>
       </c>
       <c r="C58" t="str">
-        <v>P90</v>
+        <v>média</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B59" t="str">
-        <v>máx.</v>
+        <v>P90</v>
       </c>
       <c r="C59" t="str">
-        <v>máx.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B60" t="str">
-        <v>A analisar…</v>
+        <v>máx.</v>
       </c>
       <c r="C60" t="str">
-        <v>Analisando…</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B61" t="str">
-        <v>Análise</v>
+        <v>A analisar…</v>
       </c>
       <c r="C61" t="str">
-        <v>Análise</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B62" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Análise</v>
       </c>
       <c r="C62" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B63" t="str">
-        <v>Gráfico</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C63" t="str">
-        <v>Gráfico</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B64" t="str">
-        <v>Saída em bruto</v>
+        <v>Gráfico</v>
       </c>
       <c r="C64" t="str">
-        <v>Saída bruta</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B65" t="str">
-        <v>XML</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C65" t="str">
-        <v>XML</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="C66" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B67" t="str">
-        <v>Curvas</v>
+        <v>JSON</v>
       </c>
       <c r="C67" t="str">
-        <v>Curvas</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B68" t="str">
-        <v>Curvas de entrada</v>
+        <v>Curvas</v>
       </c>
       <c r="C68" t="str">
-        <v>Curvas de entrada</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B69" t="str">
-        <v>Curvas de saída</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C69" t="str">
-        <v>Curvas de saída</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B70" t="str">
-        <v>Imagem CLUT</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C70" t="str">
-        <v>Imagem CLUT</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B71" t="str">
-        <v>Imagem de gamut</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C71" t="str">
-        <v>Imagem de gamut</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B72" t="str">
-        <v>Cromaticidade</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C72" t="str">
-        <v>Cromaticidade</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B73" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C73" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B74" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C74" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B75" t="str">
-        <v>Tabela da curva</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C75" t="str">
-        <v>Tabela da curva</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B76" t="str">
-        <v>Tabelas</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C76" t="str">
-        <v>Tabelas</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B77" t="str">
-        <v>Dados</v>
+        <v>Tabelas</v>
       </c>
       <c r="C77" t="str">
-        <v>Dados</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B78" t="str">
-        <v>Avaliar</v>
+        <v>Dados</v>
       </c>
       <c r="C78" t="str">
-        <v>Avaliar</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B79" t="str">
-        <v>A carregar…</v>
+        <v>Avaliar</v>
       </c>
       <c r="C79" t="str">
-        <v>Carregando…</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B80" t="str">
-        <v>Entrada</v>
+        <v>A carregar…</v>
       </c>
       <c r="C80" t="str">
-        <v>Entrada</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B81" t="str">
-        <v>Saída</v>
+        <v>Entrada</v>
       </c>
       <c r="C81" t="str">
-        <v>Saída</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B82" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Saída</v>
       </c>
       <c r="C82" t="str">
-        <v>Ponto flutuante</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B83" t="str">
-        <v>Ponto da grelha</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C83" t="str">
-        <v>Ponto da grade</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B84" t="str">
-        <v>Normalizado</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C84" t="str">
-        <v>Normalizado</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B85" t="str">
-        <v>Legível</v>
+        <v>Normalizado</v>
       </c>
       <c r="C85" t="str">
-        <v>Legível</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B86" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Legível</v>
       </c>
       <c r="C86" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B87" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C87" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B88" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C88" t="str">
-        <v>Sem grade CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B89" t="str">
-        <v>A carregar…</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C89" t="str">
-        <v>Carregando…</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B90" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>A carregar…</v>
       </c>
       <c r="C90" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B91" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C91" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B92" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C92" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B93" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C93" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B94" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C94" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B95" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C95" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B96" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C96" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B97" t="str">
-        <v>Segurança</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C97" t="str">
-        <v>Segurança</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B98" t="str">
-        <v>Conformidade</v>
+        <v>Segurança</v>
       </c>
       <c r="C98" t="str">
-        <v>Conformidade</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B99" t="str">
-        <v>Qualidade</v>
+        <v>Conformidade</v>
       </c>
       <c r="C99" t="str">
-        <v>Qualidade</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B100" t="str">
-        <v>RELATÓRIO</v>
+        <v>Qualidade</v>
       </c>
       <c r="C100" t="str">
-        <v>RELATÓRIO</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B101" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C101" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B102" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C102" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B103" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
       <c r="C103" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B104" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C104" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B105" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C105" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B106" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C106" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B107" t="str">
-        <v>Subscrever</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C107" t="str">
-        <v>Inscrever-se</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B108" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Subscrever</v>
       </c>
       <c r="C108" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B109" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C109" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B110" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C110" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B111" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
       <c r="C111" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B112" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C112" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B113" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C113" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B114" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C114" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B115" t="str">
-        <v>(opcional)</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C115" t="str">
-        <v>(opcional)</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B116" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>(opcional)</v>
       </c>
       <c r="C116" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B117" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C117" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B118" t="str">
-        <v>Cancelar</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C118" t="str">
-        <v>Cancelar</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B119" t="str">
-        <v>Subscrever</v>
+        <v>Cancelar</v>
       </c>
       <c r="C119" t="str">
-        <v>Inscrever-se</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B120" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C120" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B121" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C121" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B122" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C122" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B123" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
       <c r="C123" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B124" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C124" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B125" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C125" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B126" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C126" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B127" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C127" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B128" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C128" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B129" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C129" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B130" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
       <c r="C130" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B131" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C131" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B132" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C132" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B133" t="str">
-        <v>A converter para XML…</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C133" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B134" t="str">
-        <v>A converter para JSON…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C134" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B135" t="str">
-        <v>A converter para ICC…</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C135" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B136" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C136" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B137" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C137" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B138" t="str">
-        <v>ID do perfil</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C138" t="str">
-        <v>ID do perfil</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B139" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C139" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B140" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C140" t="str">
-        <v>Nome da tag</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B141" t="str">
-        <v>ID</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C141" t="str">
-        <v>ID</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B142" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
       <c r="C142" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B143" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C143" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B144" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
       <c r="C144" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B145" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C145" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B146" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C146" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B147" t="str">
-        <v>Vetor de {type}</v>
+        <v>Tipo</v>
       </c>
       <c r="C147" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B148" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C148" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B149" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C149" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B150" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>bytes</v>
       </c>
       <c r="C150" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B151" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C151" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B152" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C152" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B153" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C153" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B154" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C154" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B155" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C155" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B156" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C156" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B157" t="str">
-        <v>O perfil não é conforme</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C157" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B158" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C158" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B159" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C159" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B160" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C160" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B161" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C161" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B162" t="str">
-        <v>Válido</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C162" t="str">
-        <v>Válido</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B163" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
       <c r="C163" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B164" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
       <c r="C164" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B165" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
       <c r="C165" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B166" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C166" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B167" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
       <c r="C167" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B168" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
       <c r="C168" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B169" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C169" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B170" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C170" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B171" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
       <c r="C171" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B172" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
       <c r="C172" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B173" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
       <c r="C173" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B174" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C174" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B175" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C175" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B176" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
       <c r="C176" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B177" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C177" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B178" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Fechar</v>
       </c>
       <c r="C178" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B179" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C179" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B180" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C180" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B181" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C181" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B182" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C182" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B183" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C183" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B184" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C184" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B185" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C185" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B186" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C186" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B187" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
       <c r="C187" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B188" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C188" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B188" t="str">
+      <c r="B189" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C188" t="str">
+      <c r="C189" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C189"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C189"/>
+  <dimension ref="A1:C236"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -417,2075 +417,2592 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Settings</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B2" t="str">
-        <v>Definições</v>
+        <v>Ida e volta (PRMG)</v>
       </c>
       <c r="C2" t="str">
-        <v>Configurações</v>
+        <v>Ida e volta (PRMG)</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Display</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B3" t="str">
-        <v>Visualização</v>
+        <v>Ida e volta sobre o cubo do dispositivo do perfil, igual à ferramenta de referência iccRoundTrip. A ida e volta 1 é o erro dispositivo→PCS→dispositivo (ΔE*ab); a ida e volta 2 mede a estabilidade do ciclo PCS. O histograma PRMG indica a interoperabilidade em relação ao Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="C3" t="str">
-        <v>Exibição</v>
+        <v>Ida e volta sobre o cubo do dispositivo do perfil, igual à ferramenta de referência iccRoundTrip. A ida e volta 1 é o erro dispositivo→PCS→dispositivo (ΔE*ab); a ida e volta 2 mede a estabilidade do ciclo PCS. O histograma PRMG indica a interoperabilidade em relação ao Perceptual Reference Medium Gamut.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Background</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B4" t="str">
-        <v>Fundo</v>
+        <v>Usar etiquetas MPE (cor)</v>
       </c>
       <c r="C4" t="str">
-        <v>Fundo</v>
+        <v>Usar tags MPE (cor)</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Language</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B5" t="str">
-        <v>Idioma</v>
+        <v>Este perfil não permite ida e volta: faltam as transformações dispositivo↔PCS necessárias (por ex. um perfil unidirecional ou abstrato).</v>
       </c>
       <c r="C5" t="str">
-        <v>Idioma</v>
+        <v>Este perfil não permite ida e volta: faltam as transformações dispositivo↔PCS necessárias (por ex. um perfil unidirecional ou abstrato).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>System</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B6" t="str">
-        <v>Sistema</v>
+        <v>Ida e volta ignorada: o espaço de cor do dispositivo é demasiado amplo para avaliar (demasiadas amostras).</v>
       </c>
       <c r="C6" t="str">
-        <v>Sistema</v>
+        <v>Ida e volta ignorada: o espaço de cor do dispositivo é amplo demais para avaliar (amostras demais).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Light</v>
+        <v>Metric</v>
       </c>
       <c r="B7" t="str">
-        <v>Claro</v>
+        <v>Métrica</v>
       </c>
       <c r="C7" t="str">
-        <v>Claro</v>
+        <v>Métrica</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dark</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B8" t="str">
-        <v>Escuro</v>
+        <v>Ida e volta 1</v>
       </c>
       <c r="C8" t="str">
-        <v>Escuro</v>
+        <v>Ida e volta 1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>System default</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B9" t="str">
-        <v>Predefinição do sistema</v>
+        <v>Ida e volta 2</v>
       </c>
       <c r="C9" t="str">
-        <v>Padrão do sistema</v>
+        <v>Ida e volta 2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Number format</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B10" t="str">
-        <v>Formato numérico</v>
+        <v>dispositivo → PCS → dispositivo</v>
       </c>
       <c r="C10" t="str">
-        <v>Formato numérico</v>
+        <v>dispositivo → PCS → dispositivo</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Hexadecimal</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B11" t="str">
-        <v>Hexadecimal</v>
+        <v>estabilidade do ciclo PCS</v>
       </c>
       <c r="C11" t="str">
-        <v>Hexadecimal</v>
+        <v>estabilidade do ciclo PCS</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Decimal</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B12" t="str">
-        <v>Decimal</v>
+        <v>ΔE mín</v>
       </c>
       <c r="C12" t="str">
-        <v>Decimal</v>
+        <v>ΔE mín</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Help</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>Ajuda</v>
+        <v>ΔE médio</v>
       </c>
       <c r="C13" t="str">
-        <v>Ajuda</v>
+        <v>ΔE médio</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Contact</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>Contacto</v>
+        <v>ΔE máx</v>
       </c>
       <c r="C14" t="str">
-        <v>Contato</v>
+        <v>ΔE máx</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>User guide</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B15" t="str">
-        <v>Guia do utilizador</v>
+        <v>Pior L, a, b</v>
       </c>
       <c r="C15" t="str">
-        <v>Guia do usuário</v>
+        <v>Pior L, a, b</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Search guide</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B16" t="str">
-        <v>Pesquisar no guia</v>
+        <v>Gama especificada</v>
       </c>
       <c r="C16" t="str">
-        <v>Pesquisar no guia</v>
+        <v>Gama especificada</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Search the user guide</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Pesquisar no guia do utilizador</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="C17" t="str">
-        <v>Pesquisar no guia do usuário</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Previous match</v>
+        <v>Not specified</v>
       </c>
       <c r="B18" t="str">
-        <v>Resultado anterior</v>
+        <v>Não especificada</v>
       </c>
       <c r="C18" t="str">
-        <v>Resultado anterior</v>
+        <v>Não especificada</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Next match</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B19" t="str">
-        <v>Resultado seguinte</v>
+        <v>Não avaliada</v>
       </c>
       <c r="C19" t="str">
-        <v>Próximo resultado</v>
+        <v>Não avaliada</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Close user guide</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B20" t="str">
-        <v>Fechar o guia</v>
+        <v>Interoperabilidade PRMG</v>
       </c>
       <c r="C20" t="str">
-        <v>Fechar o guia</v>
+        <v>Interoperabilidade PRMG</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B21" t="str">
-        <v>A carregar…</v>
+        <v>ΔE de ida e volta</v>
       </c>
       <c r="C21" t="str">
-        <v>Carregando…</v>
+        <v>ΔE de ida e volta</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Count</v>
       </c>
       <c r="B22" t="str">
-        <v>Não foi possível carregar o guia do utilizador.</v>
+        <v>Contagem</v>
       </c>
       <c r="C22" t="str">
-        <v>Não foi possível carregar o guia do usuário.</v>
+        <v>Contagem</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>None</v>
+        <v>Share</v>
       </c>
       <c r="B23" t="str">
-        <v>Nenhum</v>
+        <v>Proporção</v>
       </c>
       <c r="C23" t="str">
-        <v>Nenhum</v>
+        <v>Proporção</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Total</v>
       </c>
       <c r="B24" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Total</v>
       </c>
       <c r="C24" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Total</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B25" t="str">
-        <v>Carregue um perfil ICC para o validar segundo a especificação</v>
+        <v>PRMG não avaliado</v>
       </c>
       <c r="C25" t="str">
-        <v>Envie um perfil ICC para validá-lo conforme a especificação</v>
+        <v>PRMG não avaliado</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>specification using the</v>
+        <v>Settings</v>
       </c>
       <c r="B26" t="str">
-        <v>através da implementação de demonstração</v>
+        <v>Definições</v>
       </c>
       <c r="C26" t="str">
-        <v>usando a implementação de demonstração</v>
+        <v>Configurações</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>demo implementation.</v>
+        <v>Display</v>
       </c>
       <c r="B27" t="str">
-        <v>.</v>
+        <v>Visualização</v>
       </c>
       <c r="C27" t="str">
-        <v>.</v>
+        <v>Exibição</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Based on</v>
+        <v>Background</v>
       </c>
       <c r="B28" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Fundo</v>
       </c>
       <c r="C28" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Fundo</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>demo implementation</v>
+        <v>Language</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Idioma</v>
       </c>
       <c r="C29" t="str">
-        <v/>
+        <v>Idioma</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Validating…</v>
+        <v>System</v>
       </c>
       <c r="B30" t="str">
-        <v>A validar…</v>
+        <v>Sistema</v>
       </c>
       <c r="C30" t="str">
-        <v>Validando…</v>
+        <v>Sistema</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Save ICC profile</v>
+        <v>Light</v>
       </c>
       <c r="B31" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>Claro</v>
       </c>
       <c r="C31" t="str">
-        <v>Salvar perfil ICC</v>
+        <v>Claro</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Dark</v>
       </c>
       <c r="B32" t="str">
-        <v>● Modificado — não guardado</v>
+        <v>Escuro</v>
       </c>
       <c r="C32" t="str">
-        <v>● Modificado — não salvo</v>
+        <v>Escuro</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>System default</v>
       </c>
       <c r="B33" t="str">
-        <v>Largue um perfil ICC aqui</v>
+        <v>Predefinição do sistema</v>
       </c>
       <c r="C33" t="str">
-        <v>Solte um perfil ICC aqui</v>
+        <v>Padrão do sistema</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>or</v>
+        <v>Number format</v>
       </c>
       <c r="B34" t="str">
-        <v>ou</v>
+        <v>Formato numérico</v>
       </c>
       <c r="C34" t="str">
-        <v>ou</v>
+        <v>Formato numérico</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Choose file</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B35" t="str">
-        <v>Escolher ficheiro</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="C35" t="str">
-        <v>Escolher arquivo</v>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>.icc and .icm files</v>
+        <v>Decimal</v>
       </c>
       <c r="B36" t="str">
-        <v>Ficheiros .icc e .icm</v>
+        <v>Decimal</v>
       </c>
       <c r="C36" t="str">
-        <v>Arquivos .icc e .icm</v>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Header</v>
+        <v>Help</v>
       </c>
       <c r="B37" t="str">
-        <v>Cabeçalho</v>
+        <v>Ajuda</v>
       </c>
       <c r="C37" t="str">
-        <v>Cabeçalho</v>
+        <v>Ajuda</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Tags</v>
+        <v>Contact</v>
       </c>
       <c r="B38" t="str">
-        <v>Etiquetas</v>
+        <v>Contacto</v>
       </c>
       <c r="C38" t="str">
-        <v>Tags</v>
+        <v>Contato</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Validation</v>
+        <v>User guide</v>
       </c>
       <c r="B39" t="str">
-        <v>Validação</v>
+        <v>Guia do utilizador</v>
       </c>
       <c r="C39" t="str">
-        <v>Validação</v>
+        <v>Guia do usuário</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Analysis</v>
+        <v>Search guide</v>
       </c>
       <c r="B40" t="str">
-        <v>Análise</v>
+        <v>Pesquisar no guia</v>
       </c>
       <c r="C40" t="str">
-        <v>Análise</v>
+        <v>Pesquisar no guia</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B41" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Pesquisar no guia do utilizador</v>
       </c>
       <c r="C41" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Pesquisar no guia do usuário</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Previous match</v>
       </c>
       <c r="B42" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
+        <v>Resultado anterior</v>
       </c>
       <c r="C42" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
+        <v>Resultado anterior</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Next match</v>
       </c>
       <c r="B43" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Resultado seguinte</v>
       </c>
       <c r="C43" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Próximo resultado</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Close user guide</v>
       </c>
       <c r="B44" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>Fechar o guia</v>
       </c>
       <c r="C44" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>Fechar o guia</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Rendering intent</v>
+        <v>Loading…</v>
       </c>
       <c r="B45" t="str">
-        <v>Intenção de renderização</v>
+        <v>A carregar…</v>
       </c>
       <c r="C45" t="str">
-        <v>Intenção de renderização</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>% ink</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B46" t="str">
-        <v>% tinta</v>
+        <v>Não foi possível carregar o guia do utilizador.</v>
       </c>
       <c r="C46" t="str">
-        <v>% tinta</v>
+        <v>Não foi possível carregar o guia do usuário.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Perceptual</v>
+        <v>None</v>
       </c>
       <c r="B47" t="str">
-        <v>Perceptual</v>
+        <v>Nenhum</v>
       </c>
       <c r="C47" t="str">
-        <v>Perceptual</v>
+        <v>Nenhum</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Relative Colorimetric</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B48" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C48" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Saturation</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B49" t="str">
-        <v>Saturação</v>
+        <v>Carregue um perfil ICC para o validar segundo a especificação</v>
       </c>
       <c r="C49" t="str">
-        <v>Saturação</v>
+        <v>Envie um perfil ICC para validá-lo conforme a especificação</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>specification using the</v>
       </c>
       <c r="B50" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>através da implementação de demonstração</v>
       </c>
       <c r="C50" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>usando a implementação de demonstração</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Profile Statistics</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B51" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>.</v>
       </c>
       <c r="C51" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Based on</v>
       </c>
       <c r="B52" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
       <c r="C52" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>demo implementation</v>
       </c>
       <c r="B53" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
+        <v/>
       </c>
       <c r="C53" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Rendering intent</v>
+        <v>Validating…</v>
       </c>
       <c r="B54" t="str">
-        <v>Intenção de renderização</v>
+        <v>A validar…</v>
       </c>
       <c r="C54" t="str">
-        <v>Intenção de renderização</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B55" t="str">
-        <v>Volume de gamute (ΔE³)</v>
+        <v>Guardar perfil ICC</v>
       </c>
       <c r="C55" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Salvar perfil ICC</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Round-trip ΔE</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B56" t="str">
-        <v>ΔE de percurso</v>
+        <v>● Modificado — não guardado</v>
       </c>
       <c r="C56" t="str">
-        <v>ΔE de percurso</v>
+        <v>● Modificado — não salvo</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Profiles</v>
       </c>
       <c r="B57" t="str">
-        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
+        <v/>
       </c>
       <c r="C57" t="str">
-        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mean</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B58" t="str">
-        <v>média</v>
+        <v/>
       </c>
       <c r="C58" t="str">
-        <v>média</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>P90</v>
+        <v>Collapse</v>
       </c>
       <c r="B59" t="str">
-        <v>P90</v>
+        <v/>
       </c>
       <c r="C59" t="str">
-        <v>P90</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>max</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B60" t="str">
-        <v>máx.</v>
+        <v/>
       </c>
       <c r="C60" t="str">
-        <v>máx.</v>
+        <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Analysing…</v>
+        <v>Remove</v>
       </c>
       <c r="B61" t="str">
-        <v>A analisar…</v>
+        <v/>
       </c>
       <c r="C61" t="str">
-        <v>Analisando…</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Analysis</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B62" t="str">
-        <v>Análise</v>
+        <v/>
       </c>
       <c r="C62" t="str">
-        <v>Análise</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>or use “Load Profiles” — files stay on your device.</v>
       </c>
       <c r="B63" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v/>
       </c>
       <c r="C63" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Plot</v>
+        <v>Profile</v>
       </c>
       <c r="B64" t="str">
-        <v>Gráfico</v>
+        <v/>
       </c>
       <c r="C64" t="str">
-        <v>Gráfico</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Raw Output</v>
+        <v>Compare</v>
       </c>
       <c r="B65" t="str">
-        <v>Saída em bruto</v>
+        <v/>
       </c>
       <c r="C65" t="str">
-        <v>Saída bruta</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>XML</v>
+        <v>Link</v>
       </c>
       <c r="B66" t="str">
-        <v>XML</v>
+        <v/>
       </c>
       <c r="C66" t="str">
-        <v>XML</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>JSON</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B67" t="str">
-        <v>JSON</v>
+        <v/>
       </c>
       <c r="C67" t="str">
-        <v>JSON</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Curves</v>
+        <v>Remove</v>
       </c>
       <c r="B68" t="str">
-        <v>Curvas</v>
+        <v/>
       </c>
       <c r="C68" t="str">
-        <v>Curvas</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Input curves</v>
+        <v>No profile selected</v>
       </c>
       <c r="B69" t="str">
-        <v>Curvas de entrada</v>
+        <v/>
       </c>
       <c r="C69" t="str">
-        <v>Curvas de entrada</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Output curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B70" t="str">
-        <v>Curvas de saída</v>
+        <v/>
       </c>
       <c r="C70" t="str">
-        <v>Curvas de saída</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>CLUT image</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B71" t="str">
-        <v>Imagem CLUT</v>
+        <v/>
       </c>
       <c r="C71" t="str">
-        <v>Imagem CLUT</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Gamut image</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B72" t="str">
-        <v>Imagem de gamut</v>
+        <v/>
       </c>
       <c r="C72" t="str">
-        <v>Imagem de gamut</v>
+        <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B73" t="str">
-        <v>Cromaticidade</v>
+        <v/>
       </c>
       <c r="C73" t="str">
-        <v>Cromaticidade</v>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Scatter plot</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B74" t="str">
-        <v>Gráfico de dispersão</v>
+        <v/>
       </c>
       <c r="C74" t="str">
-        <v>Gráfico de dispersão</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tone response curve</v>
+        <v>Linking</v>
       </c>
       <c r="B75" t="str">
-        <v>Curva de resposta tonal</v>
+        <v/>
       </c>
       <c r="C75" t="str">
-        <v>Curva de resposta tonal</v>
+        <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Curve table</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B76" t="str">
-        <v>Tabela da curva</v>
+        <v/>
       </c>
       <c r="C76" t="str">
-        <v>Tabela da curva</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Tables</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B77" t="str">
-        <v>Tabelas</v>
+        <v/>
       </c>
       <c r="C77" t="str">
-        <v>Tabelas</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Data</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B78" t="str">
-        <v>Dados</v>
+        <v/>
       </c>
       <c r="C78" t="str">
-        <v>Dados</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Evaluate</v>
+        <v>OK</v>
       </c>
       <c r="B79" t="str">
-        <v>Avaliar</v>
+        <v/>
       </c>
       <c r="C79" t="str">
-        <v>Avaliar</v>
+        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Loading…</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B80" t="str">
-        <v>A carregar…</v>
+        <v>Largue um perfil ICC aqui</v>
       </c>
       <c r="C80" t="str">
-        <v>Carregando…</v>
+        <v>Solte um perfil ICC aqui</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Input</v>
+        <v>or</v>
       </c>
       <c r="B81" t="str">
-        <v>Entrada</v>
+        <v>ou</v>
       </c>
       <c r="C81" t="str">
-        <v>Entrada</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Output</v>
+        <v>Choose file</v>
       </c>
       <c r="B82" t="str">
-        <v>Saída</v>
+        <v>Escolher ficheiro</v>
       </c>
       <c r="C82" t="str">
-        <v>Saída</v>
+        <v>Escolher arquivo</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Floating point</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B83" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Ficheiros .icc e .icm</v>
       </c>
       <c r="C83" t="str">
-        <v>Ponto flutuante</v>
+        <v>Arquivos .icc e .icm</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Grid point</v>
+        <v>Header</v>
       </c>
       <c r="B84" t="str">
-        <v>Ponto da grelha</v>
+        <v>Cabeçalho</v>
       </c>
       <c r="C84" t="str">
-        <v>Ponto da grade</v>
+        <v>Cabeçalho</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Normalized</v>
+        <v>Tags</v>
       </c>
       <c r="B85" t="str">
-        <v>Normalizado</v>
+        <v>Etiquetas</v>
       </c>
       <c r="C85" t="str">
-        <v>Normalizado</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Human</v>
+        <v>Validation</v>
       </c>
       <c r="B86" t="str">
-        <v>Legível</v>
+        <v>Validação</v>
       </c>
       <c r="C86" t="str">
-        <v>Legível</v>
+        <v>Validação</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Device → PCS</v>
+        <v>Analysis</v>
       </c>
       <c r="B87" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Análise</v>
       </c>
       <c r="C87" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B88" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
       <c r="C88" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>No CLUT grid</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B89" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
       </c>
       <c r="C89" t="str">
-        <v>Sem grade CLUT</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Loading…</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B90" t="str">
-        <v>A carregar…</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C90" t="str">
-        <v>Carregando…</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B91" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
       <c r="C91" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B92" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C92" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>% ink</v>
       </c>
       <c r="B93" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>% tinta</v>
       </c>
       <c r="C93" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Perceptual</v>
       </c>
       <c r="B94" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>Perceptual</v>
       </c>
       <c r="C94" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B95" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Colorimétrico relativo</v>
       </c>
       <c r="C95" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Saturation</v>
       </c>
       <c r="B96" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>Saturação</v>
       </c>
       <c r="C96" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Saturação</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B97" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Colorimétrico absoluto</v>
       </c>
       <c r="C97" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Security</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B98" t="str">
-        <v>Segurança</v>
+        <v>Estatísticas do perfil</v>
       </c>
       <c r="C98" t="str">
-        <v>Segurança</v>
+        <v>Estatísticas do perfil</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Conformance</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B99" t="str">
-        <v>Conformidade</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
       <c r="C99" t="str">
-        <v>Conformidade</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quality</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B100" t="str">
-        <v>Qualidade</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
       </c>
       <c r="C100" t="str">
-        <v>Qualidade</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>REPORT</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B101" t="str">
-        <v>RELATÓRIO</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C101" t="str">
-        <v>RELATÓRIO</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>FAIL</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B102" t="str">
-        <v>REPROVADO</v>
+        <v>Volume de gamute (ΔE³)</v>
       </c>
       <c r="C102" t="str">
-        <v>REPROVADO</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>checks</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B103" t="str">
-        <v>verificações</v>
+        <v>ΔE de percurso</v>
       </c>
       <c r="C103" t="str">
-        <v>verificações</v>
+        <v>ΔE de percurso</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B104" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
       </c>
       <c r="C104" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>mean</v>
       </c>
       <c r="B105" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>média</v>
       </c>
       <c r="C105" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>média</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ICC Profile Tool</v>
+        <v>P90</v>
       </c>
       <c r="B106" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>P90</v>
       </c>
       <c r="C106" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Powered by {lib}</v>
+        <v>max</v>
       </c>
       <c r="B107" t="str">
-        <v>Com {lib}</v>
+        <v>máx.</v>
       </c>
       <c r="C107" t="str">
-        <v>Com {lib}</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Subscribe</v>
+        <v>Analysing…</v>
       </c>
       <c r="B108" t="str">
-        <v>Subscrever</v>
+        <v>A analisar…</v>
       </c>
       <c r="C108" t="str">
-        <v>Inscrever-se</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Analysis</v>
       </c>
       <c r="B109" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Análise</v>
       </c>
       <c r="C109" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Get notified about new releases</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B110" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C110" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Close</v>
+        <v>Plot</v>
       </c>
       <c r="B111" t="str">
-        <v>Fechar</v>
+        <v>Gráfico</v>
       </c>
       <c r="C111" t="str">
-        <v>Fechar</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Raw Output</v>
       </c>
       <c r="B112" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C112" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Email address</v>
+        <v>XML</v>
       </c>
       <c r="B113" t="str">
-        <v>Endereço de e-mail</v>
+        <v>XML</v>
       </c>
       <c r="C113" t="str">
-        <v>Endereço de e-mail</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>you@example.com</v>
+        <v>JSON</v>
       </c>
       <c r="B114" t="str">
-        <v>voce@exemplo.com</v>
+        <v>JSON</v>
       </c>
       <c r="C114" t="str">
-        <v>voce@exemplo.com</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Curves</v>
       </c>
       <c r="B115" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Curvas</v>
       </c>
       <c r="C115" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>(optional)</v>
+        <v>Input curves</v>
       </c>
       <c r="B116" t="str">
-        <v>(opcional)</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C116" t="str">
-        <v>(opcional)</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Output curves</v>
       </c>
       <c r="B117" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C117" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B118" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C118" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Cancel</v>
+        <v>Gamut image</v>
       </c>
       <c r="B119" t="str">
-        <v>Cancelar</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C119" t="str">
-        <v>Cancelar</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Subscribe</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B120" t="str">
-        <v>Subscrever</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C120" t="str">
-        <v>Inscrever-se</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B121" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C121" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B122" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C122" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Close</v>
+        <v>Curve table</v>
       </c>
       <c r="B123" t="str">
-        <v>Fechar</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C123" t="str">
-        <v>Fechar</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Privacy notice</v>
+        <v>Tables</v>
       </c>
       <c r="B124" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Tabelas</v>
       </c>
       <c r="C124" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Data</v>
       </c>
       <c r="B125" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Dados</v>
       </c>
       <c r="C125" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B126" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Avaliar</v>
       </c>
       <c r="C126" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Loading…</v>
       </c>
       <c r="B127" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>A carregar…</v>
       </c>
       <c r="C127" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Input</v>
       </c>
       <c r="B128" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Entrada</v>
       </c>
       <c r="C128" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Output</v>
       </c>
       <c r="B129" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Saída</v>
       </c>
       <c r="C129" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Error:</v>
+        <v>Floating point</v>
       </c>
       <c r="B130" t="str">
-        <v>Erro:</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C130" t="str">
-        <v>Erro:</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Convert to XML</v>
+        <v>Grid point</v>
       </c>
       <c r="B131" t="str">
-        <v>Converter para XML</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C131" t="str">
-        <v>Converter para XML</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Convert to JSON</v>
+        <v>Normalized</v>
       </c>
       <c r="B132" t="str">
-        <v>Converter para JSON</v>
+        <v>Normalizado</v>
       </c>
       <c r="C132" t="str">
-        <v>Converter para JSON</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Convert to ICC</v>
+        <v>Human</v>
       </c>
       <c r="B133" t="str">
-        <v>Converter para ICC</v>
+        <v>Legível</v>
       </c>
       <c r="C133" t="str">
-        <v>Converter para ICC</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Converting to XML…</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B134" t="str">
-        <v>A converter para XML…</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C134" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Converting to JSON…</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B135" t="str">
-        <v>A converter para JSON…</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C135" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Converting to ICC…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B136" t="str">
-        <v>A converter para ICC…</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C136" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Load ICC profile</v>
+        <v>Loading…</v>
       </c>
       <c r="B137" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A carregar…</v>
       </c>
       <c r="C137" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B138" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C138" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Profile ID</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B139" t="str">
-        <v>ID do perfil</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C139" t="str">
-        <v>ID do perfil</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>No tags found.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B140" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C140" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Tag Name</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B141" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C141" t="str">
-        <v>Nome da tag</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ID</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B142" t="str">
-        <v>ID</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C142" t="str">
-        <v>ID</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Offset</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B143" t="str">
-        <v>Deslocamento</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C143" t="str">
-        <v>Deslocamento</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Size</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B144" t="str">
-        <v>Tamanho</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C144" t="str">
-        <v>Tamanho</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Pad</v>
+        <v>Security</v>
       </c>
       <c r="B145" t="str">
-        <v>Preenchimento</v>
+        <v>Segurança</v>
       </c>
       <c r="C145" t="str">
-        <v>Preenchimento</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Bytes changed since load</v>
+        <v>Conformance</v>
       </c>
       <c r="B146" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Conformidade</v>
       </c>
       <c r="C146" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Type</v>
+        <v>Quality</v>
       </c>
       <c r="B147" t="str">
-        <v>Tipo</v>
+        <v>Qualidade</v>
       </c>
       <c r="C147" t="str">
-        <v>Tipo</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Array of {type}</v>
+        <v>REPORT</v>
       </c>
       <c r="B148" t="str">
-        <v>Vetor de {type}</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C148" t="str">
-        <v>Array de {type}</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>(No content)</v>
+        <v>FAIL</v>
       </c>
       <c r="B149" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C149" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>bytes</v>
+        <v>checks</v>
       </c>
       <c r="B150" t="str">
-        <v>bytes</v>
+        <v>verificações</v>
       </c>
       <c r="C150" t="str">
-        <v>bytes</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Loading full description…</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B151" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C151" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Could not load full description:</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B152" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C152" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B153" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C153" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B154" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C154" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>No validation output</v>
+        <v>Subscribe</v>
       </c>
       <c r="B155" t="str">
-        <v>Sem saída de validação</v>
+        <v>Subscrever</v>
       </c>
       <c r="C155" t="str">
-        <v>Sem saída de validação</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Profile is valid</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B156" t="str">
-        <v>O perfil é válido</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C156" t="str">
-        <v>O perfil é válido</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B157" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C157" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Close</v>
       </c>
       <c r="B158" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Fechar</v>
       </c>
       <c r="C158" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Critical validation error</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B159" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C159" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Unknown validation status</v>
+        <v>Email address</v>
       </c>
       <c r="B160" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C160" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>you@example.com</v>
       </c>
       <c r="B161" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C161" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>No warnings or errors found.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B162" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C162" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Valid</v>
+        <v>(optional)</v>
       </c>
       <c r="B163" t="str">
-        <v>Válido</v>
+        <v>(opcional)</v>
       </c>
       <c r="C163" t="str">
-        <v>Válido</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Warning</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B164" t="str">
-        <v>Aviso</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C164" t="str">
-        <v>Aviso</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Error</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B165" t="str">
-        <v>Erro</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C165" t="str">
-        <v>Erro</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Unknown</v>
+        <v>Cancel</v>
       </c>
       <c r="B166" t="str">
-        <v>Desconhecido</v>
+        <v>Cancelar</v>
       </c>
       <c r="C166" t="str">
-        <v>Desconhecido</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Pass</v>
+        <v>Subscribe</v>
       </c>
       <c r="B167" t="str">
-        <v>Aprovado</v>
+        <v>Subscrever</v>
       </c>
       <c r="C167" t="str">
-        <v>Aprovado</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fail</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B168" t="str">
-        <v>Reprovado</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C168" t="str">
-        <v>Reprovado</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>View in context</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B169" t="str">
-        <v>Ver no contexto</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C169" t="str">
-        <v>Ver no contexto</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Validation detail</v>
+        <v>Close</v>
       </c>
       <c r="B170" t="str">
-        <v>Detalhe de validação</v>
+        <v>Fechar</v>
       </c>
       <c r="C170" t="str">
-        <v>Detalhe de validação</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Triggered by</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B171" t="str">
-        <v>Acionado por</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C171" t="str">
-        <v>Acionado por</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Field</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B172" t="str">
-        <v>Campo</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C172" t="str">
-        <v>Campo</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Current value</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B173" t="str">
-        <v>Valor atual</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C173" t="str">
-        <v>Valor atual</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Required: 0</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B174" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C174" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Expected: {value}</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B175" t="str">
-        <v>Esperado: {value}</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C175" t="str">
-        <v>Esperado: {value}</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Invalid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B176" t="str">
-        <v>Inválido</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C176" t="str">
-        <v>Inválido</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Error:</v>
       </c>
       <c r="B177" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Erro:</v>
       </c>
       <c r="C177" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Close</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B178" t="str">
-        <v>Fechar</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C178" t="str">
-        <v>Fechar</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Loading XML editor…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B179" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C179" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B180" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C180" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B181" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C181" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B182" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C182" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B183" t="str">
-        <v>● edições XML por guardar</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C183" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B184" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C184" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B185" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C185" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B186" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C186" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>indent</v>
+        <v>No tags found.</v>
       </c>
       <c r="B187" t="str">
-        <v>indentação</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C187" t="str">
-        <v>indentação</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>sort keys</v>
+        <v>Tag Name</v>
       </c>
       <c r="B188" t="str">
-        <v>ordenar chaves</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C188" t="str">
-        <v>ordenar chaves</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B189" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C189" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Deslocamento</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Deslocamento</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Tamanho</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Tamanho</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Preenchimento</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Preenchimento</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Bytes alterados desde o carregamento</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Bytes alterados desde o carregamento</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Vetor de {type}</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Array de {type}</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B196" t="str">
+        <v>(Sem conteúdo)</v>
+      </c>
+      <c r="C196" t="str">
+        <v>(Sem conteúdo)</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B197" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="C197" t="str">
+        <v>bytes</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B198" t="str">
+        <v>A carregar descrição completa…</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Carregando descrição completa…</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Não foi possível carregar a descrição completa:</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Não foi possível carregar a descrição completa:</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B203" t="str">
+        <v>O perfil é válido</v>
+      </c>
+      <c r="C203" t="str">
+        <v>O perfil é válido</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B204" t="str">
+        <v>O perfil tem avisos</v>
+      </c>
+      <c r="C204" t="str">
+        <v>O perfil tem avisos</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B205" t="str">
+        <v>O perfil não é conforme</v>
+      </c>
+      <c r="C205" t="str">
+        <v>O perfil não está em conformidade</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Erro de validação crítico</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Erro de validação crítico</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Estado de validação desconhecido</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Status de validação desconhecido</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Crítico — apresentado apenas para inspeção</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Crítico — exibido apenas para inspeção</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Sem avisos nem erros encontrados.</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Nenhum aviso ou erro encontrado.</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Válido</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Aviso</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Aviso</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Erro</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Erro</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Desconhecido</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Desconhecido</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Aprovado</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Reprovado</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Reprovado</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Ver no contexto</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Ver no contexto</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Acionado por</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Acionado por</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B220" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C220" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B221" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C221" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B222" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C222" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B223" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C223" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B224" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C224" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B225" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C225" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B226" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C226" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B227" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C227" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B228" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C228" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B229" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C229" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B230" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C230" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B231" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C231" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B232" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C232" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B233" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C233" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B234" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C234" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B235" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C235" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B189" t="str">
+      <c r="B236" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C189" t="str">
+      <c r="C236" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C189"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C236"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C236"/>
+  <dimension ref="A1:C319"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -681,2328 +681,3250 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Settings</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B26" t="str">
-        <v>Definições</v>
+        <v>Métricas de todo o perfil para uma intenção de renderização: o volume do gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e uma métrica de precisão de ida e volta. Escolha a intenção de renderização e o tipo de ida e volta — a tabela e o histograma são atualizados em conformidade.</v>
       </c>
       <c r="C26" t="str">
-        <v>Configurações</v>
+        <v>Métricas de todo o perfil para uma intenção de renderização: o volume do gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e uma métrica de precisão de ida e volta. Escolha a intenção de renderização e o tipo de ida e volta — a tabela e o histograma são atualizados de acordo.</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Display</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B27" t="str">
-        <v>Visualização</v>
+        <v>Tipo de ida e volta</v>
       </c>
       <c r="C27" t="str">
-        <v>Exibição</v>
+        <v>Tipo de ida e volta</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Background</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>Fundo</v>
+        <v>Não afeta este tipo de ida e volta</v>
       </c>
       <c r="C28" t="str">
-        <v>Fundo</v>
+        <v>Não afeta este tipo de ida e volta</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Language</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B29" t="str">
-        <v>Idioma</v>
+        <v>Este tipo de ida e volta não está disponível para este perfil.</v>
       </c>
       <c r="C29" t="str">
-        <v>Idioma</v>
+        <v>Este tipo de ida e volta não está disponível para este perfil.</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>System</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B30" t="str">
-        <v>Sistema</v>
+        <v>Distribuição do ΔE de ida e volta</v>
       </c>
       <c r="C30" t="str">
-        <v>Sistema</v>
+        <v>Distribuição do ΔE de ida e volta</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Light</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B31" t="str">
-        <v>Claro</v>
+        <v>Nenhuma amostra de ida e volta caiu dentro da região avaliada.</v>
       </c>
       <c r="C31" t="str">
-        <v>Claro</v>
+        <v>Nenhuma amostra de ida e volta caiu dentro da região avaliada.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Dark</v>
+        <v>Std Dev</v>
       </c>
       <c r="B32" t="str">
-        <v>Escuro</v>
+        <v>Desvio padrão</v>
       </c>
       <c r="C32" t="str">
-        <v>Escuro</v>
+        <v>Desvio padrão</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>System default</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B33" t="str">
-        <v>Predefinição do sistema</v>
+        <v>Frequência relativa</v>
       </c>
       <c r="C33" t="str">
-        <v>Padrão do sistema</v>
+        <v>Frequência relativa</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Number format</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>Formato numérico</v>
+        <v>Frequência cumulativa</v>
       </c>
       <c r="C34" t="str">
-        <v>Formato numérico</v>
+        <v>Frequência cumulativa</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Hexadecimal</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B35" t="str">
-        <v>Hexadecimal</v>
+        <v>Escala horizontal</v>
       </c>
       <c r="C35" t="str">
-        <v>Hexadecimal</v>
+        <v>Escala horizontal</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Decimal</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B36" t="str">
-        <v>Decimal</v>
+        <v>ΔE inteiro</v>
       </c>
       <c r="C36" t="str">
-        <v>Decimal</v>
+        <v>ΔE inteiro</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Help</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B37" t="str">
-        <v>Ajuda</v>
+        <v>Escala automática</v>
       </c>
       <c r="C37" t="str">
-        <v>Ajuda</v>
+        <v>Escala automática</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Contact</v>
+        <v>Bins</v>
       </c>
       <c r="B38" t="str">
-        <v>Contacto</v>
+        <v>Classes</v>
       </c>
       <c r="C38" t="str">
-        <v>Contato</v>
+        <v>Classes</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>User guide</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B39" t="str">
-        <v>Guia do utilizador</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C39" t="str">
-        <v>Guia do usuário</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Search guide</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B40" t="str">
-        <v>Pesquisar no guia</v>
+        <v>A tabela de consulta de cor (CLUT) de uma transformação dispositivo↔PCS, disposta em mosaico numa imagem. Escolha que tabela de intenção de renderização ver.</v>
       </c>
       <c r="C40" t="str">
-        <v>Pesquisar no guia</v>
+        <v>A tabela de consulta de cor (CLUT) de uma transformação dispositivo↔PCS, disposta em mosaico em uma imagem. Escolha qual tabela de intenção de renderização visualizar.</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Search the user guide</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B41" t="str">
-        <v>Pesquisar no guia do utilizador</v>
+        <v>Este perfil não tem tabelas dispositivo↔PCS baseadas em CLUT para visualizar.</v>
       </c>
       <c r="C41" t="str">
-        <v>Pesquisar no guia do usuário</v>
+        <v>Este perfil não tem tabelas dispositivo↔PCS baseadas em CLUT para visualizar.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Previous match</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B42" t="str">
-        <v>Resultado anterior</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C42" t="str">
-        <v>Resultado anterior</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Next match</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B43" t="str">
-        <v>Resultado seguinte</v>
+        <v>O mapa dentro/fora do gamut da etiqueta gamut: neutro onde uma cor PCS é reproduzível, vermelho onde fica fora do gamut do dispositivo.</v>
       </c>
       <c r="C43" t="str">
-        <v>Próximo resultado</v>
+        <v>O mapa dentro/fora do gamut da etiqueta gamut: neutro onde uma cor PCS é reproduzível, vermelho onde fica fora do gamut do dispositivo.</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Close user guide</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B44" t="str">
-        <v>Fechar o guia</v>
+        <v>Este perfil não tem etiqueta gamut para visualizar.</v>
       </c>
       <c r="C44" t="str">
-        <v>Fechar o guia</v>
+        <v>Este perfil não tem etiqueta gamut para visualizar.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Loading…</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B45" t="str">
-        <v>A carregar…</v>
+        <v>Escala vertical</v>
       </c>
       <c r="C45" t="str">
-        <v>Carregando…</v>
+        <v>Escala vertical</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Could not load the user guide.</v>
+        <v>X–Y</v>
       </c>
       <c r="B46" t="str">
-        <v>Não foi possível carregar o guia do utilizador.</v>
+        <v>X–Y</v>
       </c>
       <c r="C46" t="str">
-        <v>Não foi possível carregar o guia do usuário.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>None</v>
+        <v>Tone increase</v>
       </c>
       <c r="B47" t="str">
-        <v>Nenhum</v>
+        <v>Aumento tonal</v>
       </c>
       <c r="C47" t="str">
-        <v>Nenhum</v>
+        <v>Aumento tonal</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B48" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Aumento tonal (saída − entrada)</v>
       </c>
       <c r="C48" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Aumento tonal (saída − entrada)</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Show full dump</v>
       </c>
       <c r="B49" t="str">
-        <v>Carregue um perfil ICC para o validar segundo a especificação</v>
+        <v>Mostrar despejo completo</v>
       </c>
       <c r="C49" t="str">
-        <v>Envie um perfil ICC para validá-lo conforme a especificação</v>
+        <v>Mostrar despejo completo</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>specification using the</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B50" t="str">
-        <v>através da implementação de demonstração</v>
+        <v>Saída truncada por desempenho.</v>
       </c>
       <c r="C50" t="str">
-        <v>usando a implementação de demonstração</v>
+        <v>Saída truncada por desempenho.</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>demo implementation.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B51" t="str">
-        <v>.</v>
+        <v>Visão geral dentro do gamut (RT0)</v>
       </c>
       <c r="C51" t="str">
-        <v>.</v>
+        <v>Visão geral dentro do gamut (RT0)</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Based on</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B52" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Inversão + gamut (RT1)</v>
       </c>
       <c r="C52" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Inversão + gamut (RT1)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>demo implementation</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Reprodutibilidade (RT2)</v>
       </c>
       <c r="C53" t="str">
-        <v/>
+        <v>Reprodutibilidade (RT2)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Validating…</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B54" t="str">
-        <v>A validar…</v>
+        <v>Interoperabilidade PRMG</v>
       </c>
       <c r="C54" t="str">
-        <v>Validando…</v>
+        <v>Interoperabilidade PRMG</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Save ICC profile</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B55" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>Visão geral do iccviz: uma grelha de valores do dispositivo é levada ao PCS, de volta ao dispositivo e novamente ao PCS; o ΔE*ab é medido entre as duas passagens PCS. Uma verificação rápida de estabilidade dentro do gamut.</v>
       </c>
       <c r="C55" t="str">
-        <v>Salvar perfil ICC</v>
+        <v>Visão geral do iccviz: uma grade de valores do dispositivo é levada ao PCS, de volta ao dispositivo e novamente ao PCS; o ΔE*ab é medido entre as duas passagens PCS. Uma verificação rápida de estabilidade dentro do gamut.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B56" t="str">
-        <v>● Modificado — não guardado</v>
+        <v>iccRoundTrip Ida e volta 1: ΔE*ab entre o PCS de cada cor do dispositivo e o seu PCS após uma ida e volta Lab → dispositivo → Lab. Reflete a precisão de inversão e o mapeamento de gamut.</v>
       </c>
       <c r="C56" t="str">
-        <v>● Modificado — não salvo</v>
+        <v>iccRoundTrip Ida e volta 1: ΔE*ab entre o PCS de cada cor do dispositivo e o seu PCS após uma ida e volta Lab → dispositivo → Lab. Reflete a precisão de inversão e o mapeamento de gamut.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Profiles</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>iccRoundTrip Ida e volta 2: ΔE*ab entre a primeira e a segunda ida e volta — o quão estável é uma ida e volta de PCS repetida (reprodutibilidade, independente do recorte de gamut da primeira passagem).</v>
       </c>
       <c r="C57" t="str">
-        <v/>
+        <v>iccRoundTrip Ida e volta 2: ΔE*ab entre a primeira e a segunda ida e volta — o quão estável é uma ida e volta de PCS repetida (reprodutibilidade, independente do recorte de gamut da primeira passagem).</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Show profile pool</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B58" t="str">
-        <v/>
+        <v>iccRoundTrip PRMG: as cores PCS dentro do Perceptual Reference Medium Gamut fazem uma única ida e volta (Lab → dispositivo → Lab); a distribuição do ΔE*ab indica a interoperabilidade entre perfis.</v>
       </c>
       <c r="C58" t="str">
-        <v/>
+        <v>iccRoundTrip PRMG: as cores PCS dentro do Perceptual Reference Medium Gamut fazem uma única ida e volta (Lab → dispositivo → Lab); a distribuição do ΔE*ab indica a interoperabilidade entre perfis.</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Collapse</v>
+        <v>Settings</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Definições</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>Configurações</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Load Profiles</v>
+        <v>Display</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Visualização</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>Exibição</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Remove</v>
+        <v>Background</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Fundo</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>Fundo</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Language</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Idioma</v>
       </c>
       <c r="C62" t="str">
-        <v/>
+        <v>Idioma</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>or use “Load Profiles” — files stay on your device.</v>
+        <v>System</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Sistema</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>Sistema</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Profile</v>
+        <v>Light</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Claro</v>
       </c>
       <c r="C64" t="str">
-        <v/>
+        <v>Claro</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Compare</v>
+        <v>Dark</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>Escuro</v>
       </c>
       <c r="C65" t="str">
-        <v/>
+        <v>Escuro</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Link</v>
+        <v>System default</v>
       </c>
       <c r="B66" t="str">
-        <v/>
+        <v>Predefinição do sistema</v>
       </c>
       <c r="C66" t="str">
-        <v/>
+        <v>Padrão do sistema</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Number format</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Formato numérico</v>
       </c>
       <c r="C67" t="str">
-        <v/>
+        <v>Formato numérico</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Remove</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Hexadecimal</v>
       </c>
       <c r="C68" t="str">
-        <v/>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>No profile selected</v>
+        <v>Decimal</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Decimal</v>
       </c>
       <c r="C69" t="str">
-        <v/>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Help</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>Ajuda</v>
       </c>
       <c r="C70" t="str">
-        <v/>
+        <v>Ajuda</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Contact</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>Contacto</v>
       </c>
       <c r="C71" t="str">
-        <v/>
+        <v>Contato</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>User guide</v>
       </c>
       <c r="B72" t="str">
-        <v/>
+        <v>Guia do utilizador</v>
       </c>
       <c r="C72" t="str">
-        <v/>
+        <v>Guia do usuário</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Gamut comparison</v>
+        <v>Search guide</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Pesquisar no guia</v>
       </c>
       <c r="C73" t="str">
-        <v/>
+        <v>Pesquisar no guia</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>Pesquisar no guia do utilizador</v>
       </c>
       <c r="C74" t="str">
-        <v/>
+        <v>Pesquisar no guia do usuário</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Linking</v>
+        <v>Previous match</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>Resultado anterior</v>
       </c>
       <c r="C75" t="str">
-        <v/>
+        <v>Resultado anterior</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Next match</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>Resultado seguinte</v>
       </c>
       <c r="C76" t="str">
-        <v/>
+        <v>Próximo resultado</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Close user guide</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>Fechar o guia</v>
       </c>
       <c r="C77" t="str">
-        <v/>
+        <v>Fechar o guia</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Loading…</v>
       </c>
       <c r="B78" t="str">
-        <v/>
+        <v>A carregar…</v>
       </c>
       <c r="C78" t="str">
-        <v/>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>OK</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>Não foi possível carregar o guia do utilizador.</v>
       </c>
       <c r="C79" t="str">
-        <v/>
+        <v>Não foi possível carregar o guia do usuário.</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>None</v>
       </c>
       <c r="B80" t="str">
-        <v>Largue um perfil ICC aqui</v>
+        <v>Nenhum</v>
       </c>
       <c r="C80" t="str">
-        <v>Solte um perfil ICC aqui</v>
+        <v>Nenhum</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>or</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B81" t="str">
-        <v>ou</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C81" t="str">
-        <v>ou</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Choose file</v>
+        <v>Upload an ICC profile to validate it against the</v>
       </c>
       <c r="B82" t="str">
-        <v>Escolher ficheiro</v>
+        <v>Carregue um perfil ICC para o validar segundo a especificação</v>
       </c>
       <c r="C82" t="str">
-        <v>Escolher arquivo</v>
+        <v>Envie um perfil ICC para validá-lo conforme a especificação</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>.icc and .icm files</v>
+        <v>specification using the</v>
       </c>
       <c r="B83" t="str">
-        <v>Ficheiros .icc e .icm</v>
+        <v>através da implementação de demonstração</v>
       </c>
       <c r="C83" t="str">
-        <v>Arquivos .icc e .icm</v>
+        <v>usando a implementação de demonstração</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Header</v>
+        <v>demo implementation.</v>
       </c>
       <c r="B84" t="str">
-        <v>Cabeçalho</v>
+        <v>.</v>
       </c>
       <c r="C84" t="str">
-        <v>Cabeçalho</v>
+        <v>.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Tags</v>
+        <v>Based on</v>
       </c>
       <c r="B85" t="str">
-        <v>Etiquetas</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
       <c r="C85" t="str">
-        <v>Tags</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Validation</v>
+        <v>demo implementation</v>
       </c>
       <c r="B86" t="str">
-        <v>Validação</v>
+        <v/>
       </c>
       <c r="C86" t="str">
-        <v>Validação</v>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Analysis</v>
+        <v>Validating…</v>
       </c>
       <c r="B87" t="str">
-        <v>Análise</v>
+        <v>A validar…</v>
       </c>
       <c r="C87" t="str">
-        <v>Análise</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B88" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Guardar perfil ICC</v>
       </c>
       <c r="C88" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Salvar perfil ICC</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B89" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
+        <v>● Modificado — não guardado</v>
       </c>
       <c r="C89" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
+        <v>● Modificado — não salvo</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Perfis</v>
       </c>
       <c r="C90" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Perfis</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B91" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>Mostrar o conjunto de perfis</v>
       </c>
       <c r="C91" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>Mostrar o conjunto de perfis</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Rendering intent</v>
+        <v>Collapse</v>
       </c>
       <c r="B92" t="str">
-        <v>Intenção de renderização</v>
+        <v>Recolher</v>
       </c>
       <c r="C92" t="str">
-        <v>Intenção de renderização</v>
+        <v>Recolher</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>% ink</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B93" t="str">
-        <v>% tinta</v>
+        <v>Carregar perfis</v>
       </c>
       <c r="C93" t="str">
-        <v>% tinta</v>
+        <v>Carregar perfis</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Perceptual</v>
+        <v>Remove</v>
       </c>
       <c r="B94" t="str">
-        <v>Perceptual</v>
+        <v>Remover</v>
       </c>
       <c r="C94" t="str">
-        <v>Perceptual</v>
+        <v>Remover</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B95" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Largue perfis ICC aqui</v>
       </c>
       <c r="C95" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Solte perfis ICC aqui</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Saturation</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B96" t="str">
-        <v>Saturação</v>
+        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o respetivo perfil incorporado — os ficheiros permanecem no seu dispositivo.</v>
       </c>
       <c r="C96" t="str">
-        <v>Saturação</v>
+        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o perfil incorporado — os arquivos permanecem no seu dispositivo.</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>New from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Novo a partir de .cube</v>
       </c>
       <c r="C97" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Novo a partir de .cube</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Profile Statistics</v>
+        <v>Sort by name</v>
       </c>
       <c r="B98" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Ordenar por nome</v>
       </c>
       <c r="C98" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Ordenar por nome</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>A–Z</v>
       </c>
       <c r="B99" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>A–Z</v>
       </c>
       <c r="C99" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B100" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
+        <v>Novo perfil a partir de .cube</v>
       </c>
       <c r="C100" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
+        <v>Novo perfil a partir de .cube</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Rendering intent</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B101" t="str">
-        <v>Intenção de renderização</v>
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e transferido.</v>
       </c>
       <c r="C101" t="str">
-        <v>Intenção de renderização</v>
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e baixado.</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B102" t="str">
-        <v>Volume de gamute (ΔE³)</v>
+        <v>Escolher ficheiro .cube</v>
       </c>
       <c r="C102" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Escolher arquivo .cube</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Round-trip ΔE</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B103" t="str">
-        <v>ΔE de percurso</v>
+        <v>ou largue-o aqui, ou cole abaixo</v>
       </c>
       <c r="C103" t="str">
-        <v>ΔE de percurso</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
-      </c>
-      <c r="B104" t="str">
-        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
-      </c>
-      <c r="C104" t="str">
-        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
+        <v>ou solte-o aqui, ou cole abaixo</v>
+      </c>
+    </row>
+    <row r="104" xml:space="preserve">
+      <c r="A104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
+      </c>
+      <c r="B104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
+      </c>
+      <c r="C104" t="str" xml:space="preserve">
+        <v xml:space="preserve">TITLE "My LUT"
+LUT_3D_SIZE 33
+0.0 0.0 0.0
+…</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>mean</v>
+        <v>Cancel</v>
       </c>
       <c r="B105" t="str">
-        <v>média</v>
+        <v>Cancelar</v>
       </c>
       <c r="C105" t="str">
-        <v>média</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>P90</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B106" t="str">
-        <v>P90</v>
+        <v>Criar DeviceLink</v>
       </c>
       <c r="C106" t="str">
-        <v>P90</v>
+        <v>Criar DeviceLink</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>max</v>
+        <v>Creating…</v>
       </c>
       <c r="B107" t="str">
-        <v>máx.</v>
+        <v>A criar…</v>
       </c>
       <c r="C107" t="str">
-        <v>máx.</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Analysing…</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B108" t="str">
-        <v>A analisar…</v>
+        <v>Não foi possível ler esse ficheiro.</v>
       </c>
       <c r="C108" t="str">
-        <v>Analisando…</v>
+        <v>Não foi possível ler esse arquivo.</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Analysis</v>
+        <v>Profile</v>
       </c>
       <c r="B109" t="str">
-        <v>Análise</v>
+        <v>Perfil</v>
       </c>
       <c r="C109" t="str">
-        <v>Análise</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Compare</v>
       </c>
       <c r="B110" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Comparar</v>
       </c>
       <c r="C110" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Comparar</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Plot</v>
+        <v>Link</v>
       </c>
       <c r="B111" t="str">
-        <v>Gráfico</v>
+        <v>Ligar</v>
       </c>
       <c r="C111" t="str">
-        <v>Gráfico</v>
+        <v>Vincular</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Raw Output</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B112" t="str">
-        <v>Saída em bruto</v>
+        <v>Arraste perfis do conjunto para este separador</v>
       </c>
       <c r="C112" t="str">
-        <v>Saída bruta</v>
+        <v>Arraste perfis do conjunto para esta aba</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>XML</v>
+        <v>Remove</v>
       </c>
       <c r="B113" t="str">
-        <v>XML</v>
+        <v>Remover</v>
       </c>
       <c r="C113" t="str">
-        <v>XML</v>
+        <v>Remover</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>JSON</v>
+        <v>No profile selected</v>
       </c>
       <c r="B114" t="str">
-        <v>JSON</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
       <c r="C114" t="str">
-        <v>JSON</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Curves</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B115" t="str">
-        <v>Curvas</v>
+        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
       </c>
       <c r="C115" t="str">
-        <v>Curvas</v>
+        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Input curves</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B116" t="str">
-        <v>Curvas de entrada</v>
+        <v>Ainda nada para comparar</v>
       </c>
       <c r="C116" t="str">
-        <v>Curvas de entrada</v>
+        <v>Ainda nada para comparar</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Output curves</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B117" t="str">
-        <v>Curvas de saída</v>
+        <v>Arraste um ou mais perfis para o separador Comparar.</v>
       </c>
       <c r="C117" t="str">
-        <v>Curvas de saída</v>
+        <v>Arraste um ou mais perfis para a aba Comparar.</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>CLUT image</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B118" t="str">
-        <v>Imagem CLUT</v>
+        <v>Comparação de gamut</v>
       </c>
       <c r="C118" t="str">
-        <v>Imagem CLUT</v>
+        <v>Comparação de gamut</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut image</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B119" t="str">
-        <v>Imagem de gamut</v>
+        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
       <c r="C119" t="str">
-        <v>Imagem de gamut</v>
+        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Chromaticity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B120" t="str">
-        <v>Cromaticidade</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C120" t="str">
-        <v>Cromaticidade</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Scatter plot</v>
+        <v>Shell</v>
       </c>
       <c r="B121" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Invólucro</v>
       </c>
       <c r="C121" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Invólucro</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tone response curve</v>
+        <v>Wireframe</v>
       </c>
       <c r="B122" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Malha de arame</v>
       </c>
       <c r="C122" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Malha de arame</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Curve table</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>Tabela da curva</v>
+        <v>Opacidade</v>
       </c>
       <c r="C123" t="str">
-        <v>Tabela da curva</v>
+        <v>Opacidade</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tables</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>Tabelas</v>
+        <v>Cor</v>
       </c>
       <c r="C124" t="str">
-        <v>Tabelas</v>
+        <v>Cor</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Data</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>Dados</v>
+        <v>Sólido</v>
       </c>
       <c r="C125" t="str">
-        <v>Dados</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Evaluate</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>Avaliar</v>
+        <v>Por valor</v>
       </c>
       <c r="C126" t="str">
-        <v>Avaliar</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Loading…</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>A carregar…</v>
+        <v>Por matiz</v>
       </c>
       <c r="C127" t="str">
-        <v>Carregando…</v>
+        <v>Por matiz</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Input</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>Entrada</v>
+        <v>Rotação</v>
       </c>
       <c r="C128" t="str">
-        <v>Entrada</v>
+        <v>Rotação</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Output</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>Saída</v>
+        <v>Prato giratório</v>
       </c>
       <c r="C129" t="str">
-        <v>Saída</v>
+        <v>Prato giratório</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Floating point</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Órbita</v>
       </c>
       <c r="C130" t="str">
-        <v>Ponto flutuante</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Grid point</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>Ponto da grelha</v>
+        <v>Velocidade de arrasto</v>
       </c>
       <c r="C131" t="str">
-        <v>Ponto da grade</v>
+        <v>Velocidade de arrasto</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Normalized</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>Normalizado</v>
+        <v>Rolamento</v>
       </c>
       <c r="C132" t="str">
-        <v>Normalizado</v>
+        <v>Rolagem</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Human</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Legível</v>
+        <v>Velocidade de rolamento</v>
       </c>
       <c r="C133" t="str">
-        <v>Legível</v>
+        <v>Velocidade de rolagem</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Device → PCS</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>A construir o gamut…</v>
       </c>
       <c r="C134" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Construindo o gamut…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>PCS → Device</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>sem gamut</v>
       </c>
       <c r="C135" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>sem gamut</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>No CLUT grid</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>Mostrar / ocultar</v>
       </c>
       <c r="C136" t="str">
-        <v>Sem grade CLUT</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Loading…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>A carregar…</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
       <c r="C137" t="str">
-        <v>Carregando…</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Corte de gamut 2D</v>
       </c>
       <c r="C138" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Corte de gamut 2D</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Plano</v>
       </c>
       <c r="C139" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>L*</v>
       </c>
       <c r="C140" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>a*</v>
       </c>
       <c r="C141" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>b*</v>
       </c>
       <c r="C142" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
       <c r="C143" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Ligação</v>
       </c>
       <c r="C144" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Vínculo</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Security</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>Segurança</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
       </c>
       <c r="C145" t="str">
-        <v>Segurança</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Conformance</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>Conformidade</v>
+        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
       </c>
       <c r="C146" t="str">
-        <v>Conformidade</v>
+        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Quality</v>
+        <v>V4 Display Maker</v>
       </c>
       <c r="B147" t="str">
-        <v>Qualidade</v>
+        <v>Criador de ecrã V4</v>
       </c>
       <c r="C147" t="str">
-        <v>Qualidade</v>
+        <v>Criador de tela V4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>REPORT</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>RELATÓRIO</v>
+        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
       </c>
       <c r="C148" t="str">
-        <v>RELATÓRIO</v>
+        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FAIL</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>REPROVADO</v>
+        <v>Ecrã RGB V5</v>
       </c>
       <c r="C149" t="str">
-        <v>REPROVADO</v>
+        <v>Tela RGB V5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>checks</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>verificações</v>
+        <v>largue um perfil de ecrã</v>
       </c>
       <c r="C150" t="str">
-        <v>verificações</v>
+        <v>solte um perfil de tela</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Observador V5 (PCC)</v>
       </c>
       <c r="C151" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>largue um perfil de observador</v>
       </c>
       <c r="C152" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>solte um perfil de observador</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
       </c>
       <c r="C153" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Powered by {lib}</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Com {lib}</v>
+        <v>Criar perfil de ecrã V4</v>
       </c>
       <c r="C154" t="str">
-        <v>Com {lib}</v>
+        <v>Criar perfil de tela V4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Subscribe</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>Subscrever</v>
+        <v>Nome do perfil</v>
       </c>
       <c r="C155" t="str">
-        <v>Inscrever-se</v>
+        <v>Nome do perfil</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Criar</v>
       </c>
       <c r="C156" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Criar</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Get notified about new releases</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>A criar…</v>
       </c>
       <c r="C157" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Close</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>Fechar</v>
+        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C158" t="str">
-        <v>Fechar</v>
+        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Cancel</v>
       </c>
       <c r="B159" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Cancelar</v>
       </c>
       <c r="C159" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Email address</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B160" t="str">
-        <v>Endereço de e-mail</v>
+        <v>{n} ficheiro(s) não carregados</v>
       </c>
       <c r="C160" t="str">
-        <v>Endereço de e-mail</v>
+        <v>{n} arquivo(s) não carregados</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>you@example.com</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B161" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
       </c>
       <c r="C161" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>How will you use profiletool?</v>
+        <v>OK</v>
       </c>
       <c r="B162" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>OK</v>
       </c>
       <c r="C162" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>(optional)</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B163" t="str">
-        <v>(opcional)</v>
+        <v>Largue um perfil ICC aqui</v>
       </c>
       <c r="C163" t="str">
-        <v>(opcional)</v>
+        <v>Solte um perfil ICC aqui</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>or</v>
       </c>
       <c r="B164" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>ou</v>
       </c>
       <c r="C164" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Choose file</v>
       </c>
       <c r="B165" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Escolher ficheiro</v>
       </c>
       <c r="C165" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Escolher arquivo</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Cancel</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B166" t="str">
-        <v>Cancelar</v>
+        <v>Ficheiros .icc e .icm</v>
       </c>
       <c r="C166" t="str">
-        <v>Cancelar</v>
+        <v>Arquivos .icc e .icm</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Subscribe</v>
+        <v>Header</v>
       </c>
       <c r="B167" t="str">
-        <v>Subscrever</v>
+        <v>Cabeçalho</v>
       </c>
       <c r="C167" t="str">
-        <v>Inscrever-se</v>
+        <v>Cabeçalho</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Tags</v>
       </c>
       <c r="B168" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Etiquetas</v>
       </c>
       <c r="C168" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Validation</v>
       </c>
       <c r="B169" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Validação</v>
       </c>
       <c r="C169" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Validação</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Close</v>
+        <v>Analysis</v>
       </c>
       <c r="B170" t="str">
-        <v>Fechar</v>
+        <v>Análise</v>
       </c>
       <c r="C170" t="str">
-        <v>Fechar</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Privacy notice</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B171" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
       <c r="C171" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B172" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
       </c>
       <c r="C172" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B173" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C173" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Please check the form and try again.</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B174" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
       <c r="C174" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B175" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C175" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Network error. Please try again.</v>
+        <v>% ink</v>
       </c>
       <c r="B176" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>% tinta</v>
       </c>
       <c r="C176" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Error:</v>
+        <v>Perceptual</v>
       </c>
       <c r="B177" t="str">
-        <v>Erro:</v>
+        <v>Perceptual</v>
       </c>
       <c r="C177" t="str">
-        <v>Erro:</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Convert to XML</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B178" t="str">
-        <v>Converter para XML</v>
+        <v>Colorimétrico relativo</v>
       </c>
       <c r="C178" t="str">
-        <v>Converter para XML</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Convert to JSON</v>
+        <v>Saturation</v>
       </c>
       <c r="B179" t="str">
-        <v>Converter para JSON</v>
+        <v>Saturação</v>
       </c>
       <c r="C179" t="str">
-        <v>Converter para JSON</v>
+        <v>Saturação</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Convert to ICC</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B180" t="str">
-        <v>Converter para ICC</v>
+        <v>Colorimétrico absoluto</v>
       </c>
       <c r="C180" t="str">
-        <v>Converter para ICC</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Converting to XML…</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B181" t="str">
-        <v>A converter para XML…</v>
+        <v>Estatísticas do perfil</v>
       </c>
       <c r="C181" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Estatísticas do perfil</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Converting to JSON…</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B182" t="str">
-        <v>A converter para JSON…</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
       <c r="C182" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Converting to ICC…</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B183" t="str">
-        <v>A converter para ICC…</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
       </c>
       <c r="C183" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Load ICC profile</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B184" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C184" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B185" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Volume de gamute (ΔE³)</v>
       </c>
       <c r="C185" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Profile ID</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B186" t="str">
-        <v>ID do perfil</v>
+        <v>ΔE de percurso</v>
       </c>
       <c r="C186" t="str">
-        <v>ID do perfil</v>
+        <v>ΔE de percurso</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>No tags found.</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B187" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
       </c>
       <c r="C187" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Tag Name</v>
+        <v>mean</v>
       </c>
       <c r="B188" t="str">
-        <v>Nome da etiqueta</v>
+        <v>média</v>
       </c>
       <c r="C188" t="str">
-        <v>Nome da tag</v>
+        <v>média</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
       <c r="B189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
       <c r="C189" t="str">
-        <v>ID</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Offset</v>
+        <v>max</v>
       </c>
       <c r="B190" t="str">
-        <v>Deslocamento</v>
+        <v>máx.</v>
       </c>
       <c r="C190" t="str">
-        <v>Deslocamento</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Size</v>
+        <v>Analysing…</v>
       </c>
       <c r="B191" t="str">
-        <v>Tamanho</v>
+        <v>A analisar…</v>
       </c>
       <c r="C191" t="str">
-        <v>Tamanho</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Pad</v>
+        <v>Analysis</v>
       </c>
       <c r="B192" t="str">
-        <v>Preenchimento</v>
+        <v>Análise</v>
       </c>
       <c r="C192" t="str">
-        <v>Preenchimento</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Bytes changed since load</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B193" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C193" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Type</v>
+        <v>Plot</v>
       </c>
       <c r="B194" t="str">
-        <v>Tipo</v>
+        <v>Gráfico</v>
       </c>
       <c r="C194" t="str">
-        <v>Tipo</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Array of {type}</v>
+        <v>Raw Output</v>
       </c>
       <c r="B195" t="str">
-        <v>Vetor de {type}</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C195" t="str">
-        <v>Array de {type}</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>(No content)</v>
+        <v>XML</v>
       </c>
       <c r="B196" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>XML</v>
       </c>
       <c r="C196" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>bytes</v>
+        <v>JSON</v>
       </c>
       <c r="B197" t="str">
-        <v>bytes</v>
+        <v>JSON</v>
       </c>
       <c r="C197" t="str">
-        <v>bytes</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Loading full description…</v>
+        <v>Curves</v>
       </c>
       <c r="B198" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Curvas</v>
       </c>
       <c r="C198" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Could not load full description:</v>
+        <v>Input curves</v>
       </c>
       <c r="B199" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C199" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Output curves</v>
       </c>
       <c r="B200" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C200" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>CLUT image</v>
       </c>
       <c r="B201" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C201" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>No validation output</v>
+        <v>Gamut image</v>
       </c>
       <c r="B202" t="str">
-        <v>Sem saída de validação</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C202" t="str">
-        <v>Sem saída de validação</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Profile is valid</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B203" t="str">
-        <v>O perfil é válido</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C203" t="str">
-        <v>O perfil é válido</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B204" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C204" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B205" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C205" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Critical validation error</v>
+        <v>Curve table</v>
       </c>
       <c r="B206" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C206" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Unknown validation status</v>
+        <v>Tables</v>
       </c>
       <c r="B207" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Tabelas</v>
       </c>
       <c r="C207" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Data</v>
       </c>
       <c r="B208" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Dados</v>
       </c>
       <c r="C208" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Evaluate</v>
       </c>
       <c r="B209" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Avaliar</v>
       </c>
       <c r="C209" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Valid</v>
+        <v>Loading…</v>
       </c>
       <c r="B210" t="str">
-        <v>Válido</v>
+        <v>A carregar…</v>
       </c>
       <c r="C210" t="str">
-        <v>Válido</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Warning</v>
+        <v>Input</v>
       </c>
       <c r="B211" t="str">
-        <v>Aviso</v>
+        <v>Entrada</v>
       </c>
       <c r="C211" t="str">
-        <v>Aviso</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Error</v>
+        <v>Output</v>
       </c>
       <c r="B212" t="str">
-        <v>Erro</v>
+        <v>Saída</v>
       </c>
       <c r="C212" t="str">
-        <v>Erro</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Unknown</v>
+        <v>Floating point</v>
       </c>
       <c r="B213" t="str">
-        <v>Desconhecido</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C213" t="str">
-        <v>Desconhecido</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Pass</v>
+        <v>Grid point</v>
       </c>
       <c r="B214" t="str">
-        <v>Aprovado</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C214" t="str">
-        <v>Aprovado</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Fail</v>
+        <v>Normalized</v>
       </c>
       <c r="B215" t="str">
-        <v>Reprovado</v>
+        <v>Normalizado</v>
       </c>
       <c r="C215" t="str">
-        <v>Reprovado</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>View in context</v>
+        <v>Human</v>
       </c>
       <c r="B216" t="str">
-        <v>Ver no contexto</v>
+        <v>Legível</v>
       </c>
       <c r="C216" t="str">
-        <v>Ver no contexto</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Validation detail</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B217" t="str">
-        <v>Detalhe de validação</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C217" t="str">
-        <v>Detalhe de validação</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Triggered by</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B218" t="str">
-        <v>Acionado por</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C218" t="str">
-        <v>Acionado por</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Field</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B219" t="str">
-        <v>Campo</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C219" t="str">
-        <v>Campo</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Current value</v>
+        <v>Loading…</v>
       </c>
       <c r="B220" t="str">
-        <v>Valor atual</v>
+        <v>A carregar…</v>
       </c>
       <c r="C220" t="str">
-        <v>Valor atual</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Required: 0</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B221" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C221" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Expected: {value}</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B222" t="str">
-        <v>Esperado: {value}</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C222" t="str">
-        <v>Esperado: {value}</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Invalid</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B223" t="str">
-        <v>Inválido</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C223" t="str">
-        <v>Inválido</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B224" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C224" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Close</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B225" t="str">
-        <v>Fechar</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C225" t="str">
-        <v>Fechar</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Loading XML editor…</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B226" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C226" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B227" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C227" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Security</v>
       </c>
       <c r="B228" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Segurança</v>
       </c>
       <c r="C228" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Conformance</v>
       </c>
       <c r="B229" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Conformidade</v>
       </c>
       <c r="C229" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Quality</v>
       </c>
       <c r="B230" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Qualidade</v>
       </c>
       <c r="C230" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>REPORT</v>
       </c>
       <c r="B231" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C231" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>FAIL</v>
       </c>
       <c r="B232" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C232" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>checks</v>
       </c>
       <c r="B233" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>verificações</v>
       </c>
       <c r="C233" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>indent</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B234" t="str">
-        <v>indentação</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C234" t="str">
-        <v>indentação</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>sort keys</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B235" t="str">
-        <v>ordenar chaves</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C235" t="str">
-        <v>ordenar chaves</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Ferramenta de perfis ICC</v>
+      </c>
+      <c r="C236" t="str">
+        <v>Ferramenta de perfis ICC</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Com {lib}</v>
+      </c>
+      <c r="C237" t="str">
+        <v>Com {lib}</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Subscrever</v>
+      </c>
+      <c r="C238" t="str">
+        <v>Inscrever-se</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Receber notificações sobre novas versões do profiletool</v>
+      </c>
+      <c r="C239" t="str">
+        <v>Receber notificações sobre novas versões do profiletool</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Receber notificações sobre novas versões</v>
+      </c>
+      <c r="C240" t="str">
+        <v>Receber notificações sobre novas versões</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C241" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+      </c>
+      <c r="C242" t="str">
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Endereço de e-mail</v>
+      </c>
+      <c r="C243" t="str">
+        <v>Endereço de e-mail</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B244" t="str">
+        <v>voce@exemplo.com</v>
+      </c>
+      <c r="C244" t="str">
+        <v>voce@exemplo.com</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Como vai utilizar o profiletool?</v>
+      </c>
+      <c r="C245" t="str">
+        <v>Como você vai usar o profiletool?</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B246" t="str">
+        <v>(opcional)</v>
+      </c>
+      <c r="C246" t="str">
+        <v>(opcional)</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B247" t="str">
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+      </c>
+      <c r="C247" t="str">
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+      </c>
+      <c r="C248" t="str">
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B249" t="str">
+        <v>Cancelar</v>
+      </c>
+      <c r="C249" t="str">
+        <v>Cancelar</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Subscrever</v>
+      </c>
+      <c r="C250" t="str">
+        <v>Inscrever-se</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Obrigado — entraremos em contacto.</v>
+      </c>
+      <c r="C251" t="str">
+        <v>Obrigado — entraremos em contato.</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+      </c>
+      <c r="C252" t="str">
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C253" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Aviso de privacidade</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Aviso de privacidade</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Introduza um endereço de e-mail válido.</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Insira um endereço de e-mail válido.</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Verifique o formulário e tente novamente.</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Verifique o formulário e tente novamente.</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+      </c>
+      <c r="C258" t="str">
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Erro de rede. Tente novamente.</v>
+      </c>
+      <c r="C259" t="str">
+        <v>Erro de rede. Tente novamente.</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Erro:</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Erro:</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Converter para XML</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Converter para XML</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Converter para JSON</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Converter para JSON</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Converter para ICC</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Converter para ICC</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B264" t="str">
+        <v>A converter para XML…</v>
+      </c>
+      <c r="C264" t="str">
+        <v>Convertendo para XML…</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B265" t="str">
+        <v>A converter para JSON…</v>
+      </c>
+      <c r="C265" t="str">
+        <v>Convertendo para JSON…</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B266" t="str">
+        <v>A converter para ICC…</v>
+      </c>
+      <c r="C266" t="str">
+        <v>Convertendo para ICC…</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B267" t="str">
+        <v>Carregar perfil ICC</v>
+      </c>
+      <c r="C267" t="str">
+        <v>Carregar perfil ICC</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B268" t="str">
+        <v>Zona de largada para ficheiros de perfil ICC</v>
+      </c>
+      <c r="C268" t="str">
+        <v>Área de soltar para arquivos de perfil ICC</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B269" t="str">
+        <v>ID do perfil</v>
+      </c>
+      <c r="C269" t="str">
+        <v>ID do perfil</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B270" t="str">
+        <v>Nenhuma etiqueta encontrada.</v>
+      </c>
+      <c r="C270" t="str">
+        <v>Nenhuma tag encontrada.</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B271" t="str">
+        <v>Nome da etiqueta</v>
+      </c>
+      <c r="C271" t="str">
+        <v>Nome da tag</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B272" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C272" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B273" t="str">
+        <v>Deslocamento</v>
+      </c>
+      <c r="C273" t="str">
+        <v>Deslocamento</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B274" t="str">
+        <v>Tamanho</v>
+      </c>
+      <c r="C274" t="str">
+        <v>Tamanho</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B275" t="str">
+        <v>Preenchimento</v>
+      </c>
+      <c r="C275" t="str">
+        <v>Preenchimento</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B276" t="str">
+        <v>Bytes alterados desde o carregamento</v>
+      </c>
+      <c r="C276" t="str">
+        <v>Bytes alterados desde o carregamento</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B277" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C277" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B278" t="str">
+        <v>Vetor de {type}</v>
+      </c>
+      <c r="C278" t="str">
+        <v>Array de {type}</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B279" t="str">
+        <v>(Sem conteúdo)</v>
+      </c>
+      <c r="C279" t="str">
+        <v>(Sem conteúdo)</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B280" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="C280" t="str">
+        <v>bytes</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B281" t="str">
+        <v>A carregar descrição completa…</v>
+      </c>
+      <c r="C281" t="str">
+        <v>Carregando descrição completa…</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B282" t="str">
+        <v>Não foi possível carregar a descrição completa:</v>
+      </c>
+      <c r="C282" t="str">
+        <v>Não foi possível carregar a descrição completa:</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B283" t="str">
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+      </c>
+      <c r="C283" t="str">
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B284" t="str">
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+      </c>
+      <c r="C284" t="str">
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B285" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+      <c r="C285" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B286" t="str">
+        <v>O perfil é válido</v>
+      </c>
+      <c r="C286" t="str">
+        <v>O perfil é válido</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B287" t="str">
+        <v>O perfil tem avisos</v>
+      </c>
+      <c r="C287" t="str">
+        <v>O perfil tem avisos</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B288" t="str">
+        <v>O perfil não é conforme</v>
+      </c>
+      <c r="C288" t="str">
+        <v>O perfil não está em conformidade</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B289" t="str">
+        <v>Erro de validação crítico</v>
+      </c>
+      <c r="C289" t="str">
+        <v>Erro de validação crítico</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B290" t="str">
+        <v>Estado de validação desconhecido</v>
+      </c>
+      <c r="C290" t="str">
+        <v>Status de validação desconhecido</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B291" t="str">
+        <v>Crítico — apresentado apenas para inspeção</v>
+      </c>
+      <c r="C291" t="str">
+        <v>Crítico — exibido apenas para inspeção</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B292" t="str">
+        <v>Sem avisos nem erros encontrados.</v>
+      </c>
+      <c r="C292" t="str">
+        <v>Nenhum aviso ou erro encontrado.</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B293" t="str">
+        <v>Válido</v>
+      </c>
+      <c r="C293" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B294" t="str">
+        <v>Aviso</v>
+      </c>
+      <c r="C294" t="str">
+        <v>Aviso</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B295" t="str">
+        <v>Erro</v>
+      </c>
+      <c r="C295" t="str">
+        <v>Erro</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B296" t="str">
+        <v>Desconhecido</v>
+      </c>
+      <c r="C296" t="str">
+        <v>Desconhecido</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B297" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="C297" t="str">
+        <v>Aprovado</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B298" t="str">
+        <v>Reprovado</v>
+      </c>
+      <c r="C298" t="str">
+        <v>Reprovado</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B299" t="str">
+        <v>Ver no contexto</v>
+      </c>
+      <c r="C299" t="str">
+        <v>Ver no contexto</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B300" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+      <c r="C300" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B301" t="str">
+        <v>Acionado por</v>
+      </c>
+      <c r="C301" t="str">
+        <v>Acionado por</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B302" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C302" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B303" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C303" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B304" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C304" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B305" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C305" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B306" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C306" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B307" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C307" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B308" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C308" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B309" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C309" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B310" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C310" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B311" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C311" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B312" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C312" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B313" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C313" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B314" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C314" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B315" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C315" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B316" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C316" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B317" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C317" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B318" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C318" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B236" t="str">
+      <c r="B319" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C236" t="str">
+      <c r="C319" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C236"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C319"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C319"/>
+  <dimension ref="A1:C413"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1625,7 +1625,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Link</v>
+        <v>Combine</v>
       </c>
       <c r="B111" t="str">
         <v>Ligar</v>
@@ -1636,2295 +1636,3329 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B112" t="str">
-        <v>Arraste perfis do conjunto para este separador</v>
+        <v>Espectral</v>
       </c>
       <c r="C112" t="str">
-        <v>Arraste perfis do conjunto para esta aba</v>
+        <v>Espectral</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B113" t="str">
-        <v>Remover</v>
+        <v>Arraste perfis do conjunto para este separador</v>
       </c>
       <c r="C113" t="str">
-        <v>Remover</v>
+        <v>Arraste perfis do conjunto para esta aba</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B114" t="str">
-        <v>Nenhum perfil selecionado</v>
+        <v>Remover</v>
       </c>
       <c r="C114" t="str">
-        <v>Nenhum perfil selecionado</v>
+        <v>Remover</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B115" t="str">
-        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
       <c r="C115" t="str">
-        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B116" t="str">
-        <v>Ainda nada para comparar</v>
+        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
       </c>
       <c r="C116" t="str">
-        <v>Ainda nada para comparar</v>
+        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B117" t="str">
-        <v>Arraste um ou mais perfis para o separador Comparar.</v>
+        <v>Ainda nada para comparar</v>
       </c>
       <c r="C117" t="str">
-        <v>Arraste um ou mais perfis para a aba Comparar.</v>
+        <v>Ainda nada para comparar</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B118" t="str">
-        <v>Comparação de gamut</v>
+        <v>Arraste um ou mais perfis para o separador Comparar.</v>
       </c>
       <c r="C118" t="str">
-        <v>Comparação de gamut</v>
+        <v>Arraste um ou mais perfis para a aba Comparar.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B119" t="str">
-        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
+        <v>Comparação de gamut</v>
       </c>
       <c r="C119" t="str">
-        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
+        <v>Comparação de gamut</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B120" t="str">
-        <v>Intenção de renderização</v>
+        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
       <c r="C120" t="str">
-        <v>Intenção de renderização</v>
+        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B121" t="str">
-        <v>Invólucro</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C121" t="str">
-        <v>Invólucro</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B122" t="str">
-        <v>Malha de arame</v>
+        <v>Invólucro</v>
       </c>
       <c r="C122" t="str">
-        <v>Malha de arame</v>
+        <v>Invólucro</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Wireframe</v>
       </c>
       <c r="B123" t="str">
-        <v>Opacidade</v>
+        <v>Malha de arame</v>
       </c>
       <c r="C123" t="str">
-        <v>Opacidade</v>
+        <v>Malha de arame</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B124" t="str">
-        <v>Cor</v>
+        <v>Números dos eixos</v>
       </c>
       <c r="C124" t="str">
-        <v>Cor</v>
+        <v>Números dos eixos</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Opacity</v>
       </c>
       <c r="B125" t="str">
-        <v>Sólido</v>
+        <v>Opacidade</v>
       </c>
       <c r="C125" t="str">
-        <v>Sólido</v>
+        <v>Opacidade</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Colour</v>
       </c>
       <c r="B126" t="str">
-        <v>Por valor</v>
+        <v>Cor</v>
       </c>
       <c r="C126" t="str">
-        <v>Por valor</v>
+        <v>Cor</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Solid</v>
       </c>
       <c r="B127" t="str">
-        <v>Por matiz</v>
+        <v>Sólido</v>
       </c>
       <c r="C127" t="str">
-        <v>Por matiz</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>By value</v>
       </c>
       <c r="B128" t="str">
-        <v>Rotação</v>
+        <v>Por valor</v>
       </c>
       <c r="C128" t="str">
-        <v>Rotação</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>By hue</v>
       </c>
       <c r="B129" t="str">
-        <v>Prato giratório</v>
+        <v>Por matiz</v>
       </c>
       <c r="C129" t="str">
-        <v>Prato giratório</v>
+        <v>Por matiz</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>Rotation</v>
       </c>
       <c r="B130" t="str">
-        <v>Órbita</v>
+        <v>Rotação</v>
       </c>
       <c r="C130" t="str">
-        <v>Órbita</v>
+        <v>Rotação</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B131" t="str">
-        <v>Velocidade de arrasto</v>
+        <v>Prato giratório</v>
       </c>
       <c r="C131" t="str">
-        <v>Velocidade de arrasto</v>
+        <v>Prato giratório</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Orbit</v>
       </c>
       <c r="B132" t="str">
-        <v>Rolamento</v>
+        <v>Órbita</v>
       </c>
       <c r="C132" t="str">
-        <v>Rolagem</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Drag speed</v>
       </c>
       <c r="B133" t="str">
-        <v>Velocidade de rolamento</v>
+        <v>Velocidade de arrasto</v>
       </c>
       <c r="C133" t="str">
-        <v>Velocidade de rolagem</v>
+        <v>Velocidade de arrasto</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Roll</v>
       </c>
       <c r="B134" t="str">
-        <v>A construir o gamut…</v>
+        <v>Rolamento</v>
       </c>
       <c r="C134" t="str">
-        <v>Construindo o gamut…</v>
+        <v>Rolagem</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Roll speed</v>
       </c>
       <c r="B135" t="str">
-        <v>sem gamut</v>
+        <v>Velocidade de rolamento</v>
       </c>
       <c r="C135" t="str">
-        <v>sem gamut</v>
+        <v>Velocidade de rolagem</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B136" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>A construir o gamut…</v>
       </c>
       <c r="C136" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>Construindo o gamut…</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>no gamut</v>
       </c>
       <c r="B137" t="str">
-        <v>Invólucro de gamut 3D</v>
+        <v>sem gamut</v>
       </c>
       <c r="C137" t="str">
-        <v>Invólucro de gamut 3D</v>
+        <v>sem gamut</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Show / hide</v>
       </c>
       <c r="B138" t="str">
-        <v>Corte de gamut 2D</v>
+        <v>Mostrar / ocultar</v>
       </c>
       <c r="C138" t="str">
-        <v>Corte de gamut 2D</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B139" t="str">
-        <v>Plano</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
       <c r="C139" t="str">
-        <v>Plano</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>Corte de gamut 2D</v>
       </c>
       <c r="C140" t="str">
-        <v>L*</v>
+        <v>Corte de gamut 2D</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>Plane</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>Plano</v>
       </c>
       <c r="C141" t="str">
-        <v>a*</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
       <c r="C142" t="str">
-        <v>b*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>a*</v>
       </c>
       <c r="B143" t="str">
-        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
+        <v>a*</v>
       </c>
       <c r="C143" t="str">
-        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>b*</v>
       </c>
       <c r="B144" t="str">
-        <v>Ligação</v>
+        <v>b*</v>
       </c>
       <c r="C144" t="str">
-        <v>Vínculo</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B145" t="str">
-        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
       <c r="C145" t="str">
-        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>Linking</v>
       </c>
       <c r="B146" t="str">
-        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
+        <v>Ligação</v>
       </c>
       <c r="C146" t="str">
-        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
+        <v>Vínculo</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>V4 Display Maker</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B147" t="str">
-        <v>Criador de ecrã V4</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
       </c>
       <c r="C147" t="str">
-        <v>Criador de tela V4</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B148" t="str">
-        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
+        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
       </c>
       <c r="C148" t="str">
-        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
+        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>Observer Change</v>
       </c>
       <c r="B149" t="str">
-        <v>Ecrã RGB V5</v>
+        <v>Criador de ecrã V4</v>
       </c>
       <c r="C149" t="str">
-        <v>Tela RGB V5</v>
+        <v>Criador de tela V4</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B150" t="str">
-        <v>largue um perfil de ecrã</v>
+        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
       </c>
       <c r="C150" t="str">
-        <v>solte um perfil de tela</v>
+        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B151" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>Ecrã RGB V5</v>
       </c>
       <c r="C151" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>Tela RGB V5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B152" t="str">
-        <v>largue um perfil de observador</v>
+        <v>largue um perfil de ecrã</v>
       </c>
       <c r="C152" t="str">
-        <v>solte um perfil de observador</v>
+        <v>solte um perfil de tela</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B153" t="str">
-        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
+        <v>Observador V5 (PCC)</v>
       </c>
       <c r="C153" t="str">
-        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Criar perfil de ecrã V4</v>
+        <v>largue um perfil de observador</v>
       </c>
       <c r="C154" t="str">
-        <v>Criar perfil de tela V4</v>
+        <v>solte um perfil de observador</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B155" t="str">
-        <v>Nome do perfil</v>
+        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
       </c>
       <c r="C155" t="str">
-        <v>Nome do perfil</v>
+        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B156" t="str">
-        <v>Criar</v>
+        <v>Criar perfil de ecrã V4</v>
       </c>
       <c r="C156" t="str">
-        <v>Criar</v>
+        <v>Criar perfil de tela V4</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Profile name</v>
       </c>
       <c r="B157" t="str">
-        <v>A criar…</v>
+        <v>Nome do perfil</v>
       </c>
       <c r="C157" t="str">
-        <v>Criando…</v>
+        <v>Nome do perfil</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Create</v>
       </c>
       <c r="B158" t="str">
-        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
+        <v>Criar</v>
       </c>
       <c r="C158" t="str">
-        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
+        <v>Criar</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Cancel</v>
+        <v>Making…</v>
       </c>
       <c r="B159" t="str">
-        <v>Cancelar</v>
+        <v>A criar…</v>
       </c>
       <c r="C159" t="str">
-        <v>Cancelar</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B160" t="str">
-        <v>{n} ficheiro(s) não carregados</v>
+        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C160" t="str">
-        <v>{n} arquivo(s) não carregados</v>
+        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B161" t="str">
-        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
+        <v>Fluxo de ligação</v>
       </c>
       <c r="C161" t="str">
-        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
+        <v>Fluxo de vinculação</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>OK</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B162" t="str">
-        <v>OK</v>
+        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
       </c>
       <c r="C162" t="str">
-        <v>OK</v>
+        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Done</v>
       </c>
       <c r="B163" t="str">
-        <v>Largue um perfil ICC aqui</v>
+        <v>Concluído</v>
       </c>
       <c r="C163" t="str">
-        <v>Solte um perfil ICC aqui</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>or</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B164" t="str">
-        <v>ou</v>
+        <v>Largue uma imagem para transformar (TIFF/PNG/JPEG)</v>
       </c>
       <c r="C164" t="str">
-        <v>ou</v>
+        <v>Solte uma imagem para transformar (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Choose file</v>
+        <v>Checking image…</v>
       </c>
       <c r="B165" t="str">
-        <v>Escolher ficheiro</v>
+        <v>A verificar imagem…</v>
       </c>
       <c r="C165" t="str">
-        <v>Escolher arquivo</v>
+        <v>Verificando imagem…</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>.icc and .icm files</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B166" t="str">
-        <v>Ficheiros .icc e .icm</v>
+        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
       </c>
       <c r="C166" t="str">
-        <v>Arquivos .icc e .icm</v>
+        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Header</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B167" t="str">
-        <v>Cabeçalho</v>
+        <v>Imagem demasiado grande ({mp} MP; limite {max} MP).</v>
       </c>
       <c r="C167" t="str">
-        <v>Cabeçalho</v>
+        <v>Imagem grande demais ({mp} MP; limite {max} MP).</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Tags</v>
+        <v>Transform Image</v>
       </c>
       <c r="B168" t="str">
-        <v>Etiquetas</v>
+        <v>Transformar imagem</v>
       </c>
       <c r="C168" t="str">
-        <v>Tags</v>
+        <v>Transformar imagem</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Validation</v>
+        <v>Transforming…</v>
       </c>
       <c r="B169" t="str">
-        <v>Validação</v>
+        <v>A transformar…</v>
       </c>
       <c r="C169" t="str">
-        <v>Validação</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Analysis</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B170" t="str">
-        <v>Análise</v>
+        <v>Largue perfis para iniciar a cadeia</v>
       </c>
       <c r="C170" t="str">
-        <v>Análise</v>
+        <v>Solte perfis para iniciar a cadeia</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>removed</v>
       </c>
       <c r="B171" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>removido</v>
       </c>
       <c r="C171" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>removido</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Move earlier</v>
       </c>
       <c r="B172" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
+        <v>Mover antes</v>
       </c>
       <c r="C172" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
+        <v>Mover antes</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Move later</v>
       </c>
       <c r="B173" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Mover depois</v>
       </c>
       <c r="C173" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Mover depois</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Move up</v>
       </c>
       <c r="B174" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>Mover para cima</v>
       </c>
       <c r="C174" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>Mover para cima</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent</v>
+        <v>Move down</v>
       </c>
       <c r="B175" t="str">
-        <v>Intenção de renderização</v>
+        <v>Mover para baixo</v>
       </c>
       <c r="C175" t="str">
-        <v>Intenção de renderização</v>
+        <v>Mover para baixo</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>% ink</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B176" t="str">
-        <v>% tinta</v>
+        <v>Intenção de renderização (todas)</v>
       </c>
       <c r="C176" t="str">
-        <v>% tinta</v>
+        <v>Intenção de renderização (todas)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Perceptual</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B177" t="str">
-        <v>Perceptual</v>
+        <v>Intenção de renderização para esta transformação</v>
       </c>
       <c r="C177" t="str">
-        <v>Perceptual</v>
+        <v>Intenção de renderização para esta transformação</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B178" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>As transformações usam intenções de renderização diferentes</v>
       </c>
       <c r="C178" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>As transformações usam intenções de renderização diferentes</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Saturation</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B179" t="str">
-        <v>Saturação</v>
+        <v>Inverter direção da cadeia (inverte a transformação inicial e propaga-se por toda a cadeia)</v>
       </c>
       <c r="C179" t="str">
-        <v>Saturação</v>
+        <v>Inverter direção da cadeia (inverte a transformação inicial e se propaga por toda a cadeia)</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B180" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
       </c>
       <c r="C180" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Profile Statistics</v>
+        <v>Chain</v>
       </c>
       <c r="B181" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Cadeia</v>
       </c>
       <c r="C181" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Cadeia</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B182" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Não foi possível analisar a cadeia.</v>
       </c>
       <c r="C182" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Não foi possível analisar a cadeia.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B183" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
+        <v>A verificar cadeia…</v>
       </c>
       <c r="C183" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
+        <v>Verificando cadeia…</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Rendering intent</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B184" t="str">
-        <v>Intenção de renderização</v>
+        <v>A cadeia não liga ({detail}).</v>
       </c>
       <c r="C184" t="str">
-        <v>Intenção de renderização</v>
+        <v>A cadeia não conecta ({detail}).</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B185" t="str">
-        <v>Volume de gamute (ΔE³)</v>
+        <v>O perfil {n} não liga à etapa anterior ({detail}).</v>
       </c>
       <c r="C185" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>O perfil {n} não conecta com a etapa anterior ({detail}).</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B186" t="str">
-        <v>ΔE de percurso</v>
+        <v>Corrija a cadeia antes de processar imagens</v>
       </c>
       <c r="C186" t="str">
-        <v>ΔE de percurso</v>
+        <v>Corrija a cadeia antes de processar imagens</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Clear</v>
       </c>
       <c r="B187" t="str">
-        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
+        <v>Limpar</v>
       </c>
       <c r="C187" t="str">
-        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
+        <v>Limpar</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>mean</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B188" t="str">
-        <v>média</v>
+        <v>Criar DeviceLink</v>
       </c>
       <c r="C188" t="str">
-        <v>média</v>
+        <v>Criar DeviceLink</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>P90</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B189" t="str">
-        <v>P90</v>
+        <v>Nome do DeviceLink</v>
       </c>
       <c r="C189" t="str">
-        <v>P90</v>
+        <v>Nome do DeviceLink</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>max</v>
+        <v>Making…</v>
       </c>
       <c r="B190" t="str">
-        <v>máx.</v>
+        <v>A criar…</v>
       </c>
       <c r="C190" t="str">
-        <v>máx.</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Analysing…</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B191" t="str">
-        <v>A analisar…</v>
+        <v>Criado “{name}” — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C191" t="str">
-        <v>Analisando…</v>
+        <v>Criado “{name}” — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Analysis</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B192" t="str">
-        <v>Análise</v>
+        <v>Largue imagens {src} para converter para {dst} — os resultados são descarregados, nada é armazenado.</v>
       </c>
       <c r="C192" t="str">
-        <v>Análise</v>
+        <v>Solte imagens {src} para converter para {dst} — os resultados são baixados, nada é armazenado.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B193" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Crie uma cadeia para processar imagens</v>
       </c>
       <c r="C193" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Crie uma cadeia para processar imagens</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Plot</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B194" t="str">
-        <v>Gráfico</v>
+        <v>Esta cadeia não começa nem termina num espaço de cor de imagem</v>
       </c>
       <c r="C194" t="str">
-        <v>Gráfico</v>
+        <v>Esta cadeia não começa nem termina em um espaço de cor de imagem</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Raw Output</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B195" t="str">
-        <v>Saída em bruto</v>
+        <v>Imagem transformada guardada.</v>
       </c>
       <c r="C195" t="str">
-        <v>Saída bruta</v>
+        <v>Imagem transformada salva.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>XML</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B196" t="str">
-        <v>XML</v>
+        <v>Largue um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="C196" t="str">
-        <v>XML</v>
+        <v>Solte um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>JSON</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B197" t="str">
-        <v>JSON</v>
+        <v>Não foi possível ler esse ficheiro.</v>
       </c>
       <c r="C197" t="str">
-        <v>JSON</v>
+        <v>Não foi possível ler esse arquivo.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Curves</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B198" t="str">
-        <v>Curvas</v>
+        <v>Ficheiro de dados demasiado grande.</v>
       </c>
       <c r="C198" t="str">
-        <v>Curvas</v>
+        <v>Arquivo de dados grande demais.</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Input curves</v>
+        <v>Transform Data</v>
       </c>
       <c r="B199" t="str">
-        <v>Curvas de entrada</v>
+        <v>Transformar dados</v>
       </c>
       <c r="C199" t="str">
-        <v>Curvas de entrada</v>
+        <v>Transformar dados</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Output curves</v>
+        <v>Transforming…</v>
       </c>
       <c r="B200" t="str">
-        <v>Curvas de saída</v>
+        <v>A transformar…</v>
       </c>
       <c r="C200" t="str">
-        <v>Curvas de saída</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>CLUT image</v>
+        <v>Prefer</v>
       </c>
       <c r="B201" t="str">
-        <v>Imagem CLUT</v>
+        <v>Preferir</v>
       </c>
       <c r="C201" t="str">
-        <v>Imagem CLUT</v>
+        <v>Preferir</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Gamut image</v>
+        <v>Observer</v>
       </c>
       <c r="B202" t="str">
-        <v>Imagem de gamut</v>
+        <v>Observador</v>
       </c>
       <c r="C202" t="str">
-        <v>Imagem de gamut</v>
+        <v>Observador</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Chromaticity</v>
+        <v>Illuminant</v>
       </c>
       <c r="B203" t="str">
-        <v>Cromaticidade</v>
+        <v>Iluminante</v>
       </c>
       <c r="C203" t="str">
-        <v>Cromaticidade</v>
+        <v>Iluminante</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Scatter plot</v>
+        <v>Condition</v>
       </c>
       <c r="B204" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Condição</v>
       </c>
       <c r="C204" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Condição</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Tone response curve</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B205" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
       <c r="C205" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Curve table</v>
+        <v>median</v>
       </c>
       <c r="B206" t="str">
-        <v>Tabela da curva</v>
+        <v>mediana</v>
       </c>
       <c r="C206" t="str">
-        <v>Tabela da curva</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Tables</v>
+        <v>mean</v>
       </c>
       <c r="B207" t="str">
-        <v>Tabelas</v>
+        <v>média</v>
       </c>
       <c r="C207" t="str">
-        <v>Tabelas</v>
+        <v>média</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Data</v>
+        <v>patches</v>
       </c>
       <c r="B208" t="str">
-        <v>Dados</v>
+        <v>patches</v>
       </c>
       <c r="C208" t="str">
-        <v>Dados</v>
+        <v>patches</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Evaluate</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B209" t="str">
-        <v>Avaliar</v>
+        <v>{n} duplicados</v>
       </c>
       <c r="C209" t="str">
-        <v>Avaliar</v>
+        <v>{n} duplicados</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Loading…</v>
+        <v>Transform result</v>
       </c>
       <c r="B210" t="str">
-        <v>A carregar…</v>
+        <v>Resultado da transformação</v>
       </c>
       <c r="C210" t="str">
-        <v>Carregando…</v>
+        <v>Resultado da transformação</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Input</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B211" t="str">
-        <v>Entrada</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="C211" t="str">
-        <v>Entrada</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Output</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B212" t="str">
-        <v>Saída</v>
+        <v>A mostrar os primeiros {shown} de {total} — Guardar grava todos.</v>
       </c>
       <c r="C212" t="str">
-        <v>Saída</v>
+        <v>Mostrando os primeiros {shown} de {total} — Salvar grava todos.</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Floating point</v>
+        <v>Save as</v>
       </c>
       <c r="B213" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Guardar como</v>
       </c>
       <c r="C213" t="str">
-        <v>Ponto flutuante</v>
+        <v>Salvar como</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Grid point</v>
+        <v>Save</v>
       </c>
       <c r="B214" t="str">
-        <v>Ponto da grelha</v>
+        <v>Guardar</v>
       </c>
       <c r="C214" t="str">
-        <v>Ponto da grade</v>
+        <v>Salvar</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Normalized</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B215" t="str">
-        <v>Normalizado</v>
+        <v>Inverter transformação</v>
       </c>
       <c r="C215" t="str">
-        <v>Normalizado</v>
+        <v>Inverter transformação</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Human</v>
+        <v>Inverting…</v>
       </c>
       <c r="B216" t="str">
-        <v>Legível</v>
+        <v>A inverter…</v>
       </c>
       <c r="C216" t="str">
-        <v>Legível</v>
+        <v>Invertendo…</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Device → PCS</v>
+        <v>Invert</v>
       </c>
       <c r="B217" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Inverter</v>
       </c>
       <c r="C217" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Inverter</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>PCS → Device</v>
+        <v>last stage</v>
       </c>
       <c r="B218" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>última etapa</v>
       </c>
       <c r="C218" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>última etapa</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>No CLUT grid</v>
+        <v>first stage</v>
       </c>
       <c r="B219" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>primeira etapa</v>
       </c>
       <c r="C219" t="str">
-        <v>Sem grade CLUT</v>
+        <v>primeira etapa</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Loading…</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B220" t="str">
-        <v>A carregar…</v>
+        <v>Dados em {in} → procurar {out}</v>
       </c>
       <c r="C220" t="str">
-        <v>Carregando…</v>
+        <v>Dados em {in} → buscar {out}</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B221" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
       </c>
       <c r="C221" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Invalid profile URL:</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B222" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>O conjunto de dados deve estar em {in}; a procura inversa produz {out} mais um custo de invertibilidade por patch.</v>
       </c>
       <c r="C222" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>O conjunto de dados deve estar em {in}; a busca inversa produz {out} mais um custo de invertibilidade por patch.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B223" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>Custo ΔE</v>
       </c>
       <c r="C223" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>Custo ΔE</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B224" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>Esta imagem tem um perfil ICC incorporado.</v>
       </c>
       <c r="C224" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Esta imagem tem um perfil ICC incorporado.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B225" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Extrair e adicionar à cadeia</v>
       </c>
       <c r="C225" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Extrair e adicionar à cadeia</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Extracting…</v>
       </c>
       <c r="B226" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>A extrair…</v>
       </c>
       <c r="C226" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Extraindo…</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Dismiss</v>
       </c>
       <c r="B227" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Dispensar</v>
       </c>
       <c r="C227" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Dispensar</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Security</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B228" t="str">
-        <v>Segurança</v>
+        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro lugar na cadeia.</v>
       </c>
       <c r="C228" t="str">
-        <v>Segurança</v>
+        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro na cadeia.</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Conformance</v>
+        <v>Image output options</v>
       </c>
       <c r="B229" t="str">
-        <v>Conformidade</v>
+        <v>Opções de saída de imagem</v>
       </c>
       <c r="C229" t="str">
-        <v>Conformidade</v>
+        <v>Opções de saída de imagem</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Quality</v>
+        <v>Encoding</v>
       </c>
       <c r="B230" t="str">
-        <v>Qualidade</v>
+        <v>Codificação</v>
       </c>
       <c r="C230" t="str">
-        <v>Qualidade</v>
+        <v>Codificação</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>REPORT</v>
+        <v>Same as source</v>
       </c>
       <c r="B231" t="str">
-        <v>RELATÓRIO</v>
+        <v>Igual à origem</v>
       </c>
       <c r="C231" t="str">
-        <v>RELATÓRIO</v>
+        <v>Igual à origem</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>FAIL</v>
+        <v>8-bit</v>
       </c>
       <c r="B232" t="str">
-        <v>REPROVADO</v>
+        <v>8 bits</v>
       </c>
       <c r="C232" t="str">
-        <v>REPROVADO</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>checks</v>
+        <v>16-bit</v>
       </c>
       <c r="B233" t="str">
-        <v>verificações</v>
+        <v>16 bits</v>
       </c>
       <c r="C233" t="str">
-        <v>verificações</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B234" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Flutuante (32 bits)</v>
       </c>
       <c r="C234" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Flutuante (32 bits)</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Compression</v>
       </c>
       <c r="B235" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Compressão</v>
       </c>
       <c r="C235" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Compressão</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B236" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Nenhuma</v>
       </c>
       <c r="C236" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Nenhuma</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Powered by {lib}</v>
+        <v>Planar</v>
       </c>
       <c r="B237" t="str">
-        <v>Com {lib}</v>
+        <v>Planar</v>
       </c>
       <c r="C237" t="str">
-        <v>Com {lib}</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Subscribe</v>
+        <v>Composite</v>
       </c>
       <c r="B238" t="str">
-        <v>Subscrever</v>
+        <v>Composto</v>
       </c>
       <c r="C238" t="str">
-        <v>Inscrever-se</v>
+        <v>Composto</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Separated</v>
       </c>
       <c r="B239" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Separado</v>
       </c>
       <c r="C239" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Separado</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Get notified about new releases</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B240" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Interpolação CMM</v>
       </c>
       <c r="C240" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Interpolação CMM</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Close</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B241" t="str">
-        <v>Fechar</v>
+        <v>Tetraédrica</v>
       </c>
       <c r="C241" t="str">
-        <v>Fechar</v>
+        <v>Tetraédrica</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Linear</v>
       </c>
       <c r="B242" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Linear</v>
       </c>
       <c r="C242" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Linear</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Email address</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B243" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Incorporar ICC</v>
       </c>
       <c r="C243" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Incorporar ICC</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>you@example.com</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B244" t="str">
-        <v>voce@exemplo.com</v>
+        <v>A codificação, a compressão e o formato planar determinam o TIFF guardado. A saída RGB/Gray mantém-se em PNG, salvo se for definida uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado).</v>
       </c>
       <c r="C244" t="str">
-        <v>voce@exemplo.com</v>
+        <v>A codificação, a compressão e o formato planar determinam o TIFF salvo. A saída RGB/Gray permanece em PNG, a menos que uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado) seja definida.</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B245" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Montar TIFF espectral</v>
       </c>
       <c r="C245" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Montar TIFF espectral</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>(optional)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B246" t="str">
-        <v>(opcional)</v>
+        <v>Largue imagens espectrais de canal único pela ordem dos canais e depois monte-as num único TIFF multicanal.</v>
       </c>
       <c r="C246" t="str">
-        <v>(opcional)</v>
+        <v>Solte imagens espectrais de canal único na ordem dos canais e depois monte-as em um único TIFF multicanal.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B247" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Largue imagens espectrais aqui (ou clique para escolher)</v>
       </c>
       <c r="C247" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Solte imagens espectrais aqui (ou clique para escolher)</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>ch</v>
       </c>
       <c r="B248" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>can</v>
       </c>
       <c r="C248" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>can</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B249" t="str">
-        <v>Cancelar</v>
+        <v>Montar e guardar</v>
       </c>
       <c r="C249" t="str">
-        <v>Cancelar</v>
+        <v>Montar e salvar</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Subscribe</v>
+        <v>Assembling…</v>
       </c>
       <c r="B250" t="str">
-        <v>Subscrever</v>
+        <v>A montar…</v>
       </c>
       <c r="C250" t="str">
-        <v>Inscrever-se</v>
+        <v>Montando…</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B251" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Foram montados {n} canais.</v>
       </c>
       <c r="C251" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Foram montados {n} canais.</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B252" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
       </c>
       <c r="C252" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B253" t="str">
-        <v>Fechar</v>
+        <v>Cancelar</v>
       </c>
       <c r="C253" t="str">
-        <v>Fechar</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Privacy notice</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B254" t="str">
-        <v>Aviso de privacidade</v>
+        <v>{n} ficheiro(s) não carregados</v>
       </c>
       <c r="C254" t="str">
-        <v>Aviso de privacidade</v>
+        <v>{n} arquivo(s) não carregados</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B255" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
       </c>
       <c r="C255" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>OK</v>
       </c>
       <c r="B256" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>OK</v>
       </c>
       <c r="C256" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B257" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Largue um perfil ICC aqui</v>
       </c>
       <c r="C257" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Solte um perfil ICC aqui</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>or</v>
       </c>
       <c r="B258" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>ou</v>
       </c>
       <c r="C258" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Choose file</v>
       </c>
       <c r="B259" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Escolher ficheiro</v>
       </c>
       <c r="C259" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Escolher arquivo</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Error:</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B260" t="str">
-        <v>Erro:</v>
+        <v>Ficheiros .icc e .icm</v>
       </c>
       <c r="C260" t="str">
-        <v>Erro:</v>
+        <v>Arquivos .icc e .icm</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Convert to XML</v>
+        <v>Header</v>
       </c>
       <c r="B261" t="str">
-        <v>Converter para XML</v>
+        <v>Cabeçalho</v>
       </c>
       <c r="C261" t="str">
-        <v>Converter para XML</v>
+        <v>Cabeçalho</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Convert to JSON</v>
+        <v>Tags</v>
       </c>
       <c r="B262" t="str">
-        <v>Converter para JSON</v>
+        <v>Etiquetas</v>
       </c>
       <c r="C262" t="str">
-        <v>Converter para JSON</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Convert to ICC</v>
+        <v>Validation</v>
       </c>
       <c r="B263" t="str">
-        <v>Converter para ICC</v>
+        <v>Validação</v>
       </c>
       <c r="C263" t="str">
-        <v>Converter para ICC</v>
+        <v>Validação</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Converting to XML…</v>
+        <v>Analysis</v>
       </c>
       <c r="B264" t="str">
-        <v>A converter para XML…</v>
+        <v>Análise</v>
       </c>
       <c r="C264" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Converting to JSON…</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B265" t="str">
-        <v>A converter para JSON…</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
       <c r="C265" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Converting to ICC…</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B266" t="str">
-        <v>A converter para ICC…</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
       </c>
       <c r="C266" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Load ICC profile</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B267" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C267" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B268" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
       <c r="C268" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Profile ID</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B269" t="str">
-        <v>ID do perfil</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C269" t="str">
-        <v>ID do perfil</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>No tags found.</v>
+        <v>% ink</v>
       </c>
       <c r="B270" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>% tinta</v>
       </c>
       <c r="C270" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Tag Name</v>
+        <v>Perceptual</v>
       </c>
       <c r="B271" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Perceptual</v>
       </c>
       <c r="C271" t="str">
-        <v>Nome da tag</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>ID</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>ID</v>
+        <v>Colorimétrico relativo</v>
       </c>
       <c r="C272" t="str">
-        <v>ID</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Offset</v>
+        <v>Saturation</v>
       </c>
       <c r="B273" t="str">
-        <v>Deslocamento</v>
+        <v>Saturação</v>
       </c>
       <c r="C273" t="str">
-        <v>Deslocamento</v>
+        <v>Saturação</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Size</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B274" t="str">
-        <v>Tamanho</v>
+        <v>Colorimétrico absoluto</v>
       </c>
       <c r="C274" t="str">
-        <v>Tamanho</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Pad</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B275" t="str">
-        <v>Preenchimento</v>
+        <v>Estatísticas do perfil</v>
       </c>
       <c r="C275" t="str">
-        <v>Preenchimento</v>
+        <v>Estatísticas do perfil</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Bytes changed since load</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B276" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
       <c r="C276" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Type</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B277" t="str">
-        <v>Tipo</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
       </c>
       <c r="C277" t="str">
-        <v>Tipo</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Array of {type}</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B278" t="str">
-        <v>Vetor de {type}</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C278" t="str">
-        <v>Array de {type}</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>(No content)</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B279" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Volume de gamute (ΔE³)</v>
       </c>
       <c r="C279" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>bytes</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B280" t="str">
-        <v>bytes</v>
+        <v>ΔE de percurso</v>
       </c>
       <c r="C280" t="str">
-        <v>bytes</v>
+        <v>ΔE de percurso</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Loading full description…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B281" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
       </c>
       <c r="C281" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Could not load full description:</v>
+        <v>mean</v>
       </c>
       <c r="B282" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>média</v>
       </c>
       <c r="C282" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>média</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>P90</v>
       </c>
       <c r="B283" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>P90</v>
       </c>
       <c r="C283" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>max</v>
       </c>
       <c r="B284" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>máx.</v>
       </c>
       <c r="C284" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>No validation output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B285" t="str">
-        <v>Sem saída de validação</v>
+        <v>A analisar…</v>
       </c>
       <c r="C285" t="str">
-        <v>Sem saída de validação</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Profile is valid</v>
+        <v>Analysis</v>
       </c>
       <c r="B286" t="str">
-        <v>O perfil é válido</v>
+        <v>Análise</v>
       </c>
       <c r="C286" t="str">
-        <v>O perfil é válido</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B287" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C287" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Plot</v>
       </c>
       <c r="B288" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Gráfico</v>
       </c>
       <c r="C288" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Critical validation error</v>
+        <v>Raw Output</v>
       </c>
       <c r="B289" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C289" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Unknown validation status</v>
+        <v>XML</v>
       </c>
       <c r="B290" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>XML</v>
       </c>
       <c r="C290" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>JSON</v>
       </c>
       <c r="B291" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>JSON</v>
       </c>
       <c r="C291" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Curves</v>
       </c>
       <c r="B292" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Curvas</v>
       </c>
       <c r="C292" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Valid</v>
+        <v>Input curves</v>
       </c>
       <c r="B293" t="str">
-        <v>Válido</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C293" t="str">
-        <v>Válido</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Warning</v>
+        <v>Output curves</v>
       </c>
       <c r="B294" t="str">
-        <v>Aviso</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C294" t="str">
-        <v>Aviso</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Error</v>
+        <v>CLUT image</v>
       </c>
       <c r="B295" t="str">
-        <v>Erro</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C295" t="str">
-        <v>Erro</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Unknown</v>
+        <v>Gamut image</v>
       </c>
       <c r="B296" t="str">
-        <v>Desconhecido</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C296" t="str">
-        <v>Desconhecido</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Pass</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B297" t="str">
-        <v>Aprovado</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C297" t="str">
-        <v>Aprovado</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Fail</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B298" t="str">
-        <v>Reprovado</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C298" t="str">
-        <v>Reprovado</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>View in context</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B299" t="str">
-        <v>Ver no contexto</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C299" t="str">
-        <v>Ver no contexto</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Validation detail</v>
+        <v>Curve table</v>
       </c>
       <c r="B300" t="str">
-        <v>Detalhe de validação</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C300" t="str">
-        <v>Detalhe de validação</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Triggered by</v>
+        <v>Tables</v>
       </c>
       <c r="B301" t="str">
-        <v>Acionado por</v>
+        <v>Tabelas</v>
       </c>
       <c r="C301" t="str">
-        <v>Acionado por</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Field</v>
+        <v>Data</v>
       </c>
       <c r="B302" t="str">
-        <v>Campo</v>
+        <v>Dados</v>
       </c>
       <c r="C302" t="str">
-        <v>Campo</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Current value</v>
+        <v>Evaluate</v>
       </c>
       <c r="B303" t="str">
-        <v>Valor atual</v>
+        <v>Avaliar</v>
       </c>
       <c r="C303" t="str">
-        <v>Valor atual</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Required: 0</v>
+        <v>Loading…</v>
       </c>
       <c r="B304" t="str">
-        <v>Obrigatório: 0</v>
+        <v>A carregar…</v>
       </c>
       <c r="C304" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Expected: {value}</v>
+        <v>Input</v>
       </c>
       <c r="B305" t="str">
-        <v>Esperado: {value}</v>
+        <v>Entrada</v>
       </c>
       <c r="C305" t="str">
-        <v>Esperado: {value}</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Invalid</v>
+        <v>Output</v>
       </c>
       <c r="B306" t="str">
-        <v>Inválido</v>
+        <v>Saída</v>
       </c>
       <c r="C306" t="str">
-        <v>Inválido</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Floating point</v>
       </c>
       <c r="B307" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C307" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Close</v>
+        <v>Grid point</v>
       </c>
       <c r="B308" t="str">
-        <v>Fechar</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C308" t="str">
-        <v>Fechar</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Loading XML editor…</v>
+        <v>Normalized</v>
       </c>
       <c r="B309" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Normalizado</v>
       </c>
       <c r="C309" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Human</v>
       </c>
       <c r="B310" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Legível</v>
       </c>
       <c r="C310" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B311" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C311" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B312" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C312" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>● unsaved XML edits</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B313" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C313" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading…</v>
       </c>
       <c r="B314" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>A carregar…</v>
       </c>
       <c r="C314" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B315" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C315" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B316" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C316" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>indent</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B317" t="str">
-        <v>indentação</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C317" t="str">
-        <v>indentação</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>sort keys</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B318" t="str">
-        <v>ordenar chaves</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C318" t="str">
-        <v>ordenar chaves</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
+        <v>Loading Profile Assessment WG report…</v>
+      </c>
+      <c r="B319" t="str">
+        <v>A carregar o relatório Profile Assessment WG…</v>
+      </c>
+      <c r="C319" t="str">
+        <v>Carregando o relatório Profile Assessment WG…</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>Running Profile Assessment WG checks…</v>
+      </c>
+      <c r="B320" t="str">
+        <v>A executar as verificações Profile Assessment WG…</v>
+      </c>
+      <c r="C320" t="str">
+        <v>Executando as verificações Profile Assessment WG…</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>Profile Assessment WG Report</v>
+      </c>
+      <c r="B321" t="str">
+        <v>Relatório Profile Assessment WG</v>
+      </c>
+      <c r="C321" t="str">
+        <v>Relatório Profile Assessment WG</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>Security</v>
+      </c>
+      <c r="B322" t="str">
+        <v>Segurança</v>
+      </c>
+      <c r="C322" t="str">
+        <v>Segurança</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>Conformance</v>
+      </c>
+      <c r="B323" t="str">
+        <v>Conformidade</v>
+      </c>
+      <c r="C323" t="str">
+        <v>Conformidade</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>Quality</v>
+      </c>
+      <c r="B324" t="str">
+        <v>Qualidade</v>
+      </c>
+      <c r="C324" t="str">
+        <v>Qualidade</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>REPORT</v>
+      </c>
+      <c r="B325" t="str">
+        <v>RELATÓRIO</v>
+      </c>
+      <c r="C325" t="str">
+        <v>RELATÓRIO</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="B326" t="str">
+        <v>REPROVADO</v>
+      </c>
+      <c r="C326" t="str">
+        <v>REPROVADO</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>checks</v>
+      </c>
+      <c r="B327" t="str">
+        <v>verificações</v>
+      </c>
+      <c r="C327" t="str">
+        <v>verificações</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+      </c>
+      <c r="B328" t="str">
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+      </c>
+      <c r="C328" t="str">
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>ICC Profile Tool · powered by IccProfLib</v>
+      </c>
+      <c r="B329" t="str">
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+      </c>
+      <c r="C329" t="str">
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>ICC Profile Tool</v>
+      </c>
+      <c r="B330" t="str">
+        <v>Ferramenta de perfis ICC</v>
+      </c>
+      <c r="C330" t="str">
+        <v>Ferramenta de perfis ICC</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>Powered by {lib}</v>
+      </c>
+      <c r="B331" t="str">
+        <v>Com {lib}</v>
+      </c>
+      <c r="C331" t="str">
+        <v>Com {lib}</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B332" t="str">
+        <v>Subscrever</v>
+      </c>
+      <c r="C332" t="str">
+        <v>Inscrever-se</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>Get notified about new profiletool releases</v>
+      </c>
+      <c r="B333" t="str">
+        <v>Receber notificações sobre novas versões do profiletool</v>
+      </c>
+      <c r="C333" t="str">
+        <v>Receber notificações sobre novas versões do profiletool</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>Get notified about new releases</v>
+      </c>
+      <c r="B334" t="str">
+        <v>Receber notificações sobre novas versões</v>
+      </c>
+      <c r="C334" t="str">
+        <v>Receber notificações sobre novas versões</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B335" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C335" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+      </c>
+      <c r="B336" t="str">
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+      </c>
+      <c r="C336" t="str">
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>Email address</v>
+      </c>
+      <c r="B337" t="str">
+        <v>Endereço de e-mail</v>
+      </c>
+      <c r="C337" t="str">
+        <v>Endereço de e-mail</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>you@example.com</v>
+      </c>
+      <c r="B338" t="str">
+        <v>voce@exemplo.com</v>
+      </c>
+      <c r="C338" t="str">
+        <v>voce@exemplo.com</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>How will you use profiletool?</v>
+      </c>
+      <c r="B339" t="str">
+        <v>Como vai utilizar o profiletool?</v>
+      </c>
+      <c r="C339" t="str">
+        <v>Como você vai usar o profiletool?</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>(optional)</v>
+      </c>
+      <c r="B340" t="str">
+        <v>(opcional)</v>
+      </c>
+      <c r="C340" t="str">
+        <v>(opcional)</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>e.g. evaluating ICC profiles for press calibration</v>
+      </c>
+      <c r="B341" t="str">
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+      </c>
+      <c r="C341" t="str">
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+      </c>
+      <c r="B342" t="str">
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+      </c>
+      <c r="C342" t="str">
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B343" t="str">
+        <v>Cancelar</v>
+      </c>
+      <c r="C343" t="str">
+        <v>Cancelar</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>Subscribe</v>
+      </c>
+      <c r="B344" t="str">
+        <v>Subscrever</v>
+      </c>
+      <c r="C344" t="str">
+        <v>Inscrever-se</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>Thanks — we’ll be in touch.</v>
+      </c>
+      <c r="B345" t="str">
+        <v>Obrigado — entraremos em contacto.</v>
+      </c>
+      <c r="C345" t="str">
+        <v>Obrigado — entraremos em contato.</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+      </c>
+      <c r="B346" t="str">
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+      </c>
+      <c r="C346" t="str">
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B347" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C347" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>Privacy notice</v>
+      </c>
+      <c r="B348" t="str">
+        <v>Aviso de privacidade</v>
+      </c>
+      <c r="C348" t="str">
+        <v>Aviso de privacidade</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>Please enter a valid email address.</v>
+      </c>
+      <c r="B349" t="str">
+        <v>Introduza um endereço de e-mail válido.</v>
+      </c>
+      <c r="C349" t="str">
+        <v>Insira um endereço de e-mail válido.</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>Too many requests. Please try again later.</v>
+      </c>
+      <c r="B350" t="str">
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+      </c>
+      <c r="C350" t="str">
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>Please check the form and try again.</v>
+      </c>
+      <c r="B351" t="str">
+        <v>Verifique o formulário e tente novamente.</v>
+      </c>
+      <c r="C351" t="str">
+        <v>Verifique o formulário e tente novamente.</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>Could not send your request. Please try again.</v>
+      </c>
+      <c r="B352" t="str">
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+      </c>
+      <c r="C352" t="str">
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>Network error. Please try again.</v>
+      </c>
+      <c r="B353" t="str">
+        <v>Erro de rede. Tente novamente.</v>
+      </c>
+      <c r="C353" t="str">
+        <v>Erro de rede. Tente novamente.</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>Error:</v>
+      </c>
+      <c r="B354" t="str">
+        <v>Erro:</v>
+      </c>
+      <c r="C354" t="str">
+        <v>Erro:</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>Convert to XML</v>
+      </c>
+      <c r="B355" t="str">
+        <v>Converter para XML</v>
+      </c>
+      <c r="C355" t="str">
+        <v>Converter para XML</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>Convert to JSON</v>
+      </c>
+      <c r="B356" t="str">
+        <v>Converter para JSON</v>
+      </c>
+      <c r="C356" t="str">
+        <v>Converter para JSON</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>Convert to ICC</v>
+      </c>
+      <c r="B357" t="str">
+        <v>Converter para ICC</v>
+      </c>
+      <c r="C357" t="str">
+        <v>Converter para ICC</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>Converting to XML…</v>
+      </c>
+      <c r="B358" t="str">
+        <v>A converter para XML…</v>
+      </c>
+      <c r="C358" t="str">
+        <v>Convertendo para XML…</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>Converting to JSON…</v>
+      </c>
+      <c r="B359" t="str">
+        <v>A converter para JSON…</v>
+      </c>
+      <c r="C359" t="str">
+        <v>Convertendo para JSON…</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>Converting to ICC…</v>
+      </c>
+      <c r="B360" t="str">
+        <v>A converter para ICC…</v>
+      </c>
+      <c r="C360" t="str">
+        <v>Convertendo para ICC…</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>Load ICC profile</v>
+      </c>
+      <c r="B361" t="str">
+        <v>Carregar perfil ICC</v>
+      </c>
+      <c r="C361" t="str">
+        <v>Carregar perfil ICC</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>Drop zone for ICC profile files</v>
+      </c>
+      <c r="B362" t="str">
+        <v>Zona de largada para ficheiros de perfil ICC</v>
+      </c>
+      <c r="C362" t="str">
+        <v>Área de soltar para arquivos de perfil ICC</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>Profile ID</v>
+      </c>
+      <c r="B363" t="str">
+        <v>ID do perfil</v>
+      </c>
+      <c r="C363" t="str">
+        <v>ID do perfil</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>No tags found.</v>
+      </c>
+      <c r="B364" t="str">
+        <v>Nenhuma etiqueta encontrada.</v>
+      </c>
+      <c r="C364" t="str">
+        <v>Nenhuma tag encontrada.</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>Tag Name</v>
+      </c>
+      <c r="B365" t="str">
+        <v>Nome da etiqueta</v>
+      </c>
+      <c r="C365" t="str">
+        <v>Nome da tag</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B366" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C366" t="str">
+        <v>ID</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>Offset</v>
+      </c>
+      <c r="B367" t="str">
+        <v>Deslocamento</v>
+      </c>
+      <c r="C367" t="str">
+        <v>Deslocamento</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>Size</v>
+      </c>
+      <c r="B368" t="str">
+        <v>Tamanho</v>
+      </c>
+      <c r="C368" t="str">
+        <v>Tamanho</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>Pad</v>
+      </c>
+      <c r="B369" t="str">
+        <v>Preenchimento</v>
+      </c>
+      <c r="C369" t="str">
+        <v>Preenchimento</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>Bytes changed since load</v>
+      </c>
+      <c r="B370" t="str">
+        <v>Bytes alterados desde o carregamento</v>
+      </c>
+      <c r="C370" t="str">
+        <v>Bytes alterados desde o carregamento</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>Type</v>
+      </c>
+      <c r="B371" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C371" t="str">
+        <v>Tipo</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>Array of {type}</v>
+      </c>
+      <c r="B372" t="str">
+        <v>Vetor de {type}</v>
+      </c>
+      <c r="C372" t="str">
+        <v>Array de {type}</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>(No content)</v>
+      </c>
+      <c r="B373" t="str">
+        <v>(Sem conteúdo)</v>
+      </c>
+      <c r="C373" t="str">
+        <v>(Sem conteúdo)</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="B374" t="str">
+        <v>bytes</v>
+      </c>
+      <c r="C374" t="str">
+        <v>bytes</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>Loading full description…</v>
+      </c>
+      <c r="B375" t="str">
+        <v>A carregar descrição completa…</v>
+      </c>
+      <c r="C375" t="str">
+        <v>Carregando descrição completa…</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>Could not load full description:</v>
+      </c>
+      <c r="B376" t="str">
+        <v>Não foi possível carregar a descrição completa:</v>
+      </c>
+      <c r="C376" t="str">
+        <v>Não foi possível carregar a descrição completa:</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+      </c>
+      <c r="B377" t="str">
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+      </c>
+      <c r="C377" t="str">
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+      </c>
+      <c r="B378" t="str">
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+      </c>
+      <c r="C378" t="str">
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B379" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+      <c r="C379" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B380" t="str">
+        <v>O perfil é válido</v>
+      </c>
+      <c r="C380" t="str">
+        <v>O perfil é válido</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B381" t="str">
+        <v>O perfil tem avisos</v>
+      </c>
+      <c r="C381" t="str">
+        <v>O perfil tem avisos</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B382" t="str">
+        <v>O perfil não é conforme</v>
+      </c>
+      <c r="C382" t="str">
+        <v>O perfil não está em conformidade</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B383" t="str">
+        <v>Erro de validação crítico</v>
+      </c>
+      <c r="C383" t="str">
+        <v>Erro de validação crítico</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B384" t="str">
+        <v>Estado de validação desconhecido</v>
+      </c>
+      <c r="C384" t="str">
+        <v>Status de validação desconhecido</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B385" t="str">
+        <v>Crítico — apresentado apenas para inspeção</v>
+      </c>
+      <c r="C385" t="str">
+        <v>Crítico — exibido apenas para inspeção</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B386" t="str">
+        <v>Sem avisos nem erros encontrados.</v>
+      </c>
+      <c r="C386" t="str">
+        <v>Nenhum aviso ou erro encontrado.</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B387" t="str">
+        <v>Válido</v>
+      </c>
+      <c r="C387" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B388" t="str">
+        <v>Aviso</v>
+      </c>
+      <c r="C388" t="str">
+        <v>Aviso</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B389" t="str">
+        <v>Erro</v>
+      </c>
+      <c r="C389" t="str">
+        <v>Erro</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B390" t="str">
+        <v>Desconhecido</v>
+      </c>
+      <c r="C390" t="str">
+        <v>Desconhecido</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B391" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="C391" t="str">
+        <v>Aprovado</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B392" t="str">
+        <v>Reprovado</v>
+      </c>
+      <c r="C392" t="str">
+        <v>Reprovado</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B393" t="str">
+        <v>Ver no contexto</v>
+      </c>
+      <c r="C393" t="str">
+        <v>Ver no contexto</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B394" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+      <c r="C394" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B395" t="str">
+        <v>Acionado por</v>
+      </c>
+      <c r="C395" t="str">
+        <v>Acionado por</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B396" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C396" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B397" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C397" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B398" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C398" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B399" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C399" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B400" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C400" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B401" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C401" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B402" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C402" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B403" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C403" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B404" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C404" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B405" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C405" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B406" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C406" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B407" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C407" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B408" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C408" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B409" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C409" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B410" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C410" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B411" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C411" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B412" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C412" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B319" t="str">
+      <c r="B413" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C319" t="str">
+      <c r="C413" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C319"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C413"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C413"/>
+  <dimension ref="A1:C410"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -1297,3668 +1297,3635 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Upload an ICC profile to validate it against the</v>
+        <v>Based on</v>
       </c>
       <c r="B82" t="str">
-        <v>Carregue um perfil ICC para o validar segundo a especificação</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
       <c r="C82" t="str">
-        <v>Envie um perfil ICC para validá-lo conforme a especificação</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>specification using the</v>
+        <v>demo implementation</v>
       </c>
       <c r="B83" t="str">
-        <v>através da implementação de demonstração</v>
+        <v/>
       </c>
       <c r="C83" t="str">
-        <v>usando a implementação de demonstração</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation.</v>
+        <v>Validating…</v>
       </c>
       <c r="B84" t="str">
-        <v>.</v>
+        <v>A validar…</v>
       </c>
       <c r="C84" t="str">
-        <v>.</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Based on</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B85" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Guardar perfil ICC</v>
       </c>
       <c r="C85" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Salvar perfil ICC</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>demo implementation</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B86" t="str">
-        <v/>
+        <v>● Modificado — não guardado</v>
       </c>
       <c r="C86" t="str">
-        <v/>
+        <v>● Modificado — não salvo</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Validating…</v>
+        <v>Profiles</v>
       </c>
       <c r="B87" t="str">
-        <v>A validar…</v>
+        <v>Perfis</v>
       </c>
       <c r="C87" t="str">
-        <v>Validando…</v>
+        <v>Perfis</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Save ICC profile</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B88" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>Mostrar o conjunto de perfis</v>
       </c>
       <c r="C88" t="str">
-        <v>Salvar perfil ICC</v>
+        <v>Mostrar o conjunto de perfis</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Collapse</v>
       </c>
       <c r="B89" t="str">
-        <v>● Modificado — não guardado</v>
+        <v>Recolher</v>
       </c>
       <c r="C89" t="str">
-        <v>● Modificado — não salvo</v>
+        <v>Recolher</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Profiles</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B90" t="str">
-        <v>Perfis</v>
+        <v>Carregar perfis</v>
       </c>
       <c r="C90" t="str">
-        <v>Perfis</v>
+        <v>Carregar perfis</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Show profile pool</v>
+        <v>Remove</v>
       </c>
       <c r="B91" t="str">
-        <v>Mostrar o conjunto de perfis</v>
+        <v>Remover</v>
       </c>
       <c r="C91" t="str">
-        <v>Mostrar o conjunto de perfis</v>
+        <v>Remover</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Collapse</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B92" t="str">
-        <v>Recolher</v>
+        <v>Largue perfis ICC aqui</v>
       </c>
       <c r="C92" t="str">
-        <v>Recolher</v>
+        <v>Solte perfis ICC aqui</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Load Profiles</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B93" t="str">
-        <v>Carregar perfis</v>
+        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o respetivo perfil incorporado — os ficheiros permanecem no seu dispositivo.</v>
       </c>
       <c r="C93" t="str">
-        <v>Carregar perfis</v>
+        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o perfil incorporado — os arquivos permanecem no seu dispositivo.</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Remove</v>
+        <v>New from .cube</v>
       </c>
       <c r="B94" t="str">
-        <v>Remover</v>
+        <v>Novo a partir de .cube</v>
       </c>
       <c r="C94" t="str">
-        <v>Remover</v>
+        <v>Novo a partir de .cube</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Sort by name</v>
       </c>
       <c r="B95" t="str">
-        <v>Largue perfis ICC aqui</v>
+        <v>Ordenar por nome</v>
       </c>
       <c r="C95" t="str">
-        <v>Solte perfis ICC aqui</v>
+        <v>Ordenar por nome</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>A–Z</v>
       </c>
       <c r="B96" t="str">
-        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o respetivo perfil incorporado — os ficheiros permanecem no seu dispositivo.</v>
+        <v>A–Z</v>
       </c>
       <c r="C96" t="str">
-        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o perfil incorporado — os arquivos permanecem no seu dispositivo.</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New from .cube</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B97" t="str">
-        <v>Novo a partir de .cube</v>
+        <v>Novo perfil a partir de .cube</v>
       </c>
       <c r="C97" t="str">
-        <v>Novo a partir de .cube</v>
+        <v>Novo perfil a partir de .cube</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Sort by name</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B98" t="str">
-        <v>Ordenar por nome</v>
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e transferido.</v>
       </c>
       <c r="C98" t="str">
-        <v>Ordenar por nome</v>
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e baixado.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>A–Z</v>
+        <v>Choose .cube file</v>
       </c>
       <c r="B99" t="str">
-        <v>A–Z</v>
+        <v>Escolher ficheiro .cube</v>
       </c>
       <c r="C99" t="str">
-        <v>A–Z</v>
+        <v>Escolher arquivo .cube</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>New profile from .cube</v>
+        <v>or drop it here, or paste below</v>
       </c>
       <c r="B100" t="str">
-        <v>Novo perfil a partir de .cube</v>
+        <v>ou largue-o aqui, ou cole abaixo</v>
       </c>
       <c r="C100" t="str">
-        <v>Novo perfil a partir de .cube</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
-      </c>
-      <c r="B101" t="str">
-        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e transferido.</v>
-      </c>
-      <c r="C101" t="str">
-        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e baixado.</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Choose .cube file</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Escolher ficheiro .cube</v>
-      </c>
-      <c r="C102" t="str">
-        <v>Escolher arquivo .cube</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>or drop it here, or paste below</v>
-      </c>
-      <c r="B103" t="str">
-        <v>ou largue-o aqui, ou cole abaixo</v>
-      </c>
-      <c r="C103" t="str">
         <v>ou solte-o aqui, ou cole abaixo</v>
       </c>
     </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104" t="str" xml:space="preserve">
+    <row r="101" xml:space="preserve">
+      <c r="A101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B104" t="str" xml:space="preserve">
+      <c r="B101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="C104" t="str" xml:space="preserve">
+      <c r="C101" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Cancel</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Cancelar</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Cancelar</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Create DeviceLink</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Criar DeviceLink</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Criar DeviceLink</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Creating…</v>
+      </c>
+      <c r="B104" t="str">
+        <v>A criar…</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Criando…</v>
+      </c>
+    </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Cancel</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B105" t="str">
-        <v>Cancelar</v>
+        <v>Não foi possível ler esse ficheiro.</v>
       </c>
       <c r="C105" t="str">
-        <v>Cancelar</v>
+        <v>Não foi possível ler esse arquivo.</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Create DeviceLink</v>
+        <v>Profile</v>
       </c>
       <c r="B106" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Perfil</v>
       </c>
       <c r="C106" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Creating…</v>
+        <v>Compare</v>
       </c>
       <c r="B107" t="str">
-        <v>A criar…</v>
+        <v>Comparar</v>
       </c>
       <c r="C107" t="str">
-        <v>Criando…</v>
+        <v>Comparar</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Could not read that file.</v>
+        <v>Combine</v>
       </c>
       <c r="B108" t="str">
-        <v>Não foi possível ler esse ficheiro.</v>
+        <v>Ligar</v>
       </c>
       <c r="C108" t="str">
-        <v>Não foi possível ler esse arquivo.</v>
+        <v>Vincular</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Profile</v>
+        <v>Spectral</v>
       </c>
       <c r="B109" t="str">
-        <v>Perfil</v>
+        <v>Espectral</v>
       </c>
       <c r="C109" t="str">
-        <v>Perfil</v>
+        <v>Espectral</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Compare</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B110" t="str">
-        <v>Comparar</v>
+        <v>Arraste perfis do conjunto para este separador</v>
       </c>
       <c r="C110" t="str">
-        <v>Comparar</v>
+        <v>Arraste perfis do conjunto para esta aba</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Combine</v>
+        <v>Remove</v>
       </c>
       <c r="B111" t="str">
-        <v>Ligar</v>
+        <v>Remover</v>
       </c>
       <c r="C111" t="str">
-        <v>Vincular</v>
+        <v>Remover</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Spectral</v>
+        <v>No profile selected</v>
       </c>
       <c r="B112" t="str">
-        <v>Espectral</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
       <c r="C112" t="str">
-        <v>Espectral</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B113" t="str">
-        <v>Arraste perfis do conjunto para este separador</v>
+        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
       </c>
       <c r="C113" t="str">
-        <v>Arraste perfis do conjunto para esta aba</v>
+        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Remove</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B114" t="str">
-        <v>Remover</v>
+        <v>Ainda nada para comparar</v>
       </c>
       <c r="C114" t="str">
-        <v>Remover</v>
+        <v>Ainda nada para comparar</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>No profile selected</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B115" t="str">
-        <v>Nenhum perfil selecionado</v>
+        <v>Arraste um ou mais perfis para o separador Comparar.</v>
       </c>
       <c r="C115" t="str">
-        <v>Nenhum perfil selecionado</v>
+        <v>Arraste um ou mais perfis para a aba Comparar.</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B116" t="str">
-        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
+        <v>Comparação de gamut</v>
       </c>
       <c r="C116" t="str">
-        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
+        <v>Comparação de gamut</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Nothing to compare yet</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B117" t="str">
-        <v>Ainda nada para comparar</v>
+        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
       <c r="C117" t="str">
-        <v>Ainda nada para comparar</v>
+        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B118" t="str">
-        <v>Arraste um ou mais perfis para o separador Comparar.</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C118" t="str">
-        <v>Arraste um ou mais perfis para a aba Comparar.</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Gamut comparison</v>
+        <v>Shell</v>
       </c>
       <c r="B119" t="str">
-        <v>Comparação de gamut</v>
+        <v>Invólucro</v>
       </c>
       <c r="C119" t="str">
-        <v>Comparação de gamut</v>
+        <v>Invólucro</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Wireframe</v>
       </c>
       <c r="B120" t="str">
-        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
+        <v>Malha de arame</v>
       </c>
       <c r="C120" t="str">
-        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
+        <v>Malha de arame</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Rendering intent</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B121" t="str">
-        <v>Intenção de renderização</v>
+        <v>Números dos eixos</v>
       </c>
       <c r="C121" t="str">
-        <v>Intenção de renderização</v>
+        <v>Números dos eixos</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Shell</v>
+        <v>Opacity</v>
       </c>
       <c r="B122" t="str">
-        <v>Invólucro</v>
+        <v>Opacidade</v>
       </c>
       <c r="C122" t="str">
-        <v>Invólucro</v>
+        <v>Opacidade</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Wireframe</v>
+        <v>Colour</v>
       </c>
       <c r="B123" t="str">
-        <v>Malha de arame</v>
+        <v>Cor</v>
       </c>
       <c r="C123" t="str">
-        <v>Malha de arame</v>
+        <v>Cor</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Axis numbers</v>
+        <v>Solid</v>
       </c>
       <c r="B124" t="str">
-        <v>Números dos eixos</v>
+        <v>Sólido</v>
       </c>
       <c r="C124" t="str">
-        <v>Números dos eixos</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Opacity</v>
+        <v>By value</v>
       </c>
       <c r="B125" t="str">
-        <v>Opacidade</v>
+        <v>Por valor</v>
       </c>
       <c r="C125" t="str">
-        <v>Opacidade</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Colour</v>
+        <v>By hue</v>
       </c>
       <c r="B126" t="str">
-        <v>Cor</v>
+        <v>Por matiz</v>
       </c>
       <c r="C126" t="str">
-        <v>Cor</v>
+        <v>Por matiz</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Solid</v>
+        <v>Rotation</v>
       </c>
       <c r="B127" t="str">
-        <v>Sólido</v>
+        <v>Rotação</v>
       </c>
       <c r="C127" t="str">
-        <v>Sólido</v>
+        <v>Rotação</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>By value</v>
+        <v>Turntable</v>
       </c>
       <c r="B128" t="str">
-        <v>Por valor</v>
+        <v>Prato giratório</v>
       </c>
       <c r="C128" t="str">
-        <v>Por valor</v>
+        <v>Prato giratório</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>By hue</v>
+        <v>Orbit</v>
       </c>
       <c r="B129" t="str">
-        <v>Por matiz</v>
+        <v>Órbita</v>
       </c>
       <c r="C129" t="str">
-        <v>Por matiz</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Rotation</v>
+        <v>Drag speed</v>
       </c>
       <c r="B130" t="str">
-        <v>Rotação</v>
+        <v>Velocidade de arrasto</v>
       </c>
       <c r="C130" t="str">
-        <v>Rotação</v>
+        <v>Velocidade de arrasto</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Turntable</v>
+        <v>Roll</v>
       </c>
       <c r="B131" t="str">
-        <v>Prato giratório</v>
+        <v>Rolamento</v>
       </c>
       <c r="C131" t="str">
-        <v>Prato giratório</v>
+        <v>Rolagem</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Orbit</v>
+        <v>Roll speed</v>
       </c>
       <c r="B132" t="str">
-        <v>Órbita</v>
+        <v>Velocidade de rolamento</v>
       </c>
       <c r="C132" t="str">
-        <v>Órbita</v>
+        <v>Velocidade de rolagem</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Drag speed</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B133" t="str">
-        <v>Velocidade de arrasto</v>
+        <v>A construir o gamut…</v>
       </c>
       <c r="C133" t="str">
-        <v>Velocidade de arrasto</v>
+        <v>Construindo o gamut…</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Roll</v>
+        <v>no gamut</v>
       </c>
       <c r="B134" t="str">
-        <v>Rolamento</v>
+        <v>sem gamut</v>
       </c>
       <c r="C134" t="str">
-        <v>Rolagem</v>
+        <v>sem gamut</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Roll speed</v>
+        <v>Show / hide</v>
       </c>
       <c r="B135" t="str">
-        <v>Velocidade de rolamento</v>
+        <v>Mostrar / ocultar</v>
       </c>
       <c r="C135" t="str">
-        <v>Velocidade de rolagem</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Building gamut…</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B136" t="str">
-        <v>A construir o gamut…</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
       <c r="C136" t="str">
-        <v>Construindo o gamut…</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>no gamut</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B137" t="str">
-        <v>sem gamut</v>
+        <v>Corte de gamut 2D</v>
       </c>
       <c r="C137" t="str">
-        <v>sem gamut</v>
+        <v>Corte de gamut 2D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Show / hide</v>
+        <v>Plane</v>
       </c>
       <c r="B138" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>Plano</v>
       </c>
       <c r="C138" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>3-D gamut shell</v>
+        <v>L*</v>
       </c>
       <c r="B139" t="str">
-        <v>Invólucro de gamut 3D</v>
+        <v>L*</v>
       </c>
       <c r="C139" t="str">
-        <v>Invólucro de gamut 3D</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>2-D gamut slice</v>
+        <v>a*</v>
       </c>
       <c r="B140" t="str">
-        <v>Corte de gamut 2D</v>
+        <v>a*</v>
       </c>
       <c r="C140" t="str">
-        <v>Corte de gamut 2D</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Plane</v>
+        <v>b*</v>
       </c>
       <c r="B141" t="str">
-        <v>Plano</v>
+        <v>b*</v>
       </c>
       <c r="C141" t="str">
-        <v>Plano</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>L*</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B142" t="str">
-        <v>L*</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
       <c r="C142" t="str">
-        <v>L*</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>a*</v>
+        <v>Linking</v>
       </c>
       <c r="B143" t="str">
-        <v>a*</v>
+        <v>Ligação</v>
       </c>
       <c r="C143" t="str">
-        <v>a*</v>
+        <v>Vínculo</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>b*</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B144" t="str">
-        <v>b*</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
       </c>
       <c r="C144" t="str">
-        <v>b*</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B145" t="str">
-        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
+        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
       </c>
       <c r="C145" t="str">
-        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
+        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Linking</v>
+        <v>Observer Change</v>
       </c>
       <c r="B146" t="str">
-        <v>Ligação</v>
+        <v>Criador de ecrã V4</v>
       </c>
       <c r="C146" t="str">
-        <v>Vínculo</v>
+        <v>Criador de tela V4</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B147" t="str">
-        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
+        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
       </c>
       <c r="C147" t="str">
-        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
+        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B148" t="str">
-        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
+        <v>Ecrã RGB V5</v>
       </c>
       <c r="C148" t="str">
-        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
+        <v>Tela RGB V5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Observer Change</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B149" t="str">
-        <v>Criador de ecrã V4</v>
+        <v>largue um perfil de ecrã</v>
       </c>
       <c r="C149" t="str">
-        <v>Criador de tela V4</v>
+        <v>solte um perfil de tela</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B150" t="str">
-        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
+        <v>Observador V5 (PCC)</v>
       </c>
       <c r="C150" t="str">
-        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 RGB display</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B151" t="str">
-        <v>Ecrã RGB V5</v>
+        <v>largue um perfil de observador</v>
       </c>
       <c r="C151" t="str">
-        <v>Tela RGB V5</v>
+        <v>solte um perfil de observador</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop a display profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B152" t="str">
-        <v>largue um perfil de ecrã</v>
+        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
       </c>
       <c r="C152" t="str">
-        <v>solte um perfil de tela</v>
+        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B153" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>Criar perfil de ecrã V4</v>
       </c>
       <c r="C153" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>Criar perfil de tela V4</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>drop an observer profile</v>
+        <v>Profile name</v>
       </c>
       <c r="B154" t="str">
-        <v>largue um perfil de observador</v>
+        <v>Nome do perfil</v>
       </c>
       <c r="C154" t="str">
-        <v>solte um perfil de observador</v>
+        <v>Nome do perfil</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>Create</v>
       </c>
       <c r="B155" t="str">
-        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
+        <v>Criar</v>
       </c>
       <c r="C155" t="str">
-        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
+        <v>Criar</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Making…</v>
       </c>
       <c r="B156" t="str">
-        <v>Criar perfil de ecrã V4</v>
+        <v>A criar…</v>
       </c>
       <c r="C156" t="str">
-        <v>Criar perfil de tela V4</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Profile name</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B157" t="str">
-        <v>Nome do perfil</v>
+        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C157" t="str">
-        <v>Nome do perfil</v>
+        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Create</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B158" t="str">
-        <v>Criar</v>
+        <v>Fluxo de ligação</v>
       </c>
       <c r="C158" t="str">
-        <v>Criar</v>
+        <v>Fluxo de vinculação</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Making…</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B159" t="str">
-        <v>A criar…</v>
+        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
       </c>
       <c r="C159" t="str">
-        <v>Criando…</v>
+        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Done</v>
       </c>
       <c r="B160" t="str">
-        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
+        <v>Concluído</v>
       </c>
       <c r="C160" t="str">
-        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Link Pipeline</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B161" t="str">
-        <v>Fluxo de ligação</v>
+        <v>Largue uma imagem para transformar (TIFF/PNG/JPEG)</v>
       </c>
       <c r="C161" t="str">
-        <v>Fluxo de vinculação</v>
+        <v>Solte uma imagem para transformar (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Checking image…</v>
       </c>
       <c r="B162" t="str">
-        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
+        <v>A verificar imagem…</v>
       </c>
       <c r="C162" t="str">
-        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
+        <v>Verificando imagem…</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Done</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B163" t="str">
-        <v>Concluído</v>
+        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
       </c>
       <c r="C163" t="str">
-        <v>Concluído</v>
+        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B164" t="str">
-        <v>Largue uma imagem para transformar (TIFF/PNG/JPEG)</v>
+        <v>Imagem demasiado grande ({mp} MP; limite {max} MP).</v>
       </c>
       <c r="C164" t="str">
-        <v>Solte uma imagem para transformar (TIFF/PNG/JPEG)</v>
+        <v>Imagem grande demais ({mp} MP; limite {max} MP).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Checking image…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B165" t="str">
-        <v>A verificar imagem…</v>
+        <v>Transformar imagem</v>
       </c>
       <c r="C165" t="str">
-        <v>Verificando imagem…</v>
+        <v>Transformar imagem</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Transforming…</v>
       </c>
       <c r="B166" t="str">
-        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
+        <v>A transformar…</v>
       </c>
       <c r="C166" t="str">
-        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B167" t="str">
-        <v>Imagem demasiado grande ({mp} MP; limite {max} MP).</v>
+        <v>Largue perfis para iniciar a cadeia</v>
       </c>
       <c r="C167" t="str">
-        <v>Imagem grande demais ({mp} MP; limite {max} MP).</v>
+        <v>Solte perfis para iniciar a cadeia</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Transform Image</v>
+        <v>removed</v>
       </c>
       <c r="B168" t="str">
-        <v>Transformar imagem</v>
+        <v>removido</v>
       </c>
       <c r="C168" t="str">
-        <v>Transformar imagem</v>
+        <v>removido</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Transforming…</v>
+        <v>Move earlier</v>
       </c>
       <c r="B169" t="str">
-        <v>A transformar…</v>
+        <v>Mover antes</v>
       </c>
       <c r="C169" t="str">
-        <v>Transformando…</v>
+        <v>Mover antes</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Move later</v>
       </c>
       <c r="B170" t="str">
-        <v>Largue perfis para iniciar a cadeia</v>
+        <v>Mover depois</v>
       </c>
       <c r="C170" t="str">
-        <v>Solte perfis para iniciar a cadeia</v>
+        <v>Mover depois</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>removed</v>
+        <v>Move up</v>
       </c>
       <c r="B171" t="str">
-        <v>removido</v>
+        <v>Mover para cima</v>
       </c>
       <c r="C171" t="str">
-        <v>removido</v>
+        <v>Mover para cima</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move earlier</v>
+        <v>Move down</v>
       </c>
       <c r="B172" t="str">
-        <v>Mover antes</v>
+        <v>Mover para baixo</v>
       </c>
       <c r="C172" t="str">
-        <v>Mover antes</v>
+        <v>Mover para baixo</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move later</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B173" t="str">
-        <v>Mover depois</v>
+        <v>Intenção de renderização (todas)</v>
       </c>
       <c r="C173" t="str">
-        <v>Mover depois</v>
+        <v>Intenção de renderização (todas)</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Move up</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B174" t="str">
-        <v>Mover para cima</v>
+        <v>Intenção de renderização para esta transformação</v>
       </c>
       <c r="C174" t="str">
-        <v>Mover para cima</v>
+        <v>Intenção de renderização para esta transformação</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Move down</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B175" t="str">
-        <v>Mover para baixo</v>
+        <v>As transformações usam intenções de renderização diferentes</v>
       </c>
       <c r="C175" t="str">
-        <v>Mover para baixo</v>
+        <v>As transformações usam intenções de renderização diferentes</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B176" t="str">
-        <v>Intenção de renderização (todas)</v>
+        <v>Inverter direção da cadeia (inverte a transformação inicial e propaga-se por toda a cadeia)</v>
       </c>
       <c r="C176" t="str">
-        <v>Intenção de renderização (todas)</v>
+        <v>Inverter direção da cadeia (inverte a transformação inicial e se propaga por toda a cadeia)</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B177" t="str">
-        <v>Intenção de renderização para esta transformação</v>
+        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
       </c>
       <c r="C177" t="str">
-        <v>Intenção de renderização para esta transformação</v>
+        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Chain</v>
       </c>
       <c r="B178" t="str">
-        <v>As transformações usam intenções de renderização diferentes</v>
+        <v>Cadeia</v>
       </c>
       <c r="C178" t="str">
-        <v>As transformações usam intenções de renderização diferentes</v>
+        <v>Cadeia</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B179" t="str">
-        <v>Inverter direção da cadeia (inverte a transformação inicial e propaga-se por toda a cadeia)</v>
+        <v>Não foi possível analisar a cadeia.</v>
       </c>
       <c r="C179" t="str">
-        <v>Inverter direção da cadeia (inverte a transformação inicial e se propaga por toda a cadeia)</v>
+        <v>Não foi possível analisar a cadeia.</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B180" t="str">
-        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
+        <v>A verificar cadeia…</v>
       </c>
       <c r="C180" t="str">
-        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
+        <v>Verificando cadeia…</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Chain</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B181" t="str">
-        <v>Cadeia</v>
+        <v>A cadeia não liga ({detail}).</v>
       </c>
       <c r="C181" t="str">
-        <v>Cadeia</v>
+        <v>A cadeia não conecta ({detail}).</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>Não foi possível analisar a cadeia.</v>
+        <v>O perfil {n} não liga à etapa anterior ({detail}).</v>
       </c>
       <c r="C182" t="str">
-        <v>Não foi possível analisar a cadeia.</v>
+        <v>O perfil {n} não conecta com a etapa anterior ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Checking chain…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B183" t="str">
-        <v>A verificar cadeia…</v>
+        <v>Corrija a cadeia antes de processar imagens</v>
       </c>
       <c r="C183" t="str">
-        <v>Verificando cadeia…</v>
+        <v>Corrija a cadeia antes de processar imagens</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Clear</v>
       </c>
       <c r="B184" t="str">
-        <v>A cadeia não liga ({detail}).</v>
+        <v>Limpar</v>
       </c>
       <c r="C184" t="str">
-        <v>A cadeia não conecta ({detail}).</v>
+        <v>Limpar</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B185" t="str">
-        <v>O perfil {n} não liga à etapa anterior ({detail}).</v>
+        <v>Criar DeviceLink</v>
       </c>
       <c r="C185" t="str">
-        <v>O perfil {n} não conecta com a etapa anterior ({detail}).</v>
+        <v>Criar DeviceLink</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B186" t="str">
-        <v>Corrija a cadeia antes de processar imagens</v>
+        <v>Nome do DeviceLink</v>
       </c>
       <c r="C186" t="str">
-        <v>Corrija a cadeia antes de processar imagens</v>
+        <v>Nome do DeviceLink</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Clear</v>
+        <v>Making…</v>
       </c>
       <c r="B187" t="str">
-        <v>Limpar</v>
+        <v>A criar…</v>
       </c>
       <c r="C187" t="str">
-        <v>Limpar</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Make DeviceLink</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B188" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Criado “{name}” — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C188" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Criado “{name}” — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>DeviceLink name</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B189" t="str">
-        <v>Nome do DeviceLink</v>
+        <v>Largue imagens {src} para converter para {dst} — os resultados são descarregados, nada é armazenado.</v>
       </c>
       <c r="C189" t="str">
-        <v>Nome do DeviceLink</v>
+        <v>Solte imagens {src} para converter para {dst} — os resultados são baixados, nada é armazenado.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Making…</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B190" t="str">
-        <v>A criar…</v>
+        <v>Crie uma cadeia para processar imagens</v>
       </c>
       <c r="C190" t="str">
-        <v>Criando…</v>
+        <v>Crie uma cadeia para processar imagens</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B191" t="str">
-        <v>Criado “{name}” — adicionado ao conjunto e a este separador.</v>
+        <v>Esta cadeia não começa nem termina num espaço de cor de imagem</v>
       </c>
       <c r="C191" t="str">
-        <v>Criado “{name}” — adicionado ao conjunto e a esta aba.</v>
+        <v>Esta cadeia não começa nem termina em um espaço de cor de imagem</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B192" t="str">
-        <v>Largue imagens {src} para converter para {dst} — os resultados são descarregados, nada é armazenado.</v>
+        <v>Imagem transformada guardada.</v>
       </c>
       <c r="C192" t="str">
-        <v>Solte imagens {src} para converter para {dst} — os resultados são baixados, nada é armazenado.</v>
+        <v>Imagem transformada salva.</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B193" t="str">
-        <v>Crie uma cadeia para processar imagens</v>
+        <v>Largue um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="C193" t="str">
-        <v>Crie uma cadeia para processar imagens</v>
+        <v>Solte um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B194" t="str">
-        <v>Esta cadeia não começa nem termina num espaço de cor de imagem</v>
+        <v>Não foi possível ler esse ficheiro.</v>
       </c>
       <c r="C194" t="str">
-        <v>Esta cadeia não começa nem termina em um espaço de cor de imagem</v>
+        <v>Não foi possível ler esse arquivo.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B195" t="str">
-        <v>Imagem transformada guardada.</v>
+        <v>Ficheiro de dados demasiado grande.</v>
       </c>
       <c r="C195" t="str">
-        <v>Imagem transformada salva.</v>
+        <v>Arquivo de dados grande demais.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Transform Data</v>
       </c>
       <c r="B196" t="str">
-        <v>Largue um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
+        <v>Transformar dados</v>
       </c>
       <c r="C196" t="str">
-        <v>Solte um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
+        <v>Transformar dados</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Could not read that file.</v>
+        <v>Transforming…</v>
       </c>
       <c r="B197" t="str">
-        <v>Não foi possível ler esse ficheiro.</v>
+        <v>A transformar…</v>
       </c>
       <c r="C197" t="str">
-        <v>Não foi possível ler esse arquivo.</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Data file too large.</v>
+        <v>Prefer</v>
       </c>
       <c r="B198" t="str">
-        <v>Ficheiro de dados demasiado grande.</v>
+        <v>Preferir</v>
       </c>
       <c r="C198" t="str">
-        <v>Arquivo de dados grande demais.</v>
+        <v>Preferir</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Transform Data</v>
+        <v>Observer</v>
       </c>
       <c r="B199" t="str">
-        <v>Transformar dados</v>
+        <v>Observador</v>
       </c>
       <c r="C199" t="str">
-        <v>Transformar dados</v>
+        <v>Observador</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Transforming…</v>
+        <v>Illuminant</v>
       </c>
       <c r="B200" t="str">
-        <v>A transformar…</v>
+        <v>Iluminante</v>
       </c>
       <c r="C200" t="str">
-        <v>Transformando…</v>
+        <v>Iluminante</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Prefer</v>
+        <v>Condition</v>
       </c>
       <c r="B201" t="str">
-        <v>Preferir</v>
+        <v>Condição</v>
       </c>
       <c r="C201" t="str">
-        <v>Preferir</v>
+        <v>Condição</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Observer</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B202" t="str">
-        <v>Observador</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
       <c r="C202" t="str">
-        <v>Observador</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Illuminant</v>
+        <v>median</v>
       </c>
       <c r="B203" t="str">
-        <v>Iluminante</v>
+        <v>mediana</v>
       </c>
       <c r="C203" t="str">
-        <v>Iluminante</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Condition</v>
+        <v>mean</v>
       </c>
       <c r="B204" t="str">
-        <v>Condição</v>
+        <v>média</v>
       </c>
       <c r="C204" t="str">
-        <v>Condição</v>
+        <v>média</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>patches</v>
       </c>
       <c r="B205" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>patches</v>
       </c>
       <c r="C205" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>patches</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>median</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B206" t="str">
-        <v>mediana</v>
+        <v>{n} duplicados</v>
       </c>
       <c r="C206" t="str">
-        <v>mediana</v>
+        <v>{n} duplicados</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>mean</v>
+        <v>Transform result</v>
       </c>
       <c r="B207" t="str">
-        <v>média</v>
+        <v>Resultado da transformação</v>
       </c>
       <c r="C207" t="str">
-        <v>média</v>
+        <v>Resultado da transformação</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>patches</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B208" t="str">
-        <v>patches</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="C208" t="str">
-        <v>patches</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{n} duplicates</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B209" t="str">
-        <v>{n} duplicados</v>
+        <v>A mostrar os primeiros {shown} de {total} — Guardar grava todos.</v>
       </c>
       <c r="C209" t="str">
-        <v>{n} duplicados</v>
+        <v>Mostrando os primeiros {shown} de {total} — Salvar grava todos.</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Transform result</v>
+        <v>Save as</v>
       </c>
       <c r="B210" t="str">
-        <v>Resultado da transformação</v>
+        <v>Guardar como</v>
       </c>
       <c r="C210" t="str">
-        <v>Resultado da transformação</v>
+        <v>Salvar como</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Save</v>
       </c>
       <c r="B211" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Guardar</v>
       </c>
       <c r="C211" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Salvar</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B212" t="str">
-        <v>A mostrar os primeiros {shown} de {total} — Guardar grava todos.</v>
+        <v>Inverter transformação</v>
       </c>
       <c r="C212" t="str">
-        <v>Mostrando os primeiros {shown} de {total} — Salvar grava todos.</v>
+        <v>Inverter transformação</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Save as</v>
+        <v>Inverting…</v>
       </c>
       <c r="B213" t="str">
-        <v>Guardar como</v>
+        <v>A inverter…</v>
       </c>
       <c r="C213" t="str">
-        <v>Salvar como</v>
+        <v>Invertendo…</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Save</v>
+        <v>Invert</v>
       </c>
       <c r="B214" t="str">
-        <v>Guardar</v>
+        <v>Inverter</v>
       </c>
       <c r="C214" t="str">
-        <v>Salvar</v>
+        <v>Inverter</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert Transform</v>
+        <v>last stage</v>
       </c>
       <c r="B215" t="str">
-        <v>Inverter transformação</v>
+        <v>última etapa</v>
       </c>
       <c r="C215" t="str">
-        <v>Inverter transformação</v>
+        <v>última etapa</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Inverting…</v>
+        <v>first stage</v>
       </c>
       <c r="B216" t="str">
-        <v>A inverter…</v>
+        <v>primeira etapa</v>
       </c>
       <c r="C216" t="str">
-        <v>Invertendo…</v>
+        <v>primeira etapa</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Invert</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B217" t="str">
-        <v>Inverter</v>
+        <v>Dados em {in} → procurar {out}</v>
       </c>
       <c r="C217" t="str">
-        <v>Inverter</v>
+        <v>Dados em {in} → buscar {out}</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>last stage</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B218" t="str">
-        <v>última etapa</v>
+        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
       </c>
       <c r="C218" t="str">
-        <v>última etapa</v>
+        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>first stage</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B219" t="str">
-        <v>primeira etapa</v>
+        <v>O conjunto de dados deve estar em {in}; a procura inversa produz {out} mais um custo de invertibilidade por patch.</v>
       </c>
       <c r="C219" t="str">
-        <v>primeira etapa</v>
+        <v>O conjunto de dados deve estar em {in}; a busca inversa produz {out} mais um custo de invertibilidade por patch.</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B220" t="str">
-        <v>Dados em {in} → procurar {out}</v>
+        <v>Custo ΔE</v>
       </c>
       <c r="C220" t="str">
-        <v>Dados em {in} → buscar {out}</v>
+        <v>Custo ΔE</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B221" t="str">
-        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
+        <v>Esta imagem tem um perfil ICC incorporado.</v>
       </c>
       <c r="C221" t="str">
-        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
+        <v>Esta imagem tem um perfil ICC incorporado.</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B222" t="str">
-        <v>O conjunto de dados deve estar em {in}; a procura inversa produz {out} mais um custo de invertibilidade por patch.</v>
+        <v>Extrair e adicionar à cadeia</v>
       </c>
       <c r="C222" t="str">
-        <v>O conjunto de dados deve estar em {in}; a busca inversa produz {out} mais um custo de invertibilidade por patch.</v>
+        <v>Extrair e adicionar à cadeia</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>ΔE cost</v>
+        <v>Extracting…</v>
       </c>
       <c r="B223" t="str">
-        <v>Custo ΔE</v>
+        <v>A extrair…</v>
       </c>
       <c r="C223" t="str">
-        <v>Custo ΔE</v>
+        <v>Extraindo…</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B224" t="str">
-        <v>Esta imagem tem um perfil ICC incorporado.</v>
+        <v>Dispensar</v>
       </c>
       <c r="C224" t="str">
-        <v>Esta imagem tem um perfil ICC incorporado.</v>
+        <v>Dispensar</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B225" t="str">
-        <v>Extrair e adicionar à cadeia</v>
+        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro lugar na cadeia.</v>
       </c>
       <c r="C225" t="str">
-        <v>Extrair e adicionar à cadeia</v>
+        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro na cadeia.</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracting…</v>
+        <v>Image output options</v>
       </c>
       <c r="B226" t="str">
-        <v>A extrair…</v>
+        <v>Opções de saída de imagem</v>
       </c>
       <c r="C226" t="str">
-        <v>Extraindo…</v>
+        <v>Opções de saída de imagem</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Dismiss</v>
+        <v>Encoding</v>
       </c>
       <c r="B227" t="str">
-        <v>Dispensar</v>
+        <v>Codificação</v>
       </c>
       <c r="C227" t="str">
-        <v>Dispensar</v>
+        <v>Codificação</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Same as source</v>
       </c>
       <c r="B228" t="str">
-        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro lugar na cadeia.</v>
+        <v>Igual à origem</v>
       </c>
       <c r="C228" t="str">
-        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro na cadeia.</v>
+        <v>Igual à origem</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Image output options</v>
+        <v>8-bit</v>
       </c>
       <c r="B229" t="str">
-        <v>Opções de saída de imagem</v>
+        <v>8 bits</v>
       </c>
       <c r="C229" t="str">
-        <v>Opções de saída de imagem</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Encoding</v>
+        <v>16-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>Codificação</v>
+        <v>16 bits</v>
       </c>
       <c r="C230" t="str">
-        <v>Codificação</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Same as source</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B231" t="str">
-        <v>Igual à origem</v>
+        <v>Flutuante (32 bits)</v>
       </c>
       <c r="C231" t="str">
-        <v>Igual à origem</v>
+        <v>Flutuante (32 bits)</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>8-bit</v>
+        <v>Compression</v>
       </c>
       <c r="B232" t="str">
-        <v>8 bits</v>
+        <v>Compressão</v>
       </c>
       <c r="C232" t="str">
-        <v>8 bits</v>
+        <v>Compressão</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>16-bit</v>
+        <v>None</v>
       </c>
       <c r="B233" t="str">
-        <v>16 bits</v>
+        <v>Nenhuma</v>
       </c>
       <c r="C233" t="str">
-        <v>16 bits</v>
+        <v>Nenhuma</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Float (32-bit)</v>
+        <v>Planar</v>
       </c>
       <c r="B234" t="str">
-        <v>Flutuante (32 bits)</v>
+        <v>Planar</v>
       </c>
       <c r="C234" t="str">
-        <v>Flutuante (32 bits)</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Compression</v>
+        <v>Composite</v>
       </c>
       <c r="B235" t="str">
-        <v>Compressão</v>
+        <v>Composto</v>
       </c>
       <c r="C235" t="str">
-        <v>Compressão</v>
+        <v>Composto</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>None</v>
+        <v>Separated</v>
       </c>
       <c r="B236" t="str">
-        <v>Nenhuma</v>
+        <v>Separado</v>
       </c>
       <c r="C236" t="str">
-        <v>Nenhuma</v>
+        <v>Separado</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Planar</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B237" t="str">
-        <v>Planar</v>
+        <v>Interpolação CMM</v>
       </c>
       <c r="C237" t="str">
-        <v>Planar</v>
+        <v>Interpolação CMM</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Composite</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B238" t="str">
-        <v>Composto</v>
+        <v>Tetraédrica</v>
       </c>
       <c r="C238" t="str">
-        <v>Composto</v>
+        <v>Tetraédrica</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Separated</v>
+        <v>Linear</v>
       </c>
       <c r="B239" t="str">
-        <v>Separado</v>
+        <v>Linear</v>
       </c>
       <c r="C239" t="str">
-        <v>Separado</v>
+        <v>Linear</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>CMM interpolation</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B240" t="str">
-        <v>Interpolação CMM</v>
+        <v>Incorporar ICC</v>
       </c>
       <c r="C240" t="str">
-        <v>Interpolação CMM</v>
+        <v>Incorporar ICC</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Tetrahedral</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B241" t="str">
-        <v>Tetraédrica</v>
+        <v>A codificação, a compressão e o formato planar determinam o TIFF guardado. A saída RGB/Gray mantém-se em PNG, salvo se for definida uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado).</v>
       </c>
       <c r="C241" t="str">
-        <v>Tetraédrica</v>
+        <v>A codificação, a compressão e o formato planar determinam o TIFF salvo. A saída RGB/Gray permanece em PNG, a menos que uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado) seja definida.</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Linear</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B242" t="str">
-        <v>Linear</v>
+        <v>Montar TIFF espectral</v>
       </c>
       <c r="C242" t="str">
-        <v>Linear</v>
+        <v>Montar TIFF espectral</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Embed ICC</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B243" t="str">
-        <v>Incorporar ICC</v>
+        <v>Largue imagens espectrais de canal único pela ordem dos canais e depois monte-as num único TIFF multicanal.</v>
       </c>
       <c r="C243" t="str">
-        <v>Incorporar ICC</v>
+        <v>Solte imagens espectrais de canal único na ordem dos canais e depois monte-as em um único TIFF multicanal.</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B244" t="str">
-        <v>A codificação, a compressão e o formato planar determinam o TIFF guardado. A saída RGB/Gray mantém-se em PNG, salvo se for definida uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado).</v>
+        <v>Largue imagens espectrais aqui (ou clique para escolher)</v>
       </c>
       <c r="C244" t="str">
-        <v>A codificação, a compressão e o formato planar determinam o TIFF salvo. A saída RGB/Gray permanece em PNG, a menos que uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado) seja definida.</v>
+        <v>Solte imagens espectrais aqui (ou clique para escolher)</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>ch</v>
       </c>
       <c r="B245" t="str">
-        <v>Montar TIFF espectral</v>
+        <v>can</v>
       </c>
       <c r="C245" t="str">
-        <v>Montar TIFF espectral</v>
+        <v>can</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B246" t="str">
-        <v>Largue imagens espectrais de canal único pela ordem dos canais e depois monte-as num único TIFF multicanal.</v>
+        <v>Montar e guardar</v>
       </c>
       <c r="C246" t="str">
-        <v>Solte imagens espectrais de canal único na ordem dos canais e depois monte-as em um único TIFF multicanal.</v>
+        <v>Montar e salvar</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Assembling…</v>
       </c>
       <c r="B247" t="str">
-        <v>Largue imagens espectrais aqui (ou clique para escolher)</v>
+        <v>A montar…</v>
       </c>
       <c r="C247" t="str">
-        <v>Solte imagens espectrais aqui (ou clique para escolher)</v>
+        <v>Montando…</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>ch</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B248" t="str">
-        <v>can</v>
+        <v>Foram montados {n} canais.</v>
       </c>
       <c r="C248" t="str">
-        <v>can</v>
+        <v>Foram montados {n} canais.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B249" t="str">
-        <v>Montar e guardar</v>
+        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
       </c>
       <c r="C249" t="str">
-        <v>Montar e salvar</v>
+        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Assembling…</v>
+        <v>Cancel</v>
       </c>
       <c r="B250" t="str">
-        <v>A montar…</v>
+        <v>Cancelar</v>
       </c>
       <c r="C250" t="str">
-        <v>Montando…</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B251" t="str">
-        <v>Foram montados {n} canais.</v>
+        <v>{n} ficheiro(s) não carregados</v>
       </c>
       <c r="C251" t="str">
-        <v>Foram montados {n} canais.</v>
+        <v>{n} arquivo(s) não carregados</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B252" t="str">
-        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
+        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
       </c>
       <c r="C252" t="str">
-        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
+        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>Cancel</v>
+        <v>OK</v>
       </c>
       <c r="B253" t="str">
-        <v>Cancelar</v>
+        <v>OK</v>
       </c>
       <c r="C253" t="str">
-        <v>Cancelar</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B254" t="str">
-        <v>{n} ficheiro(s) não carregados</v>
+        <v>Largue um perfil ICC aqui</v>
       </c>
       <c r="C254" t="str">
-        <v>{n} arquivo(s) não carregados</v>
+        <v>Solte um perfil ICC aqui</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>or</v>
       </c>
       <c r="B255" t="str">
-        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
+        <v>ou</v>
       </c>
       <c r="C255" t="str">
-        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>OK</v>
+        <v>Choose file</v>
       </c>
       <c r="B256" t="str">
-        <v>OK</v>
+        <v>Escolher ficheiro</v>
       </c>
       <c r="C256" t="str">
-        <v>OK</v>
+        <v>Escolher arquivo</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B257" t="str">
-        <v>Largue um perfil ICC aqui</v>
+        <v>Ficheiros .icc e .icm</v>
       </c>
       <c r="C257" t="str">
-        <v>Solte um perfil ICC aqui</v>
+        <v>Arquivos .icc e .icm</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>or</v>
+        <v>Header</v>
       </c>
       <c r="B258" t="str">
-        <v>ou</v>
+        <v>Cabeçalho</v>
       </c>
       <c r="C258" t="str">
-        <v>ou</v>
+        <v>Cabeçalho</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Choose file</v>
+        <v>Tags</v>
       </c>
       <c r="B259" t="str">
-        <v>Escolher ficheiro</v>
+        <v>Etiquetas</v>
       </c>
       <c r="C259" t="str">
-        <v>Escolher arquivo</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>.icc and .icm files</v>
+        <v>Validation</v>
       </c>
       <c r="B260" t="str">
-        <v>Ficheiros .icc e .icm</v>
+        <v>Validação</v>
       </c>
       <c r="C260" t="str">
-        <v>Arquivos .icc e .icm</v>
+        <v>Validação</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Header</v>
+        <v>Analysis</v>
       </c>
       <c r="B261" t="str">
-        <v>Cabeçalho</v>
+        <v>Análise</v>
       </c>
       <c r="C261" t="str">
-        <v>Cabeçalho</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Tags</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B262" t="str">
-        <v>Etiquetas</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
       <c r="C262" t="str">
-        <v>Tags</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Validation</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B263" t="str">
-        <v>Validação</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
       </c>
       <c r="C263" t="str">
-        <v>Validação</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Analysis</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B264" t="str">
-        <v>Análise</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C264" t="str">
-        <v>Análise</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B265" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
       <c r="C265" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B266" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C266" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>% ink</v>
       </c>
       <c r="B267" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>% tinta</v>
       </c>
       <c r="C267" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Perceptual</v>
       </c>
       <c r="B268" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>Perceptual</v>
       </c>
       <c r="C268" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Rendering intent</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B269" t="str">
-        <v>Intenção de renderização</v>
+        <v>Colorimétrico relativo</v>
       </c>
       <c r="C269" t="str">
-        <v>Intenção de renderização</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>% ink</v>
+        <v>Saturation</v>
       </c>
       <c r="B270" t="str">
-        <v>% tinta</v>
+        <v>Saturação</v>
       </c>
       <c r="C270" t="str">
-        <v>% tinta</v>
+        <v>Saturação</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Perceptual</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B271" t="str">
-        <v>Perceptual</v>
+        <v>Colorimétrico absoluto</v>
       </c>
       <c r="C271" t="str">
-        <v>Perceptual</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B272" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Estatísticas do perfil</v>
       </c>
       <c r="C272" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Estatísticas do perfil</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Saturation</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B273" t="str">
-        <v>Saturação</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
       <c r="C273" t="str">
-        <v>Saturação</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B274" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
       </c>
       <c r="C274" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Profile Statistics</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B275" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C275" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B276" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Volume de gamute (ΔE³)</v>
       </c>
       <c r="C276" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B277" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
+        <v>ΔE de percurso</v>
       </c>
       <c r="C277" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
+        <v>ΔE de percurso</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Rendering intent</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B278" t="str">
-        <v>Intenção de renderização</v>
+        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
       </c>
       <c r="C278" t="str">
-        <v>Intenção de renderização</v>
+        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>mean</v>
       </c>
       <c r="B279" t="str">
-        <v>Volume de gamute (ΔE³)</v>
+        <v>média</v>
       </c>
       <c r="C279" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>média</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>Round-trip ΔE</v>
+        <v>P90</v>
       </c>
       <c r="B280" t="str">
-        <v>ΔE de percurso</v>
+        <v>P90</v>
       </c>
       <c r="C280" t="str">
-        <v>ΔE de percurso</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>max</v>
       </c>
       <c r="B281" t="str">
-        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
+        <v>máx.</v>
       </c>
       <c r="C281" t="str">
-        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>mean</v>
+        <v>Analysing…</v>
       </c>
       <c r="B282" t="str">
-        <v>média</v>
+        <v>A analisar…</v>
       </c>
       <c r="C282" t="str">
-        <v>média</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>P90</v>
+        <v>Analysis</v>
       </c>
       <c r="B283" t="str">
-        <v>P90</v>
+        <v>Análise</v>
       </c>
       <c r="C283" t="str">
-        <v>P90</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>max</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B284" t="str">
-        <v>máx.</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C284" t="str">
-        <v>máx.</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Analysing…</v>
+        <v>Plot</v>
       </c>
       <c r="B285" t="str">
-        <v>A analisar…</v>
+        <v>Gráfico</v>
       </c>
       <c r="C285" t="str">
-        <v>Analisando…</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Analysis</v>
+        <v>Raw Output</v>
       </c>
       <c r="B286" t="str">
-        <v>Análise</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C286" t="str">
-        <v>Análise</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>XML</v>
       </c>
       <c r="B287" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>XML</v>
       </c>
       <c r="C287" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Plot</v>
+        <v>JSON</v>
       </c>
       <c r="B288" t="str">
-        <v>Gráfico</v>
+        <v>JSON</v>
       </c>
       <c r="C288" t="str">
-        <v>Gráfico</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Raw Output</v>
+        <v>Curves</v>
       </c>
       <c r="B289" t="str">
-        <v>Saída em bruto</v>
+        <v>Curvas</v>
       </c>
       <c r="C289" t="str">
-        <v>Saída bruta</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>XML</v>
+        <v>Input curves</v>
       </c>
       <c r="B290" t="str">
-        <v>XML</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C290" t="str">
-        <v>XML</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>JSON</v>
+        <v>Output curves</v>
       </c>
       <c r="B291" t="str">
-        <v>JSON</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C291" t="str">
-        <v>JSON</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Curves</v>
+        <v>CLUT image</v>
       </c>
       <c r="B292" t="str">
-        <v>Curvas</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C292" t="str">
-        <v>Curvas</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Input curves</v>
+        <v>Gamut image</v>
       </c>
       <c r="B293" t="str">
-        <v>Curvas de entrada</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C293" t="str">
-        <v>Curvas de entrada</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Output curves</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B294" t="str">
-        <v>Curvas de saída</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C294" t="str">
-        <v>Curvas de saída</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>CLUT image</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B295" t="str">
-        <v>Imagem CLUT</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C295" t="str">
-        <v>Imagem CLUT</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Gamut image</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B296" t="str">
-        <v>Imagem de gamut</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C296" t="str">
-        <v>Imagem de gamut</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Chromaticity</v>
+        <v>Curve table</v>
       </c>
       <c r="B297" t="str">
-        <v>Cromaticidade</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C297" t="str">
-        <v>Cromaticidade</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Scatter plot</v>
+        <v>Tables</v>
       </c>
       <c r="B298" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Tabelas</v>
       </c>
       <c r="C298" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tone response curve</v>
+        <v>Data</v>
       </c>
       <c r="B299" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Dados</v>
       </c>
       <c r="C299" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Curve table</v>
+        <v>Evaluate</v>
       </c>
       <c r="B300" t="str">
-        <v>Tabela da curva</v>
+        <v>Avaliar</v>
       </c>
       <c r="C300" t="str">
-        <v>Tabela da curva</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Tables</v>
+        <v>Loading…</v>
       </c>
       <c r="B301" t="str">
-        <v>Tabelas</v>
+        <v>A carregar…</v>
       </c>
       <c r="C301" t="str">
-        <v>Tabelas</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Data</v>
+        <v>Input</v>
       </c>
       <c r="B302" t="str">
-        <v>Dados</v>
+        <v>Entrada</v>
       </c>
       <c r="C302" t="str">
-        <v>Dados</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Evaluate</v>
+        <v>Output</v>
       </c>
       <c r="B303" t="str">
-        <v>Avaliar</v>
+        <v>Saída</v>
       </c>
       <c r="C303" t="str">
-        <v>Avaliar</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Loading…</v>
+        <v>Floating point</v>
       </c>
       <c r="B304" t="str">
-        <v>A carregar…</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C304" t="str">
-        <v>Carregando…</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Input</v>
+        <v>Grid point</v>
       </c>
       <c r="B305" t="str">
-        <v>Entrada</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C305" t="str">
-        <v>Entrada</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Output</v>
+        <v>Normalized</v>
       </c>
       <c r="B306" t="str">
-        <v>Saída</v>
+        <v>Normalizado</v>
       </c>
       <c r="C306" t="str">
-        <v>Saída</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Floating point</v>
+        <v>Human</v>
       </c>
       <c r="B307" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Legível</v>
       </c>
       <c r="C307" t="str">
-        <v>Ponto flutuante</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Grid point</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B308" t="str">
-        <v>Ponto da grelha</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C308" t="str">
-        <v>Ponto da grade</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Normalized</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B309" t="str">
-        <v>Normalizado</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C309" t="str">
-        <v>Normalizado</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Human</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B310" t="str">
-        <v>Legível</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C310" t="str">
-        <v>Legível</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Device → PCS</v>
+        <v>Loading…</v>
       </c>
       <c r="B311" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>A carregar…</v>
       </c>
       <c r="C311" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>PCS → Device</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B312" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C312" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No CLUT grid</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B313" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C313" t="str">
-        <v>Sem grade CLUT</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Loading…</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B314" t="str">
-        <v>A carregar…</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C314" t="str">
-        <v>Carregando…</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B315" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C315" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B316" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C316" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B317" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C317" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B318" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C318" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Security</v>
       </c>
       <c r="B319" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Segurança</v>
       </c>
       <c r="C319" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Conformance</v>
       </c>
       <c r="B320" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>Conformidade</v>
       </c>
       <c r="C320" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Quality</v>
       </c>
       <c r="B321" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Qualidade</v>
       </c>
       <c r="C321" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Security</v>
+        <v>REPORT</v>
       </c>
       <c r="B322" t="str">
-        <v>Segurança</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C322" t="str">
-        <v>Segurança</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Conformance</v>
+        <v>FAIL</v>
       </c>
       <c r="B323" t="str">
-        <v>Conformidade</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C323" t="str">
-        <v>Conformidade</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Quality</v>
+        <v>checks</v>
       </c>
       <c r="B324" t="str">
-        <v>Qualidade</v>
+        <v>verificações</v>
       </c>
       <c r="C324" t="str">
-        <v>Qualidade</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>REPORT</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B325" t="str">
-        <v>RELATÓRIO</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C325" t="str">
-        <v>RELATÓRIO</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>FAIL</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B326" t="str">
-        <v>REPROVADO</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C326" t="str">
-        <v>REPROVADO</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>checks</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B327" t="str">
-        <v>verificações</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C327" t="str">
-        <v>verificações</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B328" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C328" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Subscribe</v>
       </c>
       <c r="B329" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Subscrever</v>
       </c>
       <c r="C329" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B330" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C330" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Powered by {lib}</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B331" t="str">
-        <v>Com {lib}</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C331" t="str">
-        <v>Com {lib}</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B332" t="str">
-        <v>Subscrever</v>
+        <v>Fechar</v>
       </c>
       <c r="C332" t="str">
-        <v>Inscrever-se</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B333" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C333" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Get notified about new releases</v>
+        <v>Email address</v>
       </c>
       <c r="B334" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C334" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Close</v>
+        <v>you@example.com</v>
       </c>
       <c r="B335" t="str">
-        <v>Fechar</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C335" t="str">
-        <v>Fechar</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B336" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C336" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Email address</v>
+        <v>(optional)</v>
       </c>
       <c r="B337" t="str">
-        <v>Endereço de e-mail</v>
+        <v>(opcional)</v>
       </c>
       <c r="C337" t="str">
-        <v>Endereço de e-mail</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>you@example.com</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B338" t="str">
-        <v>voce@exemplo.com</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C338" t="str">
-        <v>voce@exemplo.com</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>How will you use profiletool?</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B339" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C339" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>(optional)</v>
+        <v>Cancel</v>
       </c>
       <c r="B340" t="str">
-        <v>(opcional)</v>
+        <v>Cancelar</v>
       </c>
       <c r="C340" t="str">
-        <v>(opcional)</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Subscribe</v>
       </c>
       <c r="B341" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Subscrever</v>
       </c>
       <c r="C341" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B342" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C342" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Cancel</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B343" t="str">
-        <v>Cancelar</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C343" t="str">
-        <v>Cancelar</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Subscribe</v>
+        <v>Close</v>
       </c>
       <c r="B344" t="str">
-        <v>Subscrever</v>
+        <v>Fechar</v>
       </c>
       <c r="C344" t="str">
-        <v>Inscrever-se</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B345" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C345" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B346" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C346" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Close</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B347" t="str">
-        <v>Fechar</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C347" t="str">
-        <v>Fechar</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Privacy notice</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B348" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C348" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C349" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C350" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Error:</v>
       </c>
       <c r="B351" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Erro:</v>
       </c>
       <c r="C351" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B352" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C352" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B353" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C353" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Error:</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B354" t="str">
-        <v>Erro:</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C354" t="str">
-        <v>Erro:</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to XML</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B355" t="str">
-        <v>Converter para XML</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C355" t="str">
-        <v>Converter para XML</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Convert to JSON</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B356" t="str">
-        <v>Converter para JSON</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C356" t="str">
-        <v>Converter para JSON</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Convert to ICC</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B357" t="str">
-        <v>Converter para ICC</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C357" t="str">
-        <v>Converter para ICC</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to XML…</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B358" t="str">
-        <v>A converter para XML…</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C358" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Converting to JSON…</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B359" t="str">
-        <v>A converter para JSON…</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C359" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Converting to ICC…</v>
+        <v>Profile ID</v>
       </c>
       <c r="B360" t="str">
-        <v>A converter para ICC…</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C360" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Load ICC profile</v>
+        <v>No tags found.</v>
       </c>
       <c r="B361" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C361" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Tag Name</v>
       </c>
       <c r="B362" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C362" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Profile ID</v>
+        <v>ID</v>
       </c>
       <c r="B363" t="str">
-        <v>ID do perfil</v>
+        <v>ID</v>
       </c>
       <c r="C363" t="str">
-        <v>ID do perfil</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>No tags found.</v>
+        <v>Offset</v>
       </c>
       <c r="B364" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C364" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Tag Name</v>
+        <v>Size</v>
       </c>
       <c r="B365" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Tamanho</v>
       </c>
       <c r="C365" t="str">
-        <v>Nome da tag</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ID</v>
+        <v>Pad</v>
       </c>
       <c r="B366" t="str">
-        <v>ID</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C366" t="str">
-        <v>ID</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Offset</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B367" t="str">
-        <v>Deslocamento</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C367" t="str">
-        <v>Deslocamento</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Size</v>
+        <v>Type</v>
       </c>
       <c r="B368" t="str">
-        <v>Tamanho</v>
+        <v>Tipo</v>
       </c>
       <c r="C368" t="str">
-        <v>Tamanho</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Pad</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B369" t="str">
-        <v>Preenchimento</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C369" t="str">
-        <v>Preenchimento</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Bytes changed since load</v>
+        <v>(No content)</v>
       </c>
       <c r="B370" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C370" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Type</v>
+        <v>bytes</v>
       </c>
       <c r="B371" t="str">
-        <v>Tipo</v>
+        <v>bytes</v>
       </c>
       <c r="C371" t="str">
-        <v>Tipo</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Array of {type}</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B372" t="str">
-        <v>Vetor de {type}</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C372" t="str">
-        <v>Array de {type}</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>(No content)</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B373" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C373" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>bytes</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B374" t="str">
-        <v>bytes</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C374" t="str">
-        <v>bytes</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Loading full description…</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B375" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C375" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Could not load full description:</v>
+        <v>No validation output</v>
       </c>
       <c r="B376" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C376" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B377" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C377" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B378" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C378" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>No validation output</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B379" t="str">
-        <v>Sem saída de validação</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C379" t="str">
-        <v>Sem saída de validação</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B380" t="str">
-        <v>O perfil é válido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C380" t="str">
-        <v>O perfil é válido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B381" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C381" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B382" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C382" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical validation error</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B383" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C383" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Unknown validation status</v>
+        <v>Valid</v>
       </c>
       <c r="B384" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Válido</v>
       </c>
       <c r="C384" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Warning</v>
       </c>
       <c r="B385" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Aviso</v>
       </c>
       <c r="C385" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Error</v>
       </c>
       <c r="B386" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Erro</v>
       </c>
       <c r="C386" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Valid</v>
+        <v>Unknown</v>
       </c>
       <c r="B387" t="str">
-        <v>Válido</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C387" t="str">
-        <v>Válido</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Warning</v>
+        <v>Pass</v>
       </c>
       <c r="B388" t="str">
-        <v>Aviso</v>
+        <v>Aprovado</v>
       </c>
       <c r="C388" t="str">
-        <v>Aviso</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Error</v>
+        <v>Fail</v>
       </c>
       <c r="B389" t="str">
-        <v>Erro</v>
+        <v>Reprovado</v>
       </c>
       <c r="C389" t="str">
-        <v>Erro</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Unknown</v>
+        <v>View in context</v>
       </c>
       <c r="B390" t="str">
-        <v>Desconhecido</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C390" t="str">
-        <v>Desconhecido</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Pass</v>
+        <v>Validation detail</v>
       </c>
       <c r="B391" t="str">
-        <v>Aprovado</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C391" t="str">
-        <v>Aprovado</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Fail</v>
+        <v>Triggered by</v>
       </c>
       <c r="B392" t="str">
-        <v>Reprovado</v>
+        <v>Acionado por</v>
       </c>
       <c r="C392" t="str">
-        <v>Reprovado</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>View in context</v>
+        <v>Field</v>
       </c>
       <c r="B393" t="str">
-        <v>Ver no contexto</v>
+        <v>Campo</v>
       </c>
       <c r="C393" t="str">
-        <v>Ver no contexto</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Validation detail</v>
+        <v>Current value</v>
       </c>
       <c r="B394" t="str">
-        <v>Detalhe de validação</v>
+        <v>Valor atual</v>
       </c>
       <c r="C394" t="str">
-        <v>Detalhe de validação</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Triggered by</v>
+        <v>Required: 0</v>
       </c>
       <c r="B395" t="str">
-        <v>Acionado por</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C395" t="str">
-        <v>Acionado por</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Field</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B396" t="str">
-        <v>Campo</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C396" t="str">
-        <v>Campo</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Current value</v>
+        <v>Invalid</v>
       </c>
       <c r="B397" t="str">
-        <v>Valor atual</v>
+        <v>Inválido</v>
       </c>
       <c r="C397" t="str">
-        <v>Valor atual</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Required: 0</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B398" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C398" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Expected: {value}</v>
+        <v>Close</v>
       </c>
       <c r="B399" t="str">
-        <v>Esperado: {value}</v>
+        <v>Fechar</v>
       </c>
       <c r="C399" t="str">
-        <v>Esperado: {value}</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Invalid</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B400" t="str">
-        <v>Inválido</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C400" t="str">
-        <v>Inválido</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C401" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Close</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B402" t="str">
-        <v>Fechar</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C402" t="str">
-        <v>Fechar</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Loading XML editor…</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C403" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Loading JSON editor…</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B404" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C404" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B405" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C405" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B406" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C406" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C407" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>indent</v>
       </c>
       <c r="B408" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>indentação</v>
       </c>
       <c r="C408" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>indentação</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>sort keys</v>
       </c>
       <c r="B409" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>ordenar chaves</v>
       </c>
       <c r="C409" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>ordenar chaves</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Profile written from edits, but re-validation failed:</v>
       </c>
       <c r="B410" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
       <c r="C410" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="str">
-        <v>indent</v>
-      </c>
-      <c r="B411" t="str">
-        <v>indentação</v>
-      </c>
-      <c r="C411" t="str">
-        <v>indentação</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="str">
-        <v>sort keys</v>
-      </c>
-      <c r="B412" t="str">
-        <v>ordenar chaves</v>
-      </c>
-      <c r="C412" t="str">
-        <v>ordenar chaves</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="str">
-        <v>Profile written from edits, but re-validation failed:</v>
-      </c>
-      <c r="B413" t="str">
-        <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
-      </c>
-      <c r="C413" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C413"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C410"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C410"/>
+  <dimension ref="A1:C411"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -417,4515 +417,4526 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Round-Trip (PRMG)</v>
+        <v>{pct}% of samples were out of range and were clamped.</v>
       </c>
       <c r="B2" t="str">
-        <v>Ida e volta (PRMG)</v>
+        <v>{pct}% das amostras estavam fora do intervalo e foram limitadas.</v>
       </c>
       <c r="C2" t="str">
-        <v>Ida e volta (PRMG)</v>
+        <v>{pct}% das amostras estavam fora da faixa e foram limitadas.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
+        <v>Round-Trip (PRMG)</v>
       </c>
       <c r="B3" t="str">
-        <v>Ida e volta sobre o cubo do dispositivo do perfil, igual à ferramenta de referência iccRoundTrip. A ida e volta 1 é o erro dispositivo→PCS→dispositivo (ΔE*ab); a ida e volta 2 mede a estabilidade do ciclo PCS. O histograma PRMG indica a interoperabilidade em relação ao Perceptual Reference Medium Gamut.</v>
+        <v>Ida e volta (PRMG)</v>
       </c>
       <c r="C3" t="str">
-        <v>Ida e volta sobre o cubo do dispositivo do perfil, igual à ferramenta de referência iccRoundTrip. A ida e volta 1 é o erro dispositivo→PCS→dispositivo (ΔE*ab); a ida e volta 2 mede a estabilidade do ciclo PCS. O histograma PRMG indica a interoperabilidade em relação ao Perceptual Reference Medium Gamut.</v>
+        <v>Ida e volta (PRMG)</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Use MPE (color) tags</v>
+        <v>Device-cube round trip through the profile, matching the iccRoundTrip reference tool. Round Trip 1 is the device→PCS→device error (ΔE*ab); Round Trip 2 is the PCS round-trip stability. The PRMG histogram reports interoperability against the Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="B4" t="str">
-        <v>Usar etiquetas MPE (cor)</v>
+        <v>Ida e volta sobre o cubo do dispositivo do perfil, igual à ferramenta de referência iccRoundTrip. A ida e volta 1 é o erro dispositivo→PCS→dispositivo (ΔE*ab); a ida e volta 2 mede a estabilidade do ciclo PCS. O histograma PRMG indica a interoperabilidade em relação ao Perceptual Reference Medium Gamut.</v>
       </c>
       <c r="C4" t="str">
-        <v>Usar tags MPE (cor)</v>
+        <v>Ida e volta sobre o cubo do dispositivo do perfil, igual à ferramenta de referência iccRoundTrip. A ida e volta 1 é o erro dispositivo→PCS→dispositivo (ΔE*ab); a ida e volta 2 mede a estabilidade do ciclo PCS. O histograma PRMG indica a interoperabilidade em relação ao Perceptual Reference Medium Gamut.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
+        <v>Use MPE (color) tags</v>
       </c>
       <c r="B5" t="str">
-        <v>Este perfil não permite ida e volta: faltam as transformações dispositivo↔PCS necessárias (por ex. um perfil unidirecional ou abstrato).</v>
+        <v>Usar etiquetas MPE (cor)</v>
       </c>
       <c r="C5" t="str">
-        <v>Este perfil não permite ida e volta: faltam as transformações dispositivo↔PCS necessárias (por ex. um perfil unidirecional ou abstrato).</v>
+        <v>Usar tags MPE (cor)</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
+        <v>This profile cannot be round-tripped — it lacks the device↔PCS transforms this metric needs (e.g. a one-way or abstract profile).</v>
       </c>
       <c r="B6" t="str">
-        <v>Ida e volta ignorada: o espaço de cor do dispositivo é demasiado amplo para avaliar (demasiadas amostras).</v>
+        <v>Este perfil não permite ida e volta: faltam as transformações dispositivo↔PCS necessárias (por ex. um perfil unidirecional ou abstrato).</v>
       </c>
       <c r="C6" t="str">
-        <v>Ida e volta ignorada: o espaço de cor do dispositivo é amplo demais para avaliar (amostras demais).</v>
+        <v>Este perfil não permite ida e volta: faltam as transformações dispositivo↔PCS necessárias (por ex. um perfil unidirecional ou abstrato).</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Metric</v>
+        <v>Round trip skipped: the device colour space is too wide to evaluate (too many samples).</v>
       </c>
       <c r="B7" t="str">
-        <v>Métrica</v>
+        <v>Ida e volta ignorada: o espaço de cor do dispositivo é demasiado amplo para avaliar (demasiadas amostras).</v>
       </c>
       <c r="C7" t="str">
-        <v>Métrica</v>
+        <v>Ida e volta ignorada: o espaço de cor do dispositivo é amplo demais para avaliar (amostras demais).</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Round Trip 1</v>
+        <v>Metric</v>
       </c>
       <c r="B8" t="str">
-        <v>Ida e volta 1</v>
+        <v>Métrica</v>
       </c>
       <c r="C8" t="str">
-        <v>Ida e volta 1</v>
+        <v>Métrica</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Round Trip 2</v>
+        <v>Round Trip 1</v>
       </c>
       <c r="B9" t="str">
-        <v>Ida e volta 2</v>
+        <v>Ida e volta 1</v>
       </c>
       <c r="C9" t="str">
-        <v>Ida e volta 2</v>
+        <v>Ida e volta 1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>device → PCS → device</v>
+        <v>Round Trip 2</v>
       </c>
       <c r="B10" t="str">
-        <v>dispositivo → PCS → dispositivo</v>
+        <v>Ida e volta 2</v>
       </c>
       <c r="C10" t="str">
-        <v>dispositivo → PCS → dispositivo</v>
+        <v>Ida e volta 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>PCS round-trip stability</v>
+        <v>device → PCS → device</v>
       </c>
       <c r="B11" t="str">
-        <v>estabilidade do ciclo PCS</v>
+        <v>dispositivo → PCS → dispositivo</v>
       </c>
       <c r="C11" t="str">
-        <v>estabilidade do ciclo PCS</v>
+        <v>dispositivo → PCS → dispositivo</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Min ΔE</v>
+        <v>PCS round-trip stability</v>
       </c>
       <c r="B12" t="str">
-        <v>ΔE mín</v>
+        <v>estabilidade do ciclo PCS</v>
       </c>
       <c r="C12" t="str">
-        <v>ΔE mín</v>
+        <v>estabilidade do ciclo PCS</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mean ΔE</v>
+        <v>Min ΔE</v>
       </c>
       <c r="B13" t="str">
-        <v>ΔE médio</v>
+        <v>ΔE mín</v>
       </c>
       <c r="C13" t="str">
-        <v>ΔE médio</v>
+        <v>ΔE mín</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Max ΔE</v>
+        <v>Mean ΔE</v>
       </c>
       <c r="B14" t="str">
-        <v>ΔE máx</v>
+        <v>ΔE médio</v>
       </c>
       <c r="C14" t="str">
-        <v>ΔE máx</v>
+        <v>ΔE médio</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Worst L, a, b</v>
+        <v>Max ΔE</v>
       </c>
       <c r="B15" t="str">
-        <v>Pior L, a, b</v>
+        <v>ΔE máx</v>
       </c>
       <c r="C15" t="str">
-        <v>Pior L, a, b</v>
+        <v>ΔE máx</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Specified gamut</v>
+        <v>Worst L, a, b</v>
       </c>
       <c r="B16" t="str">
-        <v>Gama especificada</v>
+        <v>Pior L, a, b</v>
       </c>
       <c r="C16" t="str">
-        <v>Gama especificada</v>
+        <v>Pior L, a, b</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Gama especificada</v>
       </c>
       <c r="C17" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>Gama especificada</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Not specified</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B18" t="str">
-        <v>Não especificada</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="C18" t="str">
-        <v>Não especificada</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not evaluated</v>
+        <v>Not specified</v>
       </c>
       <c r="B19" t="str">
-        <v>Não avaliada</v>
+        <v>Não especificada</v>
       </c>
       <c r="C19" t="str">
-        <v>Não avaliada</v>
+        <v>Não especificada</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>PRMG interoperability</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B20" t="str">
-        <v>Interoperabilidade PRMG</v>
+        <v>Não avaliada</v>
       </c>
       <c r="C20" t="str">
-        <v>Interoperabilidade PRMG</v>
+        <v>Não avaliada</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Round-trip ΔE</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B21" t="str">
-        <v>ΔE de ida e volta</v>
+        <v>Interoperabilidade PRMG</v>
       </c>
       <c r="C21" t="str">
-        <v>ΔE de ida e volta</v>
+        <v>Interoperabilidade PRMG</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Count</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B22" t="str">
-        <v>Contagem</v>
+        <v>ΔE de ida e volta</v>
       </c>
       <c r="C22" t="str">
-        <v>Contagem</v>
+        <v>ΔE de ida e volta</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Share</v>
+        <v>Count</v>
       </c>
       <c r="B23" t="str">
-        <v>Proporção</v>
+        <v>Contagem</v>
       </c>
       <c r="C23" t="str">
-        <v>Proporção</v>
+        <v>Contagem</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Total</v>
+        <v>Share</v>
       </c>
       <c r="B24" t="str">
-        <v>Total</v>
+        <v>Proporção</v>
       </c>
       <c r="C24" t="str">
-        <v>Total</v>
+        <v>Proporção</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Total</v>
       </c>
       <c r="B25" t="str">
-        <v>PRMG não avaliado</v>
+        <v>Total</v>
       </c>
       <c r="C25" t="str">
-        <v>PRMG não avaliado</v>
+        <v>Total</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B26" t="str">
-        <v>Métricas de todo o perfil para uma intenção de renderização: o volume do gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e uma métrica de precisão de ida e volta. Escolha a intenção de renderização e o tipo de ida e volta — a tabela e o histograma são atualizados em conformidade.</v>
+        <v>PRMG não avaliado</v>
       </c>
       <c r="C26" t="str">
-        <v>Métricas de todo o perfil para uma intenção de renderização: o volume do gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e uma métrica de precisão de ida e volta. Escolha a intenção de renderização e o tipo de ida e volta — a tabela e o histograma são atualizados de acordo.</v>
+        <v>PRMG não avaliado</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Round-trip type</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B27" t="str">
-        <v>Tipo de ida e volta</v>
+        <v>Métricas de todo o perfil para uma intenção de renderização: o volume do gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e uma métrica de precisão de ida e volta. Escolha a intenção de renderização e o tipo de ida e volta — a tabela e o histograma são atualizados em conformidade.</v>
       </c>
       <c r="C27" t="str">
-        <v>Tipo de ida e volta</v>
+        <v>Métricas de todo o perfil para uma intenção de renderização: o volume do gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e uma métrica de precisão de ida e volta. Escolha a intenção de renderização e o tipo de ida e volta — a tabela e o histograma são atualizados de acordo.</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B28" t="str">
-        <v>Não afeta este tipo de ida e volta</v>
+        <v>Tipo de ida e volta</v>
       </c>
       <c r="C28" t="str">
-        <v>Não afeta este tipo de ida e volta</v>
+        <v>Tipo de ida e volta</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B29" t="str">
-        <v>Este tipo de ida e volta não está disponível para este perfil.</v>
+        <v>Não afeta este tipo de ida e volta</v>
       </c>
       <c r="C29" t="str">
-        <v>Este tipo de ida e volta não está disponível para este perfil.</v>
+        <v>Não afeta este tipo de ida e volta</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B30" t="str">
-        <v>Distribuição do ΔE de ida e volta</v>
+        <v>Este tipo de ida e volta não está disponível para este perfil.</v>
       </c>
       <c r="C30" t="str">
-        <v>Distribuição do ΔE de ida e volta</v>
+        <v>Este tipo de ida e volta não está disponível para este perfil.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B31" t="str">
-        <v>Nenhuma amostra de ida e volta caiu dentro da região avaliada.</v>
+        <v>Distribuição do ΔE de ida e volta</v>
       </c>
       <c r="C31" t="str">
-        <v>Nenhuma amostra de ida e volta caiu dentro da região avaliada.</v>
+        <v>Distribuição do ΔE de ida e volta</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Std Dev</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B32" t="str">
-        <v>Desvio padrão</v>
+        <v>Nenhuma amostra de ida e volta caiu dentro da região avaliada.</v>
       </c>
       <c r="C32" t="str">
-        <v>Desvio padrão</v>
+        <v>Nenhuma amostra de ida e volta caiu dentro da região avaliada.</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Relative frequency</v>
+        <v>Std Dev</v>
       </c>
       <c r="B33" t="str">
-        <v>Frequência relativa</v>
+        <v>Desvio padrão</v>
       </c>
       <c r="C33" t="str">
-        <v>Frequência relativa</v>
+        <v>Desvio padrão</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Cumulative frequency</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B34" t="str">
-        <v>Frequência cumulativa</v>
+        <v>Frequência relativa</v>
       </c>
       <c r="C34" t="str">
-        <v>Frequência cumulativa</v>
+        <v>Frequência relativa</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Horizontal scale</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B35" t="str">
-        <v>Escala horizontal</v>
+        <v>Frequência cumulativa</v>
       </c>
       <c r="C35" t="str">
-        <v>Escala horizontal</v>
+        <v>Frequência cumulativa</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Integer ΔE</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B36" t="str">
-        <v>ΔE inteiro</v>
+        <v>Escala horizontal</v>
       </c>
       <c r="C36" t="str">
-        <v>ΔE inteiro</v>
+        <v>Escala horizontal</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Auto-scale</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B37" t="str">
-        <v>Escala automática</v>
+        <v>ΔE inteiro</v>
       </c>
       <c r="C37" t="str">
-        <v>Escala automática</v>
+        <v>ΔE inteiro</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bins</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B38" t="str">
-        <v>Classes</v>
+        <v>Escala automática</v>
       </c>
       <c r="C38" t="str">
-        <v>Classes</v>
+        <v>Escala automática</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>CLUT Image</v>
+        <v>Bins</v>
       </c>
       <c r="B39" t="str">
-        <v>Imagem CLUT</v>
+        <v>Classes</v>
       </c>
       <c r="C39" t="str">
-        <v>Imagem CLUT</v>
+        <v>Classes</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B40" t="str">
-        <v>A tabela de consulta de cor (CLUT) de uma transformação dispositivo↔PCS, disposta em mosaico numa imagem. Escolha que tabela de intenção de renderização ver.</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C40" t="str">
-        <v>A tabela de consulta de cor (CLUT) de uma transformação dispositivo↔PCS, disposta em mosaico em uma imagem. Escolha qual tabela de intenção de renderização visualizar.</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B41" t="str">
-        <v>Este perfil não tem tabelas dispositivo↔PCS baseadas em CLUT para visualizar.</v>
+        <v>A tabela de consulta de cor (CLUT) de uma transformação dispositivo↔PCS, disposta em mosaico numa imagem. Escolha que tabela de intenção de renderização ver.</v>
       </c>
       <c r="C41" t="str">
-        <v>Este perfil não tem tabelas dispositivo↔PCS baseadas em CLUT para visualizar.</v>
+        <v>A tabela de consulta de cor (CLUT) de uma transformação dispositivo↔PCS, disposta em mosaico em uma imagem. Escolha qual tabela de intenção de renderização visualizar.</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Gamut Image</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B42" t="str">
-        <v>Imagem de gamut</v>
+        <v>Este perfil não tem tabelas dispositivo↔PCS baseadas em CLUT para visualizar.</v>
       </c>
       <c r="C42" t="str">
-        <v>Imagem de gamut</v>
+        <v>Este perfil não tem tabelas dispositivo↔PCS baseadas em CLUT para visualizar.</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B43" t="str">
-        <v>O mapa dentro/fora do gamut da etiqueta gamut: neutro onde uma cor PCS é reproduzível, vermelho onde fica fora do gamut do dispositivo.</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C43" t="str">
-        <v>O mapa dentro/fora do gamut da etiqueta gamut: neutro onde uma cor PCS é reproduzível, vermelho onde fica fora do gamut do dispositivo.</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B44" t="str">
-        <v>Este perfil não tem etiqueta gamut para visualizar.</v>
+        <v>O mapa dentro/fora do gamut da etiqueta gamut: neutro onde uma cor PCS é reproduzível, vermelho onde fica fora do gamut do dispositivo.</v>
       </c>
       <c r="C44" t="str">
-        <v>Este perfil não tem etiqueta gamut para visualizar.</v>
+        <v>O mapa dentro/fora do gamut da etiqueta gamut: neutro onde uma cor PCS é reproduzível, vermelho onde fica fora do gamut do dispositivo.</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B45" t="str">
-        <v>Escala vertical</v>
+        <v>Este perfil não tem etiqueta gamut para visualizar.</v>
       </c>
       <c r="C45" t="str">
-        <v>Escala vertical</v>
+        <v>Este perfil não tem etiqueta gamut para visualizar.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>X–Y</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B46" t="str">
-        <v>X–Y</v>
+        <v>Escala vertical</v>
       </c>
       <c r="C46" t="str">
-        <v>X–Y</v>
+        <v>Escala vertical</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Tone increase</v>
+        <v>X–Y</v>
       </c>
       <c r="B47" t="str">
-        <v>Aumento tonal</v>
+        <v>X–Y</v>
       </c>
       <c r="C47" t="str">
-        <v>Aumento tonal</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B48" t="str">
-        <v>Aumento tonal (saída − entrada)</v>
+        <v>Aumento tonal</v>
       </c>
       <c r="C48" t="str">
-        <v>Aumento tonal (saída − entrada)</v>
+        <v>Aumento tonal</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Show full dump</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B49" t="str">
-        <v>Mostrar despejo completo</v>
+        <v>Aumento tonal (saída − entrada)</v>
       </c>
       <c r="C49" t="str">
-        <v>Mostrar despejo completo</v>
+        <v>Aumento tonal (saída − entrada)</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Output truncated for performance.</v>
+        <v>Show full dump</v>
       </c>
       <c r="B50" t="str">
-        <v>Saída truncada por desempenho.</v>
+        <v>Mostrar despejo completo</v>
       </c>
       <c r="C50" t="str">
-        <v>Saída truncada por desempenho.</v>
+        <v>Mostrar despejo completo</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B51" t="str">
-        <v>Visão geral dentro do gamut (RT0)</v>
+        <v>Saída truncada por desempenho.</v>
       </c>
       <c r="C51" t="str">
-        <v>Visão geral dentro do gamut (RT0)</v>
+        <v>Saída truncada por desempenho.</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B52" t="str">
-        <v>Inversão + gamut (RT1)</v>
+        <v>Visão geral dentro do gamut (RT0)</v>
       </c>
       <c r="C52" t="str">
-        <v>Inversão + gamut (RT1)</v>
+        <v>Visão geral dentro do gamut (RT0)</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B53" t="str">
-        <v>Reprodutibilidade (RT2)</v>
+        <v>Inversão + gamut (RT1)</v>
       </c>
       <c r="C53" t="str">
-        <v>Reprodutibilidade (RT2)</v>
+        <v>Inversão + gamut (RT1)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>PRMG interoperability</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B54" t="str">
-        <v>Interoperabilidade PRMG</v>
+        <v>Reprodutibilidade (RT2)</v>
       </c>
       <c r="C54" t="str">
-        <v>Interoperabilidade PRMG</v>
+        <v>Reprodutibilidade (RT2)</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B55" t="str">
-        <v>Visão geral do iccviz: uma grelha de valores do dispositivo é levada ao PCS, de volta ao dispositivo e novamente ao PCS; o ΔE*ab é medido entre as duas passagens PCS. Uma verificação rápida de estabilidade dentro do gamut.</v>
+        <v>Interoperabilidade PRMG</v>
       </c>
       <c r="C55" t="str">
-        <v>Visão geral do iccviz: uma grade de valores do dispositivo é levada ao PCS, de volta ao dispositivo e novamente ao PCS; o ΔE*ab é medido entre as duas passagens PCS. Uma verificação rápida de estabilidade dentro do gamut.</v>
+        <v>Interoperabilidade PRMG</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B56" t="str">
-        <v>iccRoundTrip Ida e volta 1: ΔE*ab entre o PCS de cada cor do dispositivo e o seu PCS após uma ida e volta Lab → dispositivo → Lab. Reflete a precisão de inversão e o mapeamento de gamut.</v>
+        <v>Visão geral do iccviz: uma grelha de valores do dispositivo é levada ao PCS, de volta ao dispositivo e novamente ao PCS; o ΔE*ab é medido entre as duas passagens PCS. Uma verificação rápida de estabilidade dentro do gamut.</v>
       </c>
       <c r="C56" t="str">
-        <v>iccRoundTrip Ida e volta 1: ΔE*ab entre o PCS de cada cor do dispositivo e o seu PCS após uma ida e volta Lab → dispositivo → Lab. Reflete a precisão de inversão e o mapeamento de gamut.</v>
+        <v>Visão geral do iccviz: uma grade de valores do dispositivo é levada ao PCS, de volta ao dispositivo e novamente ao PCS; o ΔE*ab é medido entre as duas passagens PCS. Uma verificação rápida de estabilidade dentro do gamut.</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip Ida e volta 2: ΔE*ab entre a primeira e a segunda ida e volta — o quão estável é uma ida e volta de PCS repetida (reprodutibilidade, independente do recorte de gamut da primeira passagem).</v>
+        <v>iccRoundTrip Ida e volta 1: ΔE*ab entre o PCS de cada cor do dispositivo e o seu PCS após uma ida e volta Lab → dispositivo → Lab. Reflete a precisão de inversão e o mapeamento de gamut.</v>
       </c>
       <c r="C57" t="str">
-        <v>iccRoundTrip Ida e volta 2: ΔE*ab entre a primeira e a segunda ida e volta — o quão estável é uma ida e volta de PCS repetida (reprodutibilidade, independente do recorte de gamut da primeira passagem).</v>
+        <v>iccRoundTrip Ida e volta 1: ΔE*ab entre o PCS de cada cor do dispositivo e o seu PCS após uma ida e volta Lab → dispositivo → Lab. Reflete a precisão de inversão e o mapeamento de gamut.</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip PRMG: as cores PCS dentro do Perceptual Reference Medium Gamut fazem uma única ida e volta (Lab → dispositivo → Lab); a distribuição do ΔE*ab indica a interoperabilidade entre perfis.</v>
+        <v>iccRoundTrip Ida e volta 2: ΔE*ab entre a primeira e a segunda ida e volta — o quão estável é uma ida e volta de PCS repetida (reprodutibilidade, independente do recorte de gamut da primeira passagem).</v>
       </c>
       <c r="C58" t="str">
-        <v>iccRoundTrip PRMG: as cores PCS dentro do Perceptual Reference Medium Gamut fazem uma única ida e volta (Lab → dispositivo → Lab); a distribuição do ΔE*ab indica a interoperabilidade entre perfis.</v>
+        <v>iccRoundTrip Ida e volta 2: ΔE*ab entre a primeira e a segunda ida e volta — o quão estável é uma ida e volta de PCS repetida (reprodutibilidade, independente do recorte de gamut da primeira passagem).</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Settings</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B59" t="str">
-        <v>Definições</v>
+        <v>iccRoundTrip PRMG: as cores PCS dentro do Perceptual Reference Medium Gamut fazem uma única ida e volta (Lab → dispositivo → Lab); a distribuição do ΔE*ab indica a interoperabilidade entre perfis.</v>
       </c>
       <c r="C59" t="str">
-        <v>Configurações</v>
+        <v>iccRoundTrip PRMG: as cores PCS dentro do Perceptual Reference Medium Gamut fazem uma única ida e volta (Lab → dispositivo → Lab); a distribuição do ΔE*ab indica a interoperabilidade entre perfis.</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Display</v>
+        <v>Settings</v>
       </c>
       <c r="B60" t="str">
-        <v>Visualização</v>
+        <v>Definições</v>
       </c>
       <c r="C60" t="str">
-        <v>Exibição</v>
+        <v>Configurações</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Background</v>
+        <v>Display</v>
       </c>
       <c r="B61" t="str">
-        <v>Fundo</v>
+        <v>Visualização</v>
       </c>
       <c r="C61" t="str">
-        <v>Fundo</v>
+        <v>Exibição</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Language</v>
+        <v>Background</v>
       </c>
       <c r="B62" t="str">
-        <v>Idioma</v>
+        <v>Fundo</v>
       </c>
       <c r="C62" t="str">
-        <v>Idioma</v>
+        <v>Fundo</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>System</v>
+        <v>Language</v>
       </c>
       <c r="B63" t="str">
-        <v>Sistema</v>
+        <v>Idioma</v>
       </c>
       <c r="C63" t="str">
-        <v>Sistema</v>
+        <v>Idioma</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Light</v>
+        <v>System</v>
       </c>
       <c r="B64" t="str">
-        <v>Claro</v>
+        <v>Sistema</v>
       </c>
       <c r="C64" t="str">
-        <v>Claro</v>
+        <v>Sistema</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dark</v>
+        <v>Light</v>
       </c>
       <c r="B65" t="str">
-        <v>Escuro</v>
+        <v>Claro</v>
       </c>
       <c r="C65" t="str">
-        <v>Escuro</v>
+        <v>Claro</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>System default</v>
+        <v>Dark</v>
       </c>
       <c r="B66" t="str">
-        <v>Predefinição do sistema</v>
+        <v>Escuro</v>
       </c>
       <c r="C66" t="str">
-        <v>Padrão do sistema</v>
+        <v>Escuro</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Number format</v>
+        <v>System default</v>
       </c>
       <c r="B67" t="str">
-        <v>Formato numérico</v>
+        <v>Predefinição do sistema</v>
       </c>
       <c r="C67" t="str">
-        <v>Formato numérico</v>
+        <v>Padrão do sistema</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Hexadecimal</v>
+        <v>Number format</v>
       </c>
       <c r="B68" t="str">
-        <v>Hexadecimal</v>
+        <v>Formato numérico</v>
       </c>
       <c r="C68" t="str">
-        <v>Hexadecimal</v>
+        <v>Formato numérico</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="C69" t="str">
-        <v>Decimal</v>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Help</v>
+        <v>Decimal</v>
       </c>
       <c r="B70" t="str">
-        <v>Ajuda</v>
+        <v>Decimal</v>
       </c>
       <c r="C70" t="str">
-        <v>Ajuda</v>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Contact</v>
+        <v>Help</v>
       </c>
       <c r="B71" t="str">
-        <v>Contacto</v>
+        <v>Ajuda</v>
       </c>
       <c r="C71" t="str">
-        <v>Contato</v>
+        <v>Ajuda</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>User guide</v>
+        <v>Contact</v>
       </c>
       <c r="B72" t="str">
-        <v>Guia do utilizador</v>
+        <v>Contacto</v>
       </c>
       <c r="C72" t="str">
-        <v>Guia do usuário</v>
+        <v>Contato</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Search guide</v>
+        <v>User guide</v>
       </c>
       <c r="B73" t="str">
-        <v>Pesquisar no guia</v>
+        <v>Guia do utilizador</v>
       </c>
       <c r="C73" t="str">
-        <v>Pesquisar no guia</v>
+        <v>Guia do usuário</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search the user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B74" t="str">
-        <v>Pesquisar no guia do utilizador</v>
+        <v>Pesquisar no guia</v>
       </c>
       <c r="C74" t="str">
-        <v>Pesquisar no guia do usuário</v>
+        <v>Pesquisar no guia</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Previous match</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B75" t="str">
-        <v>Resultado anterior</v>
+        <v>Pesquisar no guia do utilizador</v>
       </c>
       <c r="C75" t="str">
-        <v>Resultado anterior</v>
+        <v>Pesquisar no guia do usuário</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Next match</v>
+        <v>Previous match</v>
       </c>
       <c r="B76" t="str">
-        <v>Resultado seguinte</v>
+        <v>Resultado anterior</v>
       </c>
       <c r="C76" t="str">
-        <v>Próximo resultado</v>
+        <v>Resultado anterior</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Close user guide</v>
+        <v>Next match</v>
       </c>
       <c r="B77" t="str">
-        <v>Fechar o guia</v>
+        <v>Resultado seguinte</v>
       </c>
       <c r="C77" t="str">
-        <v>Fechar o guia</v>
+        <v>Próximo resultado</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Loading…</v>
+        <v>Close user guide</v>
       </c>
       <c r="B78" t="str">
-        <v>A carregar…</v>
+        <v>Fechar o guia</v>
       </c>
       <c r="C78" t="str">
-        <v>Carregando…</v>
+        <v>Fechar o guia</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Loading…</v>
       </c>
       <c r="B79" t="str">
-        <v>Não foi possível carregar o guia do utilizador.</v>
+        <v>A carregar…</v>
       </c>
       <c r="C79" t="str">
-        <v>Não foi possível carregar o guia do usuário.</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>None</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B80" t="str">
-        <v>Nenhum</v>
+        <v>Não foi possível carregar o guia do utilizador.</v>
       </c>
       <c r="C80" t="str">
-        <v>Nenhum</v>
+        <v>Não foi possível carregar o guia do usuário.</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ICC Profile Tool</v>
+        <v>None</v>
       </c>
       <c r="B81" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Nenhum</v>
       </c>
       <c r="C81" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Nenhum</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Based on</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B82" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C82" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>demo implementation</v>
+        <v>Based on</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
       <c r="C83" t="str">
-        <v/>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Validating…</v>
+        <v>demo implementation</v>
       </c>
       <c r="B84" t="str">
-        <v>A validar…</v>
+        <v/>
       </c>
       <c r="C84" t="str">
-        <v>Validando…</v>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Save ICC profile</v>
+        <v>Validating…</v>
       </c>
       <c r="B85" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>A validar…</v>
       </c>
       <c r="C85" t="str">
-        <v>Salvar perfil ICC</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B86" t="str">
-        <v>● Modificado — não guardado</v>
+        <v>Guardar perfil ICC</v>
       </c>
       <c r="C86" t="str">
-        <v>● Modificado — não salvo</v>
+        <v>Salvar perfil ICC</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B87" t="str">
-        <v>Perfis</v>
+        <v>● Modificado — não guardado</v>
       </c>
       <c r="C87" t="str">
-        <v>Perfis</v>
+        <v>● Modificado — não salvo</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Show profile pool</v>
+        <v>Profiles</v>
       </c>
       <c r="B88" t="str">
-        <v>Mostrar o conjunto de perfis</v>
+        <v>Perfis</v>
       </c>
       <c r="C88" t="str">
-        <v>Mostrar o conjunto de perfis</v>
+        <v>Perfis</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Collapse</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B89" t="str">
-        <v>Recolher</v>
+        <v>Mostrar o conjunto de perfis</v>
       </c>
       <c r="C89" t="str">
-        <v>Recolher</v>
+        <v>Mostrar o conjunto de perfis</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Load Profiles</v>
+        <v>Collapse</v>
       </c>
       <c r="B90" t="str">
-        <v>Carregar perfis</v>
+        <v>Recolher</v>
       </c>
       <c r="C90" t="str">
-        <v>Carregar perfis</v>
+        <v>Recolher</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Remove</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B91" t="str">
-        <v>Remover</v>
+        <v>Carregar perfis</v>
       </c>
       <c r="C91" t="str">
-        <v>Remover</v>
+        <v>Carregar perfis</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Remove</v>
       </c>
       <c r="B92" t="str">
-        <v>Largue perfis ICC aqui</v>
+        <v>Remover</v>
       </c>
       <c r="C92" t="str">
-        <v>Solte perfis ICC aqui</v>
+        <v>Remover</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B93" t="str">
-        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o respetivo perfil incorporado — os ficheiros permanecem no seu dispositivo.</v>
+        <v>Largue perfis ICC aqui</v>
       </c>
       <c r="C93" t="str">
-        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o perfil incorporado — os arquivos permanecem no seu dispositivo.</v>
+        <v>Solte perfis ICC aqui</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>New from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B94" t="str">
-        <v>Novo a partir de .cube</v>
+        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o respetivo perfil incorporado — os ficheiros permanecem no seu dispositivo.</v>
       </c>
       <c r="C94" t="str">
-        <v>Novo a partir de .cube</v>
+        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o perfil incorporado — os arquivos permanecem no seu dispositivo.</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Sort by name</v>
+        <v>New from .cube</v>
       </c>
       <c r="B95" t="str">
-        <v>Ordenar por nome</v>
+        <v>Novo a partir de .cube</v>
       </c>
       <c r="C95" t="str">
-        <v>Ordenar por nome</v>
+        <v>Novo a partir de .cube</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>A–Z</v>
+        <v>Sort by name</v>
       </c>
       <c r="B96" t="str">
-        <v>A–Z</v>
+        <v>Ordenar por nome</v>
       </c>
       <c r="C96" t="str">
-        <v>A–Z</v>
+        <v>Ordenar por nome</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>New profile from .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="B97" t="str">
-        <v>Novo perfil a partir de .cube</v>
+        <v>A–Z</v>
       </c>
       <c r="C97" t="str">
-        <v>Novo perfil a partir de .cube</v>
+        <v>A–Z</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New profile from .cube</v>
       </c>
       <c r="B98" t="str">
-        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e transferido.</v>
+        <v>Novo perfil a partir de .cube</v>
       </c>
       <c r="C98" t="str">
-        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e baixado.</v>
+        <v>Novo perfil a partir de .cube</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Choose .cube file</v>
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
       </c>
       <c r="B99" t="str">
-        <v>Escolher ficheiro .cube</v>
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e transferido.</v>
       </c>
       <c r="C99" t="str">
-        <v>Escolher arquivo .cube</v>
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e baixado.</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Escolher ficheiro .cube</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Escolher arquivo .cube</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B101" t="str">
         <v>ou largue-o aqui, ou cole abaixo</v>
       </c>
-      <c r="C100" t="str">
+      <c r="C101" t="str">
         <v>ou solte-o aqui, ou cole abaixo</v>
       </c>
     </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str" xml:space="preserve">
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B101" t="str" xml:space="preserve">
+      <c r="B102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="C101" t="str" xml:space="preserve">
+      <c r="C102" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B102" t="str">
-        <v>Cancelar</v>
-      </c>
-      <c r="C102" t="str">
-        <v>Cancelar</v>
-      </c>
-    </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Create DeviceLink</v>
+        <v>Cancel</v>
       </c>
       <c r="B103" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Cancelar</v>
       </c>
       <c r="C103" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Creating…</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B104" t="str">
-        <v>A criar…</v>
+        <v>Criar DeviceLink</v>
       </c>
       <c r="C104" t="str">
-        <v>Criando…</v>
+        <v>Criar DeviceLink</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Could not read that file.</v>
+        <v>Creating…</v>
       </c>
       <c r="B105" t="str">
-        <v>Não foi possível ler esse ficheiro.</v>
+        <v>A criar…</v>
       </c>
       <c r="C105" t="str">
-        <v>Não foi possível ler esse arquivo.</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Profile</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B106" t="str">
-        <v>Perfil</v>
+        <v>Não foi possível ler esse ficheiro.</v>
       </c>
       <c r="C106" t="str">
-        <v>Perfil</v>
+        <v>Não foi possível ler esse arquivo.</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Compare</v>
+        <v>Profile</v>
       </c>
       <c r="B107" t="str">
-        <v>Comparar</v>
+        <v>Perfil</v>
       </c>
       <c r="C107" t="str">
-        <v>Comparar</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Combine</v>
+        <v>Compare</v>
       </c>
       <c r="B108" t="str">
-        <v>Ligar</v>
+        <v>Comparar</v>
       </c>
       <c r="C108" t="str">
-        <v>Vincular</v>
+        <v>Comparar</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Spectral</v>
+        <v>Combine</v>
       </c>
       <c r="B109" t="str">
-        <v>Espectral</v>
+        <v>Ligar</v>
       </c>
       <c r="C109" t="str">
-        <v>Espectral</v>
+        <v>Vincular</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Spectral</v>
       </c>
       <c r="B110" t="str">
-        <v>Arraste perfis do conjunto para este separador</v>
+        <v>Espectral</v>
       </c>
       <c r="C110" t="str">
-        <v>Arraste perfis do conjunto para esta aba</v>
+        <v>Espectral</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Remove</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B111" t="str">
-        <v>Remover</v>
+        <v>Arraste perfis do conjunto para este separador</v>
       </c>
       <c r="C111" t="str">
-        <v>Remover</v>
+        <v>Arraste perfis do conjunto para esta aba</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>No profile selected</v>
+        <v>Remove</v>
       </c>
       <c r="B112" t="str">
-        <v>Nenhum perfil selecionado</v>
+        <v>Remover</v>
       </c>
       <c r="C112" t="str">
-        <v>Nenhum perfil selecionado</v>
+        <v>Remover</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>No profile selected</v>
       </c>
       <c r="B113" t="str">
-        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
       <c r="C113" t="str">
-        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B114" t="str">
-        <v>Ainda nada para comparar</v>
+        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
       </c>
       <c r="C114" t="str">
-        <v>Ainda nada para comparar</v>
+        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B115" t="str">
-        <v>Arraste um ou mais perfis para o separador Comparar.</v>
+        <v>Ainda nada para comparar</v>
       </c>
       <c r="C115" t="str">
-        <v>Arraste um ou mais perfis para a aba Comparar.</v>
+        <v>Ainda nada para comparar</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Gamut comparison</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B116" t="str">
-        <v>Comparação de gamut</v>
+        <v>Arraste um ou mais perfis para o separador Comparar.</v>
       </c>
       <c r="C116" t="str">
-        <v>Comparação de gamut</v>
+        <v>Arraste um ou mais perfis para a aba Comparar.</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B117" t="str">
-        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
+        <v>Comparação de gamut</v>
       </c>
       <c r="C117" t="str">
-        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
+        <v>Comparação de gamut</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Rendering intent</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B118" t="str">
-        <v>Intenção de renderização</v>
+        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
       <c r="C118" t="str">
-        <v>Intenção de renderização</v>
+        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Shell</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B119" t="str">
-        <v>Invólucro</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C119" t="str">
-        <v>Invólucro</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Wireframe</v>
+        <v>Shell</v>
       </c>
       <c r="B120" t="str">
-        <v>Malha de arame</v>
+        <v>Invólucro</v>
       </c>
       <c r="C120" t="str">
-        <v>Malha de arame</v>
+        <v>Invólucro</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Axis numbers</v>
+        <v>Wireframe</v>
       </c>
       <c r="B121" t="str">
-        <v>Números dos eixos</v>
+        <v>Malha de arame</v>
       </c>
       <c r="C121" t="str">
-        <v>Números dos eixos</v>
+        <v>Malha de arame</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Opacity</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B122" t="str">
-        <v>Opacidade</v>
+        <v>Números dos eixos</v>
       </c>
       <c r="C122" t="str">
-        <v>Opacidade</v>
+        <v>Números dos eixos</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Colour</v>
+        <v>Opacity</v>
       </c>
       <c r="B123" t="str">
-        <v>Cor</v>
+        <v>Opacidade</v>
       </c>
       <c r="C123" t="str">
-        <v>Cor</v>
+        <v>Opacidade</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Solid</v>
+        <v>Colour</v>
       </c>
       <c r="B124" t="str">
-        <v>Sólido</v>
+        <v>Cor</v>
       </c>
       <c r="C124" t="str">
-        <v>Sólido</v>
+        <v>Cor</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>By value</v>
+        <v>Solid</v>
       </c>
       <c r="B125" t="str">
-        <v>Por valor</v>
+        <v>Sólido</v>
       </c>
       <c r="C125" t="str">
-        <v>Por valor</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By hue</v>
+        <v>By value</v>
       </c>
       <c r="B126" t="str">
-        <v>Por matiz</v>
+        <v>Por valor</v>
       </c>
       <c r="C126" t="str">
-        <v>Por matiz</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Rotation</v>
+        <v>By hue</v>
       </c>
       <c r="B127" t="str">
-        <v>Rotação</v>
+        <v>Por matiz</v>
       </c>
       <c r="C127" t="str">
-        <v>Rotação</v>
+        <v>Por matiz</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Turntable</v>
+        <v>Rotation</v>
       </c>
       <c r="B128" t="str">
-        <v>Prato giratório</v>
+        <v>Rotação</v>
       </c>
       <c r="C128" t="str">
-        <v>Prato giratório</v>
+        <v>Rotação</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Orbit</v>
+        <v>Turntable</v>
       </c>
       <c r="B129" t="str">
-        <v>Órbita</v>
+        <v>Prato giratório</v>
       </c>
       <c r="C129" t="str">
-        <v>Órbita</v>
+        <v>Prato giratório</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Drag speed</v>
+        <v>Orbit</v>
       </c>
       <c r="B130" t="str">
-        <v>Velocidade de arrasto</v>
+        <v>Órbita</v>
       </c>
       <c r="C130" t="str">
-        <v>Velocidade de arrasto</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Roll</v>
+        <v>Drag speed</v>
       </c>
       <c r="B131" t="str">
-        <v>Rolamento</v>
+        <v>Velocidade de arrasto</v>
       </c>
       <c r="C131" t="str">
-        <v>Rolagem</v>
+        <v>Velocidade de arrasto</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll speed</v>
+        <v>Roll</v>
       </c>
       <c r="B132" t="str">
-        <v>Velocidade de rolamento</v>
+        <v>Rolamento</v>
       </c>
       <c r="C132" t="str">
-        <v>Velocidade de rolagem</v>
+        <v>Rolagem</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Building gamut…</v>
+        <v>Roll speed</v>
       </c>
       <c r="B133" t="str">
-        <v>A construir o gamut…</v>
+        <v>Velocidade de rolamento</v>
       </c>
       <c r="C133" t="str">
-        <v>Construindo o gamut…</v>
+        <v>Velocidade de rolagem</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>no gamut</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B134" t="str">
-        <v>sem gamut</v>
+        <v>A construir o gamut…</v>
       </c>
       <c r="C134" t="str">
-        <v>sem gamut</v>
+        <v>Construindo o gamut…</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Show / hide</v>
+        <v>no gamut</v>
       </c>
       <c r="B135" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>sem gamut</v>
       </c>
       <c r="C135" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>sem gamut</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>3-D gamut shell</v>
+        <v>Show / hide</v>
       </c>
       <c r="B136" t="str">
-        <v>Invólucro de gamut 3D</v>
+        <v>Mostrar / ocultar</v>
       </c>
       <c r="C136" t="str">
-        <v>Invólucro de gamut 3D</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2-D gamut slice</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B137" t="str">
-        <v>Corte de gamut 2D</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
       <c r="C137" t="str">
-        <v>Corte de gamut 2D</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Plane</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B138" t="str">
-        <v>Plano</v>
+        <v>Corte de gamut 2D</v>
       </c>
       <c r="C138" t="str">
-        <v>Plano</v>
+        <v>Corte de gamut 2D</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>L*</v>
+        <v>Plane</v>
       </c>
       <c r="B139" t="str">
-        <v>L*</v>
+        <v>Plano</v>
       </c>
       <c r="C139" t="str">
-        <v>L*</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="B140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
       <c r="C140" t="str">
-        <v>a*</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="B141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
       <c r="C141" t="str">
-        <v>b*</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>b*</v>
       </c>
       <c r="B142" t="str">
-        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
+        <v>b*</v>
       </c>
       <c r="C142" t="str">
-        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Linking</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B143" t="str">
-        <v>Ligação</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
       <c r="C143" t="str">
-        <v>Vínculo</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>Linking</v>
       </c>
       <c r="B144" t="str">
-        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
+        <v>Ligação</v>
       </c>
       <c r="C144" t="str">
-        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
+        <v>Vínculo</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B145" t="str">
-        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
       </c>
       <c r="C145" t="str">
-        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Observer Change</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B146" t="str">
-        <v>Criador de ecrã V4</v>
+        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
       </c>
       <c r="C146" t="str">
-        <v>Criador de tela V4</v>
+        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Observer Change</v>
       </c>
       <c r="B147" t="str">
-        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
+        <v>Criador de ecrã V4</v>
       </c>
       <c r="C147" t="str">
-        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
+        <v>Criador de tela V4</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>V5 RGB display</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B148" t="str">
-        <v>Ecrã RGB V5</v>
+        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
       </c>
       <c r="C148" t="str">
-        <v>Tela RGB V5</v>
+        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>drop a display profile</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B149" t="str">
-        <v>largue um perfil de ecrã</v>
+        <v>Ecrã RGB V5</v>
       </c>
       <c r="C149" t="str">
-        <v>solte um perfil de tela</v>
+        <v>Tela RGB V5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B150" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>largue um perfil de ecrã</v>
       </c>
       <c r="C150" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>solte um perfil de tela</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>drop an observer profile</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B151" t="str">
-        <v>largue um perfil de observador</v>
+        <v>Observador V5 (PCC)</v>
       </c>
       <c r="C151" t="str">
-        <v>solte um perfil de observador</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B152" t="str">
-        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
+        <v>largue um perfil de observador</v>
       </c>
       <c r="C152" t="str">
-        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
+        <v>solte um perfil de observador</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B153" t="str">
-        <v>Criar perfil de ecrã V4</v>
+        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
       </c>
       <c r="C153" t="str">
-        <v>Criar perfil de tela V4</v>
+        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Profile name</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Nome do perfil</v>
+        <v>Criar perfil de ecrã V4</v>
       </c>
       <c r="C154" t="str">
-        <v>Nome do perfil</v>
+        <v>Criar perfil de tela V4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Create</v>
+        <v>Profile name</v>
       </c>
       <c r="B155" t="str">
-        <v>Criar</v>
+        <v>Nome do perfil</v>
       </c>
       <c r="C155" t="str">
-        <v>Criar</v>
+        <v>Nome do perfil</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Making…</v>
+        <v>Create</v>
       </c>
       <c r="B156" t="str">
-        <v>A criar…</v>
+        <v>Criar</v>
       </c>
       <c r="C156" t="str">
-        <v>Criando…</v>
+        <v>Criar</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B157" t="str">
-        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
+        <v>A criar…</v>
       </c>
       <c r="C157" t="str">
-        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Link Pipeline</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B158" t="str">
-        <v>Fluxo de ligação</v>
+        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C158" t="str">
-        <v>Fluxo de vinculação</v>
+        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B159" t="str">
-        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
+        <v>Fluxo de ligação</v>
       </c>
       <c r="C159" t="str">
-        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
+        <v>Fluxo de vinculação</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Done</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B160" t="str">
-        <v>Concluído</v>
+        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
       </c>
       <c r="C160" t="str">
-        <v>Concluído</v>
+        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Done</v>
       </c>
       <c r="B161" t="str">
-        <v>Largue uma imagem para transformar (TIFF/PNG/JPEG)</v>
+        <v>Concluído</v>
       </c>
       <c r="C161" t="str">
-        <v>Solte uma imagem para transformar (TIFF/PNG/JPEG)</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Checking image…</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B162" t="str">
-        <v>A verificar imagem…</v>
+        <v>Largue uma imagem para transformar (TIFF/PNG/JPEG)</v>
       </c>
       <c r="C162" t="str">
-        <v>Verificando imagem…</v>
+        <v>Solte uma imagem para transformar (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Checking image…</v>
       </c>
       <c r="B163" t="str">
-        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
+        <v>A verificar imagem…</v>
       </c>
       <c r="C163" t="str">
-        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
+        <v>Verificando imagem…</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B164" t="str">
-        <v>Imagem demasiado grande ({mp} MP; limite {max} MP).</v>
+        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
       </c>
       <c r="C164" t="str">
-        <v>Imagem grande demais ({mp} MP; limite {max} MP).</v>
+        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Transform Image</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B165" t="str">
-        <v>Transformar imagem</v>
+        <v>Imagem demasiado grande ({mp} MP; limite {max} MP).</v>
       </c>
       <c r="C165" t="str">
-        <v>Transformar imagem</v>
+        <v>Imagem grande demais ({mp} MP; limite {max} MP).</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transforming…</v>
+        <v>Transform Image</v>
       </c>
       <c r="B166" t="str">
-        <v>A transformar…</v>
+        <v>Transformar imagem</v>
       </c>
       <c r="C166" t="str">
-        <v>Transformando…</v>
+        <v>Transformar imagem</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Transforming…</v>
       </c>
       <c r="B167" t="str">
-        <v>Largue perfis para iniciar a cadeia</v>
+        <v>A transformar…</v>
       </c>
       <c r="C167" t="str">
-        <v>Solte perfis para iniciar a cadeia</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>removed</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B168" t="str">
-        <v>removido</v>
+        <v>Largue perfis para iniciar a cadeia</v>
       </c>
       <c r="C168" t="str">
-        <v>removido</v>
+        <v>Solte perfis para iniciar a cadeia</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Move earlier</v>
+        <v>removed</v>
       </c>
       <c r="B169" t="str">
-        <v>Mover antes</v>
+        <v>removido</v>
       </c>
       <c r="C169" t="str">
-        <v>Mover antes</v>
+        <v>removido</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move later</v>
+        <v>Move earlier</v>
       </c>
       <c r="B170" t="str">
-        <v>Mover depois</v>
+        <v>Mover antes</v>
       </c>
       <c r="C170" t="str">
-        <v>Mover depois</v>
+        <v>Mover antes</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move up</v>
+        <v>Move later</v>
       </c>
       <c r="B171" t="str">
-        <v>Mover para cima</v>
+        <v>Mover depois</v>
       </c>
       <c r="C171" t="str">
-        <v>Mover para cima</v>
+        <v>Mover depois</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move down</v>
+        <v>Move up</v>
       </c>
       <c r="B172" t="str">
-        <v>Mover para baixo</v>
+        <v>Mover para cima</v>
       </c>
       <c r="C172" t="str">
-        <v>Mover para baixo</v>
+        <v>Mover para cima</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move down</v>
       </c>
       <c r="B173" t="str">
-        <v>Intenção de renderização (todas)</v>
+        <v>Mover para baixo</v>
       </c>
       <c r="C173" t="str">
-        <v>Intenção de renderização (todas)</v>
+        <v>Mover para baixo</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B174" t="str">
-        <v>Intenção de renderização para esta transformação</v>
+        <v>Intenção de renderização (todas)</v>
       </c>
       <c r="C174" t="str">
-        <v>Intenção de renderização para esta transformação</v>
+        <v>Intenção de renderização (todas)</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B175" t="str">
-        <v>As transformações usam intenções de renderização diferentes</v>
+        <v>Intenção de renderização para esta transformação</v>
       </c>
       <c r="C175" t="str">
-        <v>As transformações usam intenções de renderização diferentes</v>
+        <v>Intenção de renderização para esta transformação</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B176" t="str">
-        <v>Inverter direção da cadeia (inverte a transformação inicial e propaga-se por toda a cadeia)</v>
+        <v>As transformações usam intenções de renderização diferentes</v>
       </c>
       <c r="C176" t="str">
-        <v>Inverter direção da cadeia (inverte a transformação inicial e se propaga por toda a cadeia)</v>
+        <v>As transformações usam intenções de renderização diferentes</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B177" t="str">
-        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
+        <v>Inverter direção da cadeia (inverte a transformação inicial e propaga-se por toda a cadeia)</v>
       </c>
       <c r="C177" t="str">
-        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
+        <v>Inverter direção da cadeia (inverte a transformação inicial e se propaga por toda a cadeia)</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Chain</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B178" t="str">
-        <v>Cadeia</v>
+        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
       </c>
       <c r="C178" t="str">
-        <v>Cadeia</v>
+        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Chain</v>
       </c>
       <c r="B179" t="str">
-        <v>Não foi possível analisar a cadeia.</v>
+        <v>Cadeia</v>
       </c>
       <c r="C179" t="str">
-        <v>Não foi possível analisar a cadeia.</v>
+        <v>Cadeia</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Checking chain…</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B180" t="str">
-        <v>A verificar cadeia…</v>
+        <v>Não foi possível analisar a cadeia.</v>
       </c>
       <c r="C180" t="str">
-        <v>Verificando cadeia…</v>
+        <v>Não foi possível analisar a cadeia.</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B181" t="str">
-        <v>A cadeia não liga ({detail}).</v>
+        <v>A verificar cadeia…</v>
       </c>
       <c r="C181" t="str">
-        <v>A cadeia não conecta ({detail}).</v>
+        <v>Verificando cadeia…</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B182" t="str">
-        <v>O perfil {n} não liga à etapa anterior ({detail}).</v>
+        <v>A cadeia não liga ({detail}).</v>
       </c>
       <c r="C182" t="str">
-        <v>O perfil {n} não conecta com a etapa anterior ({detail}).</v>
+        <v>A cadeia não conecta ({detail}).</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B183" t="str">
-        <v>Corrija a cadeia antes de processar imagens</v>
+        <v>O perfil {n} não liga à etapa anterior ({detail}).</v>
       </c>
       <c r="C183" t="str">
-        <v>Corrija a cadeia antes de processar imagens</v>
+        <v>O perfil {n} não conecta com a etapa anterior ({detail}).</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Clear</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B184" t="str">
-        <v>Limpar</v>
+        <v>Corrija a cadeia antes de processar imagens</v>
       </c>
       <c r="C184" t="str">
-        <v>Limpar</v>
+        <v>Corrija a cadeia antes de processar imagens</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Make DeviceLink</v>
+        <v>Clear</v>
       </c>
       <c r="B185" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Limpar</v>
       </c>
       <c r="C185" t="str">
-        <v>Criar DeviceLink</v>
+        <v>Limpar</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>DeviceLink name</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B186" t="str">
-        <v>Nome do DeviceLink</v>
+        <v>Criar DeviceLink</v>
       </c>
       <c r="C186" t="str">
-        <v>Nome do DeviceLink</v>
+        <v>Criar DeviceLink</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Making…</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B187" t="str">
-        <v>A criar…</v>
+        <v>Nome do DeviceLink</v>
       </c>
       <c r="C187" t="str">
-        <v>Criando…</v>
+        <v>Nome do DeviceLink</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Making…</v>
       </c>
       <c r="B188" t="str">
-        <v>Criado “{name}” — adicionado ao conjunto e a este separador.</v>
+        <v>A criar…</v>
       </c>
       <c r="C188" t="str">
-        <v>Criado “{name}” — adicionado ao conjunto e a esta aba.</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B189" t="str">
-        <v>Largue imagens {src} para converter para {dst} — os resultados são descarregados, nada é armazenado.</v>
+        <v>Criado “{name}” — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C189" t="str">
-        <v>Solte imagens {src} para converter para {dst} — os resultados são baixados, nada é armazenado.</v>
+        <v>Criado “{name}” — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Build a chain to process images</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B190" t="str">
-        <v>Crie uma cadeia para processar imagens</v>
+        <v>Largue imagens {src} para converter para {dst} — os resultados são descarregados, nada é armazenado.</v>
       </c>
       <c r="C190" t="str">
-        <v>Crie uma cadeia para processar imagens</v>
+        <v>Solte imagens {src} para converter para {dst} — os resultados são baixados, nada é armazenado.</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B191" t="str">
-        <v>Esta cadeia não começa nem termina num espaço de cor de imagem</v>
+        <v>Crie uma cadeia para processar imagens</v>
       </c>
       <c r="C191" t="str">
-        <v>Esta cadeia não começa nem termina em um espaço de cor de imagem</v>
+        <v>Crie uma cadeia para processar imagens</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Saved the transformed image.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B192" t="str">
-        <v>Imagem transformada guardada.</v>
+        <v>Esta cadeia não começa nem termina num espaço de cor de imagem</v>
       </c>
       <c r="C192" t="str">
-        <v>Imagem transformada salva.</v>
+        <v>Esta cadeia não começa nem termina em um espaço de cor de imagem</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B193" t="str">
-        <v>Largue um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
+        <v>Imagem transformada guardada.</v>
       </c>
       <c r="C193" t="str">
-        <v>Solte um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
+        <v>Imagem transformada salva.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Could not read that file.</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B194" t="str">
-        <v>Não foi possível ler esse ficheiro.</v>
+        <v>Largue um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="C194" t="str">
-        <v>Não foi possível ler esse arquivo.</v>
+        <v>Solte um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Data file too large.</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B195" t="str">
-        <v>Ficheiro de dados demasiado grande.</v>
+        <v>Não foi possível ler esse ficheiro.</v>
       </c>
       <c r="C195" t="str">
-        <v>Arquivo de dados grande demais.</v>
+        <v>Não foi possível ler esse arquivo.</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Transform Data</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B196" t="str">
-        <v>Transformar dados</v>
+        <v>Ficheiro de dados demasiado grande.</v>
       </c>
       <c r="C196" t="str">
-        <v>Transformar dados</v>
+        <v>Arquivo de dados grande demais.</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transforming…</v>
+        <v>Transform Data</v>
       </c>
       <c r="B197" t="str">
-        <v>A transformar…</v>
+        <v>Transformar dados</v>
       </c>
       <c r="C197" t="str">
-        <v>Transformando…</v>
+        <v>Transformar dados</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Prefer</v>
+        <v>Transforming…</v>
       </c>
       <c r="B198" t="str">
-        <v>Preferir</v>
+        <v>A transformar…</v>
       </c>
       <c r="C198" t="str">
-        <v>Preferir</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Observer</v>
+        <v>Prefer</v>
       </c>
       <c r="B199" t="str">
-        <v>Observador</v>
+        <v>Preferir</v>
       </c>
       <c r="C199" t="str">
-        <v>Observador</v>
+        <v>Preferir</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Illuminant</v>
+        <v>Observer</v>
       </c>
       <c r="B200" t="str">
-        <v>Iluminante</v>
+        <v>Observador</v>
       </c>
       <c r="C200" t="str">
-        <v>Iluminante</v>
+        <v>Observador</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Condition</v>
+        <v>Illuminant</v>
       </c>
       <c r="B201" t="str">
-        <v>Condição</v>
+        <v>Iluminante</v>
       </c>
       <c r="C201" t="str">
-        <v>Condição</v>
+        <v>Iluminante</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Condition</v>
       </c>
       <c r="B202" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>Condição</v>
       </c>
       <c r="C202" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>Condição</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>median</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B203" t="str">
-        <v>mediana</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
       <c r="C203" t="str">
-        <v>mediana</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>mean</v>
+        <v>median</v>
       </c>
       <c r="B204" t="str">
-        <v>média</v>
+        <v>mediana</v>
       </c>
       <c r="C204" t="str">
-        <v>média</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>patches</v>
+        <v>mean</v>
       </c>
       <c r="B205" t="str">
-        <v>patches</v>
+        <v>média</v>
       </c>
       <c r="C205" t="str">
-        <v>patches</v>
+        <v>média</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>{n} duplicates</v>
+        <v>patches</v>
       </c>
       <c r="B206" t="str">
-        <v>{n} duplicados</v>
+        <v>patches</v>
       </c>
       <c r="C206" t="str">
-        <v>{n} duplicados</v>
+        <v>patches</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Transform result</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B207" t="str">
-        <v>Resultado da transformação</v>
+        <v>{n} duplicados</v>
       </c>
       <c r="C207" t="str">
-        <v>Resultado da transformação</v>
+        <v>{n} duplicados</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Transform result</v>
       </c>
       <c r="B208" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Resultado da transformação</v>
       </c>
       <c r="C208" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>Resultado da transformação</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B209" t="str">
-        <v>A mostrar os primeiros {shown} de {total} — Guardar grava todos.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="C209" t="str">
-        <v>Mostrando os primeiros {shown} de {total} — Salvar grava todos.</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Save as</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B210" t="str">
-        <v>Guardar como</v>
+        <v>A mostrar os primeiros {shown} de {total} — Guardar grava todos.</v>
       </c>
       <c r="C210" t="str">
-        <v>Salvar como</v>
+        <v>Mostrando os primeiros {shown} de {total} — Salvar grava todos.</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save</v>
+        <v>Save as</v>
       </c>
       <c r="B211" t="str">
-        <v>Guardar</v>
+        <v>Guardar como</v>
       </c>
       <c r="C211" t="str">
-        <v>Salvar</v>
+        <v>Salvar como</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Invert Transform</v>
+        <v>Save</v>
       </c>
       <c r="B212" t="str">
-        <v>Inverter transformação</v>
+        <v>Guardar</v>
       </c>
       <c r="C212" t="str">
-        <v>Inverter transformação</v>
+        <v>Salvar</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Inverting…</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B213" t="str">
-        <v>A inverter…</v>
+        <v>Inverter transformação</v>
       </c>
       <c r="C213" t="str">
-        <v>Invertendo…</v>
+        <v>Inverter transformação</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Invert</v>
+        <v>Inverting…</v>
       </c>
       <c r="B214" t="str">
-        <v>Inverter</v>
+        <v>A inverter…</v>
       </c>
       <c r="C214" t="str">
-        <v>Inverter</v>
+        <v>Invertendo…</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>last stage</v>
+        <v>Invert</v>
       </c>
       <c r="B215" t="str">
-        <v>última etapa</v>
+        <v>Inverter</v>
       </c>
       <c r="C215" t="str">
-        <v>última etapa</v>
+        <v>Inverter</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>first stage</v>
+        <v>last stage</v>
       </c>
       <c r="B216" t="str">
-        <v>primeira etapa</v>
+        <v>última etapa</v>
       </c>
       <c r="C216" t="str">
-        <v>primeira etapa</v>
+        <v>última etapa</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>first stage</v>
       </c>
       <c r="B217" t="str">
-        <v>Dados em {in} → procurar {out}</v>
+        <v>primeira etapa</v>
       </c>
       <c r="C217" t="str">
-        <v>Dados em {in} → buscar {out}</v>
+        <v>primeira etapa</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B218" t="str">
-        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
+        <v>Dados em {in} → procurar {out}</v>
       </c>
       <c r="C218" t="str">
-        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
+        <v>Dados em {in} → buscar {out}</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B219" t="str">
-        <v>O conjunto de dados deve estar em {in}; a procura inversa produz {out} mais um custo de invertibilidade por patch.</v>
+        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
       </c>
       <c r="C219" t="str">
-        <v>O conjunto de dados deve estar em {in}; a busca inversa produz {out} mais um custo de invertibilidade por patch.</v>
+        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>ΔE cost</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B220" t="str">
-        <v>Custo ΔE</v>
+        <v>O conjunto de dados deve estar em {in}; a procura inversa produz {out} mais um custo de invertibilidade por patch.</v>
       </c>
       <c r="C220" t="str">
-        <v>Custo ΔE</v>
+        <v>O conjunto de dados deve estar em {in}; a busca inversa produz {out} mais um custo de invertibilidade por patch.</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B221" t="str">
-        <v>Esta imagem tem um perfil ICC incorporado.</v>
+        <v>Custo ΔE</v>
       </c>
       <c r="C221" t="str">
-        <v>Esta imagem tem um perfil ICC incorporado.</v>
+        <v>Custo ΔE</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B222" t="str">
-        <v>Extrair e adicionar à cadeia</v>
+        <v>Esta imagem tem um perfil ICC incorporado.</v>
       </c>
       <c r="C222" t="str">
-        <v>Extrair e adicionar à cadeia</v>
+        <v>Esta imagem tem um perfil ICC incorporado.</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extracting…</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B223" t="str">
-        <v>A extrair…</v>
+        <v>Extrair e adicionar à cadeia</v>
       </c>
       <c r="C223" t="str">
-        <v>Extraindo…</v>
+        <v>Extrair e adicionar à cadeia</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Dismiss</v>
+        <v>Extracting…</v>
       </c>
       <c r="B224" t="str">
-        <v>Dispensar</v>
+        <v>A extrair…</v>
       </c>
       <c r="C224" t="str">
-        <v>Dispensar</v>
+        <v>Extraindo…</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>Dismiss</v>
       </c>
       <c r="B225" t="str">
-        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro lugar na cadeia.</v>
+        <v>Dispensar</v>
       </c>
       <c r="C225" t="str">
-        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro na cadeia.</v>
+        <v>Dispensar</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Image output options</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B226" t="str">
-        <v>Opções de saída de imagem</v>
+        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro lugar na cadeia.</v>
       </c>
       <c r="C226" t="str">
-        <v>Opções de saída de imagem</v>
+        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro na cadeia.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Encoding</v>
+        <v>Image output options</v>
       </c>
       <c r="B227" t="str">
-        <v>Codificação</v>
+        <v>Opções de saída de imagem</v>
       </c>
       <c r="C227" t="str">
-        <v>Codificação</v>
+        <v>Opções de saída de imagem</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Same as source</v>
+        <v>Encoding</v>
       </c>
       <c r="B228" t="str">
-        <v>Igual à origem</v>
+        <v>Codificação</v>
       </c>
       <c r="C228" t="str">
-        <v>Igual à origem</v>
+        <v>Codificação</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>8-bit</v>
+        <v>Same as source</v>
       </c>
       <c r="B229" t="str">
-        <v>8 bits</v>
+        <v>Igual à origem</v>
       </c>
       <c r="C229" t="str">
-        <v>8 bits</v>
+        <v>Igual à origem</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>16-bit</v>
+        <v>8-bit</v>
       </c>
       <c r="B230" t="str">
-        <v>16 bits</v>
+        <v>8 bits</v>
       </c>
       <c r="C230" t="str">
-        <v>16 bits</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Float (32-bit)</v>
+        <v>16-bit</v>
       </c>
       <c r="B231" t="str">
-        <v>Flutuante (32 bits)</v>
+        <v>16 bits</v>
       </c>
       <c r="C231" t="str">
-        <v>Flutuante (32 bits)</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Compression</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B232" t="str">
-        <v>Compressão</v>
+        <v>Flutuante (32 bits)</v>
       </c>
       <c r="C232" t="str">
-        <v>Compressão</v>
+        <v>Flutuante (32 bits)</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>None</v>
+        <v>Compression</v>
       </c>
       <c r="B233" t="str">
-        <v>Nenhuma</v>
+        <v>Compressão</v>
       </c>
       <c r="C233" t="str">
-        <v>Nenhuma</v>
+        <v>Compressão</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>Planar</v>
+        <v>None</v>
       </c>
       <c r="B234" t="str">
-        <v>Planar</v>
+        <v>Nenhuma</v>
       </c>
       <c r="C234" t="str">
-        <v>Planar</v>
+        <v>Nenhuma</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Composite</v>
+        <v>Planar</v>
       </c>
       <c r="B235" t="str">
-        <v>Composto</v>
+        <v>Planar</v>
       </c>
       <c r="C235" t="str">
-        <v>Composto</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Separated</v>
+        <v>Composite</v>
       </c>
       <c r="B236" t="str">
-        <v>Separado</v>
+        <v>Composto</v>
       </c>
       <c r="C236" t="str">
-        <v>Separado</v>
+        <v>Composto</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>CMM interpolation</v>
+        <v>Separated</v>
       </c>
       <c r="B237" t="str">
-        <v>Interpolação CMM</v>
+        <v>Separado</v>
       </c>
       <c r="C237" t="str">
-        <v>Interpolação CMM</v>
+        <v>Separado</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>Tetrahedral</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B238" t="str">
-        <v>Tetraédrica</v>
+        <v>Interpolação CMM</v>
       </c>
       <c r="C238" t="str">
-        <v>Tetraédrica</v>
+        <v>Interpolação CMM</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Linear</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B239" t="str">
-        <v>Linear</v>
+        <v>Tetraédrica</v>
       </c>
       <c r="C239" t="str">
-        <v>Linear</v>
+        <v>Tetraédrica</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Embed ICC</v>
+        <v>Linear</v>
       </c>
       <c r="B240" t="str">
-        <v>Incorporar ICC</v>
+        <v>Linear</v>
       </c>
       <c r="C240" t="str">
-        <v>Incorporar ICC</v>
+        <v>Linear</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B241" t="str">
-        <v>A codificação, a compressão e o formato planar determinam o TIFF guardado. A saída RGB/Gray mantém-se em PNG, salvo se for definida uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado).</v>
+        <v>Incorporar ICC</v>
       </c>
       <c r="C241" t="str">
-        <v>A codificação, a compressão e o formato planar determinam o TIFF salvo. A saída RGB/Gray permanece em PNG, a menos que uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado) seja definida.</v>
+        <v>Incorporar ICC</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B242" t="str">
-        <v>Montar TIFF espectral</v>
+        <v>A codificação, a compressão e o formato planar determinam o TIFF guardado. A saída RGB/Gray mantém-se em PNG, salvo se for definida uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado).</v>
       </c>
       <c r="C242" t="str">
-        <v>Montar TIFF espectral</v>
+        <v>A codificação, a compressão e o formato planar determinam o TIFF salvo. A saída RGB/Gray permanece em PNG, a menos que uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado) seja definida.</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B243" t="str">
-        <v>Largue imagens espectrais de canal único pela ordem dos canais e depois monte-as num único TIFF multicanal.</v>
+        <v>Montar TIFF espectral</v>
       </c>
       <c r="C243" t="str">
-        <v>Solte imagens espectrais de canal único na ordem dos canais e depois monte-as em um único TIFF multicanal.</v>
+        <v>Montar TIFF espectral</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B244" t="str">
-        <v>Largue imagens espectrais aqui (ou clique para escolher)</v>
+        <v>Largue imagens espectrais de canal único pela ordem dos canais e depois monte-as num único TIFF multicanal.</v>
       </c>
       <c r="C244" t="str">
-        <v>Solte imagens espectrais aqui (ou clique para escolher)</v>
+        <v>Solte imagens espectrais de canal único na ordem dos canais e depois monte-as em um único TIFF multicanal.</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>ch</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B245" t="str">
-        <v>can</v>
+        <v>Largue imagens espectrais aqui (ou clique para escolher)</v>
       </c>
       <c r="C245" t="str">
-        <v>can</v>
+        <v>Solte imagens espectrais aqui (ou clique para escolher)</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>ch</v>
       </c>
       <c r="B246" t="str">
-        <v>Montar e guardar</v>
+        <v>can</v>
       </c>
       <c r="C246" t="str">
-        <v>Montar e salvar</v>
+        <v>can</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assembling…</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B247" t="str">
-        <v>A montar…</v>
+        <v>Montar e guardar</v>
       </c>
       <c r="C247" t="str">
-        <v>Montando…</v>
+        <v>Montar e salvar</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Assembling…</v>
       </c>
       <c r="B248" t="str">
-        <v>Foram montados {n} canais.</v>
+        <v>A montar…</v>
       </c>
       <c r="C248" t="str">
-        <v>Foram montados {n} canais.</v>
+        <v>Montando…</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B249" t="str">
-        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
+        <v>Foram montados {n} canais.</v>
       </c>
       <c r="C249" t="str">
-        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
+        <v>Foram montados {n} canais.</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>Cancel</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B250" t="str">
-        <v>Cancelar</v>
+        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
       </c>
       <c r="C250" t="str">
-        <v>Cancelar</v>
+        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Cancel</v>
       </c>
       <c r="B251" t="str">
-        <v>{n} ficheiro(s) não carregados</v>
+        <v>Cancelar</v>
       </c>
       <c r="C251" t="str">
-        <v>{n} arquivo(s) não carregados</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B252" t="str">
-        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
+        <v>{n} ficheiro(s) não carregados</v>
       </c>
       <c r="C252" t="str">
-        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
+        <v>{n} arquivo(s) não carregados</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>OK</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B253" t="str">
-        <v>OK</v>
+        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
       </c>
       <c r="C253" t="str">
-        <v>OK</v>
+        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>OK</v>
       </c>
       <c r="B254" t="str">
-        <v>Largue um perfil ICC aqui</v>
+        <v>OK</v>
       </c>
       <c r="C254" t="str">
-        <v>Solte um perfil ICC aqui</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>or</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B255" t="str">
-        <v>ou</v>
+        <v>Largue um perfil ICC aqui</v>
       </c>
       <c r="C255" t="str">
-        <v>ou</v>
+        <v>Solte um perfil ICC aqui</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>Choose file</v>
+        <v>or</v>
       </c>
       <c r="B256" t="str">
-        <v>Escolher ficheiro</v>
+        <v>ou</v>
       </c>
       <c r="C256" t="str">
-        <v>Escolher arquivo</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>.icc and .icm files</v>
+        <v>Choose file</v>
       </c>
       <c r="B257" t="str">
-        <v>Ficheiros .icc e .icm</v>
+        <v>Escolher ficheiro</v>
       </c>
       <c r="C257" t="str">
-        <v>Arquivos .icc e .icm</v>
+        <v>Escolher arquivo</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>Header</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B258" t="str">
-        <v>Cabeçalho</v>
+        <v>Ficheiros .icc e .icm</v>
       </c>
       <c r="C258" t="str">
-        <v>Cabeçalho</v>
+        <v>Arquivos .icc e .icm</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Tags</v>
+        <v>Header</v>
       </c>
       <c r="B259" t="str">
-        <v>Etiquetas</v>
+        <v>Cabeçalho</v>
       </c>
       <c r="C259" t="str">
-        <v>Tags</v>
+        <v>Cabeçalho</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Validation</v>
+        <v>Tags</v>
       </c>
       <c r="B260" t="str">
-        <v>Validação</v>
+        <v>Etiquetas</v>
       </c>
       <c r="C260" t="str">
-        <v>Validação</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Analysis</v>
+        <v>Validation</v>
       </c>
       <c r="B261" t="str">
-        <v>Análise</v>
+        <v>Validação</v>
       </c>
       <c r="C261" t="str">
-        <v>Análise</v>
+        <v>Validação</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Analysis</v>
       </c>
       <c r="B262" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Análise</v>
       </c>
       <c r="C262" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B263" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
       <c r="C263" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B264" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
       </c>
       <c r="C264" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B265" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C265" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>Rendering intent</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B266" t="str">
-        <v>Intenção de renderização</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
       <c r="C266" t="str">
-        <v>Intenção de renderização</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>% ink</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B267" t="str">
-        <v>% tinta</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C267" t="str">
-        <v>% tinta</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>Perceptual</v>
+        <v>% ink</v>
       </c>
       <c r="B268" t="str">
-        <v>Perceptual</v>
+        <v>% tinta</v>
       </c>
       <c r="C268" t="str">
-        <v>Perceptual</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Perceptual</v>
       </c>
       <c r="B269" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Perceptual</v>
       </c>
       <c r="C269" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Saturation</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B270" t="str">
-        <v>Saturação</v>
+        <v>Colorimétrico relativo</v>
       </c>
       <c r="C270" t="str">
-        <v>Saturação</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Saturation</v>
       </c>
       <c r="B271" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Saturação</v>
       </c>
       <c r="C271" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Saturação</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Profile Statistics</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B272" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Colorimétrico absoluto</v>
       </c>
       <c r="C272" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B273" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Estatísticas do perfil</v>
       </c>
       <c r="C273" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Estatísticas do perfil</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B274" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
       <c r="C274" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Rendering intent</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B275" t="str">
-        <v>Intenção de renderização</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
       </c>
       <c r="C275" t="str">
-        <v>Intenção de renderização</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B276" t="str">
-        <v>Volume de gamute (ΔE³)</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C276" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B277" t="str">
-        <v>ΔE de percurso</v>
+        <v>Volume de gamute (ΔE³)</v>
       </c>
       <c r="C277" t="str">
-        <v>ΔE de percurso</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B278" t="str">
-        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
+        <v>ΔE de percurso</v>
       </c>
       <c r="C278" t="str">
-        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
+        <v>ΔE de percurso</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>mean</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B279" t="str">
-        <v>média</v>
+        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
       </c>
       <c r="C279" t="str">
-        <v>média</v>
+        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>P90</v>
+        <v>mean</v>
       </c>
       <c r="B280" t="str">
-        <v>P90</v>
+        <v>média</v>
       </c>
       <c r="C280" t="str">
-        <v>P90</v>
+        <v>média</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>max</v>
+        <v>P90</v>
       </c>
       <c r="B281" t="str">
-        <v>máx.</v>
+        <v>P90</v>
       </c>
       <c r="C281" t="str">
-        <v>máx.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Analysing…</v>
+        <v>max</v>
       </c>
       <c r="B282" t="str">
-        <v>A analisar…</v>
+        <v>máx.</v>
       </c>
       <c r="C282" t="str">
-        <v>Analisando…</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysis</v>
+        <v>Analysing…</v>
       </c>
       <c r="B283" t="str">
-        <v>Análise</v>
+        <v>A analisar…</v>
       </c>
       <c r="C283" t="str">
-        <v>Análise</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Analysis</v>
       </c>
       <c r="B284" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Análise</v>
       </c>
       <c r="C284" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Plot</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B285" t="str">
-        <v>Gráfico</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C285" t="str">
-        <v>Gráfico</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Raw Output</v>
+        <v>Plot</v>
       </c>
       <c r="B286" t="str">
-        <v>Saída em bruto</v>
+        <v>Gráfico</v>
       </c>
       <c r="C286" t="str">
-        <v>Saída bruta</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>XML</v>
+        <v>Raw Output</v>
       </c>
       <c r="B287" t="str">
-        <v>XML</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C287" t="str">
-        <v>XML</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="B288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
       <c r="C288" t="str">
-        <v>JSON</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Curves</v>
+        <v>JSON</v>
       </c>
       <c r="B289" t="str">
-        <v>Curvas</v>
+        <v>JSON</v>
       </c>
       <c r="C289" t="str">
-        <v>Curvas</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Input curves</v>
+        <v>Curves</v>
       </c>
       <c r="B290" t="str">
-        <v>Curvas de entrada</v>
+        <v>Curvas</v>
       </c>
       <c r="C290" t="str">
-        <v>Curvas de entrada</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Output curves</v>
+        <v>Input curves</v>
       </c>
       <c r="B291" t="str">
-        <v>Curvas de saída</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C291" t="str">
-        <v>Curvas de saída</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>CLUT image</v>
+        <v>Output curves</v>
       </c>
       <c r="B292" t="str">
-        <v>Imagem CLUT</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C292" t="str">
-        <v>Imagem CLUT</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>Gamut image</v>
+        <v>CLUT image</v>
       </c>
       <c r="B293" t="str">
-        <v>Imagem de gamut</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C293" t="str">
-        <v>Imagem de gamut</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Chromaticity</v>
+        <v>Gamut image</v>
       </c>
       <c r="B294" t="str">
-        <v>Cromaticidade</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C294" t="str">
-        <v>Cromaticidade</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Scatter plot</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B295" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C295" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Tone response curve</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B296" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C296" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Curve table</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B297" t="str">
-        <v>Tabela da curva</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C297" t="str">
-        <v>Tabela da curva</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Tables</v>
+        <v>Curve table</v>
       </c>
       <c r="B298" t="str">
-        <v>Tabelas</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C298" t="str">
-        <v>Tabelas</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Data</v>
+        <v>Tables</v>
       </c>
       <c r="B299" t="str">
-        <v>Dados</v>
+        <v>Tabelas</v>
       </c>
       <c r="C299" t="str">
-        <v>Dados</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Evaluate</v>
+        <v>Data</v>
       </c>
       <c r="B300" t="str">
-        <v>Avaliar</v>
+        <v>Dados</v>
       </c>
       <c r="C300" t="str">
-        <v>Avaliar</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Loading…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B301" t="str">
-        <v>A carregar…</v>
+        <v>Avaliar</v>
       </c>
       <c r="C301" t="str">
-        <v>Carregando…</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Input</v>
+        <v>Loading…</v>
       </c>
       <c r="B302" t="str">
-        <v>Entrada</v>
+        <v>A carregar…</v>
       </c>
       <c r="C302" t="str">
-        <v>Entrada</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Output</v>
+        <v>Input</v>
       </c>
       <c r="B303" t="str">
-        <v>Saída</v>
+        <v>Entrada</v>
       </c>
       <c r="C303" t="str">
-        <v>Saída</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Floating point</v>
+        <v>Output</v>
       </c>
       <c r="B304" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Saída</v>
       </c>
       <c r="C304" t="str">
-        <v>Ponto flutuante</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Grid point</v>
+        <v>Floating point</v>
       </c>
       <c r="B305" t="str">
-        <v>Ponto da grelha</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C305" t="str">
-        <v>Ponto da grade</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Normalized</v>
+        <v>Grid point</v>
       </c>
       <c r="B306" t="str">
-        <v>Normalizado</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C306" t="str">
-        <v>Normalizado</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Human</v>
+        <v>Normalized</v>
       </c>
       <c r="B307" t="str">
-        <v>Legível</v>
+        <v>Normalizado</v>
       </c>
       <c r="C307" t="str">
-        <v>Legível</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Device → PCS</v>
+        <v>Human</v>
       </c>
       <c r="B308" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Legível</v>
       </c>
       <c r="C308" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>PCS → Device</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B309" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C309" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>No CLUT grid</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B310" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C310" t="str">
-        <v>Sem grade CLUT</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Loading…</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B311" t="str">
-        <v>A carregar…</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C311" t="str">
-        <v>Carregando…</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Loading…</v>
       </c>
       <c r="B312" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>A carregar…</v>
       </c>
       <c r="C312" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B313" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C313" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B314" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C314" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B315" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C315" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B316" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C316" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B317" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C317" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B318" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C318" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Security</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B319" t="str">
-        <v>Segurança</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C319" t="str">
-        <v>Segurança</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Conformance</v>
+        <v>Security</v>
       </c>
       <c r="B320" t="str">
-        <v>Conformidade</v>
+        <v>Segurança</v>
       </c>
       <c r="C320" t="str">
-        <v>Conformidade</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Quality</v>
+        <v>Conformance</v>
       </c>
       <c r="B321" t="str">
-        <v>Qualidade</v>
+        <v>Conformidade</v>
       </c>
       <c r="C321" t="str">
-        <v>Qualidade</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>REPORT</v>
+        <v>Quality</v>
       </c>
       <c r="B322" t="str">
-        <v>RELATÓRIO</v>
+        <v>Qualidade</v>
       </c>
       <c r="C322" t="str">
-        <v>RELATÓRIO</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>FAIL</v>
+        <v>REPORT</v>
       </c>
       <c r="B323" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C323" t="str">
-        <v>REPROVADO</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>checks</v>
+        <v>FAIL</v>
       </c>
       <c r="B324" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C324" t="str">
-        <v>verificações</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>checks</v>
       </c>
       <c r="B325" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
       <c r="C325" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B326" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C326" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B327" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C327" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Powered by {lib}</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B328" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C328" t="str">
-        <v>Com {lib}</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Subscribe</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B329" t="str">
-        <v>Subscrever</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C329" t="str">
-        <v>Inscrever-se</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Subscribe</v>
       </c>
       <c r="B330" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Subscrever</v>
       </c>
       <c r="C330" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new releases</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B331" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C331" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Close</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B332" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C332" t="str">
-        <v>Fechar</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Close</v>
       </c>
       <c r="B333" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
       <c r="C333" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Email address</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B334" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C334" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>you@example.com</v>
+        <v>Email address</v>
       </c>
       <c r="B335" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C335" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>How will you use profiletool?</v>
+        <v>you@example.com</v>
       </c>
       <c r="B336" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C336" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>(optional)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B337" t="str">
-        <v>(opcional)</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C337" t="str">
-        <v>(opcional)</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>(optional)</v>
       </c>
       <c r="B338" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>(opcional)</v>
       </c>
       <c r="C338" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B339" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C339" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Cancel</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B340" t="str">
-        <v>Cancelar</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C340" t="str">
-        <v>Cancelar</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Subscribe</v>
+        <v>Cancel</v>
       </c>
       <c r="B341" t="str">
-        <v>Subscrever</v>
+        <v>Cancelar</v>
       </c>
       <c r="C341" t="str">
-        <v>Inscrever-se</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B342" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C342" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B343" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C343" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Close</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B344" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C344" t="str">
-        <v>Fechar</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Privacy notice</v>
+        <v>Close</v>
       </c>
       <c r="B345" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
       <c r="C345" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B346" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C346" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B347" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C347" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B348" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C348" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B349" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C349" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B350" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C350" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Error:</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B351" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C351" t="str">
-        <v>Erro:</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Convert to XML</v>
+        <v>Error:</v>
       </c>
       <c r="B352" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
       <c r="C352" t="str">
-        <v>Converter para XML</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to JSON</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B353" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C353" t="str">
-        <v>Converter para JSON</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to ICC</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B354" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C354" t="str">
-        <v>Converter para ICC</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Converting to XML…</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B355" t="str">
-        <v>A converter para XML…</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C355" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to JSON…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B356" t="str">
-        <v>A converter para JSON…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C356" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to ICC…</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B357" t="str">
-        <v>A converter para ICC…</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C357" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Load ICC profile</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B358" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C358" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B359" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C359" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Profile ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B360" t="str">
-        <v>ID do perfil</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C360" t="str">
-        <v>ID do perfil</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>No tags found.</v>
+        <v>Profile ID</v>
       </c>
       <c r="B361" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C361" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>Tag Name</v>
+        <v>No tags found.</v>
       </c>
       <c r="B362" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C362" t="str">
-        <v>Nome da tag</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>ID</v>
+        <v>Tag Name</v>
       </c>
       <c r="B363" t="str">
-        <v>ID</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C363" t="str">
-        <v>ID</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Offset</v>
+        <v>ID</v>
       </c>
       <c r="B364" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
       <c r="C364" t="str">
-        <v>Deslocamento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Size</v>
+        <v>Offset</v>
       </c>
       <c r="B365" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C365" t="str">
-        <v>Tamanho</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Pad</v>
+        <v>Size</v>
       </c>
       <c r="B366" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
       <c r="C366" t="str">
-        <v>Preenchimento</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Bytes changed since load</v>
+        <v>Pad</v>
       </c>
       <c r="B367" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C367" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Type</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B368" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C368" t="str">
-        <v>Tipo</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Array of {type}</v>
+        <v>Type</v>
       </c>
       <c r="B369" t="str">
-        <v>Vetor de {type}</v>
+        <v>Tipo</v>
       </c>
       <c r="C369" t="str">
-        <v>Array de {type}</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>(No content)</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B370" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C370" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>bytes</v>
+        <v>(No content)</v>
       </c>
       <c r="B371" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C371" t="str">
-        <v>bytes</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>Loading full description…</v>
+        <v>bytes</v>
       </c>
       <c r="B372" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>bytes</v>
       </c>
       <c r="C372" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Could not load full description:</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B373" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C373" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B374" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C374" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B375" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C375" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>No validation output</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B376" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C376" t="str">
-        <v>Sem saída de validação</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Profile is valid</v>
+        <v>No validation output</v>
       </c>
       <c r="B377" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C377" t="str">
-        <v>O perfil é válido</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B378" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C378" t="str">
-        <v>O perfil tem avisos</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B379" t="str">
-        <v>O perfil não é conforme</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C379" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Critical validation error</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B380" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C380" t="str">
-        <v>Erro de validação crítico</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Unknown validation status</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B381" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C381" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B382" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C382" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B383" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C383" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Valid</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B384" t="str">
-        <v>Válido</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C384" t="str">
-        <v>Válido</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Warning</v>
+        <v>Valid</v>
       </c>
       <c r="B385" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
       <c r="C385" t="str">
-        <v>Aviso</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error</v>
+        <v>Warning</v>
       </c>
       <c r="B386" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
       <c r="C386" t="str">
-        <v>Erro</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Unknown</v>
+        <v>Error</v>
       </c>
       <c r="B387" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
       <c r="C387" t="str">
-        <v>Desconhecido</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Pass</v>
+        <v>Unknown</v>
       </c>
       <c r="B388" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C388" t="str">
-        <v>Aprovado</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Fail</v>
+        <v>Pass</v>
       </c>
       <c r="B389" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
       <c r="C389" t="str">
-        <v>Reprovado</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>View in context</v>
+        <v>Fail</v>
       </c>
       <c r="B390" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
       <c r="C390" t="str">
-        <v>Ver no contexto</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Validation detail</v>
+        <v>View in context</v>
       </c>
       <c r="B391" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C391" t="str">
-        <v>Detalhe de validação</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Triggered by</v>
+        <v>Validation detail</v>
       </c>
       <c r="B392" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C392" t="str">
-        <v>Acionado por</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Field</v>
+        <v>Triggered by</v>
       </c>
       <c r="B393" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
       <c r="C393" t="str">
-        <v>Campo</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Current value</v>
+        <v>Field</v>
       </c>
       <c r="B394" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
       <c r="C394" t="str">
-        <v>Valor atual</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Required: 0</v>
+        <v>Current value</v>
       </c>
       <c r="B395" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
       <c r="C395" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Expected: {value}</v>
+        <v>Required: 0</v>
       </c>
       <c r="B396" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C396" t="str">
-        <v>Esperado: {value}</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Invalid</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B397" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C397" t="str">
-        <v>Inválido</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Invalid</v>
       </c>
       <c r="B398" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
       <c r="C398" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Close</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B399" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C399" t="str">
-        <v>Fechar</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Loading XML editor…</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Fechar</v>
       </c>
       <c r="C400" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B401" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C401" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B402" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C402" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B403" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C403" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>● unsaved XML edits</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B404" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C404" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B405" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C405" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B406" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C406" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
       </c>
       <c r="B407" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
       <c r="C407" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>indent</v>
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
       </c>
       <c r="B408" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
       <c r="C408" t="str">
-        <v>indentação</v>
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>sort keys</v>
+        <v>indent</v>
       </c>
       <c r="B409" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
       <c r="C409" t="str">
-        <v>ordenar chaves</v>
+        <v>indentação</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B410" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C410" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B410" t="str">
+      <c r="B411" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C410" t="str">
+      <c r="C411" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C410"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C411"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C411"/>
+  <dimension ref="A1:C445"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3363,1580 +3363,1954 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>Perceptual</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B269" t="str">
-        <v>Perceptual</v>
+        <v>L* de saída (tom)</v>
       </c>
       <c r="C269" t="str">
-        <v>Perceptual</v>
+        <v>L* de saída (tom)</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B270" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Δa*b*</v>
       </c>
       <c r="C270" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Saturation</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B271" t="str">
-        <v>Saturação</v>
+        <v>Colorimetria dos extremos</v>
       </c>
       <c r="C271" t="str">
-        <v>Saturação</v>
+        <v>Colorimetria dos extremos</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B272" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Os extremos da gama de reprodução do perfil: o branco do suporte, o preto mais escuro que irá imprimir, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
       </c>
       <c r="C272" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Os extremos da faixa de reprodução do perfil: o branco do suporte, o preto mais escuro que ele imprimirá, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>Profile Statistics</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B273" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto obtém-se passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa refere-a a um branco perfeito.</v>
       </c>
       <c r="C273" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto é obtido passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa a refere a um branco perfeito.</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative</v>
       </c>
       <c r="B274" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Relativa</v>
       </c>
       <c r="C274" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Relativa</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Absolute</v>
       </c>
       <c r="B275" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
+        <v>Absoluta</v>
       </c>
       <c r="C275" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
+        <v>Absoluta</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>Rendering intent</v>
+        <v>White point</v>
       </c>
       <c r="B276" t="str">
-        <v>Intenção de renderização</v>
+        <v>Ponto branco</v>
       </c>
       <c r="C276" t="str">
-        <v>Intenção de renderização</v>
+        <v>Ponto branco</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Black point</v>
       </c>
       <c r="B277" t="str">
-        <v>Volume de gamute (ΔE³)</v>
+        <v>Ponto preto</v>
       </c>
       <c r="C277" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Ponto preto</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B278" t="str">
-        <v>ΔE de percurso</v>
+        <v>Tintagem no ponto preto</v>
       </c>
       <c r="C278" t="str">
-        <v>ΔE de percurso</v>
+        <v>Tintagem no ponto preto</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>TAC</v>
       </c>
       <c r="B279" t="str">
-        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
+        <v>TAC</v>
       </c>
       <c r="C279" t="str">
-        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>mean</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B280" t="str">
-        <v>média</v>
+        <v>Este perfil não tem etiqueta de ponto branco do meio, pelo que a colorimetria absoluta não está disponível.</v>
       </c>
       <c r="C280" t="str">
-        <v>média</v>
+        <v>Este perfil não tem tag de ponto branco do meio, portanto a colorimetria absoluta não está disponível.</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>P90</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B281" t="str">
-        <v>P90</v>
+        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — pressupõe que corante nulo significa suporte nu.</v>
       </c>
       <c r="C281" t="str">
-        <v>P90</v>
+        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — ela pressupõe que corante nulo significa suporte nu.</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>max</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B282" t="str">
-        <v>máx.</v>
+        <v>Tinta plena vs croma máximo</v>
       </c>
       <c r="C282" t="str">
-        <v>máx.</v>
+        <v>Tinta plena vs croma máximo</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Analysing…</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B283" t="str">
-        <v>A analisar…</v>
+        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, pelo que estas linhas não mudam com a intenção de renderização acima. Num perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta para além desse ponto apenas escurece.</v>
       </c>
       <c r="C283" t="str">
-        <v>Analisando…</v>
+        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, portanto estas linhas não mudam com a intenção de renderização acima. Em um perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta além desse ponto apenas escurece.</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Analysis</v>
+        <v>Hue</v>
       </c>
       <c r="B284" t="str">
-        <v>Análise</v>
+        <v>Matiz</v>
       </c>
       <c r="C284" t="str">
-        <v>Análise</v>
+        <v>Matiz</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Full tone</v>
       </c>
       <c r="B285" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Tinta plena</v>
       </c>
       <c r="C285" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Tinta plena</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Plot</v>
+        <v>Max C*</v>
       </c>
       <c r="B286" t="str">
-        <v>Gráfico</v>
+        <v>C* máx</v>
       </c>
       <c r="C286" t="str">
-        <v>Gráfico</v>
+        <v>C* máx</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>Raw Output</v>
+        <v>At ink</v>
       </c>
       <c r="B287" t="str">
-        <v>Saída em bruto</v>
+        <v>Com tintagem</v>
       </c>
       <c r="C287" t="str">
-        <v>Saída bruta</v>
+        <v>Com tintagem</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>XML</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B288" t="str">
-        <v>XML</v>
+        <v>O croma máximo é atingido antes da tinta plena — a tinta para além deste ponto apenas escurece.</v>
       </c>
       <c r="C288" t="str">
-        <v>XML</v>
+        <v>O croma máximo é atingido antes da tinta plena — a tinta além deste ponto apenas escurece.</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>JSON</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B289" t="str">
-        <v>JSON</v>
+        <v>Utilização de tinta nas sombras</v>
       </c>
       <c r="C289" t="str">
-        <v>JSON</v>
+        <v>Uso de tinta nas sombras</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Curves</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B290" t="str">
-        <v>Curvas</v>
+        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras partilham a mesma L*, pelo que qualquer degrau abrupto ou inversão de um corante resulta apenas do tratamento do matiz e do croma — a assinatura de um artefacto de mapeamento de gamut nas sombras.</v>
       </c>
       <c r="C290" t="str">
-        <v>Curvas</v>
+        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras compartilham a mesma L*, portanto qualquer degrau abrupto ou inversão de um corante vem apenas do tratamento do matiz e do croma — a assinatura de um artefato de mapeamento de gamut nas sombras.</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Input curves</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B291" t="str">
-        <v>Curvas de entrada</v>
+        <v>A utilização de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C291" t="str">
-        <v>Curvas de entrada</v>
+        <v>O uso de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Output curves</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B292" t="str">
-        <v>Curvas de saída</v>
+        <v>Plano de L* constante</v>
       </c>
       <c r="C292" t="str">
-        <v>Curvas de saída</v>
+        <v>Plano de L* constante</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>CLUT image</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B293" t="str">
-        <v>Imagem CLUT</v>
+        <v>com compensação do ponto preto a partir de</v>
       </c>
       <c r="C293" t="str">
-        <v>Imagem CLUT</v>
+        <v>com compensação do ponto preto a partir de</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Gamut image</v>
+        <v>Position along path</v>
       </c>
       <c r="B294" t="str">
-        <v>Imagem de gamut</v>
+        <v>Posição ao longo do percurso</v>
       </c>
       <c r="C294" t="str">
-        <v>Imagem de gamut</v>
+        <v>Posição ao longo do percurso</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Chromaticity</v>
+        <v>Path</v>
       </c>
       <c r="B295" t="str">
-        <v>Cromaticidade</v>
+        <v>Percurso</v>
       </c>
       <c r="C295" t="str">
-        <v>Cromaticidade</v>
+        <v>Percurso</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Scatter plot</v>
+        <v>Cyan</v>
       </c>
       <c r="B296" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Ciano</v>
       </c>
       <c r="C296" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Ciano</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Tone response curve</v>
+        <v>Magenta</v>
       </c>
       <c r="B297" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Magenta</v>
       </c>
       <c r="C297" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Curve table</v>
+        <v>Yellow</v>
       </c>
       <c r="B298" t="str">
-        <v>Tabela da curva</v>
+        <v>Amarelo</v>
       </c>
       <c r="C298" t="str">
-        <v>Tabela da curva</v>
+        <v>Amarelo</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Tables</v>
+        <v>Red</v>
       </c>
       <c r="B299" t="str">
-        <v>Tabelas</v>
+        <v>Vermelho</v>
       </c>
       <c r="C299" t="str">
-        <v>Tabelas</v>
+        <v>Vermelho</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Data</v>
+        <v>Green</v>
       </c>
       <c r="B300" t="str">
-        <v>Dados</v>
+        <v>Verde</v>
       </c>
       <c r="C300" t="str">
-        <v>Dados</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Evaluate</v>
+        <v>Blue</v>
       </c>
       <c r="B301" t="str">
-        <v>Avaliar</v>
+        <v>Azul</v>
       </c>
       <c r="C301" t="str">
-        <v>Avaliar</v>
+        <v>Azul</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Loading…</v>
+        <v>Black</v>
       </c>
       <c r="B302" t="str">
-        <v>A carregar…</v>
+        <v>Preto</v>
       </c>
       <c r="C302" t="str">
-        <v>Carregando…</v>
+        <v>Preto</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Input</v>
+        <v>Perceptual</v>
       </c>
       <c r="B303" t="str">
-        <v>Entrada</v>
+        <v>Perceptual</v>
       </c>
       <c r="C303" t="str">
-        <v>Entrada</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B304" t="str">
-        <v>Saída</v>
+        <v>Colorimétrico relativo</v>
       </c>
       <c r="C304" t="str">
-        <v>Saída</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Floating point</v>
+        <v>Saturation</v>
       </c>
       <c r="B305" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Saturação</v>
       </c>
       <c r="C305" t="str">
-        <v>Ponto flutuante</v>
+        <v>Saturação</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Grid point</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B306" t="str">
-        <v>Ponto da grelha</v>
+        <v>Colorimétrico absoluto</v>
       </c>
       <c r="C306" t="str">
-        <v>Ponto da grade</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Normalized</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B307" t="str">
-        <v>Normalizado</v>
+        <v>Estatísticas do perfil</v>
       </c>
       <c r="C307" t="str">
-        <v>Normalizado</v>
+        <v>Estatísticas do perfil</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Human</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B308" t="str">
-        <v>Legível</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
       <c r="C308" t="str">
-        <v>Legível</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Device → PCS</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B309" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
       </c>
       <c r="C309" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>PCS → Device</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B310" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C310" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B311" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>Volume de gamute (ΔE³)</v>
       </c>
       <c r="C311" t="str">
-        <v>Sem grade CLUT</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Loading…</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B312" t="str">
-        <v>A carregar…</v>
+        <v>ΔE de percurso</v>
       </c>
       <c r="C312" t="str">
-        <v>Carregando…</v>
+        <v>ΔE de percurso</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B313" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
       </c>
       <c r="C313" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Invalid profile URL:</v>
+        <v>mean</v>
       </c>
       <c r="B314" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>média</v>
       </c>
       <c r="C314" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>média</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>P90</v>
       </c>
       <c r="B315" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>P90</v>
       </c>
       <c r="C315" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>max</v>
       </c>
       <c r="B316" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>máx.</v>
       </c>
       <c r="C316" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Analysing…</v>
       </c>
       <c r="B317" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>A analisar…</v>
       </c>
       <c r="C317" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Analysis</v>
       </c>
       <c r="B318" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>Análise</v>
       </c>
       <c r="C318" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B319" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C319" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Security</v>
+        <v>Plot</v>
       </c>
       <c r="B320" t="str">
-        <v>Segurança</v>
+        <v>Gráfico</v>
       </c>
       <c r="C320" t="str">
-        <v>Segurança</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Conformance</v>
+        <v>Raw Output</v>
       </c>
       <c r="B321" t="str">
-        <v>Conformidade</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C321" t="str">
-        <v>Conformidade</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Quality</v>
+        <v>XML</v>
       </c>
       <c r="B322" t="str">
-        <v>Qualidade</v>
+        <v>XML</v>
       </c>
       <c r="C322" t="str">
-        <v>Qualidade</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>REPORT</v>
+        <v>JSON</v>
       </c>
       <c r="B323" t="str">
-        <v>RELATÓRIO</v>
+        <v>JSON</v>
       </c>
       <c r="C323" t="str">
-        <v>RELATÓRIO</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>FAIL</v>
+        <v>Curves</v>
       </c>
       <c r="B324" t="str">
-        <v>REPROVADO</v>
+        <v>Curvas</v>
       </c>
       <c r="C324" t="str">
-        <v>REPROVADO</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>checks</v>
+        <v>Input curves</v>
       </c>
       <c r="B325" t="str">
-        <v>verificações</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C325" t="str">
-        <v>verificações</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Output curves</v>
       </c>
       <c r="B326" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C326" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>CLUT image</v>
       </c>
       <c r="B327" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C327" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Gamut image</v>
       </c>
       <c r="B328" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C328" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Powered by {lib}</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B329" t="str">
-        <v>Com {lib}</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C329" t="str">
-        <v>Com {lib}</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Subscribe</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B330" t="str">
-        <v>Subscrever</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C330" t="str">
-        <v>Inscrever-se</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B331" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C331" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Get notified about new releases</v>
+        <v>Curve table</v>
       </c>
       <c r="B332" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C332" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Close</v>
+        <v>Tables</v>
       </c>
       <c r="B333" t="str">
-        <v>Fechar</v>
+        <v>Tabelas</v>
       </c>
       <c r="C333" t="str">
-        <v>Fechar</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Data</v>
       </c>
       <c r="B334" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Dados</v>
       </c>
       <c r="C334" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Email address</v>
+        <v>Evaluate</v>
       </c>
       <c r="B335" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Avaliar</v>
       </c>
       <c r="C335" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>you@example.com</v>
+        <v>Loading…</v>
       </c>
       <c r="B336" t="str">
-        <v>voce@exemplo.com</v>
+        <v>A carregar…</v>
       </c>
       <c r="C336" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Input</v>
       </c>
       <c r="B337" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Entrada</v>
       </c>
       <c r="C337" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>(optional)</v>
+        <v>Output</v>
       </c>
       <c r="B338" t="str">
-        <v>(opcional)</v>
+        <v>Saída</v>
       </c>
       <c r="C338" t="str">
-        <v>(opcional)</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Floating point</v>
       </c>
       <c r="B339" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C339" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>Grid point</v>
       </c>
       <c r="B340" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C340" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Cancel</v>
+        <v>Normalized</v>
       </c>
       <c r="B341" t="str">
-        <v>Cancelar</v>
+        <v>Normalizado</v>
       </c>
       <c r="C341" t="str">
-        <v>Cancelar</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Subscribe</v>
+        <v>Human</v>
       </c>
       <c r="B342" t="str">
-        <v>Subscrever</v>
+        <v>Legível</v>
       </c>
       <c r="C342" t="str">
-        <v>Inscrever-se</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B343" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C343" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B344" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C344" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Close</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B345" t="str">
-        <v>Fechar</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C345" t="str">
-        <v>Fechar</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Privacy notice</v>
+        <v>Loading…</v>
       </c>
       <c r="B346" t="str">
-        <v>Aviso de privacidade</v>
+        <v>A carregar…</v>
       </c>
       <c r="C346" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B347" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C347" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B348" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C348" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B349" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C349" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B350" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C350" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B351" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C351" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Error:</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B352" t="str">
-        <v>Erro:</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C352" t="str">
-        <v>Erro:</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Convert to XML</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B353" t="str">
-        <v>Converter para XML</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C353" t="str">
-        <v>Converter para XML</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Convert to JSON</v>
+        <v>Security</v>
       </c>
       <c r="B354" t="str">
-        <v>Converter para JSON</v>
+        <v>Segurança</v>
       </c>
       <c r="C354" t="str">
-        <v>Converter para JSON</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Convert to ICC</v>
+        <v>Conformance</v>
       </c>
       <c r="B355" t="str">
-        <v>Converter para ICC</v>
+        <v>Conformidade</v>
       </c>
       <c r="C355" t="str">
-        <v>Converter para ICC</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Converting to XML…</v>
+        <v>Quality</v>
       </c>
       <c r="B356" t="str">
-        <v>A converter para XML…</v>
+        <v>Qualidade</v>
       </c>
       <c r="C356" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Converting to JSON…</v>
+        <v>REPORT</v>
       </c>
       <c r="B357" t="str">
-        <v>A converter para JSON…</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C357" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Converting to ICC…</v>
+        <v>FAIL</v>
       </c>
       <c r="B358" t="str">
-        <v>A converter para ICC…</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C358" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Load ICC profile</v>
+        <v>checks</v>
       </c>
       <c r="B359" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>verificações</v>
       </c>
       <c r="C359" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B360" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C360" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>Profile ID</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B361" t="str">
-        <v>ID do perfil</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C361" t="str">
-        <v>ID do perfil</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>No tags found.</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B362" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C362" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Tag Name</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B363" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C363" t="str">
-        <v>Nome da tag</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>ID</v>
+        <v>Subscribe</v>
       </c>
       <c r="B364" t="str">
-        <v>ID</v>
+        <v>Subscrever</v>
       </c>
       <c r="C364" t="str">
-        <v>ID</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Offset</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B365" t="str">
-        <v>Deslocamento</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C365" t="str">
-        <v>Deslocamento</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Size</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B366" t="str">
-        <v>Tamanho</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C366" t="str">
-        <v>Tamanho</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Pad</v>
+        <v>Close</v>
       </c>
       <c r="B367" t="str">
-        <v>Preenchimento</v>
+        <v>Fechar</v>
       </c>
       <c r="C367" t="str">
-        <v>Preenchimento</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Bytes changed since load</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B368" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C368" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Type</v>
+        <v>Email address</v>
       </c>
       <c r="B369" t="str">
-        <v>Tipo</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C369" t="str">
-        <v>Tipo</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Array of {type}</v>
+        <v>you@example.com</v>
       </c>
       <c r="B370" t="str">
-        <v>Vetor de {type}</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C370" t="str">
-        <v>Array de {type}</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>(No content)</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B371" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C371" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>bytes</v>
+        <v>(optional)</v>
       </c>
       <c r="B372" t="str">
-        <v>bytes</v>
+        <v>(opcional)</v>
       </c>
       <c r="C372" t="str">
-        <v>bytes</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Loading full description…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B373" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C373" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>Could not load full description:</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B374" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C374" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Cancel</v>
       </c>
       <c r="B375" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>Cancelar</v>
       </c>
       <c r="C375" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B376" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C376" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>No validation output</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B377" t="str">
-        <v>Sem saída de validação</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C377" t="str">
-        <v>Sem saída de validação</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Profile is valid</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B378" t="str">
-        <v>O perfil é válido</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C378" t="str">
-        <v>O perfil é válido</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Profile has warning(s)</v>
+        <v>Close</v>
       </c>
       <c r="B379" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Fechar</v>
       </c>
       <c r="C379" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B380" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C380" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Critical validation error</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B381" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C381" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Unknown validation status</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B382" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C382" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B383" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C383" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B384" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C384" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Valid</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B385" t="str">
-        <v>Válido</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C385" t="str">
-        <v>Válido</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Warning</v>
+        <v>Error:</v>
       </c>
       <c r="B386" t="str">
-        <v>Aviso</v>
+        <v>Erro:</v>
       </c>
       <c r="C386" t="str">
-        <v>Aviso</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Error</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B387" t="str">
-        <v>Erro</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C387" t="str">
-        <v>Erro</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Unknown</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B388" t="str">
-        <v>Desconhecido</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C388" t="str">
-        <v>Desconhecido</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Pass</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B389" t="str">
-        <v>Aprovado</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C389" t="str">
-        <v>Aprovado</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Fail</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B390" t="str">
-        <v>Reprovado</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C390" t="str">
-        <v>Reprovado</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>View in context</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B391" t="str">
-        <v>Ver no contexto</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C391" t="str">
-        <v>Ver no contexto</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Validation detail</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B392" t="str">
-        <v>Detalhe de validação</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C392" t="str">
-        <v>Detalhe de validação</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Triggered by</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B393" t="str">
-        <v>Acionado por</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C393" t="str">
-        <v>Acionado por</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Field</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B394" t="str">
-        <v>Campo</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C394" t="str">
-        <v>Campo</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Current value</v>
+        <v>Profile ID</v>
       </c>
       <c r="B395" t="str">
-        <v>Valor atual</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C395" t="str">
-        <v>Valor atual</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Required: 0</v>
+        <v>No tags found.</v>
       </c>
       <c r="B396" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C396" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Expected: {value}</v>
+        <v>Tag Name</v>
       </c>
       <c r="B397" t="str">
-        <v>Esperado: {value}</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C397" t="str">
-        <v>Esperado: {value}</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Invalid</v>
+        <v>ID</v>
       </c>
       <c r="B398" t="str">
-        <v>Inválido</v>
+        <v>ID</v>
       </c>
       <c r="C398" t="str">
-        <v>Inválido</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Offset</v>
       </c>
       <c r="B399" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C399" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Close</v>
+        <v>Size</v>
       </c>
       <c r="B400" t="str">
-        <v>Fechar</v>
+        <v>Tamanho</v>
       </c>
       <c r="C400" t="str">
-        <v>Fechar</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Loading XML editor…</v>
+        <v>Pad</v>
       </c>
       <c r="B401" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C401" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B402" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C402" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Type</v>
       </c>
       <c r="B403" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Tipo</v>
       </c>
       <c r="C403" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B404" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C404" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>● unsaved XML edits</v>
+        <v>(No content)</v>
       </c>
       <c r="B405" t="str">
-        <v>● edições XML por guardar</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C405" t="str">
-        <v>● edições XML não salvas</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>bytes</v>
       </c>
       <c r="B406" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>bytes</v>
       </c>
       <c r="C406" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B407" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C407" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B408" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C408" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>indent</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B409" t="str">
-        <v>indentação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C409" t="str">
-        <v>indentação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>sort keys</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B410" t="str">
-        <v>ordenar chaves</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C410" t="str">
-        <v>ordenar chaves</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
+        <v>No validation output</v>
+      </c>
+      <c r="B411" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+      <c r="C411" t="str">
+        <v>Sem saída de validação</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>Profile is valid</v>
+      </c>
+      <c r="B412" t="str">
+        <v>O perfil é válido</v>
+      </c>
+      <c r="C412" t="str">
+        <v>O perfil é válido</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>Profile has warning(s)</v>
+      </c>
+      <c r="B413" t="str">
+        <v>O perfil tem avisos</v>
+      </c>
+      <c r="C413" t="str">
+        <v>O perfil tem avisos</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>Profile is non-compliant</v>
+      </c>
+      <c r="B414" t="str">
+        <v>O perfil não é conforme</v>
+      </c>
+      <c r="C414" t="str">
+        <v>O perfil não está em conformidade</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>Critical validation error</v>
+      </c>
+      <c r="B415" t="str">
+        <v>Erro de validação crítico</v>
+      </c>
+      <c r="C415" t="str">
+        <v>Erro de validação crítico</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>Unknown validation status</v>
+      </c>
+      <c r="B416" t="str">
+        <v>Estado de validação desconhecido</v>
+      </c>
+      <c r="C416" t="str">
+        <v>Status de validação desconhecido</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>Critical — shown for inspection only</v>
+      </c>
+      <c r="B417" t="str">
+        <v>Crítico — apresentado apenas para inspeção</v>
+      </c>
+      <c r="C417" t="str">
+        <v>Crítico — exibido apenas para inspeção</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>No warnings or errors found.</v>
+      </c>
+      <c r="B418" t="str">
+        <v>Sem avisos nem erros encontrados.</v>
+      </c>
+      <c r="C418" t="str">
+        <v>Nenhum aviso ou erro encontrado.</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>Valid</v>
+      </c>
+      <c r="B419" t="str">
+        <v>Válido</v>
+      </c>
+      <c r="C419" t="str">
+        <v>Válido</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>Warning</v>
+      </c>
+      <c r="B420" t="str">
+        <v>Aviso</v>
+      </c>
+      <c r="C420" t="str">
+        <v>Aviso</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>Error</v>
+      </c>
+      <c r="B421" t="str">
+        <v>Erro</v>
+      </c>
+      <c r="C421" t="str">
+        <v>Erro</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="B422" t="str">
+        <v>Desconhecido</v>
+      </c>
+      <c r="C422" t="str">
+        <v>Desconhecido</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="B423" t="str">
+        <v>Aprovado</v>
+      </c>
+      <c r="C423" t="str">
+        <v>Aprovado</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>Fail</v>
+      </c>
+      <c r="B424" t="str">
+        <v>Reprovado</v>
+      </c>
+      <c r="C424" t="str">
+        <v>Reprovado</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>View in context</v>
+      </c>
+      <c r="B425" t="str">
+        <v>Ver no contexto</v>
+      </c>
+      <c r="C425" t="str">
+        <v>Ver no contexto</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>Validation detail</v>
+      </c>
+      <c r="B426" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+      <c r="C426" t="str">
+        <v>Detalhe de validação</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>Triggered by</v>
+      </c>
+      <c r="B427" t="str">
+        <v>Acionado por</v>
+      </c>
+      <c r="C427" t="str">
+        <v>Acionado por</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B428" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C428" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B429" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C429" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B430" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C430" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B431" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C431" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B432" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C432" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B433" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C433" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B434" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C434" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B435" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C435" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B436" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C436" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B437" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C437" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B438" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C438" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B439" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C439" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B440" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C440" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B441" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C441" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B442" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C442" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B443" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C443" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B444" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C444" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B411" t="str">
+      <c r="B445" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C411" t="str">
+      <c r="C445" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C411"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C445"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C445"/>
+  <dimension ref="A1:C449"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -582,4735 +582,4779 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Specified gamut</v>
+        <v>Round-trip ΔE by lightness</v>
       </c>
       <c r="B17" t="str">
-        <v>Gama especificada</v>
+        <v>ΔE de ida e volta por luminosidade</v>
       </c>
       <c r="C17" t="str">
-        <v>Gama especificada</v>
+        <v>ΔE de ida e volta por luminosidade</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (lightness of the requested colour)</v>
       </c>
       <c r="B18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (luminosidade da cor solicitada)</v>
       </c>
       <c r="C18" t="str">
-        <v>Perceptual Reference Medium Gamut</v>
+        <v>L* (luminosidade da cor solicitada)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Not specified</v>
+        <v>ΔE*ab</v>
       </c>
       <c r="B19" t="str">
-        <v>Não especificada</v>
+        <v>ΔE*ab</v>
       </c>
       <c r="C19" t="str">
-        <v>Não especificada</v>
+        <v>ΔE*ab</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Not evaluated</v>
+        <v>points, gamut boundary → neutral</v>
       </c>
       <c r="B20" t="str">
-        <v>Não avaliada</v>
+        <v>pontos, limite do gamut → neutro</v>
       </c>
       <c r="C20" t="str">
-        <v>Não avaliada</v>
+        <v>pontos, limite do gamut → neutro</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>PRMG interoperability</v>
+        <v>Specified gamut</v>
       </c>
       <c r="B21" t="str">
-        <v>Interoperabilidade PRMG</v>
+        <v>Gama especificada</v>
       </c>
       <c r="C21" t="str">
-        <v>Interoperabilidade PRMG</v>
+        <v>Gama especificada</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="B22" t="str">
-        <v>ΔE de ida e volta</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
       <c r="C22" t="str">
-        <v>ΔE de ida e volta</v>
+        <v>Perceptual Reference Medium Gamut</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Count</v>
+        <v>Not specified</v>
       </c>
       <c r="B23" t="str">
-        <v>Contagem</v>
+        <v>Não especificada</v>
       </c>
       <c r="C23" t="str">
-        <v>Contagem</v>
+        <v>Não especificada</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Share</v>
+        <v>Not evaluated</v>
       </c>
       <c r="B24" t="str">
-        <v>Proporção</v>
+        <v>Não avaliada</v>
       </c>
       <c r="C24" t="str">
-        <v>Proporção</v>
+        <v>Não avaliada</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Total</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B25" t="str">
-        <v>Total</v>
+        <v>Interoperabilidade PRMG</v>
       </c>
       <c r="C25" t="str">
-        <v>Total</v>
+        <v>Interoperabilidade PRMG</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>PRMG not evaluated</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B26" t="str">
-        <v>PRMG não avaliado</v>
+        <v>ΔE de ida e volta</v>
       </c>
       <c r="C26" t="str">
-        <v>PRMG não avaliado</v>
+        <v>ΔE de ida e volta</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
+        <v>Count</v>
       </c>
       <c r="B27" t="str">
-        <v>Métricas de todo o perfil para uma intenção de renderização: o volume do gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e uma métrica de precisão de ida e volta. Escolha a intenção de renderização e o tipo de ida e volta — a tabela e o histograma são atualizados em conformidade.</v>
+        <v>Contagem</v>
       </c>
       <c r="C27" t="str">
-        <v>Métricas de todo o perfil para uma intenção de renderização: o volume do gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e uma métrica de precisão de ida e volta. Escolha a intenção de renderização e o tipo de ida e volta — a tabela e o histograma são atualizados de acordo.</v>
+        <v>Contagem</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Round-trip type</v>
+        <v>Share</v>
       </c>
       <c r="B28" t="str">
-        <v>Tipo de ida e volta</v>
+        <v>Proporção</v>
       </c>
       <c r="C28" t="str">
-        <v>Tipo de ida e volta</v>
+        <v>Proporção</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Has no effect on this round-trip type</v>
+        <v>Total</v>
       </c>
       <c r="B29" t="str">
-        <v>Não afeta este tipo de ida e volta</v>
+        <v>Total</v>
       </c>
       <c r="C29" t="str">
-        <v>Não afeta este tipo de ida e volta</v>
+        <v>Total</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>This round-trip type is not available for this profile.</v>
+        <v>PRMG not evaluated</v>
       </c>
       <c r="B30" t="str">
-        <v>Este tipo de ida e volta não está disponível para este perfil.</v>
+        <v>PRMG não avaliado</v>
       </c>
       <c r="C30" t="str">
-        <v>Este tipo de ida e volta não está disponível para este perfil.</v>
+        <v>PRMG não avaliado</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Round-trip ΔE distribution</v>
+        <v>Whole-profile metrics for one rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and a round-trip accuracy metric. Choose the rendering intent and the round-trip type — the table and histogram update to match.</v>
       </c>
       <c r="B31" t="str">
-        <v>Distribuição do ΔE de ida e volta</v>
+        <v>Métricas de todo o perfil para uma intenção de renderização: o volume do gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e uma métrica de precisão de ida e volta. Escolha a intenção de renderização e o tipo de ida e volta — a tabela e o histograma são atualizados em conformidade.</v>
       </c>
       <c r="C31" t="str">
-        <v>Distribuição do ΔE de ida e volta</v>
+        <v>Métricas de todo o perfil para uma intenção de renderização: o volume do gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e uma métrica de precisão de ida e volta. Escolha a intenção de renderização e o tipo de ida e volta — a tabela e o histograma são atualizados de acordo.</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>No round-trip samples fell inside the evaluated region.</v>
+        <v>Round-trip type</v>
       </c>
       <c r="B32" t="str">
-        <v>Nenhuma amostra de ida e volta caiu dentro da região avaliada.</v>
+        <v>Tipo de ida e volta</v>
       </c>
       <c r="C32" t="str">
-        <v>Nenhuma amostra de ida e volta caiu dentro da região avaliada.</v>
+        <v>Tipo de ida e volta</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Std Dev</v>
+        <v>Has no effect on this round-trip type</v>
       </c>
       <c r="B33" t="str">
-        <v>Desvio padrão</v>
+        <v>Não afeta este tipo de ida e volta</v>
       </c>
       <c r="C33" t="str">
-        <v>Desvio padrão</v>
+        <v>Não afeta este tipo de ida e volta</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Relative frequency</v>
+        <v>This round-trip type is not available for this profile.</v>
       </c>
       <c r="B34" t="str">
-        <v>Frequência relativa</v>
+        <v>Este tipo de ida e volta não está disponível para este perfil.</v>
       </c>
       <c r="C34" t="str">
-        <v>Frequência relativa</v>
+        <v>Este tipo de ida e volta não está disponível para este perfil.</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Cumulative frequency</v>
+        <v>Round-trip ΔE distribution</v>
       </c>
       <c r="B35" t="str">
-        <v>Frequência cumulativa</v>
+        <v>Distribuição do ΔE de ida e volta</v>
       </c>
       <c r="C35" t="str">
-        <v>Frequência cumulativa</v>
+        <v>Distribuição do ΔE de ida e volta</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Horizontal scale</v>
+        <v>No round-trip samples fell inside the evaluated region.</v>
       </c>
       <c r="B36" t="str">
-        <v>Escala horizontal</v>
+        <v>Nenhuma amostra de ida e volta caiu dentro da região avaliada.</v>
       </c>
       <c r="C36" t="str">
-        <v>Escala horizontal</v>
+        <v>Nenhuma amostra de ida e volta caiu dentro da região avaliada.</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Integer ΔE</v>
+        <v>Std Dev</v>
       </c>
       <c r="B37" t="str">
-        <v>ΔE inteiro</v>
+        <v>Desvio padrão</v>
       </c>
       <c r="C37" t="str">
-        <v>ΔE inteiro</v>
+        <v>Desvio padrão</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Auto-scale</v>
+        <v>Relative frequency</v>
       </c>
       <c r="B38" t="str">
-        <v>Escala automática</v>
+        <v>Frequência relativa</v>
       </c>
       <c r="C38" t="str">
-        <v>Escala automática</v>
+        <v>Frequência relativa</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bins</v>
+        <v>Cumulative frequency</v>
       </c>
       <c r="B39" t="str">
-        <v>Classes</v>
+        <v>Frequência cumulativa</v>
       </c>
       <c r="C39" t="str">
-        <v>Classes</v>
+        <v>Frequência cumulativa</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CLUT Image</v>
+        <v>Horizontal scale</v>
       </c>
       <c r="B40" t="str">
-        <v>Imagem CLUT</v>
+        <v>Escala horizontal</v>
       </c>
       <c r="C40" t="str">
-        <v>Imagem CLUT</v>
+        <v>Escala horizontal</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
+        <v>Integer ΔE</v>
       </c>
       <c r="B41" t="str">
-        <v>A tabela de consulta de cor (CLUT) de uma transformação dispositivo↔PCS, disposta em mosaico numa imagem. Escolha que tabela de intenção de renderização ver.</v>
+        <v>ΔE inteiro</v>
       </c>
       <c r="C41" t="str">
-        <v>A tabela de consulta de cor (CLUT) de uma transformação dispositivo↔PCS, disposta em mosaico em uma imagem. Escolha qual tabela de intenção de renderização visualizar.</v>
+        <v>ΔE inteiro</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
+        <v>Auto-scale</v>
       </c>
       <c r="B42" t="str">
-        <v>Este perfil não tem tabelas dispositivo↔PCS baseadas em CLUT para visualizar.</v>
+        <v>Escala automática</v>
       </c>
       <c r="C42" t="str">
-        <v>Este perfil não tem tabelas dispositivo↔PCS baseadas em CLUT para visualizar.</v>
+        <v>Escala automática</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Gamut Image</v>
+        <v>Bins</v>
       </c>
       <c r="B43" t="str">
-        <v>Imagem de gamut</v>
+        <v>Classes</v>
       </c>
       <c r="C43" t="str">
-        <v>Imagem de gamut</v>
+        <v>Classes</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
+        <v>CLUT Image</v>
       </c>
       <c r="B44" t="str">
-        <v>O mapa dentro/fora do gamut da etiqueta gamut: neutro onde uma cor PCS é reproduzível, vermelho onde fica fora do gamut do dispositivo.</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C44" t="str">
-        <v>O mapa dentro/fora do gamut da etiqueta gamut: neutro onde uma cor PCS é reproduzível, vermelho onde fica fora do gamut do dispositivo.</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>This profile has no gamut tag to visualize.</v>
+        <v>The colour lookup table (CLUT) of a device↔PCS transform, tiled into an image. Pick which rendering-intent table to view.</v>
       </c>
       <c r="B45" t="str">
-        <v>Este perfil não tem etiqueta gamut para visualizar.</v>
+        <v>A tabela de consulta de cor (CLUT) de uma transformação dispositivo↔PCS, disposta em mosaico numa imagem. Escolha que tabela de intenção de renderização ver.</v>
       </c>
       <c r="C45" t="str">
-        <v>Este perfil não tem etiqueta gamut para visualizar.</v>
+        <v>A tabela de consulta de cor (CLUT) de uma transformação dispositivo↔PCS, disposta em mosaico em uma imagem. Escolha qual tabela de intenção de renderização visualizar.</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Vertical scale</v>
+        <v>This profile has no CLUT-based device↔PCS tables to visualize.</v>
       </c>
       <c r="B46" t="str">
-        <v>Escala vertical</v>
+        <v>Este perfil não tem tabelas dispositivo↔PCS baseadas em CLUT para visualizar.</v>
       </c>
       <c r="C46" t="str">
-        <v>Escala vertical</v>
+        <v>Este perfil não tem tabelas dispositivo↔PCS baseadas em CLUT para visualizar.</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>X–Y</v>
+        <v>Gamut Image</v>
       </c>
       <c r="B47" t="str">
-        <v>X–Y</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C47" t="str">
-        <v>X–Y</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Tone increase</v>
+        <v>The gamut tag’s in/out-of-gamut map: neutral where a PCS colour is reproducible, red where it falls outside the device gamut.</v>
       </c>
       <c r="B48" t="str">
-        <v>Aumento tonal</v>
+        <v>O mapa dentro/fora do gamut da etiqueta gamut: neutro onde uma cor PCS é reproduzível, vermelho onde fica fora do gamut do dispositivo.</v>
       </c>
       <c r="C48" t="str">
-        <v>Aumento tonal</v>
+        <v>O mapa dentro/fora do gamut da etiqueta gamut: neutro onde uma cor PCS é reproduzível, vermelho onde fica fora do gamut do dispositivo.</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Tone increase (out − in)</v>
+        <v>This profile has no gamut tag to visualize.</v>
       </c>
       <c r="B49" t="str">
-        <v>Aumento tonal (saída − entrada)</v>
+        <v>Este perfil não tem etiqueta gamut para visualizar.</v>
       </c>
       <c r="C49" t="str">
-        <v>Aumento tonal (saída − entrada)</v>
+        <v>Este perfil não tem etiqueta gamut para visualizar.</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Show full dump</v>
+        <v>Vertical scale</v>
       </c>
       <c r="B50" t="str">
-        <v>Mostrar despejo completo</v>
+        <v>Escala vertical</v>
       </c>
       <c r="C50" t="str">
-        <v>Mostrar despejo completo</v>
+        <v>Escala vertical</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Output truncated for performance.</v>
+        <v>X–Y</v>
       </c>
       <c r="B51" t="str">
-        <v>Saída truncada por desempenho.</v>
+        <v>X–Y</v>
       </c>
       <c r="C51" t="str">
-        <v>Saída truncada por desempenho.</v>
+        <v>X–Y</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>In-gamut overview (RT0)</v>
+        <v>Tone increase</v>
       </c>
       <c r="B52" t="str">
-        <v>Visão geral dentro do gamut (RT0)</v>
+        <v>Aumento tonal</v>
       </c>
       <c r="C52" t="str">
-        <v>Visão geral dentro do gamut (RT0)</v>
+        <v>Aumento tonal</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Inversion + gamut (RT1)</v>
+        <v>Tone increase (out − in)</v>
       </c>
       <c r="B53" t="str">
-        <v>Inversão + gamut (RT1)</v>
+        <v>Aumento tonal (saída − entrada)</v>
       </c>
       <c r="C53" t="str">
-        <v>Inversão + gamut (RT1)</v>
+        <v>Aumento tonal (saída − entrada)</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Reproducibility (RT2)</v>
+        <v>Show full dump</v>
       </c>
       <c r="B54" t="str">
-        <v>Reprodutibilidade (RT2)</v>
+        <v>Mostrar despejo completo</v>
       </c>
       <c r="C54" t="str">
-        <v>Reprodutibilidade (RT2)</v>
+        <v>Mostrar despejo completo</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>PRMG interoperability</v>
+        <v>Output truncated for performance.</v>
       </c>
       <c r="B55" t="str">
-        <v>Interoperabilidade PRMG</v>
+        <v>Saída truncada por desempenho.</v>
       </c>
       <c r="C55" t="str">
-        <v>Interoperabilidade PRMG</v>
+        <v>Saída truncada por desempenho.</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
+        <v>In-gamut overview (RT0)</v>
       </c>
       <c r="B56" t="str">
-        <v>Visão geral do iccviz: uma grelha de valores do dispositivo é levada ao PCS, de volta ao dispositivo e novamente ao PCS; o ΔE*ab é medido entre as duas passagens PCS. Uma verificação rápida de estabilidade dentro do gamut.</v>
+        <v>Visão geral dentro do gamut (RT0)</v>
       </c>
       <c r="C56" t="str">
-        <v>Visão geral do iccviz: uma grade de valores do dispositivo é levada ao PCS, de volta ao dispositivo e novamente ao PCS; o ΔE*ab é medido entre as duas passagens PCS. Uma verificação rápida de estabilidade dentro do gamut.</v>
+        <v>Visão geral dentro do gamut (RT0)</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
+        <v>Inversion + gamut (RT1)</v>
       </c>
       <c r="B57" t="str">
-        <v>iccRoundTrip Ida e volta 1: ΔE*ab entre o PCS de cada cor do dispositivo e o seu PCS após uma ida e volta Lab → dispositivo → Lab. Reflete a precisão de inversão e o mapeamento de gamut.</v>
+        <v>Inversão + gamut (RT1)</v>
       </c>
       <c r="C57" t="str">
-        <v>iccRoundTrip Ida e volta 1: ΔE*ab entre o PCS de cada cor do dispositivo e o seu PCS após uma ida e volta Lab → dispositivo → Lab. Reflete a precisão de inversão e o mapeamento de gamut.</v>
+        <v>Inversão + gamut (RT1)</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
+        <v>Reproducibility (RT2)</v>
       </c>
       <c r="B58" t="str">
-        <v>iccRoundTrip Ida e volta 2: ΔE*ab entre a primeira e a segunda ida e volta — o quão estável é uma ida e volta de PCS repetida (reprodutibilidade, independente do recorte de gamut da primeira passagem).</v>
+        <v>Reprodutibilidade (RT2)</v>
       </c>
       <c r="C58" t="str">
-        <v>iccRoundTrip Ida e volta 2: ΔE*ab entre a primeira e a segunda ida e volta — o quão estável é uma ida e volta de PCS repetida (reprodutibilidade, independente do recorte de gamut da primeira passagem).</v>
+        <v>Reprodutibilidade (RT2)</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
+        <v>PRMG interoperability</v>
       </c>
       <c r="B59" t="str">
-        <v>iccRoundTrip PRMG: as cores PCS dentro do Perceptual Reference Medium Gamut fazem uma única ida e volta (Lab → dispositivo → Lab); a distribuição do ΔE*ab indica a interoperabilidade entre perfis.</v>
+        <v>Interoperabilidade PRMG</v>
       </c>
       <c r="C59" t="str">
-        <v>iccRoundTrip PRMG: as cores PCS dentro do Perceptual Reference Medium Gamut fazem uma única ida e volta (Lab → dispositivo → Lab); a distribuição do ΔE*ab indica a interoperabilidade entre perfis.</v>
+        <v>Interoperabilidade PRMG</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Settings</v>
+        <v>iccviz overview: a device-value grid is taken to PCS, back to device, and to PCS again; ΔE*ab is measured between the two PCS passes. A fast in-gamut stability check.</v>
       </c>
       <c r="B60" t="str">
-        <v>Definições</v>
+        <v>Visão geral do iccviz: uma grelha de valores do dispositivo é levada ao PCS, de volta ao dispositivo e novamente ao PCS; o ΔE*ab é medido entre as duas passagens PCS. Uma verificação rápida de estabilidade dentro do gamut.</v>
       </c>
       <c r="C60" t="str">
-        <v>Configurações</v>
+        <v>Visão geral do iccviz: uma grade de valores do dispositivo é levada ao PCS, de volta ao dispositivo e novamente ao PCS; o ΔE*ab é medido entre as duas passagens PCS. Uma verificação rápida de estabilidade dentro do gamut.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Display</v>
+        <v>iccRoundTrip Round Trip 1: ΔE*ab between each device colour’s PCS and its PCS after one Lab → device → Lab round trip. Reflects inversion accuracy and gamut mapping.</v>
       </c>
       <c r="B61" t="str">
-        <v>Visualização</v>
+        <v>iccRoundTrip Ida e volta 1: ΔE*ab entre o PCS de cada cor do dispositivo e o seu PCS após uma ida e volta Lab → dispositivo → Lab. Reflete a precisão de inversão e o mapeamento de gamut.</v>
       </c>
       <c r="C61" t="str">
-        <v>Exibição</v>
+        <v>iccRoundTrip Ida e volta 1: ΔE*ab entre o PCS de cada cor do dispositivo e o seu PCS após uma ida e volta Lab → dispositivo → Lab. Reflete a precisão de inversão e o mapeamento de gamut.</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Background</v>
+        <v>iccRoundTrip Round Trip 2: ΔE*ab between the first and second round trips — how stable a repeated PCS round trip is (reproducibility, independent of the first trip’s gamut clipping).</v>
       </c>
       <c r="B62" t="str">
-        <v>Fundo</v>
+        <v>iccRoundTrip Ida e volta 2: ΔE*ab entre a primeira e a segunda ida e volta — o quão estável é uma ida e volta de PCS repetida (reprodutibilidade, independente do recorte de gamut da primeira passagem).</v>
       </c>
       <c r="C62" t="str">
-        <v>Fundo</v>
+        <v>iccRoundTrip Ida e volta 2: ΔE*ab entre a primeira e a segunda ida e volta — o quão estável é uma ida e volta de PCS repetida (reprodutibilidade, independente do recorte de gamut da primeira passagem).</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Language</v>
+        <v>iccRoundTrip PRMG: PCS colours inside the Perceptual Reference Medium Gamut are round-tripped once (Lab → device → Lab); the ΔE*ab distribution indicates cross-profile interoperability.</v>
       </c>
       <c r="B63" t="str">
-        <v>Idioma</v>
+        <v>iccRoundTrip PRMG: as cores PCS dentro do Perceptual Reference Medium Gamut fazem uma única ida e volta (Lab → dispositivo → Lab); a distribuição do ΔE*ab indica a interoperabilidade entre perfis.</v>
       </c>
       <c r="C63" t="str">
-        <v>Idioma</v>
+        <v>iccRoundTrip PRMG: as cores PCS dentro do Perceptual Reference Medium Gamut fazem uma única ida e volta (Lab → dispositivo → Lab); a distribuição do ΔE*ab indica a interoperabilidade entre perfis.</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>System</v>
+        <v>Settings</v>
       </c>
       <c r="B64" t="str">
-        <v>Sistema</v>
+        <v>Definições</v>
       </c>
       <c r="C64" t="str">
-        <v>Sistema</v>
+        <v>Configurações</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Light</v>
+        <v>Display</v>
       </c>
       <c r="B65" t="str">
-        <v>Claro</v>
+        <v>Visualização</v>
       </c>
       <c r="C65" t="str">
-        <v>Claro</v>
+        <v>Exibição</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Dark</v>
+        <v>Background</v>
       </c>
       <c r="B66" t="str">
-        <v>Escuro</v>
+        <v>Fundo</v>
       </c>
       <c r="C66" t="str">
-        <v>Escuro</v>
+        <v>Fundo</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>System default</v>
+        <v>Language</v>
       </c>
       <c r="B67" t="str">
-        <v>Predefinição do sistema</v>
+        <v>Idioma</v>
       </c>
       <c r="C67" t="str">
-        <v>Padrão do sistema</v>
+        <v>Idioma</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Number format</v>
+        <v>System</v>
       </c>
       <c r="B68" t="str">
-        <v>Formato numérico</v>
+        <v>Sistema</v>
       </c>
       <c r="C68" t="str">
-        <v>Formato numérico</v>
+        <v>Sistema</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Hexadecimal</v>
+        <v>Light</v>
       </c>
       <c r="B69" t="str">
-        <v>Hexadecimal</v>
+        <v>Claro</v>
       </c>
       <c r="C69" t="str">
-        <v>Hexadecimal</v>
+        <v>Claro</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Decimal</v>
+        <v>Dark</v>
       </c>
       <c r="B70" t="str">
-        <v>Decimal</v>
+        <v>Escuro</v>
       </c>
       <c r="C70" t="str">
-        <v>Decimal</v>
+        <v>Escuro</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Help</v>
+        <v>System default</v>
       </c>
       <c r="B71" t="str">
-        <v>Ajuda</v>
+        <v>Predefinição do sistema</v>
       </c>
       <c r="C71" t="str">
-        <v>Ajuda</v>
+        <v>Padrão do sistema</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Contact</v>
+        <v>Number format</v>
       </c>
       <c r="B72" t="str">
-        <v>Contacto</v>
+        <v>Formato numérico</v>
       </c>
       <c r="C72" t="str">
-        <v>Contato</v>
+        <v>Formato numérico</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>User guide</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="B73" t="str">
-        <v>Guia do utilizador</v>
+        <v>Hexadecimal</v>
       </c>
       <c r="C73" t="str">
-        <v>Guia do usuário</v>
+        <v>Hexadecimal</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Search guide</v>
+        <v>Decimal</v>
       </c>
       <c r="B74" t="str">
-        <v>Pesquisar no guia</v>
+        <v>Decimal</v>
       </c>
       <c r="C74" t="str">
-        <v>Pesquisar no guia</v>
+        <v>Decimal</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Search the user guide</v>
+        <v>Help</v>
       </c>
       <c r="B75" t="str">
-        <v>Pesquisar no guia do utilizador</v>
+        <v>Ajuda</v>
       </c>
       <c r="C75" t="str">
-        <v>Pesquisar no guia do usuário</v>
+        <v>Ajuda</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Previous match</v>
+        <v>Contact</v>
       </c>
       <c r="B76" t="str">
-        <v>Resultado anterior</v>
+        <v>Contacto</v>
       </c>
       <c r="C76" t="str">
-        <v>Resultado anterior</v>
+        <v>Contato</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Next match</v>
+        <v>User guide</v>
       </c>
       <c r="B77" t="str">
-        <v>Resultado seguinte</v>
+        <v>Guia do utilizador</v>
       </c>
       <c r="C77" t="str">
-        <v>Próximo resultado</v>
+        <v>Guia do usuário</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Close user guide</v>
+        <v>Search guide</v>
       </c>
       <c r="B78" t="str">
-        <v>Fechar o guia</v>
+        <v>Pesquisar no guia</v>
       </c>
       <c r="C78" t="str">
-        <v>Fechar o guia</v>
+        <v>Pesquisar no guia</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Loading…</v>
+        <v>Search the user guide</v>
       </c>
       <c r="B79" t="str">
-        <v>A carregar…</v>
+        <v>Pesquisar no guia do utilizador</v>
       </c>
       <c r="C79" t="str">
-        <v>Carregando…</v>
+        <v>Pesquisar no guia do usuário</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Could not load the user guide.</v>
+        <v>Previous match</v>
       </c>
       <c r="B80" t="str">
-        <v>Não foi possível carregar o guia do utilizador.</v>
+        <v>Resultado anterior</v>
       </c>
       <c r="C80" t="str">
-        <v>Não foi possível carregar o guia do usuário.</v>
+        <v>Resultado anterior</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>None</v>
+        <v>Next match</v>
       </c>
       <c r="B81" t="str">
-        <v>Nenhum</v>
+        <v>Resultado seguinte</v>
       </c>
       <c r="C81" t="str">
-        <v>Nenhum</v>
+        <v>Próximo resultado</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ICC Profile Tool</v>
+        <v>Close user guide</v>
       </c>
       <c r="B82" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Fechar o guia</v>
       </c>
       <c r="C82" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Fechar o guia</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Based on</v>
+        <v>Loading…</v>
       </c>
       <c r="B83" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>A carregar…</v>
       </c>
       <c r="C83" t="str">
-        <v>Baseado na implementação de demonstração do</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>demo implementation</v>
+        <v>Could not load the user guide.</v>
       </c>
       <c r="B84" t="str">
-        <v/>
+        <v>Não foi possível carregar o guia do utilizador.</v>
       </c>
       <c r="C84" t="str">
-        <v/>
+        <v>Não foi possível carregar o guia do usuário.</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Validating…</v>
+        <v>None</v>
       </c>
       <c r="B85" t="str">
-        <v>A validar…</v>
+        <v>Nenhum</v>
       </c>
       <c r="C85" t="str">
-        <v>Validando…</v>
+        <v>Nenhum</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Save ICC profile</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B86" t="str">
-        <v>Guardar perfil ICC</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C86" t="str">
-        <v>Salvar perfil ICC</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>● Modified — unsaved edits</v>
+        <v>Based on</v>
       </c>
       <c r="B87" t="str">
-        <v>● Modificado — não guardado</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
       <c r="C87" t="str">
-        <v>● Modificado — não salvo</v>
+        <v>Baseado na implementação de demonstração do</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Profiles</v>
+        <v>demo implementation</v>
       </c>
       <c r="B88" t="str">
-        <v>Perfis</v>
+        <v/>
       </c>
       <c r="C88" t="str">
-        <v>Perfis</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Show profile pool</v>
+        <v>Validating…</v>
       </c>
       <c r="B89" t="str">
-        <v>Mostrar o conjunto de perfis</v>
+        <v>A validar…</v>
       </c>
       <c r="C89" t="str">
-        <v>Mostrar o conjunto de perfis</v>
+        <v>Validando…</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Collapse</v>
+        <v>Save ICC profile</v>
       </c>
       <c r="B90" t="str">
-        <v>Recolher</v>
+        <v>Guardar perfil ICC</v>
       </c>
       <c r="C90" t="str">
-        <v>Recolher</v>
+        <v>Salvar perfil ICC</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Load Profiles</v>
+        <v>● Modified — unsaved edits</v>
       </c>
       <c r="B91" t="str">
-        <v>Carregar perfis</v>
+        <v>● Modificado — não guardado</v>
       </c>
       <c r="C91" t="str">
-        <v>Carregar perfis</v>
+        <v>● Modificado — não salvo</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Remove</v>
+        <v>Profiles</v>
       </c>
       <c r="B92" t="str">
-        <v>Remover</v>
+        <v>Perfis</v>
       </c>
       <c r="C92" t="str">
-        <v>Remover</v>
+        <v>Perfis</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Drop ICC profiles here</v>
+        <v>Show profile pool</v>
       </c>
       <c r="B93" t="str">
-        <v>Largue perfis ICC aqui</v>
+        <v>Mostrar o conjunto de perfis</v>
       </c>
       <c r="C93" t="str">
-        <v>Solte perfis ICC aqui</v>
+        <v>Mostrar o conjunto de perfis</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
+        <v>Collapse</v>
       </c>
       <c r="B94" t="str">
-        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o respetivo perfil incorporado — os ficheiros permanecem no seu dispositivo.</v>
+        <v>Recolher</v>
       </c>
       <c r="C94" t="str">
-        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o perfil incorporado — os arquivos permanecem no seu dispositivo.</v>
+        <v>Recolher</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>New from .cube</v>
+        <v>Load Profiles</v>
       </c>
       <c r="B95" t="str">
-        <v>Novo a partir de .cube</v>
+        <v>Carregar perfis</v>
       </c>
       <c r="C95" t="str">
-        <v>Novo a partir de .cube</v>
+        <v>Carregar perfis</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Sort by name</v>
+        <v>Remove</v>
       </c>
       <c r="B96" t="str">
-        <v>Ordenar por nome</v>
+        <v>Remover</v>
       </c>
       <c r="C96" t="str">
-        <v>Ordenar por nome</v>
+        <v>Remover</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>A–Z</v>
+        <v>Drop ICC profiles here</v>
       </c>
       <c r="B97" t="str">
-        <v>A–Z</v>
+        <v>Largue perfis ICC aqui</v>
       </c>
       <c r="C97" t="str">
-        <v>A–Z</v>
+        <v>Solte perfis ICC aqui</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>New profile from .cube</v>
+        <v>or an image (TIFF/PNG/JPEG) to extract its embedded profile — files stay on your device.</v>
       </c>
       <c r="B98" t="str">
-        <v>Novo perfil a partir de .cube</v>
+        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o respetivo perfil incorporado — os ficheiros permanecem no seu dispositivo.</v>
       </c>
       <c r="C98" t="str">
-        <v>Novo perfil a partir de .cube</v>
+        <v>ou uma imagem (TIFF/PNG/JPEG) para extrair o perfil incorporado — os arquivos permanecem no seu dispositivo.</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+        <v>New from .cube</v>
       </c>
       <c r="B99" t="str">
-        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e transferido.</v>
+        <v>Novo a partir de .cube</v>
       </c>
       <c r="C99" t="str">
-        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e baixado.</v>
+        <v>Novo a partir de .cube</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Choose .cube file</v>
+        <v>Sort by name</v>
       </c>
       <c r="B100" t="str">
-        <v>Escolher ficheiro .cube</v>
+        <v>Ordenar por nome</v>
       </c>
       <c r="C100" t="str">
-        <v>Escolher arquivo .cube</v>
+        <v>Ordenar por nome</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>A–Z</v>
+      </c>
+      <c r="B101" t="str">
+        <v>A–Z</v>
+      </c>
+      <c r="C101" t="str">
+        <v>A–Z</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>New profile from .cube</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Novo perfil a partir de .cube</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Novo perfil a partir de .cube</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Build an ICC DeviceLink from an Adobe/Resolve .cube 3D-LUT. The result is added to your pool and downloaded.</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e transferido.</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Crie um DeviceLink ICC a partir de uma LUT 3D .cube da Adobe/Resolve. O resultado é adicionado ao seu conjunto e baixado.</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Choose .cube file</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Escolher ficheiro .cube</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Escolher arquivo .cube</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>or drop it here, or paste below</v>
       </c>
-      <c r="B101" t="str">
+      <c r="B105" t="str">
         <v>ou largue-o aqui, ou cole abaixo</v>
       </c>
-      <c r="C101" t="str">
+      <c r="C105" t="str">
         <v>ou solte-o aqui, ou cole abaixo</v>
       </c>
     </row>
-    <row r="102" xml:space="preserve">
-      <c r="A102" t="str" xml:space="preserve">
+    <row r="106" xml:space="preserve">
+      <c r="A106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="B102" t="str" xml:space="preserve">
+      <c r="B106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
-      <c r="C102" t="str" xml:space="preserve">
+      <c r="C106" t="str" xml:space="preserve">
         <v xml:space="preserve">TITLE "My LUT"
 LUT_3D_SIZE 33
 0.0 0.0 0.0
 …</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Cancel</v>
-      </c>
-      <c r="B103" t="str">
-        <v>Cancelar</v>
-      </c>
-      <c r="C103" t="str">
-        <v>Cancelar</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Create DeviceLink</v>
-      </c>
-      <c r="B104" t="str">
-        <v>Criar DeviceLink</v>
-      </c>
-      <c r="C104" t="str">
-        <v>Criar DeviceLink</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Creating…</v>
-      </c>
-      <c r="B105" t="str">
-        <v>A criar…</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Criando…</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Could not read that file.</v>
-      </c>
-      <c r="B106" t="str">
-        <v>Não foi possível ler esse ficheiro.</v>
-      </c>
-      <c r="C106" t="str">
-        <v>Não foi possível ler esse arquivo.</v>
-      </c>
-    </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Profile</v>
+        <v>Cancel</v>
       </c>
       <c r="B107" t="str">
-        <v>Perfil</v>
+        <v>Cancelar</v>
       </c>
       <c r="C107" t="str">
-        <v>Perfil</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Compare</v>
+        <v>Create DeviceLink</v>
       </c>
       <c r="B108" t="str">
-        <v>Comparar</v>
+        <v>Criar DeviceLink</v>
       </c>
       <c r="C108" t="str">
-        <v>Comparar</v>
+        <v>Criar DeviceLink</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Combine</v>
+        <v>Creating…</v>
       </c>
       <c r="B109" t="str">
-        <v>Ligar</v>
+        <v>A criar…</v>
       </c>
       <c r="C109" t="str">
-        <v>Vincular</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Spectral</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B110" t="str">
-        <v>Espectral</v>
+        <v>Não foi possível ler esse ficheiro.</v>
       </c>
       <c r="C110" t="str">
-        <v>Espectral</v>
+        <v>Não foi possível ler esse arquivo.</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Drag profiles from the pool onto this tab</v>
+        <v>Profile</v>
       </c>
       <c r="B111" t="str">
-        <v>Arraste perfis do conjunto para este separador</v>
+        <v>Perfil</v>
       </c>
       <c r="C111" t="str">
-        <v>Arraste perfis do conjunto para esta aba</v>
+        <v>Perfil</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Remove</v>
+        <v>Compare</v>
       </c>
       <c r="B112" t="str">
-        <v>Remover</v>
+        <v>Comparar</v>
       </c>
       <c r="C112" t="str">
-        <v>Remover</v>
+        <v>Comparar</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>No profile selected</v>
+        <v>Combine</v>
       </c>
       <c r="B113" t="str">
-        <v>Nenhum perfil selecionado</v>
+        <v>Ligar</v>
       </c>
       <c r="C113" t="str">
-        <v>Nenhum perfil selecionado</v>
+        <v>Vincular</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
+        <v>Spectral</v>
       </c>
       <c r="B114" t="str">
-        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
+        <v>Espectral</v>
       </c>
       <c r="C114" t="str">
-        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
+        <v>Espectral</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Nothing to compare yet</v>
+        <v>Drag profiles from the pool onto this tab</v>
       </c>
       <c r="B115" t="str">
-        <v>Ainda nada para comparar</v>
+        <v>Arraste perfis do conjunto para este separador</v>
       </c>
       <c r="C115" t="str">
-        <v>Ainda nada para comparar</v>
+        <v>Arraste perfis do conjunto para esta aba</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Drag one or more profiles onto the Compare tab.</v>
+        <v>Remove</v>
       </c>
       <c r="B116" t="str">
-        <v>Arraste um ou mais perfis para o separador Comparar.</v>
+        <v>Remover</v>
       </c>
       <c r="C116" t="str">
-        <v>Arraste um ou mais perfis para a aba Comparar.</v>
+        <v>Remover</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Gamut comparison</v>
+        <v>No profile selected</v>
       </c>
       <c r="B117" t="str">
-        <v>Comparação de gamut</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
       <c r="C117" t="str">
-        <v>Comparação de gamut</v>
+        <v>Nenhum perfil selecionado</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
+        <v>Drag a profile from the pool onto the Profile tab to inspect it.</v>
       </c>
       <c r="B118" t="str">
-        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
+        <v>Arraste um perfil do conjunto para o separador Perfil para o inspecionar.</v>
       </c>
       <c r="C118" t="str">
-        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
+        <v>Arraste um perfil do conjunto para a aba Perfil para inspecioná-lo.</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Rendering intent</v>
+        <v>Nothing to compare yet</v>
       </c>
       <c r="B119" t="str">
-        <v>Intenção de renderização</v>
+        <v>Ainda nada para comparar</v>
       </c>
       <c r="C119" t="str">
-        <v>Intenção de renderização</v>
+        <v>Ainda nada para comparar</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Shell</v>
+        <v>Drag one or more profiles onto the Compare tab.</v>
       </c>
       <c r="B120" t="str">
-        <v>Invólucro</v>
+        <v>Arraste um ou mais perfis para o separador Comparar.</v>
       </c>
       <c r="C120" t="str">
-        <v>Invólucro</v>
+        <v>Arraste um ou mais perfis para a aba Comparar.</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Wireframe</v>
+        <v>Gamut comparison</v>
       </c>
       <c r="B121" t="str">
-        <v>Malha de arame</v>
+        <v>Comparação de gamut</v>
       </c>
       <c r="C121" t="str">
-        <v>Malha de arame</v>
+        <v>Comparação de gamut</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Axis numbers</v>
+        <v>3D gamut &amp; 2D slice views are coming here. Accumulated:</v>
       </c>
       <c r="B122" t="str">
-        <v>Números dos eixos</v>
+        <v>As vistas de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
       <c r="C122" t="str">
-        <v>Números dos eixos</v>
+        <v>As visualizações de gamut 3D e corte 2D chegarão aqui. Acumulados:</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Opacity</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B123" t="str">
-        <v>Opacidade</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C123" t="str">
-        <v>Opacidade</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Colour</v>
+        <v>Shell</v>
       </c>
       <c r="B124" t="str">
-        <v>Cor</v>
+        <v>Invólucro</v>
       </c>
       <c r="C124" t="str">
-        <v>Cor</v>
+        <v>Invólucro</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Solid</v>
+        <v>Wireframe</v>
       </c>
       <c r="B125" t="str">
-        <v>Sólido</v>
+        <v>Malha de arame</v>
       </c>
       <c r="C125" t="str">
-        <v>Sólido</v>
+        <v>Malha de arame</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>By value</v>
+        <v>Axis numbers</v>
       </c>
       <c r="B126" t="str">
-        <v>Por valor</v>
+        <v>Números dos eixos</v>
       </c>
       <c r="C126" t="str">
-        <v>Por valor</v>
+        <v>Números dos eixos</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>By hue</v>
+        <v>Opacity</v>
       </c>
       <c r="B127" t="str">
-        <v>Por matiz</v>
+        <v>Opacidade</v>
       </c>
       <c r="C127" t="str">
-        <v>Por matiz</v>
+        <v>Opacidade</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Rotation</v>
+        <v>Colour</v>
       </c>
       <c r="B128" t="str">
-        <v>Rotação</v>
+        <v>Cor</v>
       </c>
       <c r="C128" t="str">
-        <v>Rotação</v>
+        <v>Cor</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Turntable</v>
+        <v>Solid</v>
       </c>
       <c r="B129" t="str">
-        <v>Prato giratório</v>
+        <v>Sólido</v>
       </c>
       <c r="C129" t="str">
-        <v>Prato giratório</v>
+        <v>Sólido</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Orbit</v>
+        <v>By value</v>
       </c>
       <c r="B130" t="str">
-        <v>Órbita</v>
+        <v>Por valor</v>
       </c>
       <c r="C130" t="str">
-        <v>Órbita</v>
+        <v>Por valor</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Drag speed</v>
+        <v>By hue</v>
       </c>
       <c r="B131" t="str">
-        <v>Velocidade de arrasto</v>
+        <v>Por matiz</v>
       </c>
       <c r="C131" t="str">
-        <v>Velocidade de arrasto</v>
+        <v>Por matiz</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Roll</v>
+        <v>Rotation</v>
       </c>
       <c r="B132" t="str">
-        <v>Rolamento</v>
+        <v>Rotação</v>
       </c>
       <c r="C132" t="str">
-        <v>Rolagem</v>
+        <v>Rotação</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Roll speed</v>
+        <v>Turntable</v>
       </c>
       <c r="B133" t="str">
-        <v>Velocidade de rolamento</v>
+        <v>Prato giratório</v>
       </c>
       <c r="C133" t="str">
-        <v>Velocidade de rolagem</v>
+        <v>Prato giratório</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Building gamut…</v>
+        <v>Orbit</v>
       </c>
       <c r="B134" t="str">
-        <v>A construir o gamut…</v>
+        <v>Órbita</v>
       </c>
       <c r="C134" t="str">
-        <v>Construindo o gamut…</v>
+        <v>Órbita</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>no gamut</v>
+        <v>Drag speed</v>
       </c>
       <c r="B135" t="str">
-        <v>sem gamut</v>
+        <v>Velocidade de arrasto</v>
       </c>
       <c r="C135" t="str">
-        <v>sem gamut</v>
+        <v>Velocidade de arrasto</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Show / hide</v>
+        <v>Roll</v>
       </c>
       <c r="B136" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>Rolamento</v>
       </c>
       <c r="C136" t="str">
-        <v>Mostrar / ocultar</v>
+        <v>Rolagem</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>3-D gamut shell</v>
+        <v>Roll speed</v>
       </c>
       <c r="B137" t="str">
-        <v>Invólucro de gamut 3D</v>
+        <v>Velocidade de rolamento</v>
       </c>
       <c r="C137" t="str">
-        <v>Invólucro de gamut 3D</v>
+        <v>Velocidade de rolagem</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>2-D gamut slice</v>
+        <v>Building gamut…</v>
       </c>
       <c r="B138" t="str">
-        <v>Corte de gamut 2D</v>
+        <v>A construir o gamut…</v>
       </c>
       <c r="C138" t="str">
-        <v>Corte de gamut 2D</v>
+        <v>Construindo o gamut…</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Plane</v>
+        <v>no gamut</v>
       </c>
       <c r="B139" t="str">
-        <v>Plano</v>
+        <v>sem gamut</v>
       </c>
       <c r="C139" t="str">
-        <v>Plano</v>
+        <v>sem gamut</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>L*</v>
+        <v>Show / hide</v>
       </c>
       <c r="B140" t="str">
-        <v>L*</v>
+        <v>Mostrar / ocultar</v>
       </c>
       <c r="C140" t="str">
-        <v>L*</v>
+        <v>Mostrar / ocultar</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>a*</v>
+        <v>3-D gamut shell</v>
       </c>
       <c r="B141" t="str">
-        <v>a*</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
       <c r="C141" t="str">
-        <v>a*</v>
+        <v>Invólucro de gamut 3D</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>b*</v>
+        <v>2-D gamut slice</v>
       </c>
       <c r="B142" t="str">
-        <v>b*</v>
+        <v>Corte de gamut 2D</v>
       </c>
       <c r="C142" t="str">
-        <v>b*</v>
+        <v>Corte de gamut 2D</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
+        <v>Plane</v>
       </c>
       <c r="B143" t="str">
-        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
+        <v>Plano</v>
       </c>
       <c r="C143" t="str">
-        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
+        <v>Plano</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Linking</v>
+        <v>L*</v>
       </c>
       <c r="B144" t="str">
-        <v>Ligação</v>
+        <v>L*</v>
       </c>
       <c r="C144" t="str">
-        <v>Vínculo</v>
+        <v>L*</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
+        <v>a*</v>
       </c>
       <c r="B145" t="str">
-        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
+        <v>a*</v>
       </c>
       <c r="C145" t="str">
-        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
+        <v>a*</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>More link makers (DeviceLink, …) arrive here.</v>
+        <v>b*</v>
       </c>
       <c r="B146" t="str">
-        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
+        <v>b*</v>
       </c>
       <c r="C146" t="str">
-        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
+        <v>b*</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Observer Change</v>
+        <v>None of the selected profiles has a device→PCS transform to derive a gamut from.</v>
       </c>
       <c r="B147" t="str">
-        <v>Criador de ecrã V4</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
       <c r="C147" t="str">
-        <v>Criador de tela V4</v>
+        <v>Nenhum dos perfis selecionados tem uma transformação dispositivo→PCS a partir da qual derivar um gamut.</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
+        <v>Linking</v>
       </c>
       <c r="B148" t="str">
-        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
+        <v>Ligação</v>
       </c>
       <c r="C148" t="str">
-        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
+        <v>Vínculo</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>V5 RGB display</v>
+        <v>DeviceLink production and multi-profile transforms arrive in a later phase.</v>
       </c>
       <c r="B149" t="str">
-        <v>Ecrã RGB V5</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão numa fase posterior.</v>
       </c>
       <c r="C149" t="str">
-        <v>Tela RGB V5</v>
+        <v>A produção de DeviceLink e as transformações multiperfil chegarão em uma fase posterior.</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>drop a display profile</v>
+        <v>More link makers (DeviceLink, …) arrive here.</v>
       </c>
       <c r="B150" t="str">
-        <v>largue um perfil de ecrã</v>
+        <v>Mais criadores de ligações (DeviceLink, …) chegarão aqui.</v>
       </c>
       <c r="C150" t="str">
-        <v>solte um perfil de tela</v>
+        <v>Mais criadores de vínculos (DeviceLink, …) chegarão aqui.</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>V5 observer (PCC)</v>
+        <v>Observer Change</v>
       </c>
       <c r="B151" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>Criador de ecrã V4</v>
       </c>
       <c r="C151" t="str">
-        <v>Observador V5 (PCC)</v>
+        <v>Criador de tela V4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>drop an observer profile</v>
+        <v>Drag a V5 RGB display and a V5 observer profile here to build a V4 display profile.</v>
       </c>
       <c r="B152" t="str">
-        <v>largue um perfil de observador</v>
+        <v>Arraste para aqui um perfil de ecrã RGB V5 e um perfil de observador V5 para criar um perfil de ecrã V4.</v>
       </c>
       <c r="C152" t="str">
-        <v>solte um perfil de observador</v>
+        <v>Arraste para cá um perfil de tela RGB V5 e um perfil de observador V5 para criar um perfil de tela V4.</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
+        <v>V5 RGB display</v>
       </c>
       <c r="B153" t="str">
-        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
+        <v>Ecrã RGB V5</v>
       </c>
       <c r="C153" t="str">
-        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
+        <v>Tela RGB V5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Make V4 Display Profile</v>
+        <v>drop a display profile</v>
       </c>
       <c r="B154" t="str">
-        <v>Criar perfil de ecrã V4</v>
+        <v>largue um perfil de ecrã</v>
       </c>
       <c r="C154" t="str">
-        <v>Criar perfil de tela V4</v>
+        <v>solte um perfil de tela</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Profile name</v>
+        <v>V5 observer (PCC)</v>
       </c>
       <c r="B155" t="str">
-        <v>Nome do perfil</v>
+        <v>Observador V5 (PCC)</v>
       </c>
       <c r="C155" t="str">
-        <v>Nome do perfil</v>
+        <v>Observador V5 (PCC)</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Create</v>
+        <v>drop an observer profile</v>
       </c>
       <c r="B156" t="str">
-        <v>Criar</v>
+        <v>largue um perfil de observador</v>
       </c>
       <c r="C156" t="str">
-        <v>Criar</v>
+        <v>solte um perfil de observador</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Making…</v>
+        <v>Ignored a profile that is neither a V5 RGB display nor an observer.</v>
       </c>
       <c r="B157" t="str">
-        <v>A criar…</v>
+        <v>Foi ignorado um perfil que não é um ecrã RGB V5 nem um observador.</v>
       </c>
       <c r="C157" t="str">
-        <v>Criando…</v>
+        <v>Um perfil que não é uma tela RGB V5 nem um observador foi ignorado.</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Make V4 Display Profile</v>
       </c>
       <c r="B158" t="str">
-        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
+        <v>Criar perfil de ecrã V4</v>
       </c>
       <c r="C158" t="str">
-        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
+        <v>Criar perfil de tela V4</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Link Pipeline</v>
+        <v>Profile name</v>
       </c>
       <c r="B159" t="str">
-        <v>Fluxo de ligação</v>
+        <v>Nome do perfil</v>
       </c>
       <c r="C159" t="str">
-        <v>Fluxo de vinculação</v>
+        <v>Nome do perfil</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
+        <v>Create</v>
       </c>
       <c r="B160" t="str">
-        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
+        <v>Criar</v>
       </c>
       <c r="C160" t="str">
-        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
+        <v>Criar</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Done</v>
+        <v>Making…</v>
       </c>
       <c r="B161" t="str">
-        <v>Concluído</v>
+        <v>A criar…</v>
       </c>
       <c r="C161" t="str">
-        <v>Concluído</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B162" t="str">
-        <v>Largue uma imagem para transformar (TIFF/PNG/JPEG)</v>
+        <v>«{name}» criado — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C162" t="str">
-        <v>Solte uma imagem para transformar (TIFF/PNG/JPEG)</v>
+        <v>«{name}» criado — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Checking image…</v>
+        <v>Link Pipeline</v>
       </c>
       <c r="B163" t="str">
-        <v>A verificar imagem…</v>
+        <v>Fluxo de ligação</v>
       </c>
       <c r="C163" t="str">
-        <v>Verificando imagem…</v>
+        <v>Fluxo de vinculação</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Not a supported image (TIFF, PNG or JPEG).</v>
+        <v>Build a chain of profiles, then make a DeviceLink, transform an image, or transform a colour dataset through it.</v>
       </c>
       <c r="B164" t="str">
-        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
+        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
       </c>
       <c r="C164" t="str">
-        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
+        <v>Crie uma cadeia de perfis e depois crie um DeviceLink, transforme uma imagem ou transforme um conjunto de dados de cor através dela.</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Image too large ({mp} MP; limit {max} MP).</v>
+        <v>Done</v>
       </c>
       <c r="B165" t="str">
-        <v>Imagem demasiado grande ({mp} MP; limite {max} MP).</v>
+        <v>Concluído</v>
       </c>
       <c r="C165" t="str">
-        <v>Imagem grande demais ({mp} MP; limite {max} MP).</v>
+        <v>Concluído</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Transform Image</v>
+        <v>Drop an image to transform (TIFF/PNG/JPEG)</v>
       </c>
       <c r="B166" t="str">
-        <v>Transformar imagem</v>
+        <v>Largue uma imagem para transformar (TIFF/PNG/JPEG)</v>
       </c>
       <c r="C166" t="str">
-        <v>Transformar imagem</v>
+        <v>Solte uma imagem para transformar (TIFF/PNG/JPEG)</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Transforming…</v>
+        <v>Checking image…</v>
       </c>
       <c r="B167" t="str">
-        <v>A transformar…</v>
+        <v>A verificar imagem…</v>
       </c>
       <c r="C167" t="str">
-        <v>Transformando…</v>
+        <v>Verificando imagem…</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Drop profiles to start the chain</v>
+        <v>Not a supported image (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B168" t="str">
-        <v>Largue perfis para iniciar a cadeia</v>
+        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
       </c>
       <c r="C168" t="str">
-        <v>Solte perfis para iniciar a cadeia</v>
+        <v>Imagem não suportada (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>removed</v>
+        <v>Image too large ({mp} MP; limit {max} MP).</v>
       </c>
       <c r="B169" t="str">
-        <v>removido</v>
+        <v>Imagem demasiado grande ({mp} MP; limite {max} MP).</v>
       </c>
       <c r="C169" t="str">
-        <v>removido</v>
+        <v>Imagem grande demais ({mp} MP; limite {max} MP).</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Move earlier</v>
+        <v>Transform Image</v>
       </c>
       <c r="B170" t="str">
-        <v>Mover antes</v>
+        <v>Transformar imagem</v>
       </c>
       <c r="C170" t="str">
-        <v>Mover antes</v>
+        <v>Transformar imagem</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Move later</v>
+        <v>Transforming…</v>
       </c>
       <c r="B171" t="str">
-        <v>Mover depois</v>
+        <v>A transformar…</v>
       </c>
       <c r="C171" t="str">
-        <v>Mover depois</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Move up</v>
+        <v>Drop profiles to start the chain</v>
       </c>
       <c r="B172" t="str">
-        <v>Mover para cima</v>
+        <v>Largue perfis para iniciar a cadeia</v>
       </c>
       <c r="C172" t="str">
-        <v>Mover para cima</v>
+        <v>Solte perfis para iniciar a cadeia</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Move down</v>
+        <v>removed</v>
       </c>
       <c r="B173" t="str">
-        <v>Mover para baixo</v>
+        <v>removido</v>
       </c>
       <c r="C173" t="str">
-        <v>Mover para baixo</v>
+        <v>removido</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Rendering intent (all)</v>
+        <v>Move earlier</v>
       </c>
       <c r="B174" t="str">
-        <v>Intenção de renderização (todas)</v>
+        <v>Mover antes</v>
       </c>
       <c r="C174" t="str">
-        <v>Intenção de renderização (todas)</v>
+        <v>Mover antes</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Rendering intent for this transform</v>
+        <v>Move later</v>
       </c>
       <c r="B175" t="str">
-        <v>Intenção de renderização para esta transformação</v>
+        <v>Mover depois</v>
       </c>
       <c r="C175" t="str">
-        <v>Intenção de renderização para esta transformação</v>
+        <v>Mover depois</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Transforms use different rendering intents</v>
+        <v>Move up</v>
       </c>
       <c r="B176" t="str">
-        <v>As transformações usam intenções de renderização diferentes</v>
+        <v>Mover para cima</v>
       </c>
       <c r="C176" t="str">
-        <v>As transformações usam intenções de renderização diferentes</v>
+        <v>Mover para cima</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
+        <v>Move down</v>
       </c>
       <c r="B177" t="str">
-        <v>Inverter direção da cadeia (inverte a transformação inicial e propaga-se por toda a cadeia)</v>
+        <v>Mover para baixo</v>
       </c>
       <c r="C177" t="str">
-        <v>Inverter direção da cadeia (inverte a transformação inicial e se propaga por toda a cadeia)</v>
+        <v>Mover para baixo</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>A chained profile was removed from the pool — remove it to continue.</v>
+        <v>Rendering intent (all)</v>
       </c>
       <c r="B178" t="str">
-        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
+        <v>Intenção de renderização (todas)</v>
       </c>
       <c r="C178" t="str">
-        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
+        <v>Intenção de renderização (todas)</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Chain</v>
+        <v>Rendering intent for this transform</v>
       </c>
       <c r="B179" t="str">
-        <v>Cadeia</v>
+        <v>Intenção de renderização para esta transformação</v>
       </c>
       <c r="C179" t="str">
-        <v>Cadeia</v>
+        <v>Intenção de renderização para esta transformação</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>The chain could not be analysed.</v>
+        <v>Transforms use different rendering intents</v>
       </c>
       <c r="B180" t="str">
-        <v>Não foi possível analisar a cadeia.</v>
+        <v>As transformações usam intenções de renderização diferentes</v>
       </c>
       <c r="C180" t="str">
-        <v>Não foi possível analisar a cadeia.</v>
+        <v>As transformações usam intenções de renderização diferentes</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Checking chain…</v>
+        <v>Flip chain direction (reverses the head transform, rippling through the chain)</v>
       </c>
       <c r="B181" t="str">
-        <v>A verificar cadeia…</v>
+        <v>Inverter direção da cadeia (inverte a transformação inicial e propaga-se por toda a cadeia)</v>
       </c>
       <c r="C181" t="str">
-        <v>Verificando cadeia…</v>
+        <v>Inverter direção da cadeia (inverte a transformação inicial e se propaga por toda a cadeia)</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>The chain does not connect ({detail}).</v>
+        <v>A chained profile was removed from the pool — remove it to continue.</v>
       </c>
       <c r="B182" t="str">
-        <v>A cadeia não liga ({detail}).</v>
+        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
       </c>
       <c r="C182" t="str">
-        <v>A cadeia não conecta ({detail}).</v>
+        <v>Um perfil encadeado foi removido do conjunto — remova-o para continuar.</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
+        <v>Chain</v>
       </c>
       <c r="B183" t="str">
-        <v>O perfil {n} não liga à etapa anterior ({detail}).</v>
+        <v>Cadeia</v>
       </c>
       <c r="C183" t="str">
-        <v>O perfil {n} não conecta com a etapa anterior ({detail}).</v>
+        <v>Cadeia</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Fix the chain before processing images</v>
+        <v>The chain could not be analysed.</v>
       </c>
       <c r="B184" t="str">
-        <v>Corrija a cadeia antes de processar imagens</v>
+        <v>Não foi possível analisar a cadeia.</v>
       </c>
       <c r="C184" t="str">
-        <v>Corrija a cadeia antes de processar imagens</v>
+        <v>Não foi possível analisar a cadeia.</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Clear</v>
+        <v>Checking chain…</v>
       </c>
       <c r="B185" t="str">
-        <v>Limpar</v>
+        <v>A verificar cadeia…</v>
       </c>
       <c r="C185" t="str">
-        <v>Limpar</v>
+        <v>Verificando cadeia…</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Make DeviceLink</v>
+        <v>The chain does not connect ({detail}).</v>
       </c>
       <c r="B186" t="str">
-        <v>Criar DeviceLink</v>
+        <v>A cadeia não liga ({detail}).</v>
       </c>
       <c r="C186" t="str">
-        <v>Criar DeviceLink</v>
+        <v>A cadeia não conecta ({detail}).</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>DeviceLink name</v>
+        <v>Profile {n} does not connect to the previous stage ({detail}).</v>
       </c>
       <c r="B187" t="str">
-        <v>Nome do DeviceLink</v>
+        <v>O perfil {n} não liga à etapa anterior ({detail}).</v>
       </c>
       <c r="C187" t="str">
-        <v>Nome do DeviceLink</v>
+        <v>O perfil {n} não conecta com a etapa anterior ({detail}).</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Making…</v>
+        <v>Fix the chain before processing images</v>
       </c>
       <c r="B188" t="str">
-        <v>A criar…</v>
+        <v>Corrija a cadeia antes de processar imagens</v>
       </c>
       <c r="C188" t="str">
-        <v>Criando…</v>
+        <v>Corrija a cadeia antes de processar imagens</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Created “{name}” — added to the pool and this tab.</v>
+        <v>Clear</v>
       </c>
       <c r="B189" t="str">
-        <v>Criado “{name}” — adicionado ao conjunto e a este separador.</v>
+        <v>Limpar</v>
       </c>
       <c r="C189" t="str">
-        <v>Criado “{name}” — adicionado ao conjunto e a esta aba.</v>
+        <v>Limpar</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
+        <v>Make DeviceLink</v>
       </c>
       <c r="B190" t="str">
-        <v>Largue imagens {src} para converter para {dst} — os resultados são descarregados, nada é armazenado.</v>
+        <v>Criar DeviceLink</v>
       </c>
       <c r="C190" t="str">
-        <v>Solte imagens {src} para converter para {dst} — os resultados são baixados, nada é armazenado.</v>
+        <v>Criar DeviceLink</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Build a chain to process images</v>
+        <v>DeviceLink name</v>
       </c>
       <c r="B191" t="str">
-        <v>Crie uma cadeia para processar imagens</v>
+        <v>Nome do DeviceLink</v>
       </c>
       <c r="C191" t="str">
-        <v>Crie uma cadeia para processar imagens</v>
+        <v>Nome do DeviceLink</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>This chain does not start and end in an image colour space</v>
+        <v>Making…</v>
       </c>
       <c r="B192" t="str">
-        <v>Esta cadeia não começa nem termina num espaço de cor de imagem</v>
+        <v>A criar…</v>
       </c>
       <c r="C192" t="str">
-        <v>Esta cadeia não começa nem termina em um espaço de cor de imagem</v>
+        <v>Criando…</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Saved the transformed image.</v>
+        <v>Created “{name}” — added to the pool and this tab.</v>
       </c>
       <c r="B193" t="str">
-        <v>Imagem transformada guardada.</v>
+        <v>Criado “{name}” — adicionado ao conjunto e a este separador.</v>
       </c>
       <c r="C193" t="str">
-        <v>Imagem transformada salva.</v>
+        <v>Criado “{name}” — adicionado ao conjunto e a esta aba.</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
+        <v>Drop {src} images to convert to {dst} — results download, nothing is stored.</v>
       </c>
       <c r="B194" t="str">
-        <v>Largue um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
+        <v>Largue imagens {src} para converter para {dst} — os resultados são descarregados, nada é armazenado.</v>
       </c>
       <c r="C194" t="str">
-        <v>Solte um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
+        <v>Solte imagens {src} para converter para {dst} — os resultados são baixados, nada é armazenado.</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Could not read that file.</v>
+        <v>Build a chain to process images</v>
       </c>
       <c r="B195" t="str">
-        <v>Não foi possível ler esse ficheiro.</v>
+        <v>Crie uma cadeia para processar imagens</v>
       </c>
       <c r="C195" t="str">
-        <v>Não foi possível ler esse arquivo.</v>
+        <v>Crie uma cadeia para processar imagens</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Data file too large.</v>
+        <v>This chain does not start and end in an image colour space</v>
       </c>
       <c r="B196" t="str">
-        <v>Ficheiro de dados demasiado grande.</v>
+        <v>Esta cadeia não começa nem termina num espaço de cor de imagem</v>
       </c>
       <c r="C196" t="str">
-        <v>Arquivo de dados grande demais.</v>
+        <v>Esta cadeia não começa nem termina em um espaço de cor de imagem</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Transform Data</v>
+        <v>Saved the transformed image.</v>
       </c>
       <c r="B197" t="str">
-        <v>Transformar dados</v>
+        <v>Imagem transformada guardada.</v>
       </c>
       <c r="C197" t="str">
-        <v>Transformar dados</v>
+        <v>Imagem transformada salva.</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Transforming…</v>
+        <v>Drop a colour dataset (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="B198" t="str">
-        <v>A transformar…</v>
+        <v>Largue um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
       </c>
       <c r="C198" t="str">
-        <v>Transformando…</v>
+        <v>Solte um conjunto de dados de cor (CGATS/CSV/CxF/JSON)</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Prefer</v>
+        <v>Could not read that file.</v>
       </c>
       <c r="B199" t="str">
-        <v>Preferir</v>
+        <v>Não foi possível ler esse ficheiro.</v>
       </c>
       <c r="C199" t="str">
-        <v>Preferir</v>
+        <v>Não foi possível ler esse arquivo.</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Observer</v>
+        <v>Data file too large.</v>
       </c>
       <c r="B200" t="str">
-        <v>Observador</v>
+        <v>Ficheiro de dados demasiado grande.</v>
       </c>
       <c r="C200" t="str">
-        <v>Observador</v>
+        <v>Arquivo de dados grande demais.</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Illuminant</v>
+        <v>Transform Data</v>
       </c>
       <c r="B201" t="str">
-        <v>Iluminante</v>
+        <v>Transformar dados</v>
       </c>
       <c r="C201" t="str">
-        <v>Iluminante</v>
+        <v>Transformar dados</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Condition</v>
+        <v>Transforming…</v>
       </c>
       <c r="B202" t="str">
-        <v>Condição</v>
+        <v>A transformar…</v>
       </c>
       <c r="C202" t="str">
-        <v>Condição</v>
+        <v>Transformando…</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Filter {n} duplicate(s)</v>
+        <v>Prefer</v>
       </c>
       <c r="B203" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>Preferir</v>
       </c>
       <c r="C203" t="str">
-        <v>Filtrar {n} duplicado(s)</v>
+        <v>Preferir</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>median</v>
+        <v>Observer</v>
       </c>
       <c r="B204" t="str">
-        <v>mediana</v>
+        <v>Observador</v>
       </c>
       <c r="C204" t="str">
-        <v>mediana</v>
+        <v>Observador</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>mean</v>
+        <v>Illuminant</v>
       </c>
       <c r="B205" t="str">
-        <v>média</v>
+        <v>Iluminante</v>
       </c>
       <c r="C205" t="str">
-        <v>média</v>
+        <v>Iluminante</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>patches</v>
+        <v>Condition</v>
       </c>
       <c r="B206" t="str">
-        <v>patches</v>
+        <v>Condição</v>
       </c>
       <c r="C206" t="str">
-        <v>patches</v>
+        <v>Condição</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>{n} duplicates</v>
+        <v>Filter {n} duplicate(s)</v>
       </c>
       <c r="B207" t="str">
-        <v>{n} duplicados</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
       <c r="C207" t="str">
-        <v>{n} duplicados</v>
+        <v>Filtrar {n} duplicado(s)</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Transform result</v>
+        <v>median</v>
       </c>
       <c r="B208" t="str">
-        <v>Resultado da transformação</v>
+        <v>mediana</v>
       </c>
       <c r="C208" t="str">
-        <v>Resultado da transformação</v>
+        <v>mediana</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>mean</v>
       </c>
       <c r="B209" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>média</v>
       </c>
       <c r="C209" t="str">
-        <v>{src} → {dst} · {n} patches</v>
+        <v>média</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Showing first {shown} of {total} — Save writes them all.</v>
+        <v>patches</v>
       </c>
       <c r="B210" t="str">
-        <v>A mostrar os primeiros {shown} de {total} — Guardar grava todos.</v>
+        <v>patches</v>
       </c>
       <c r="C210" t="str">
-        <v>Mostrando os primeiros {shown} de {total} — Salvar grava todos.</v>
+        <v>patches</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Save as</v>
+        <v>{n} duplicates</v>
       </c>
       <c r="B211" t="str">
-        <v>Guardar como</v>
+        <v>{n} duplicados</v>
       </c>
       <c r="C211" t="str">
-        <v>Salvar como</v>
+        <v>{n} duplicados</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Save</v>
+        <v>Transform result</v>
       </c>
       <c r="B212" t="str">
-        <v>Guardar</v>
+        <v>Resultado da transformação</v>
       </c>
       <c r="C212" t="str">
-        <v>Salvar</v>
+        <v>Resultado da transformação</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Invert Transform</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="B213" t="str">
-        <v>Inverter transformação</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
       <c r="C213" t="str">
-        <v>Inverter transformação</v>
+        <v>{src} → {dst} · {n} patches</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Inverting…</v>
+        <v>Showing first {shown} of {total} — Save writes them all.</v>
       </c>
       <c r="B214" t="str">
-        <v>A inverter…</v>
+        <v>A mostrar os primeiros {shown} de {total} — Guardar grava todos.</v>
       </c>
       <c r="C214" t="str">
-        <v>Invertendo…</v>
+        <v>Mostrando os primeiros {shown} de {total} — Salvar grava todos.</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Invert</v>
+        <v>Save as</v>
       </c>
       <c r="B215" t="str">
-        <v>Inverter</v>
+        <v>Guardar como</v>
       </c>
       <c r="C215" t="str">
-        <v>Inverter</v>
+        <v>Salvar como</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>last stage</v>
+        <v>Save</v>
       </c>
       <c r="B216" t="str">
-        <v>última etapa</v>
+        <v>Guardar</v>
       </c>
       <c r="C216" t="str">
-        <v>última etapa</v>
+        <v>Salvar</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>first stage</v>
+        <v>Invert Transform</v>
       </c>
       <c r="B217" t="str">
-        <v>primeira etapa</v>
+        <v>Inverter transformação</v>
       </c>
       <c r="C217" t="str">
-        <v>primeira etapa</v>
+        <v>Inverter transformação</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Data in {in} → search {out}</v>
+        <v>Inverting…</v>
       </c>
       <c r="B218" t="str">
-        <v>Dados em {in} → procurar {out}</v>
+        <v>A inverter…</v>
       </c>
       <c r="C218" t="str">
-        <v>Dados em {in} → buscar {out}</v>
+        <v>Invertendo…</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Invert needs a 2–3 profile chain</v>
+        <v>Invert</v>
       </c>
       <c r="B219" t="str">
-        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
+        <v>Inverter</v>
       </c>
       <c r="C219" t="str">
-        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
+        <v>Inverter</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
+        <v>last stage</v>
       </c>
       <c r="B220" t="str">
-        <v>O conjunto de dados deve estar em {in}; a procura inversa produz {out} mais um custo de invertibilidade por patch.</v>
+        <v>última etapa</v>
       </c>
       <c r="C220" t="str">
-        <v>O conjunto de dados deve estar em {in}; a busca inversa produz {out} mais um custo de invertibilidade por patch.</v>
+        <v>última etapa</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>ΔE cost</v>
+        <v>first stage</v>
       </c>
       <c r="B221" t="str">
-        <v>Custo ΔE</v>
+        <v>primeira etapa</v>
       </c>
       <c r="C221" t="str">
-        <v>Custo ΔE</v>
+        <v>primeira etapa</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>This image has an embedded ICC profile.</v>
+        <v>Data in {in} → search {out}</v>
       </c>
       <c r="B222" t="str">
-        <v>Esta imagem tem um perfil ICC incorporado.</v>
+        <v>Dados em {in} → procurar {out}</v>
       </c>
       <c r="C222" t="str">
-        <v>Esta imagem tem um perfil ICC incorporado.</v>
+        <v>Dados em {in} → buscar {out}</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extract &amp; add to chain</v>
+        <v>Invert needs a 2–3 profile chain</v>
       </c>
       <c r="B223" t="str">
-        <v>Extrair e adicionar à cadeia</v>
+        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
       </c>
       <c r="C223" t="str">
-        <v>Extrair e adicionar à cadeia</v>
+        <v>Inverter precisa de uma cadeia de 2 a 3 perfis</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Extracting…</v>
+        <v>The dataset must be {in}; the inverse search produces {out} plus a per-patch invertibility cost.</v>
       </c>
       <c r="B224" t="str">
-        <v>A extrair…</v>
+        <v>O conjunto de dados deve estar em {in}; a procura inversa produz {out} mais um custo de invertibilidade por patch.</v>
       </c>
       <c r="C224" t="str">
-        <v>Extraindo…</v>
+        <v>O conjunto de dados deve estar em {in}; a busca inversa produz {out} mais um custo de invertibilidade por patch.</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Dismiss</v>
+        <v>ΔE cost</v>
       </c>
       <c r="B225" t="str">
-        <v>Dispensar</v>
+        <v>Custo ΔE</v>
       </c>
       <c r="C225" t="str">
-        <v>Dispensar</v>
+        <v>Custo ΔE</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
+        <v>This image has an embedded ICC profile.</v>
       </c>
       <c r="B226" t="str">
-        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro lugar na cadeia.</v>
+        <v>Esta imagem tem um perfil ICC incorporado.</v>
       </c>
       <c r="C226" t="str">
-        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro na cadeia.</v>
+        <v>Esta imagem tem um perfil ICC incorporado.</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Image output options</v>
+        <v>Extract &amp; add to chain</v>
       </c>
       <c r="B227" t="str">
-        <v>Opções de saída de imagem</v>
+        <v>Extrair e adicionar à cadeia</v>
       </c>
       <c r="C227" t="str">
-        <v>Opções de saída de imagem</v>
+        <v>Extrair e adicionar à cadeia</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Encoding</v>
+        <v>Extracting…</v>
       </c>
       <c r="B228" t="str">
-        <v>Codificação</v>
+        <v>A extrair…</v>
       </c>
       <c r="C228" t="str">
-        <v>Codificação</v>
+        <v>Extraindo…</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Same as source</v>
+        <v>Dismiss</v>
       </c>
       <c r="B229" t="str">
-        <v>Igual à origem</v>
+        <v>Dispensar</v>
       </c>
       <c r="C229" t="str">
-        <v>Igual à origem</v>
+        <v>Dispensar</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>8-bit</v>
+        <v>Extracted the embedded profile — added to the pool and placed first in the chain.</v>
       </c>
       <c r="B230" t="str">
-        <v>8 bits</v>
+        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro lugar na cadeia.</v>
       </c>
       <c r="C230" t="str">
-        <v>8 bits</v>
+        <v>Perfil incorporado extraído — adicionado ao conjunto e colocado em primeiro na cadeia.</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>16-bit</v>
+        <v>Image output options</v>
       </c>
       <c r="B231" t="str">
-        <v>16 bits</v>
+        <v>Opções de saída de imagem</v>
       </c>
       <c r="C231" t="str">
-        <v>16 bits</v>
+        <v>Opções de saída de imagem</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Float (32-bit)</v>
+        <v>Encoding</v>
       </c>
       <c r="B232" t="str">
-        <v>Flutuante (32 bits)</v>
+        <v>Codificação</v>
       </c>
       <c r="C232" t="str">
-        <v>Flutuante (32 bits)</v>
+        <v>Codificação</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>Compression</v>
+        <v>Same as source</v>
       </c>
       <c r="B233" t="str">
-        <v>Compressão</v>
+        <v>Igual à origem</v>
       </c>
       <c r="C233" t="str">
-        <v>Compressão</v>
+        <v>Igual à origem</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>None</v>
+        <v>8-bit</v>
       </c>
       <c r="B234" t="str">
-        <v>Nenhuma</v>
+        <v>8 bits</v>
       </c>
       <c r="C234" t="str">
-        <v>Nenhuma</v>
+        <v>8 bits</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>Planar</v>
+        <v>16-bit</v>
       </c>
       <c r="B235" t="str">
-        <v>Planar</v>
+        <v>16 bits</v>
       </c>
       <c r="C235" t="str">
-        <v>Planar</v>
+        <v>16 bits</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>Composite</v>
+        <v>Float (32-bit)</v>
       </c>
       <c r="B236" t="str">
-        <v>Composto</v>
+        <v>Flutuante (32 bits)</v>
       </c>
       <c r="C236" t="str">
-        <v>Composto</v>
+        <v>Flutuante (32 bits)</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>Separated</v>
+        <v>Compression</v>
       </c>
       <c r="B237" t="str">
-        <v>Separado</v>
+        <v>Compressão</v>
       </c>
       <c r="C237" t="str">
-        <v>Separado</v>
+        <v>Compressão</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>CMM interpolation</v>
+        <v>None</v>
       </c>
       <c r="B238" t="str">
-        <v>Interpolação CMM</v>
+        <v>Nenhuma</v>
       </c>
       <c r="C238" t="str">
-        <v>Interpolação CMM</v>
+        <v>Nenhuma</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>Tetrahedral</v>
+        <v>Planar</v>
       </c>
       <c r="B239" t="str">
-        <v>Tetraédrica</v>
+        <v>Planar</v>
       </c>
       <c r="C239" t="str">
-        <v>Tetraédrica</v>
+        <v>Planar</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>Linear</v>
+        <v>Composite</v>
       </c>
       <c r="B240" t="str">
-        <v>Linear</v>
+        <v>Composto</v>
       </c>
       <c r="C240" t="str">
-        <v>Linear</v>
+        <v>Composto</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>Embed ICC</v>
+        <v>Separated</v>
       </c>
       <c r="B241" t="str">
-        <v>Incorporar ICC</v>
+        <v>Separado</v>
       </c>
       <c r="C241" t="str">
-        <v>Incorporar ICC</v>
+        <v>Separado</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
+        <v>CMM interpolation</v>
       </c>
       <c r="B242" t="str">
-        <v>A codificação, a compressão e o formato planar determinam o TIFF guardado. A saída RGB/Gray mantém-se em PNG, salvo se for definida uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado).</v>
+        <v>Interpolação CMM</v>
       </c>
       <c r="C242" t="str">
-        <v>A codificação, a compressão e o formato planar determinam o TIFF salvo. A saída RGB/Gray permanece em PNG, a menos que uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado) seja definida.</v>
+        <v>Interpolação CMM</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>Assemble spectral TIFF</v>
+        <v>Tetrahedral</v>
       </c>
       <c r="B243" t="str">
-        <v>Montar TIFF espectral</v>
+        <v>Tetraédrica</v>
       </c>
       <c r="C243" t="str">
-        <v>Montar TIFF espectral</v>
+        <v>Tetraédrica</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
+        <v>Linear</v>
       </c>
       <c r="B244" t="str">
-        <v>Largue imagens espectrais de canal único pela ordem dos canais e depois monte-as num único TIFF multicanal.</v>
+        <v>Linear</v>
       </c>
       <c r="C244" t="str">
-        <v>Solte imagens espectrais de canal único na ordem dos canais e depois monte-as em um único TIFF multicanal.</v>
+        <v>Linear</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>Drop spectral images here (or click to choose)</v>
+        <v>Embed ICC</v>
       </c>
       <c r="B245" t="str">
-        <v>Largue imagens espectrais aqui (ou clique para escolher)</v>
+        <v>Incorporar ICC</v>
       </c>
       <c r="C245" t="str">
-        <v>Solte imagens espectrais aqui (ou clique para escolher)</v>
+        <v>Incorporar ICC</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>ch</v>
+        <v>Encoding, compression and planar shape the saved TIFF. RGB/Gray output stays PNG unless a TIFF-only option (float, LZW/ZIP, separated) is set.</v>
       </c>
       <c r="B246" t="str">
-        <v>can</v>
+        <v>A codificação, a compressão e o formato planar determinam o TIFF guardado. A saída RGB/Gray mantém-se em PNG, salvo se for definida uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado).</v>
       </c>
       <c r="C246" t="str">
-        <v>can</v>
+        <v>A codificação, a compressão e o formato planar determinam o TIFF salvo. A saída RGB/Gray permanece em PNG, a menos que uma opção exclusiva de TIFF (flutuante, LZW/ZIP, separado) seja definida.</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>Assemble &amp; Save</v>
+        <v>Assemble spectral TIFF</v>
       </c>
       <c r="B247" t="str">
-        <v>Montar e guardar</v>
+        <v>Montar TIFF espectral</v>
       </c>
       <c r="C247" t="str">
-        <v>Montar e salvar</v>
+        <v>Montar TIFF espectral</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>Assembling…</v>
+        <v>Drop single-channel spectral images in channel order, then assemble them into one multi-channel TIFF.</v>
       </c>
       <c r="B248" t="str">
-        <v>A montar…</v>
+        <v>Largue imagens espectrais de canal único pela ordem dos canais e depois monte-as num único TIFF multicanal.</v>
       </c>
       <c r="C248" t="str">
-        <v>Montando…</v>
+        <v>Solte imagens espectrais de canal único na ordem dos canais e depois monte-as em um único TIFF multicanal.</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>Assembled {n} channels.</v>
+        <v>Drop spectral images here (or click to choose)</v>
       </c>
       <c r="B249" t="str">
-        <v>Foram montados {n} canais.</v>
+        <v>Largue imagens espectrais aqui (ou clique para escolher)</v>
       </c>
       <c r="C249" t="str">
-        <v>Foram montados {n} canais.</v>
+        <v>Solte imagens espectrais aqui (ou clique para escolher)</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>None of those look like images (TIFF, PNG or JPEG).</v>
+        <v>ch</v>
       </c>
       <c r="B250" t="str">
-        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
+        <v>can</v>
       </c>
       <c r="C250" t="str">
-        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
+        <v>can</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>Cancel</v>
+        <v>Assemble &amp; Save</v>
       </c>
       <c r="B251" t="str">
-        <v>Cancelar</v>
+        <v>Montar e guardar</v>
       </c>
       <c r="C251" t="str">
-        <v>Cancelar</v>
+        <v>Montar e salvar</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>{n} file(s) not loaded</v>
+        <v>Assembling…</v>
       </c>
       <c r="B252" t="str">
-        <v>{n} ficheiro(s) não carregados</v>
+        <v>A montar…</v>
       </c>
       <c r="C252" t="str">
-        <v>{n} arquivo(s) não carregados</v>
+        <v>Montando…</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>These files are not ICC profiles, so they were not added to the pool:</v>
+        <v>Assembled {n} channels.</v>
       </c>
       <c r="B253" t="str">
-        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
+        <v>Foram montados {n} canais.</v>
       </c>
       <c r="C253" t="str">
-        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
+        <v>Foram montados {n} canais.</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>OK</v>
+        <v>None of those look like images (TIFF, PNG or JPEG).</v>
       </c>
       <c r="B254" t="str">
-        <v>OK</v>
+        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
       </c>
       <c r="C254" t="str">
-        <v>OK</v>
+        <v>Nenhum desses parece ser uma imagem (TIFF, PNG ou JPEG).</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>Drop an ICC profile here</v>
+        <v>Cancel</v>
       </c>
       <c r="B255" t="str">
-        <v>Largue um perfil ICC aqui</v>
+        <v>Cancelar</v>
       </c>
       <c r="C255" t="str">
-        <v>Solte um perfil ICC aqui</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>or</v>
+        <v>{n} file(s) not loaded</v>
       </c>
       <c r="B256" t="str">
-        <v>ou</v>
+        <v>{n} ficheiro(s) não carregados</v>
       </c>
       <c r="C256" t="str">
-        <v>ou</v>
+        <v>{n} arquivo(s) não carregados</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>Choose file</v>
+        <v>These files are not ICC profiles, so they were not added to the pool:</v>
       </c>
       <c r="B257" t="str">
-        <v>Escolher ficheiro</v>
+        <v>Estes ficheiros não são perfis ICC, pelo que não foram adicionados ao conjunto:</v>
       </c>
       <c r="C257" t="str">
-        <v>Escolher arquivo</v>
+        <v>Estes arquivos não são perfis ICC, portanto não foram adicionados ao conjunto:</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>.icc and .icm files</v>
+        <v>OK</v>
       </c>
       <c r="B258" t="str">
-        <v>Ficheiros .icc e .icm</v>
+        <v>OK</v>
       </c>
       <c r="C258" t="str">
-        <v>Arquivos .icc e .icm</v>
+        <v>OK</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>Header</v>
+        <v>Drop an ICC profile here</v>
       </c>
       <c r="B259" t="str">
-        <v>Cabeçalho</v>
+        <v>Largue um perfil ICC aqui</v>
       </c>
       <c r="C259" t="str">
-        <v>Cabeçalho</v>
+        <v>Solte um perfil ICC aqui</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>Tags</v>
+        <v>or</v>
       </c>
       <c r="B260" t="str">
-        <v>Etiquetas</v>
+        <v>ou</v>
       </c>
       <c r="C260" t="str">
-        <v>Tags</v>
+        <v>ou</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>Validation</v>
+        <v>Choose file</v>
       </c>
       <c r="B261" t="str">
-        <v>Validação</v>
+        <v>Escolher ficheiro</v>
       </c>
       <c r="C261" t="str">
-        <v>Validação</v>
+        <v>Escolher arquivo</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>Analysis</v>
+        <v>.icc and .icm files</v>
       </c>
       <c r="B262" t="str">
-        <v>Análise</v>
+        <v>Ficheiros .icc e .icm</v>
       </c>
       <c r="C262" t="str">
-        <v>Análise</v>
+        <v>Arquivos .icc e .icm</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>Neutral Axis Inking</v>
+        <v>Header</v>
       </c>
       <c r="B263" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Cabeçalho</v>
       </c>
       <c r="C263" t="str">
-        <v>Tintagem do eixo neutro</v>
+        <v>Cabeçalho</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
+        <v>Tags</v>
       </c>
       <c r="B264" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
+        <v>Etiquetas</v>
       </c>
       <c r="C264" t="str">
-        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
+        <v>Tags</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>Neutral axis inking is only available for output (printer) profiles.</v>
+        <v>Validation</v>
       </c>
       <c r="B265" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Validação</v>
       </c>
       <c r="C265" t="str">
-        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
+        <v>Validação</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>This profile has no B2A (PCS→device) table to sample.</v>
+        <v>Analysis</v>
       </c>
       <c r="B266" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>Análise</v>
       </c>
       <c r="C266" t="str">
-        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>Rendering intent</v>
+        <v>Neutral Axis Inking</v>
       </c>
       <c r="B267" t="str">
-        <v>Intenção de renderização</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
       <c r="C267" t="str">
-        <v>Intenção de renderização</v>
+        <v>Tintagem do eixo neutro</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>% ink</v>
+        <v>Device colorant laid down along the neutral axis (a*=b*=0) as lightness goes from white (L*=100) to black (L*=0).</v>
       </c>
       <c r="B268" t="str">
-        <v>% tinta</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) à medida que a luminosidade passa de branco (L*=100) a preto (L*=0).</v>
       </c>
       <c r="C268" t="str">
-        <v>% tinta</v>
+        <v>Corante depositado ao longo do eixo neutro (a*=b*=0) conforme a luminosidade vai de branco (L*=100) a preto (L*=0).</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>L* out (tone)</v>
+        <v>Neutral axis inking is only available for output (printer) profiles.</v>
       </c>
       <c r="B269" t="str">
-        <v>L* de saída (tom)</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C269" t="str">
-        <v>L* de saída (tom)</v>
+        <v>A tintagem do eixo neutro só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>Δa*b*</v>
+        <v>This profile has no B2A (PCS→device) table to sample.</v>
       </c>
       <c r="B270" t="str">
-        <v>Δa*b*</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
       <c r="C270" t="str">
-        <v>Δa*b*</v>
+        <v>Este perfil não tem uma tabela B2A (PCS→dispositivo) para amostrar.</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>Extrema Colorimetry</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B271" t="str">
-        <v>Colorimetria dos extremos</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C271" t="str">
-        <v>Colorimetria dos extremos</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
+        <v>% ink</v>
       </c>
       <c r="B272" t="str">
-        <v>Os extremos da gama de reprodução do perfil: o branco do suporte, o preto mais escuro que irá imprimir, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
+        <v>% tinta</v>
       </c>
       <c r="C272" t="str">
-        <v>Os extremos da faixa de reprodução do perfil: o branco do suporte, o preto mais escuro que ele imprimirá, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
+        <v>% tinta</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
+        <v>L* out (tone)</v>
       </c>
       <c r="B273" t="str">
-        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto obtém-se passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa refere-a a um branco perfeito.</v>
+        <v>L* de saída (tom)</v>
       </c>
       <c r="C273" t="str">
-        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto é obtido passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa a refere a um branco perfeito.</v>
+        <v>L* de saída (tom)</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>Relative</v>
+        <v>Δa*b*</v>
       </c>
       <c r="B274" t="str">
-        <v>Relativa</v>
+        <v>Δa*b*</v>
       </c>
       <c r="C274" t="str">
-        <v>Relativa</v>
+        <v>Δa*b*</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>Absolute</v>
+        <v>Extrema Colorimetry</v>
       </c>
       <c r="B275" t="str">
-        <v>Absoluta</v>
+        <v>Colorimetria dos extremos</v>
       </c>
       <c r="C275" t="str">
-        <v>Absoluta</v>
+        <v>Colorimetria dos extremos</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>White point</v>
+        <v>The ends of the profile’s reproduction range: substrate white, the darkest black it will print, the ink that black costs, and where each hue reaches its most saturated point.</v>
       </c>
       <c r="B276" t="str">
-        <v>Ponto branco</v>
+        <v>Os extremos da gama de reprodução do perfil: o branco do suporte, o preto mais escuro que irá imprimir, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
       </c>
       <c r="C276" t="str">
-        <v>Ponto branco</v>
+        <v>Os extremos da faixa de reprodução do perfil: o branco do suporte, o preto mais escuro que ele imprimirá, a tinta que esse preto custa e o ponto em que cada matiz atinge a saturação máxima.</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>Black point</v>
+        <v>White point is the colour of zero colorant — bare substrate. Black point is found by pushing PCS black (L*=0, a*=b*=0) through the selected B2A table to get the inking the profile chooses for black, then reading that inking back through A2B1. Total area coverage (TAC) is the sum of that inking. Absolute colorimetry shows the substrate’s own colour; relative re-references it to a perfect white.</v>
       </c>
       <c r="B277" t="str">
-        <v>Ponto preto</v>
+        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto obtém-se passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa refere-a a um branco perfeito.</v>
       </c>
       <c r="C277" t="str">
-        <v>Ponto preto</v>
+        <v>O ponto branco é a cor com corante nulo — o suporte nu. O ponto preto é obtido passando o preto do PCS (L*=0, a*=b*=0) pela tabela B2A selecionada para obter a tintagem que o perfil escolhe para o preto e lendo depois essa tintagem através de A2B1. A cobertura total de tinta (TAC) é a soma dessa tintagem. A colorimetria absoluta mostra a cor própria do suporte; a relativa a refere a um branco perfeito.</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>Inking at black point</v>
+        <v>Relative</v>
       </c>
       <c r="B278" t="str">
-        <v>Tintagem no ponto preto</v>
+        <v>Relativa</v>
       </c>
       <c r="C278" t="str">
-        <v>Tintagem no ponto preto</v>
+        <v>Relativa</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>TAC</v>
+        <v>Absolute</v>
       </c>
       <c r="B279" t="str">
-        <v>TAC</v>
+        <v>Absoluta</v>
       </c>
       <c r="C279" t="str">
-        <v>TAC</v>
+        <v>Absoluta</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
+        <v>White point</v>
       </c>
       <c r="B280" t="str">
-        <v>Este perfil não tem etiqueta de ponto branco do meio, pelo que a colorimetria absoluta não está disponível.</v>
+        <v>Ponto branco</v>
       </c>
       <c r="C280" t="str">
-        <v>Este perfil não tem tag de ponto branco do meio, portanto a colorimetria absoluta não está disponível.</v>
+        <v>Ponto branco</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
+        <v>Black point</v>
       </c>
       <c r="B281" t="str">
-        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — pressupõe que corante nulo significa suporte nu.</v>
+        <v>Ponto preto</v>
       </c>
       <c r="C281" t="str">
-        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — ela pressupõe que corante nulo significa suporte nu.</v>
+        <v>Ponto preto</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>Full tone vs maximum chroma</v>
+        <v>Inking at black point</v>
       </c>
       <c r="B282" t="str">
-        <v>Tinta plena vs croma máximo</v>
+        <v>Tintagem no ponto preto</v>
       </c>
       <c r="C282" t="str">
-        <v>Tinta plena vs croma máximo</v>
+        <v>Tintagem no ponto preto</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
+        <v>TAC</v>
       </c>
       <c r="B283" t="str">
-        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, pelo que estas linhas não mudam com a intenção de renderização acima. Num perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta para além desse ponto apenas escurece.</v>
+        <v>TAC</v>
       </c>
       <c r="C283" t="str">
-        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, portanto estas linhas não mudam com a intenção de renderização acima. Em um perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta além desse ponto apenas escurece.</v>
+        <v>TAC</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>Hue</v>
+        <v>This profile has no media white point tag, so absolute colorimetry is unavailable.</v>
       </c>
       <c r="B284" t="str">
-        <v>Matiz</v>
+        <v>Este perfil não tem etiqueta de ponto branco do meio, pelo que a colorimetria absoluta não está disponível.</v>
       </c>
       <c r="C284" t="str">
-        <v>Matiz</v>
+        <v>Este perfil não tem tag de ponto branco do meio, portanto a colorimetria absoluta não está disponível.</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>Full tone</v>
+        <v>Extrema colorimetry is only available for output (printer) profiles — it assumes zero colorant means bare substrate.</v>
       </c>
       <c r="B285" t="str">
-        <v>Tinta plena</v>
+        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — pressupõe que corante nulo significa suporte nu.</v>
       </c>
       <c r="C285" t="str">
-        <v>Tinta plena</v>
+        <v>A colorimetria dos extremos só está disponível para perfis de saída (impressora) — ela pressupõe que corante nulo significa suporte nu.</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>Max C*</v>
+        <v>Full tone vs maximum chroma</v>
       </c>
       <c r="B286" t="str">
-        <v>C* máx</v>
+        <v>Tinta plena vs croma máximo</v>
       </c>
       <c r="C286" t="str">
-        <v>C* máx</v>
+        <v>Tinta plena vs croma máximo</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>At ink</v>
+        <v>Where each ink corner lands, and the most chromatic point on the way there. Measured through A2B1, so these rows do not change with the rendering intent above. On a well-behaved profile the two rows match; if maximum chroma arrives before full tone, the extra ink past that point is only darkening.</v>
       </c>
       <c r="B287" t="str">
-        <v>Com tintagem</v>
+        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, pelo que estas linhas não mudam com a intenção de renderização acima. Num perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta para além desse ponto apenas escurece.</v>
       </c>
       <c r="C287" t="str">
-        <v>Com tintagem</v>
+        <v>Onde fica cada vértice de tinta e o ponto mais cromático no caminho até lá. Medido através de A2B1, portanto estas linhas não mudam com a intenção de renderização acima. Em um perfil bem comportado as duas linhas coincidem; se o croma máximo surgir antes da tinta plena, a tinta além desse ponto apenas escurece.</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
+        <v>Hue</v>
       </c>
       <c r="B288" t="str">
-        <v>O croma máximo é atingido antes da tinta plena — a tinta para além deste ponto apenas escurece.</v>
+        <v>Matiz</v>
       </c>
       <c r="C288" t="str">
-        <v>O croma máximo é atingido antes da tinta plena — a tinta além deste ponto apenas escurece.</v>
+        <v>Matiz</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>Ink Usage in Shadows</v>
+        <v>Full tone</v>
       </c>
       <c r="B289" t="str">
-        <v>Utilização de tinta nas sombras</v>
+        <v>Tinta plena</v>
       </c>
       <c r="C289" t="str">
-        <v>Uso de tinta nas sombras</v>
+        <v>Tinta plena</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
+        <v>Max C*</v>
       </c>
       <c r="B290" t="str">
-        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras partilham a mesma L*, pelo que qualquer degrau abrupto ou inversão de um corante resulta apenas do tratamento do matiz e do croma — a assinatura de um artefacto de mapeamento de gamut nas sombras.</v>
+        <v>C* máx</v>
       </c>
       <c r="C290" t="str">
-        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras compartilham a mesma L*, portanto qualquer degrau abrupto ou inversão de um corante vem apenas do tratamento do matiz e do croma — a assinatura de um artefato de mapeamento de gamut nas sombras.</v>
+        <v>C* máx</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
+        <v>At ink</v>
       </c>
       <c r="B291" t="str">
-        <v>A utilização de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
+        <v>Com tintagem</v>
       </c>
       <c r="C291" t="str">
-        <v>O uso de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
+        <v>Com tintagem</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>Constant L* plane</v>
+        <v>Maximum chroma is reached before full tone — ink past this point only darkens.</v>
       </c>
       <c r="B292" t="str">
-        <v>Plano de L* constante</v>
+        <v>O croma máximo é atingido antes da tinta plena — a tinta para além deste ponto apenas escurece.</v>
       </c>
       <c r="C292" t="str">
-        <v>Plano de L* constante</v>
+        <v>O croma máximo é atingido antes da tinta plena — a tinta além deste ponto apenas escurece.</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>black-point compensated from</v>
+        <v>Ink Usage in Shadows</v>
       </c>
       <c r="B293" t="str">
-        <v>com compensação do ponto preto a partir de</v>
+        <v>Utilização de tinta nas sombras</v>
       </c>
       <c r="C293" t="str">
-        <v>com compensação do ponto preto a partir de</v>
+        <v>Uso de tinta nas sombras</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>Position along path</v>
+        <v>Four straight paths across the a*b* plane at one constant, deliberately dark lightness, run through the selected B2A table. Every sample shares the same L*, so any abrupt step or reversal in a colorant comes from hue and chroma handling alone — the signature of a shadow gamut-mapping artefact.</v>
       </c>
       <c r="B294" t="str">
-        <v>Posição ao longo do percurso</v>
+        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras partilham a mesma L*, pelo que qualquer degrau abrupto ou inversão de um corante resulta apenas do tratamento do matiz e do croma — a assinatura de um artefacto de mapeamento de gamut nas sombras.</v>
       </c>
       <c r="C294" t="str">
-        <v>Posição ao longo do percurso</v>
+        <v>Quatro percursos retos no plano a*b* com uma luminosidade constante e deliberadamente escura, passados pela tabela B2A selecionada. Todas as amostras compartilham a mesma L*, portanto qualquer degrau abrupto ou inversão de um corante vem apenas do tratamento do matiz e do croma — a assinatura de um artefato de mapeamento de gamut nas sombras.</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>Path</v>
+        <v>Ink usage in shadows is only available for output (printer) profiles.</v>
       </c>
       <c r="B295" t="str">
-        <v>Percurso</v>
+        <v>A utilização de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
       </c>
       <c r="C295" t="str">
-        <v>Percurso</v>
+        <v>O uso de tinta nas sombras só está disponível para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>Cyan</v>
+        <v>Constant L* plane</v>
       </c>
       <c r="B296" t="str">
-        <v>Ciano</v>
+        <v>Plano de L* constante</v>
       </c>
       <c r="C296" t="str">
-        <v>Ciano</v>
+        <v>Plano de L* constante</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>Magenta</v>
+        <v>black-point compensated from</v>
       </c>
       <c r="B297" t="str">
-        <v>Magenta</v>
+        <v>com compensação do ponto preto a partir de</v>
       </c>
       <c r="C297" t="str">
-        <v>Magenta</v>
+        <v>com compensação do ponto preto a partir de</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>Yellow</v>
+        <v>Position along path</v>
       </c>
       <c r="B298" t="str">
-        <v>Amarelo</v>
+        <v>Posição ao longo do percurso</v>
       </c>
       <c r="C298" t="str">
-        <v>Amarelo</v>
+        <v>Posição ao longo do percurso</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>Red</v>
+        <v>Path</v>
       </c>
       <c r="B299" t="str">
-        <v>Vermelho</v>
+        <v>Percurso</v>
       </c>
       <c r="C299" t="str">
-        <v>Vermelho</v>
+        <v>Percurso</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Green</v>
+        <v>Cyan</v>
       </c>
       <c r="B300" t="str">
-        <v>Verde</v>
+        <v>Ciano</v>
       </c>
       <c r="C300" t="str">
-        <v>Verde</v>
+        <v>Ciano</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Blue</v>
+        <v>Magenta</v>
       </c>
       <c r="B301" t="str">
-        <v>Azul</v>
+        <v>Magenta</v>
       </c>
       <c r="C301" t="str">
-        <v>Azul</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Black</v>
+        <v>Yellow</v>
       </c>
       <c r="B302" t="str">
-        <v>Preto</v>
+        <v>Amarelo</v>
       </c>
       <c r="C302" t="str">
-        <v>Preto</v>
+        <v>Amarelo</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Perceptual</v>
+        <v>Red</v>
       </c>
       <c r="B303" t="str">
-        <v>Perceptual</v>
+        <v>Vermelho</v>
       </c>
       <c r="C303" t="str">
-        <v>Perceptual</v>
+        <v>Vermelho</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Green</v>
       </c>
       <c r="B304" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Verde</v>
       </c>
       <c r="C304" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Saturation</v>
+        <v>Blue</v>
       </c>
       <c r="B305" t="str">
-        <v>Saturação</v>
+        <v>Azul</v>
       </c>
       <c r="C305" t="str">
-        <v>Saturação</v>
+        <v>Azul</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Black</v>
       </c>
       <c r="B306" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Preto</v>
       </c>
       <c r="C306" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Preto</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Profile Statistics</v>
+        <v>Perceptual</v>
       </c>
       <c r="B307" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Perceptual</v>
       </c>
       <c r="C307" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B308" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Colorimétrico relativo</v>
       </c>
       <c r="C308" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Saturation</v>
       </c>
       <c r="B309" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
+        <v>Saturação</v>
       </c>
       <c r="C309" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
+        <v>Saturação</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Rendering intent</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B310" t="str">
-        <v>Intenção de renderização</v>
+        <v>Colorimétrico absoluto</v>
       </c>
       <c r="C310" t="str">
-        <v>Intenção de renderização</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B311" t="str">
-        <v>Volume de gamute (ΔE³)</v>
+        <v>Estatísticas do perfil</v>
       </c>
       <c r="C311" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Estatísticas do perfil</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B312" t="str">
-        <v>ΔE de percurso</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
       <c r="C312" t="str">
-        <v>ΔE de percurso</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B313" t="str">
-        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
       </c>
       <c r="C313" t="str">
-        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>mean</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B314" t="str">
-        <v>média</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C314" t="str">
-        <v>média</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>P90</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B315" t="str">
-        <v>P90</v>
+        <v>Volume de gamute (ΔE³)</v>
       </c>
       <c r="C315" t="str">
-        <v>P90</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>max</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B316" t="str">
-        <v>máx.</v>
+        <v>ΔE de percurso</v>
       </c>
       <c r="C316" t="str">
-        <v>máx.</v>
+        <v>ΔE de percurso</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>Analysing…</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B317" t="str">
-        <v>A analisar…</v>
+        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
       </c>
       <c r="C317" t="str">
-        <v>Analisando…</v>
+        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>Analysis</v>
+        <v>mean</v>
       </c>
       <c r="B318" t="str">
-        <v>Análise</v>
+        <v>média</v>
       </c>
       <c r="C318" t="str">
-        <v>Análise</v>
+        <v>média</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>P90</v>
       </c>
       <c r="B319" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>P90</v>
       </c>
       <c r="C319" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>Plot</v>
+        <v>max</v>
       </c>
       <c r="B320" t="str">
-        <v>Gráfico</v>
+        <v>máx.</v>
       </c>
       <c r="C320" t="str">
-        <v>Gráfico</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Raw Output</v>
+        <v>Analysing…</v>
       </c>
       <c r="B321" t="str">
-        <v>Saída em bruto</v>
+        <v>A analisar…</v>
       </c>
       <c r="C321" t="str">
-        <v>Saída bruta</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>XML</v>
+        <v>Analysis</v>
       </c>
       <c r="B322" t="str">
-        <v>XML</v>
+        <v>Análise</v>
       </c>
       <c r="C322" t="str">
-        <v>XML</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>JSON</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B323" t="str">
-        <v>JSON</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C323" t="str">
-        <v>JSON</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Curves</v>
+        <v>Plot</v>
       </c>
       <c r="B324" t="str">
-        <v>Curvas</v>
+        <v>Gráfico</v>
       </c>
       <c r="C324" t="str">
-        <v>Curvas</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Input curves</v>
+        <v>Raw Output</v>
       </c>
       <c r="B325" t="str">
-        <v>Curvas de entrada</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C325" t="str">
-        <v>Curvas de entrada</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>Output curves</v>
+        <v>XML</v>
       </c>
       <c r="B326" t="str">
-        <v>Curvas de saída</v>
+        <v>XML</v>
       </c>
       <c r="C326" t="str">
-        <v>Curvas de saída</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>CLUT image</v>
+        <v>JSON</v>
       </c>
       <c r="B327" t="str">
-        <v>Imagem CLUT</v>
+        <v>JSON</v>
       </c>
       <c r="C327" t="str">
-        <v>Imagem CLUT</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Gamut image</v>
+        <v>Curves</v>
       </c>
       <c r="B328" t="str">
-        <v>Imagem de gamut</v>
+        <v>Curvas</v>
       </c>
       <c r="C328" t="str">
-        <v>Imagem de gamut</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Chromaticity</v>
+        <v>Input curves</v>
       </c>
       <c r="B329" t="str">
-        <v>Cromaticidade</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C329" t="str">
-        <v>Cromaticidade</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Scatter plot</v>
+        <v>Output curves</v>
       </c>
       <c r="B330" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C330" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>Tone response curve</v>
+        <v>CLUT image</v>
       </c>
       <c r="B331" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C331" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Curve table</v>
+        <v>Gamut image</v>
       </c>
       <c r="B332" t="str">
-        <v>Tabela da curva</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C332" t="str">
-        <v>Tabela da curva</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Tables</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B333" t="str">
-        <v>Tabelas</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C333" t="str">
-        <v>Tabelas</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Data</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B334" t="str">
-        <v>Dados</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C334" t="str">
-        <v>Dados</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Evaluate</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B335" t="str">
-        <v>Avaliar</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C335" t="str">
-        <v>Avaliar</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Loading…</v>
+        <v>Curve table</v>
       </c>
       <c r="B336" t="str">
-        <v>A carregar…</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C336" t="str">
-        <v>Carregando…</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Input</v>
+        <v>Tables</v>
       </c>
       <c r="B337" t="str">
-        <v>Entrada</v>
+        <v>Tabelas</v>
       </c>
       <c r="C337" t="str">
-        <v>Entrada</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Output</v>
+        <v>Data</v>
       </c>
       <c r="B338" t="str">
-        <v>Saída</v>
+        <v>Dados</v>
       </c>
       <c r="C338" t="str">
-        <v>Saída</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Floating point</v>
+        <v>Evaluate</v>
       </c>
       <c r="B339" t="str">
-        <v>Vírgula flutuante</v>
+        <v>Avaliar</v>
       </c>
       <c r="C339" t="str">
-        <v>Ponto flutuante</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Grid point</v>
+        <v>Loading…</v>
       </c>
       <c r="B340" t="str">
-        <v>Ponto da grelha</v>
+        <v>A carregar…</v>
       </c>
       <c r="C340" t="str">
-        <v>Ponto da grade</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Normalized</v>
+        <v>Input</v>
       </c>
       <c r="B341" t="str">
-        <v>Normalizado</v>
+        <v>Entrada</v>
       </c>
       <c r="C341" t="str">
-        <v>Normalizado</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Human</v>
+        <v>Output</v>
       </c>
       <c r="B342" t="str">
-        <v>Legível</v>
+        <v>Saída</v>
       </c>
       <c r="C342" t="str">
-        <v>Legível</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Device → PCS</v>
+        <v>Floating point</v>
       </c>
       <c r="B343" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C343" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>PCS → Device</v>
+        <v>Grid point</v>
       </c>
       <c r="B344" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C344" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>No CLUT grid</v>
+        <v>Normalized</v>
       </c>
       <c r="B345" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>Normalizado</v>
       </c>
       <c r="C345" t="str">
-        <v>Sem grade CLUT</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Loading…</v>
+        <v>Human</v>
       </c>
       <c r="B346" t="str">
-        <v>A carregar…</v>
+        <v>Legível</v>
       </c>
       <c r="C346" t="str">
-        <v>Carregando…</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B347" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C347" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>Invalid profile URL:</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B348" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C348" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B349" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C349" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Loading…</v>
       </c>
       <c r="B350" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>A carregar…</v>
       </c>
       <c r="C350" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B351" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C351" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B352" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C352" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B353" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C353" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Security</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B354" t="str">
-        <v>Segurança</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C354" t="str">
-        <v>Segurança</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Conformance</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B355" t="str">
-        <v>Conformidade</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C355" t="str">
-        <v>Conformidade</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Quality</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B356" t="str">
-        <v>Qualidade</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C356" t="str">
-        <v>Qualidade</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>REPORT</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B357" t="str">
-        <v>RELATÓRIO</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C357" t="str">
-        <v>RELATÓRIO</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>FAIL</v>
+        <v>Security</v>
       </c>
       <c r="B358" t="str">
-        <v>REPROVADO</v>
+        <v>Segurança</v>
       </c>
       <c r="C358" t="str">
-        <v>REPROVADO</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>checks</v>
+        <v>Conformance</v>
       </c>
       <c r="B359" t="str">
-        <v>verificações</v>
+        <v>Conformidade</v>
       </c>
       <c r="C359" t="str">
-        <v>verificações</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Quality</v>
       </c>
       <c r="B360" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Qualidade</v>
       </c>
       <c r="C360" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>REPORT</v>
       </c>
       <c r="B361" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C361" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>ICC Profile Tool</v>
+        <v>FAIL</v>
       </c>
       <c r="B362" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C362" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>Powered by {lib}</v>
+        <v>checks</v>
       </c>
       <c r="B363" t="str">
-        <v>Com {lib}</v>
+        <v>verificações</v>
       </c>
       <c r="C363" t="str">
-        <v>Com {lib}</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Subscribe</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B364" t="str">
-        <v>Subscrever</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C364" t="str">
-        <v>Inscrever-se</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B365" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C365" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>Get notified about new releases</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B366" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C366" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Close</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B367" t="str">
-        <v>Fechar</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C367" t="str">
-        <v>Fechar</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B368" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C368" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Email address</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B369" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C369" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>you@example.com</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B370" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C370" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Close</v>
       </c>
       <c r="B371" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Fechar</v>
       </c>
       <c r="C371" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>(optional)</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B372" t="str">
-        <v>(opcional)</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C372" t="str">
-        <v>(opcional)</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Email address</v>
       </c>
       <c r="B373" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C373" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>you@example.com</v>
       </c>
       <c r="B374" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C374" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>Cancel</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B375" t="str">
-        <v>Cancelar</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C375" t="str">
-        <v>Cancelar</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>Subscribe</v>
+        <v>(optional)</v>
       </c>
       <c r="B376" t="str">
-        <v>Subscrever</v>
+        <v>(opcional)</v>
       </c>
       <c r="C376" t="str">
-        <v>Inscrever-se</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B377" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C377" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B378" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C378" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Close</v>
+        <v>Cancel</v>
       </c>
       <c r="B379" t="str">
-        <v>Fechar</v>
+        <v>Cancelar</v>
       </c>
       <c r="C379" t="str">
-        <v>Fechar</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Privacy notice</v>
+        <v>Subscribe</v>
       </c>
       <c r="B380" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Subscrever</v>
       </c>
       <c r="C380" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B381" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C381" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B382" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C382" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Close</v>
       </c>
       <c r="B383" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Fechar</v>
       </c>
       <c r="C383" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B384" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C384" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Network error. Please try again.</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B385" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C385" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Error:</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B386" t="str">
-        <v>Erro:</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C386" t="str">
-        <v>Erro:</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Convert to XML</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B387" t="str">
-        <v>Converter para XML</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C387" t="str">
-        <v>Converter para XML</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Convert to JSON</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B388" t="str">
-        <v>Converter para JSON</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C388" t="str">
-        <v>Converter para JSON</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Convert to ICC</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B389" t="str">
-        <v>Converter para ICC</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C389" t="str">
-        <v>Converter para ICC</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Converting to XML…</v>
+        <v>Error:</v>
       </c>
       <c r="B390" t="str">
-        <v>A converter para XML…</v>
+        <v>Erro:</v>
       </c>
       <c r="C390" t="str">
-        <v>Convertendo para XML…</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Converting to JSON…</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B391" t="str">
-        <v>A converter para JSON…</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C391" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Converting to ICC…</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B392" t="str">
-        <v>A converter para ICC…</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C392" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Load ICC profile</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B393" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C393" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B394" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C394" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Profile ID</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B395" t="str">
-        <v>ID do perfil</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C395" t="str">
-        <v>ID do perfil</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>No tags found.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B396" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C396" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Tag Name</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B397" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C397" t="str">
-        <v>Nome da tag</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>ID</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B398" t="str">
-        <v>ID</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C398" t="str">
-        <v>ID</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Offset</v>
+        <v>Profile ID</v>
       </c>
       <c r="B399" t="str">
-        <v>Deslocamento</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C399" t="str">
-        <v>Deslocamento</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>Size</v>
+        <v>No tags found.</v>
       </c>
       <c r="B400" t="str">
-        <v>Tamanho</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C400" t="str">
-        <v>Tamanho</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Pad</v>
+        <v>Tag Name</v>
       </c>
       <c r="B401" t="str">
-        <v>Preenchimento</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C401" t="str">
-        <v>Preenchimento</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>Bytes changed since load</v>
+        <v>ID</v>
       </c>
       <c r="B402" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>ID</v>
       </c>
       <c r="C402" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Type</v>
+        <v>Offset</v>
       </c>
       <c r="B403" t="str">
-        <v>Tipo</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C403" t="str">
-        <v>Tipo</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Array of {type}</v>
+        <v>Size</v>
       </c>
       <c r="B404" t="str">
-        <v>Vetor de {type}</v>
+        <v>Tamanho</v>
       </c>
       <c r="C404" t="str">
-        <v>Array de {type}</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>(No content)</v>
+        <v>Pad</v>
       </c>
       <c r="B405" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C405" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>bytes</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B406" t="str">
-        <v>bytes</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C406" t="str">
-        <v>bytes</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Loading full description…</v>
+        <v>Type</v>
       </c>
       <c r="B407" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>Tipo</v>
       </c>
       <c r="C407" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Could not load full description:</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B408" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C408" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>(No content)</v>
       </c>
       <c r="B409" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C409" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>bytes</v>
       </c>
       <c r="B410" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>bytes</v>
       </c>
       <c r="C410" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>No validation output</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B411" t="str">
-        <v>Sem saída de validação</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C411" t="str">
-        <v>Sem saída de validação</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Profile is valid</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B412" t="str">
-        <v>O perfil é válido</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C412" t="str">
-        <v>O perfil é válido</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>Profile has warning(s)</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B413" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C413" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B414" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C414" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>Critical validation error</v>
+        <v>No validation output</v>
       </c>
       <c r="B415" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C415" t="str">
-        <v>Erro de validação crítico</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Unknown validation status</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B416" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C416" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B417" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C417" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B418" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C418" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Valid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B419" t="str">
-        <v>Válido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C419" t="str">
-        <v>Válido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Warning</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B420" t="str">
-        <v>Aviso</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C420" t="str">
-        <v>Aviso</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Error</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B421" t="str">
-        <v>Erro</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C421" t="str">
-        <v>Erro</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>Unknown</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B422" t="str">
-        <v>Desconhecido</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C422" t="str">
-        <v>Desconhecido</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Pass</v>
+        <v>Valid</v>
       </c>
       <c r="B423" t="str">
-        <v>Aprovado</v>
+        <v>Válido</v>
       </c>
       <c r="C423" t="str">
-        <v>Aprovado</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Fail</v>
+        <v>Warning</v>
       </c>
       <c r="B424" t="str">
-        <v>Reprovado</v>
+        <v>Aviso</v>
       </c>
       <c r="C424" t="str">
-        <v>Reprovado</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>View in context</v>
+        <v>Error</v>
       </c>
       <c r="B425" t="str">
-        <v>Ver no contexto</v>
+        <v>Erro</v>
       </c>
       <c r="C425" t="str">
-        <v>Ver no contexto</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Validation detail</v>
+        <v>Unknown</v>
       </c>
       <c r="B426" t="str">
-        <v>Detalhe de validação</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C426" t="str">
-        <v>Detalhe de validação</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Triggered by</v>
+        <v>Pass</v>
       </c>
       <c r="B427" t="str">
-        <v>Acionado por</v>
+        <v>Aprovado</v>
       </c>
       <c r="C427" t="str">
-        <v>Acionado por</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Field</v>
+        <v>Fail</v>
       </c>
       <c r="B428" t="str">
-        <v>Campo</v>
+        <v>Reprovado</v>
       </c>
       <c r="C428" t="str">
-        <v>Campo</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>Current value</v>
+        <v>View in context</v>
       </c>
       <c r="B429" t="str">
-        <v>Valor atual</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C429" t="str">
-        <v>Valor atual</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Required: 0</v>
+        <v>Validation detail</v>
       </c>
       <c r="B430" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C430" t="str">
-        <v>Obrigatório: 0</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Expected: {value}</v>
+        <v>Triggered by</v>
       </c>
       <c r="B431" t="str">
-        <v>Esperado: {value}</v>
+        <v>Acionado por</v>
       </c>
       <c r="C431" t="str">
-        <v>Esperado: {value}</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Invalid</v>
+        <v>Field</v>
       </c>
       <c r="B432" t="str">
-        <v>Inválido</v>
+        <v>Campo</v>
       </c>
       <c r="C432" t="str">
-        <v>Inválido</v>
+        <v>Campo</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Current value</v>
       </c>
       <c r="B433" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Valor atual</v>
       </c>
       <c r="C433" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Valor atual</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Close</v>
+        <v>Required: 0</v>
       </c>
       <c r="B434" t="str">
-        <v>Fechar</v>
+        <v>Obrigatório: 0</v>
       </c>
       <c r="C434" t="str">
-        <v>Fechar</v>
+        <v>Obrigatório: 0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Loading XML editor…</v>
+        <v>Expected: {value}</v>
       </c>
       <c r="B435" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Esperado: {value}</v>
       </c>
       <c r="C435" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Esperado: {value}</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Invalid</v>
       </c>
       <c r="B436" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Inválido</v>
       </c>
       <c r="C436" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Inválido</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>This finding couldn't be tied to a specific field.</v>
       </c>
       <c r="B437" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
       <c r="C437" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Não foi possível associar este resultado a um campo específico.</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Close</v>
       </c>
       <c r="B438" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Fechar</v>
       </c>
       <c r="C438" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Loading XML editor…</v>
       </c>
       <c r="B439" t="str">
-        <v>● edições XML por guardar</v>
+        <v>A carregar o editor XML…</v>
       </c>
       <c r="C439" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Carregando editor XML…</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Loading JSON editor…</v>
       </c>
       <c r="B440" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>A carregar o editor JSON…</v>
       </c>
       <c r="C440" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Carregando editor JSON…</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B441" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C441" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
       </c>
       <c r="B442" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
       </c>
       <c r="C442" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>indent</v>
+        <v>● unsaved XML edits</v>
       </c>
       <c r="B443" t="str">
-        <v>indentação</v>
+        <v>● edições XML por guardar</v>
       </c>
       <c r="C443" t="str">
-        <v>indentação</v>
+        <v>● edições XML não salvas</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>sort keys</v>
+        <v>● unsaved JSON edits</v>
       </c>
       <c r="B444" t="str">
-        <v>ordenar chaves</v>
+        <v>● edições JSON por guardar</v>
       </c>
       <c r="C444" t="str">
-        <v>ordenar chaves</v>
+        <v>● edições JSON não salvas</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B445" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C445" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B446" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C446" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B447" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C447" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B448" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C448" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B445" t="str">
+      <c r="B449" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C445" t="str">
+      <c r="C449" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C445"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C449"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/translations/Eng-Pt.xlsx
+++ b/translations/Eng-Pt.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C449"/>
+  <dimension ref="A1:C466"/>
   <cols>
     <col min="1" max="1" width="50.83203125" customWidth="1"/>
     <col min="2" max="2" width="50.83203125" customWidth="1"/>
@@ -3704,1657 +3704,1844 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>Cyan</v>
+        <v>Primary-Inking Paths through Neutral</v>
       </c>
       <c r="B300" t="str">
-        <v>Ciano</v>
+        <v>Trajetos de tintagem primária pelo neutro</v>
       </c>
       <c r="C300" t="str">
-        <v>Ciano</v>
+        <v>Caminhos de entintamento primário pelo neutro</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>Magenta</v>
+        <v>Three in-gamut paths — Cyan→Red, Magenta→Green, Yellow→Blue — each routed through the neutral axis at the midpoint lightness of its endpoints, run through the selected B2A table. Every sample is inside the gamut, so unlike the shadow paths any abrupt step or reversal in a colorant is a CLUT-smoothness defect rather than a gamut-mapping artefact.</v>
       </c>
       <c r="B301" t="str">
-        <v>Magenta</v>
+        <v>Três trajetos dentro do gamute — ciano→vermelho, magenta→verde, amarelo→azul — cada um através do eixo neutro na luminosidade média das suas extremidades, através da tabela B2A selecionada. Cada amostra está dentro do gamute, pelo que, ao contrário dos trajetos de sombra, qualquer salto ou inversão de um corante é um defeito de suavidade da CLUT e não um artefacto de mapeamento de gamute.</v>
       </c>
       <c r="C301" t="str">
-        <v>Magenta</v>
+        <v>Três caminhos dentro do gamute — ciano→vermelho, magenta→verde, amarelo→azul — cada um através do eixo neutro na luminosidade média de suas extremidades, através da tabela B2A selecionada. Cada amostra está dentro do gamute, então, diferentemente dos caminhos de sombra, qualquer salto ou inversão de um corante é um defeito de suavidade da CLUT e não um artefato de mapeamento de gamute.</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>Yellow</v>
+        <v>Primary-inking paths are only available for output (printer) profiles.</v>
       </c>
       <c r="B302" t="str">
-        <v>Amarelo</v>
+        <v>Os trajetos de tintagem primária só estão disponíveis para perfis de saída (impressora).</v>
       </c>
       <c r="C302" t="str">
-        <v>Amarelo</v>
+        <v>Os caminhos de entintamento primário só estão disponíveis para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>Red</v>
+        <v>Position along path (neutral at midpoint)</v>
       </c>
       <c r="B303" t="str">
-        <v>Vermelho</v>
+        <v>Posição ao longo do trajeto (neutro no centro)</v>
       </c>
       <c r="C303" t="str">
-        <v>Vermelho</v>
+        <v>Posição ao longo do caminho (neutro no centro)</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>Green</v>
+        <v>Black-point compensated for this intent.</v>
       </c>
       <c r="B304" t="str">
-        <v>Verde</v>
+        <v>Compensação de ponto preto aplicada para esta intenção.</v>
       </c>
       <c r="C304" t="str">
-        <v>Verde</v>
+        <v>Compensação de ponto preto aplicada para esta intenção.</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>Blue</v>
+        <v>Ink Usage Statistics</v>
       </c>
       <c r="B305" t="str">
-        <v>Azul</v>
+        <v>Estatísticas de utilização de tinta</v>
       </c>
       <c r="C305" t="str">
-        <v>Azul</v>
+        <v>Estatísticas de uso de tinta</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>Black</v>
+        <v>How much of each colorant the profile lays down, as a sum and as a share of the total — the ink-consumption signature of the separation.</v>
       </c>
       <c r="B306" t="str">
-        <v>Preto</v>
+        <v>Quanto de cada corante o perfil deposita, como soma e como quota do total — a assinatura de consumo de tinta da separação.</v>
       </c>
       <c r="C306" t="str">
-        <v>Preto</v>
+        <v>Quanto de cada corante o perfil deposita, como soma e como parcela do total — a assinatura de consumo de tinta da separação.</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>Perceptual</v>
+        <v>Ink usage statistics are only available for output (printer) profiles.</v>
       </c>
       <c r="B307" t="str">
-        <v>Perceptual</v>
+        <v>As estatísticas de utilização de tinta só estão disponíveis para perfis de saída (impressora).</v>
       </c>
       <c r="C307" t="str">
-        <v>Perceptual</v>
+        <v>As estatísticas de uso de tinta só estão disponíveis para perfis de saída (impressora).</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>Relative Colorimetric</v>
+        <v>Neutral axis</v>
       </c>
       <c r="B308" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Eixo neutro</v>
       </c>
       <c r="C308" t="str">
-        <v>Colorimétrico relativo</v>
+        <v>Eixo neutro</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>Saturation</v>
+        <v>Mean coverage</v>
       </c>
       <c r="B309" t="str">
-        <v>Saturação</v>
+        <v>Cobertura média</v>
       </c>
       <c r="C309" t="str">
-        <v>Saturação</v>
+        <v>Cobertura média</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>Absolute Colorimetric</v>
+        <v>Share of ink</v>
       </c>
       <c r="B310" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Quota de tinta</v>
       </c>
       <c r="C310" t="str">
-        <v>Colorimétrico absoluto</v>
+        <v>Parcela de tinta</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>Profile Statistics</v>
+        <v>Share of ink is the neutral-build fingerprint — each colorant’s fraction of the total ink laid down, independent of the sample count.</v>
       </c>
       <c r="B311" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>A quota de tinta é a impressão digital da construção do neutro — a fração de cada corante no total de tinta depositada, independentemente do número de amostras.</v>
       </c>
       <c r="C311" t="str">
-        <v>Estatísticas do perfil</v>
+        <v>A parcela de tinta é a impressão digital da construção do neutro — a fração de cada corante no total de tinta depositada, independentemente do número de amostras.</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
+        <v>On &amp; in-gamut points</v>
       </c>
       <c r="B312" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Pontos dentro do gamute</v>
       </c>
       <c r="C312" t="str">
-        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
+        <v>Pontos dentro do gamute</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
+        <v>Ink usage across all in-gamut colours needs the B2A-direction gamut boundary, which is not yet built — pending.</v>
       </c>
       <c r="B313" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
+        <v>A utilização de tinta em todas as cores do gamute necessita da fronteira de gamute do lado B2A, ainda não implementada — pendente.</v>
       </c>
       <c r="C313" t="str">
-        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
+        <v>O uso de tinta em todas as cores do gamute precisa da fronteira de gamute do lado B2A, ainda não implementada — pendente.</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>Rendering intent</v>
+        <v>No colorant data to summarize.</v>
       </c>
       <c r="B314" t="str">
-        <v>Intenção de renderização</v>
+        <v>Sem dados de corante para resumir.</v>
       </c>
       <c r="C314" t="str">
-        <v>Intenção de renderização</v>
+        <v>Sem dados de corante para resumir.</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>Gamut volume (ΔE³)</v>
+        <v>Select a B2A (PCS→device) table below to also see a grayscale ink-coverage image for each colorant.</v>
       </c>
       <c r="B315" t="str">
-        <v>Volume de gamute (ΔE³)</v>
+        <v>Selecione uma tabela B2A (PCS→dispositivo) abaixo para ver também uma imagem em tons de cinzento da cobertura de tinta de cada corante.</v>
       </c>
       <c r="C315" t="str">
-        <v>Volume de gamut (ΔE³)</v>
+        <v>Selecione uma tabela B2A (PCS→dispositivo) abaixo para ver também uma imagem em tons de cinza da cobertura de tinta de cada corante.</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>Round-trip ΔE</v>
+        <v>Ink coverage of each colorant across the same lattice (darker = more ink).</v>
       </c>
       <c r="B316" t="str">
-        <v>ΔE de percurso</v>
+        <v>Cobertura de tinta de cada corante sobre a mesma grelha (mais escuro = mais tinta).</v>
       </c>
       <c r="C316" t="str">
-        <v>ΔE de percurso</v>
+        <v>Cobertura de tinta de cada corante sobre a mesma grade (mais escuro = mais tinta).</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
+        <v>Cyan</v>
       </c>
       <c r="B317" t="str">
-        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
+        <v>Ciano</v>
       </c>
       <c r="C317" t="str">
-        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
+        <v>Ciano</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>mean</v>
+        <v>Magenta</v>
       </c>
       <c r="B318" t="str">
-        <v>média</v>
+        <v>Magenta</v>
       </c>
       <c r="C318" t="str">
-        <v>média</v>
+        <v>Magenta</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>P90</v>
+        <v>Yellow</v>
       </c>
       <c r="B319" t="str">
-        <v>P90</v>
+        <v>Amarelo</v>
       </c>
       <c r="C319" t="str">
-        <v>P90</v>
+        <v>Amarelo</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>max</v>
+        <v>Red</v>
       </c>
       <c r="B320" t="str">
-        <v>máx.</v>
+        <v>Vermelho</v>
       </c>
       <c r="C320" t="str">
-        <v>máx.</v>
+        <v>Vermelho</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>Analysing…</v>
+        <v>Green</v>
       </c>
       <c r="B321" t="str">
-        <v>A analisar…</v>
+        <v>Verde</v>
       </c>
       <c r="C321" t="str">
-        <v>Analisando…</v>
+        <v>Verde</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>Analysis</v>
+        <v>Blue</v>
       </c>
       <c r="B322" t="str">
-        <v>Análise</v>
+        <v>Azul</v>
       </c>
       <c r="C322" t="str">
-        <v>Análise</v>
+        <v>Azul</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
+        <v>Black</v>
       </c>
       <c r="B323" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Preto</v>
       </c>
       <c r="C323" t="str">
-        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
+        <v>Preto</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>Plot</v>
+        <v>Perceptual</v>
       </c>
       <c r="B324" t="str">
-        <v>Gráfico</v>
+        <v>Perceptual</v>
       </c>
       <c r="C324" t="str">
-        <v>Gráfico</v>
+        <v>Perceptual</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>Raw Output</v>
+        <v>Relative Colorimetric</v>
       </c>
       <c r="B325" t="str">
-        <v>Saída em bruto</v>
+        <v>Colorimétrico relativo</v>
       </c>
       <c r="C325" t="str">
-        <v>Saída bruta</v>
+        <v>Colorimétrico relativo</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>XML</v>
+        <v>Saturation</v>
       </c>
       <c r="B326" t="str">
-        <v>XML</v>
+        <v>Saturação</v>
       </c>
       <c r="C326" t="str">
-        <v>XML</v>
+        <v>Saturação</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>JSON</v>
+        <v>Absolute Colorimetric</v>
       </c>
       <c r="B327" t="str">
-        <v>JSON</v>
+        <v>Colorimétrico absoluto</v>
       </c>
       <c r="C327" t="str">
-        <v>JSON</v>
+        <v>Colorimétrico absoluto</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>Curves</v>
+        <v>Profile Statistics</v>
       </c>
       <c r="B328" t="str">
-        <v>Curvas</v>
+        <v>Estatísticas do perfil</v>
       </c>
       <c r="C328" t="str">
-        <v>Curvas</v>
+        <v>Estatísticas do perfil</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>Input curves</v>
+        <v>Whole-profile metrics per rendering intent: the gamut volume enclosed by the device→PCS transform (ΔE*ab³), and the B2A round-trip accuracy — ΔE*ab of a Lab → device → Lab round trip through the profile.</v>
       </c>
       <c r="B329" t="str">
-        <v>Curvas de entrada</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamute delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a exatidão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
       <c r="C329" t="str">
-        <v>Curvas de entrada</v>
+        <v>Métricas de todo o perfil por intenção de renderização: o volume de gamut delimitado pela transformação dispositivo→PCS (ΔE*ab³) e a precisão do percurso B2A — ΔE*ab de um percurso Lab → dispositivo → Lab através do perfil.</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>Output curves</v>
+        <v>No device↔PCS CLUTs in this profile — profile statistics do not apply (e.g. a matrix/TRC display profile).</v>
       </c>
       <c r="B330" t="str">
-        <v>Curvas de saída</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de ecrã matriz/TRC).</v>
       </c>
       <c r="C330" t="str">
-        <v>Curvas de saída</v>
+        <v>Este perfil não tem CLUTs dispositivo↔PCS — as estatísticas do perfil não se aplicam (por exemplo, um perfil de tela matriz/TRC).</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>CLUT image</v>
+        <v>Rendering intent</v>
       </c>
       <c r="B331" t="str">
-        <v>Imagem CLUT</v>
+        <v>Intenção de renderização</v>
       </c>
       <c r="C331" t="str">
-        <v>Imagem CLUT</v>
+        <v>Intenção de renderização</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>Gamut image</v>
+        <v>Gamut volume (ΔE³)</v>
       </c>
       <c r="B332" t="str">
-        <v>Imagem de gamut</v>
+        <v>Volume de gamute (ΔE³)</v>
       </c>
       <c r="C332" t="str">
-        <v>Imagem de gamut</v>
+        <v>Volume de gamut (ΔE³)</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>Chromaticity</v>
+        <v>Round-trip ΔE</v>
       </c>
       <c r="B333" t="str">
-        <v>Cromaticidade</v>
+        <v>ΔE de percurso</v>
       </c>
       <c r="C333" t="str">
-        <v>Cromaticidade</v>
+        <v>ΔE de percurso</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>Scatter plot</v>
+        <v>The gamut boundary collapsed or was mostly undefined, so this gamut volume is unreliable.</v>
       </c>
       <c r="B334" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>A fronteira do gamute colapsou ou ficou maioritariamente indefinida, pelo que este volume de gamute não é fiável.</v>
       </c>
       <c r="C334" t="str">
-        <v>Gráfico de dispersão</v>
+        <v>A fronteira do gamut colapsou ou ficou majoritariamente indefinida, então este volume de gamut não é confiável.</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>Tone response curve</v>
+        <v>mean</v>
       </c>
       <c r="B335" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>média</v>
       </c>
       <c r="C335" t="str">
-        <v>Curva de resposta tonal</v>
+        <v>média</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>Curve table</v>
+        <v>P90</v>
       </c>
       <c r="B336" t="str">
-        <v>Tabela da curva</v>
+        <v>P90</v>
       </c>
       <c r="C336" t="str">
-        <v>Tabela da curva</v>
+        <v>P90</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>Tables</v>
+        <v>max</v>
       </c>
       <c r="B337" t="str">
-        <v>Tabelas</v>
+        <v>máx.</v>
       </c>
       <c r="C337" t="str">
-        <v>Tabelas</v>
+        <v>máx.</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>Data</v>
+        <v>Analysing…</v>
       </c>
       <c r="B338" t="str">
-        <v>Dados</v>
+        <v>A analisar…</v>
       </c>
       <c r="C338" t="str">
-        <v>Dados</v>
+        <v>Analisando…</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>Evaluate</v>
+        <v>Analysis</v>
       </c>
       <c r="B339" t="str">
-        <v>Avaliar</v>
+        <v>Análise</v>
       </c>
       <c r="C339" t="str">
-        <v>Avaliar</v>
+        <v>Análise</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>Loading…</v>
+        <v>Profile-wide quality analyses derived from the device-to-PCS transform.</v>
       </c>
       <c r="B340" t="str">
-        <v>A carregar…</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
       <c r="C340" t="str">
-        <v>Carregando…</v>
+        <v>Análises de qualidade de todo o perfil, derivadas da transformação dispositivo→PCS.</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>Input</v>
+        <v>Plot</v>
       </c>
       <c r="B341" t="str">
-        <v>Entrada</v>
+        <v>Gráfico</v>
       </c>
       <c r="C341" t="str">
-        <v>Entrada</v>
+        <v>Gráfico</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>Output</v>
+        <v>Raw Output</v>
       </c>
       <c r="B342" t="str">
-        <v>Saída</v>
+        <v>Saída em bruto</v>
       </c>
       <c r="C342" t="str">
-        <v>Saída</v>
+        <v>Saída bruta</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>Floating point</v>
+        <v>XML</v>
       </c>
       <c r="B343" t="str">
-        <v>Vírgula flutuante</v>
+        <v>XML</v>
       </c>
       <c r="C343" t="str">
-        <v>Ponto flutuante</v>
+        <v>XML</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>Grid point</v>
+        <v>JSON</v>
       </c>
       <c r="B344" t="str">
-        <v>Ponto da grelha</v>
+        <v>JSON</v>
       </c>
       <c r="C344" t="str">
-        <v>Ponto da grade</v>
+        <v>JSON</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>Normalized</v>
+        <v>Curves</v>
       </c>
       <c r="B345" t="str">
-        <v>Normalizado</v>
+        <v>Curvas</v>
       </c>
       <c r="C345" t="str">
-        <v>Normalizado</v>
+        <v>Curvas</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>Human</v>
+        <v>Input curves</v>
       </c>
       <c r="B346" t="str">
-        <v>Legível</v>
+        <v>Curvas de entrada</v>
       </c>
       <c r="C346" t="str">
-        <v>Legível</v>
+        <v>Curvas de entrada</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>Device → PCS</v>
+        <v>Output curves</v>
       </c>
       <c r="B347" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Curvas de saída</v>
       </c>
       <c r="C347" t="str">
-        <v>Dispositivo → PCS</v>
+        <v>Curvas de saída</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>PCS → Device</v>
+        <v>CLUT image</v>
       </c>
       <c r="B348" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Imagem CLUT</v>
       </c>
       <c r="C348" t="str">
-        <v>PCS → Dispositivo</v>
+        <v>Imagem CLUT</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>No CLUT grid</v>
+        <v>Gamut image</v>
       </c>
       <c r="B349" t="str">
-        <v>Sem grelha CLUT</v>
+        <v>Imagem de gamut</v>
       </c>
       <c r="C349" t="str">
-        <v>Sem grade CLUT</v>
+        <v>Imagem de gamut</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>Loading…</v>
+        <v>Chromaticity</v>
       </c>
       <c r="B350" t="str">
-        <v>A carregar…</v>
+        <v>Cromaticidade</v>
       </c>
       <c r="C350" t="str">
-        <v>Carregando…</v>
+        <v>Cromaticidade</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>Neutral = in gamut · red = out of gamut</v>
+        <v>Scatter plot</v>
       </c>
       <c r="B351" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Gráfico de dispersão</v>
       </c>
       <c r="C351" t="str">
-        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
+        <v>Gráfico de dispersão</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>Invalid profile URL:</v>
+        <v>Tone response curve</v>
       </c>
       <c r="B352" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Curva de resposta tonal</v>
       </c>
       <c r="C352" t="str">
-        <v>URL de perfil inválido:</v>
+        <v>Curva de resposta tonal</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>Could not fetch the profile from</v>
+        <v>Curve table</v>
       </c>
       <c r="B353" t="str">
-        <v>Não foi possível obter o perfil de</v>
+        <v>Tabela da curva</v>
       </c>
       <c r="C353" t="str">
-        <v>Não foi possível buscar o perfil de</v>
+        <v>Tabela da curva</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>Load an ICC profile from this external site?</v>
+        <v>Tables</v>
       </c>
       <c r="B354" t="str">
-        <v>Carregar um perfil ICC a partir deste site externo?</v>
+        <v>Tabelas</v>
       </c>
       <c r="C354" t="str">
-        <v>Carregar um perfil ICC deste site externo?</v>
+        <v>Tabelas</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>Loading Profile Assessment WG report…</v>
+        <v>Data</v>
       </c>
       <c r="B355" t="str">
-        <v>A carregar o relatório Profile Assessment WG…</v>
+        <v>Dados</v>
       </c>
       <c r="C355" t="str">
-        <v>Carregando o relatório Profile Assessment WG…</v>
+        <v>Dados</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>Running Profile Assessment WG checks…</v>
+        <v>Evaluate</v>
       </c>
       <c r="B356" t="str">
-        <v>A executar as verificações Profile Assessment WG…</v>
+        <v>Avaliar</v>
       </c>
       <c r="C356" t="str">
-        <v>Executando as verificações Profile Assessment WG…</v>
+        <v>Avaliar</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>Profile Assessment WG Report</v>
+        <v>Loading…</v>
       </c>
       <c r="B357" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>A carregar…</v>
       </c>
       <c r="C357" t="str">
-        <v>Relatório Profile Assessment WG</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>Security</v>
+        <v>Input</v>
       </c>
       <c r="B358" t="str">
-        <v>Segurança</v>
+        <v>Entrada</v>
       </c>
       <c r="C358" t="str">
-        <v>Segurança</v>
+        <v>Entrada</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>Conformance</v>
+        <v>Output</v>
       </c>
       <c r="B359" t="str">
-        <v>Conformidade</v>
+        <v>Saída</v>
       </c>
       <c r="C359" t="str">
-        <v>Conformidade</v>
+        <v>Saída</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>Quality</v>
+        <v>Floating point</v>
       </c>
       <c r="B360" t="str">
-        <v>Qualidade</v>
+        <v>Vírgula flutuante</v>
       </c>
       <c r="C360" t="str">
-        <v>Qualidade</v>
+        <v>Ponto flutuante</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>REPORT</v>
+        <v>Grid point</v>
       </c>
       <c r="B361" t="str">
-        <v>RELATÓRIO</v>
+        <v>Ponto da grelha</v>
       </c>
       <c r="C361" t="str">
-        <v>RELATÓRIO</v>
+        <v>Ponto da grade</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>FAIL</v>
+        <v>Normalized</v>
       </c>
       <c r="B362" t="str">
-        <v>REPROVADO</v>
+        <v>Normalizado</v>
       </c>
       <c r="C362" t="str">
-        <v>REPROVADO</v>
+        <v>Normalizado</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>checks</v>
+        <v>Human</v>
       </c>
       <c r="B363" t="str">
-        <v>verificações</v>
+        <v>Legível</v>
       </c>
       <c r="C363" t="str">
-        <v>verificações</v>
+        <v>Legível</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
+        <v>Device → PCS</v>
       </c>
       <c r="B364" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Dispositivo → PCS</v>
       </c>
       <c r="C364" t="str">
-        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
+        <v>Dispositivo → PCS</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>ICC Profile Tool · powered by IccProfLib</v>
+        <v>PCS → Device</v>
       </c>
       <c r="B365" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>PCS → Dispositivo</v>
       </c>
       <c r="C365" t="str">
-        <v>Ferramenta de perfis ICC · com IccProfLib</v>
+        <v>PCS → Dispositivo</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>ICC Profile Tool</v>
+        <v>No CLUT grid</v>
       </c>
       <c r="B366" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Sem grelha CLUT</v>
       </c>
       <c r="C366" t="str">
-        <v>Ferramenta de perfis ICC</v>
+        <v>Sem grade CLUT</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>Powered by {lib}</v>
+        <v>Loading…</v>
       </c>
       <c r="B367" t="str">
-        <v>Com {lib}</v>
+        <v>A carregar…</v>
       </c>
       <c r="C367" t="str">
-        <v>Com {lib}</v>
+        <v>Carregando…</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>Subscribe</v>
+        <v>Neutral = in gamut · red = out of gamut</v>
       </c>
       <c r="B368" t="str">
-        <v>Subscrever</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
       <c r="C368" t="str">
-        <v>Inscrever-se</v>
+        <v>Neutro = dentro do gamut · vermelho = fora do gamut</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>Get notified about new profiletool releases</v>
+        <v>Invalid profile URL:</v>
       </c>
       <c r="B369" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>URL de perfil inválido:</v>
       </c>
       <c r="C369" t="str">
-        <v>Receber notificações sobre novas versões do profiletool</v>
+        <v>URL de perfil inválido:</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>Get notified about new releases</v>
+        <v>Could not fetch the profile from</v>
       </c>
       <c r="B370" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Não foi possível obter o perfil de</v>
       </c>
       <c r="C370" t="str">
-        <v>Receber notificações sobre novas versões</v>
+        <v>Não foi possível buscar o perfil de</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>Close</v>
+        <v>Load an ICC profile from this external site?</v>
       </c>
       <c r="B371" t="str">
-        <v>Fechar</v>
+        <v>Carregar um perfil ICC a partir deste site externo?</v>
       </c>
       <c r="C371" t="str">
-        <v>Fechar</v>
+        <v>Carregar um perfil ICC deste site externo?</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
+        <v>Loading Profile Assessment WG report…</v>
       </c>
       <c r="B372" t="str">
-        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
+        <v>A carregar o relatório Profile Assessment WG…</v>
       </c>
       <c r="C372" t="str">
-        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
+        <v>Carregando o relatório Profile Assessment WG…</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>Email address</v>
+        <v>Running Profile Assessment WG checks…</v>
       </c>
       <c r="B373" t="str">
-        <v>Endereço de e-mail</v>
+        <v>A executar as verificações Profile Assessment WG…</v>
       </c>
       <c r="C373" t="str">
-        <v>Endereço de e-mail</v>
+        <v>Executando as verificações Profile Assessment WG…</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>you@example.com</v>
+        <v>Profile Assessment WG Report</v>
       </c>
       <c r="B374" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
       <c r="C374" t="str">
-        <v>voce@exemplo.com</v>
+        <v>Relatório Profile Assessment WG</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>How will you use profiletool?</v>
+        <v>Security</v>
       </c>
       <c r="B375" t="str">
-        <v>Como vai utilizar o profiletool?</v>
+        <v>Segurança</v>
       </c>
       <c r="C375" t="str">
-        <v>Como você vai usar o profiletool?</v>
+        <v>Segurança</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>(optional)</v>
+        <v>Conformance</v>
       </c>
       <c r="B376" t="str">
-        <v>(opcional)</v>
+        <v>Conformidade</v>
       </c>
       <c r="C376" t="str">
-        <v>(opcional)</v>
+        <v>Conformidade</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>e.g. evaluating ICC profiles for press calibration</v>
+        <v>Quality</v>
       </c>
       <c r="B377" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
+        <v>Qualidade</v>
       </c>
       <c r="C377" t="str">
-        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
+        <v>Qualidade</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
+        <v>REPORT</v>
       </c>
       <c r="B378" t="str">
-        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
+        <v>RELATÓRIO</v>
       </c>
       <c r="C378" t="str">
-        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
+        <v>RELATÓRIO</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>Cancel</v>
+        <v>FAIL</v>
       </c>
       <c r="B379" t="str">
-        <v>Cancelar</v>
+        <v>REPROVADO</v>
       </c>
       <c r="C379" t="str">
-        <v>Cancelar</v>
+        <v>REPROVADO</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>Subscribe</v>
+        <v>checks</v>
       </c>
       <c r="B380" t="str">
-        <v>Subscrever</v>
+        <v>verificações</v>
       </c>
       <c r="C380" t="str">
-        <v>Inscrever-se</v>
+        <v>verificações</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>Thanks — we’ll be in touch.</v>
+        <v>Generated by iccPawgReport (iccDEV) · ICC Profile Assessment Working Group checklist.</v>
       </c>
       <c r="B381" t="str">
-        <v>Obrigado — entraremos em contacto.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
       <c r="C381" t="str">
-        <v>Obrigado — entraremos em contato.</v>
+        <v>Gerado por iccPawgReport (iccDEV) · lista de verificação do ICC Profile Assessment Working Group.</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
+        <v>ICC Profile Tool · powered by IccProfLib</v>
       </c>
       <c r="B382" t="str">
-        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
       <c r="C382" t="str">
-        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
+        <v>Ferramenta de perfis ICC · com IccProfLib</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>Close</v>
+        <v>ICC Profile Tool</v>
       </c>
       <c r="B383" t="str">
-        <v>Fechar</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
       <c r="C383" t="str">
-        <v>Fechar</v>
+        <v>Ferramenta de perfis ICC</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>Privacy notice</v>
+        <v>Powered by {lib}</v>
       </c>
       <c r="B384" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Com {lib}</v>
       </c>
       <c r="C384" t="str">
-        <v>Aviso de privacidade</v>
+        <v>Com {lib}</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>Please enter a valid email address.</v>
+        <v>Subscribe</v>
       </c>
       <c r="B385" t="str">
-        <v>Introduza um endereço de e-mail válido.</v>
+        <v>Subscrever</v>
       </c>
       <c r="C385" t="str">
-        <v>Insira um endereço de e-mail válido.</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>Too many requests. Please try again later.</v>
+        <v>Get notified about new profiletool releases</v>
       </c>
       <c r="B386" t="str">
-        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
       <c r="C386" t="str">
-        <v>Muitas solicitações. Tente novamente mais tarde.</v>
+        <v>Receber notificações sobre novas versões do profiletool</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>Please check the form and try again.</v>
+        <v>Get notified about new releases</v>
       </c>
       <c r="B387" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
       <c r="C387" t="str">
-        <v>Verifique o formulário e tente novamente.</v>
+        <v>Receber notificações sobre novas versões</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>Could not send your request. Please try again.</v>
+        <v>Close</v>
       </c>
       <c r="B388" t="str">
-        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
+        <v>Fechar</v>
       </c>
       <c r="C388" t="str">
-        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>Network error. Please try again.</v>
+        <v>We’ll email you when a new major or minor profiletool release ships. Patch releases are skipped. Your address is reviewed manually before being added.</v>
       </c>
       <c r="B389" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Enviar-lhe-emos um e-mail quando for lançada uma nova versão principal ou secundária do profiletool. As versões de correção são ignoradas. O seu endereço é revisto manualmente antes de ser adicionado.</v>
       </c>
       <c r="C389" t="str">
-        <v>Erro de rede. Tente novamente.</v>
+        <v>Vamos enviar um e-mail quando uma nova versão principal ou secundária do profiletool for lançada. Versões de correção são puladas. Seu endereço é revisado manualmente antes de ser adicionado.</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>Error:</v>
+        <v>Email address</v>
       </c>
       <c r="B390" t="str">
-        <v>Erro:</v>
+        <v>Endereço de e-mail</v>
       </c>
       <c r="C390" t="str">
-        <v>Erro:</v>
+        <v>Endereço de e-mail</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>Convert to XML</v>
+        <v>you@example.com</v>
       </c>
       <c r="B391" t="str">
-        <v>Converter para XML</v>
+        <v>voce@exemplo.com</v>
       </c>
       <c r="C391" t="str">
-        <v>Converter para XML</v>
+        <v>voce@exemplo.com</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>Convert to JSON</v>
+        <v>How will you use profiletool?</v>
       </c>
       <c r="B392" t="str">
-        <v>Converter para JSON</v>
+        <v>Como vai utilizar o profiletool?</v>
       </c>
       <c r="C392" t="str">
-        <v>Converter para JSON</v>
+        <v>Como você vai usar o profiletool?</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>Convert to ICC</v>
+        <v>(optional)</v>
       </c>
       <c r="B393" t="str">
-        <v>Converter para ICC</v>
+        <v>(opcional)</v>
       </c>
       <c r="C393" t="str">
-        <v>Converter para ICC</v>
+        <v>(opcional)</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>Converting to XML…</v>
+        <v>e.g. evaluating ICC profiles for press calibration</v>
       </c>
       <c r="B394" t="str">
-        <v>A converter para XML…</v>
+        <v>p. ex. avaliar perfis ICC para calibração de impressão</v>
       </c>
       <c r="C394" t="str">
-        <v>Convertendo para XML…</v>
+        <v>p. ex. avaliar perfis ICC para calibração de prensa</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>Converting to JSON…</v>
+        <v>I agree to receive emails about profiletool releases. I can unsubscribe at any time.</v>
       </c>
       <c r="B395" t="str">
-        <v>A converter para JSON…</v>
+        <v>Aceito receber e-mails sobre as versões do profiletool. Posso cancelar a subscrição a qualquer momento.</v>
       </c>
       <c r="C395" t="str">
-        <v>Convertendo para JSON…</v>
+        <v>Concordo em receber e-mails sobre as versões do profiletool. Posso cancelar a inscrição a qualquer momento.</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>Converting to ICC…</v>
+        <v>Cancel</v>
       </c>
       <c r="B396" t="str">
-        <v>A converter para ICC…</v>
+        <v>Cancelar</v>
       </c>
       <c r="C396" t="str">
-        <v>Convertendo para ICC…</v>
+        <v>Cancelar</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>Load ICC profile</v>
+        <v>Subscribe</v>
       </c>
       <c r="B397" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Subscrever</v>
       </c>
       <c r="C397" t="str">
-        <v>Carregar perfil ICC</v>
+        <v>Inscrever-se</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>Drop zone for ICC profile files</v>
+        <v>Thanks — we’ll be in touch.</v>
       </c>
       <c r="B398" t="str">
-        <v>Zona de largada para ficheiros de perfil ICC</v>
+        <v>Obrigado — entraremos em contacto.</v>
       </c>
       <c r="C398" t="str">
-        <v>Área de soltar para arquivos de perfil ICC</v>
+        <v>Obrigado — entraremos em contato.</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>Profile ID</v>
+        <v>Once approved you’ll receive a welcome email. After that, you’ll only hear from us when a new profiletool release ships.</v>
       </c>
       <c r="B399" t="str">
-        <v>ID do perfil</v>
+        <v>Após a aprovação, receberá um e-mail de boas-vindas. Depois disso, só receberá mensagens quando for lançada uma nova versão do profiletool.</v>
       </c>
       <c r="C399" t="str">
-        <v>ID do perfil</v>
+        <v>Após a aprovação, você receberá um e-mail de boas-vindas. Depois, só receberá mensagens quando uma nova versão do profiletool for lançada.</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>No tags found.</v>
+        <v>Close</v>
       </c>
       <c r="B400" t="str">
-        <v>Nenhuma etiqueta encontrada.</v>
+        <v>Fechar</v>
       </c>
       <c r="C400" t="str">
-        <v>Nenhuma tag encontrada.</v>
+        <v>Fechar</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>Tag Name</v>
+        <v>Privacy notice</v>
       </c>
       <c r="B401" t="str">
-        <v>Nome da etiqueta</v>
+        <v>Aviso de privacidade</v>
       </c>
       <c r="C401" t="str">
-        <v>Nome da tag</v>
+        <v>Aviso de privacidade</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>ID</v>
+        <v>Please enter a valid email address.</v>
       </c>
       <c r="B402" t="str">
-        <v>ID</v>
+        <v>Introduza um endereço de e-mail válido.</v>
       </c>
       <c r="C402" t="str">
-        <v>ID</v>
+        <v>Insira um endereço de e-mail válido.</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>Offset</v>
+        <v>Too many requests. Please try again later.</v>
       </c>
       <c r="B403" t="str">
-        <v>Deslocamento</v>
+        <v>Demasiados pedidos. Tente novamente mais tarde.</v>
       </c>
       <c r="C403" t="str">
-        <v>Deslocamento</v>
+        <v>Muitas solicitações. Tente novamente mais tarde.</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>Size</v>
+        <v>Please check the form and try again.</v>
       </c>
       <c r="B404" t="str">
-        <v>Tamanho</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
       <c r="C404" t="str">
-        <v>Tamanho</v>
+        <v>Verifique o formulário e tente novamente.</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>Pad</v>
+        <v>Could not send your request. Please try again.</v>
       </c>
       <c r="B405" t="str">
-        <v>Preenchimento</v>
+        <v>Não foi possível enviar o seu pedido. Tente novamente.</v>
       </c>
       <c r="C405" t="str">
-        <v>Preenchimento</v>
+        <v>Não foi possível enviar sua solicitação. Tente novamente.</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>Bytes changed since load</v>
+        <v>Network error. Please try again.</v>
       </c>
       <c r="B406" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
       <c r="C406" t="str">
-        <v>Bytes alterados desde o carregamento</v>
+        <v>Erro de rede. Tente novamente.</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>Type</v>
+        <v>Error:</v>
       </c>
       <c r="B407" t="str">
-        <v>Tipo</v>
+        <v>Erro:</v>
       </c>
       <c r="C407" t="str">
-        <v>Tipo</v>
+        <v>Erro:</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>Array of {type}</v>
+        <v>Convert to XML</v>
       </c>
       <c r="B408" t="str">
-        <v>Vetor de {type}</v>
+        <v>Converter para XML</v>
       </c>
       <c r="C408" t="str">
-        <v>Array de {type}</v>
+        <v>Converter para XML</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>(No content)</v>
+        <v>Convert to JSON</v>
       </c>
       <c r="B409" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Converter para JSON</v>
       </c>
       <c r="C409" t="str">
-        <v>(Sem conteúdo)</v>
+        <v>Converter para JSON</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>bytes</v>
+        <v>Convert to ICC</v>
       </c>
       <c r="B410" t="str">
-        <v>bytes</v>
+        <v>Converter para ICC</v>
       </c>
       <c r="C410" t="str">
-        <v>bytes</v>
+        <v>Converter para ICC</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>Loading full description…</v>
+        <v>Converting to XML…</v>
       </c>
       <c r="B411" t="str">
-        <v>A carregar descrição completa…</v>
+        <v>A converter para XML…</v>
       </c>
       <c r="C411" t="str">
-        <v>Carregando descrição completa…</v>
+        <v>Convertendo para XML…</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>Could not load full description:</v>
+        <v>Converting to JSON…</v>
       </c>
       <c r="B412" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>A converter para JSON…</v>
       </c>
       <c r="C412" t="str">
-        <v>Não foi possível carregar a descrição completa:</v>
+        <v>Convertendo para JSON…</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
+        <v>Converting to ICC…</v>
       </c>
       <c r="B413" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
+        <v>A converter para ICC…</v>
       </c>
       <c r="C413" t="str">
-        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
+        <v>Convertendo para ICC…</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
+        <v>Load ICC profile</v>
       </c>
       <c r="B414" t="str">
-        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Carregar perfil ICC</v>
       </c>
       <c r="C414" t="str">
-        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
+        <v>Carregar perfil ICC</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>No validation output</v>
+        <v>Drop zone for ICC profile files</v>
       </c>
       <c r="B415" t="str">
-        <v>Sem saída de validação</v>
+        <v>Zona de largada para ficheiros de perfil ICC</v>
       </c>
       <c r="C415" t="str">
-        <v>Sem saída de validação</v>
+        <v>Área de soltar para arquivos de perfil ICC</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>Profile is valid</v>
+        <v>Profile ID</v>
       </c>
       <c r="B416" t="str">
-        <v>O perfil é válido</v>
+        <v>ID do perfil</v>
       </c>
       <c r="C416" t="str">
-        <v>O perfil é válido</v>
+        <v>ID do perfil</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>Profile has warning(s)</v>
+        <v>No tags found.</v>
       </c>
       <c r="B417" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Nenhuma etiqueta encontrada.</v>
       </c>
       <c r="C417" t="str">
-        <v>O perfil tem avisos</v>
+        <v>Nenhuma tag encontrada.</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>Profile is non-compliant</v>
+        <v>Tag Name</v>
       </c>
       <c r="B418" t="str">
-        <v>O perfil não é conforme</v>
+        <v>Nome da etiqueta</v>
       </c>
       <c r="C418" t="str">
-        <v>O perfil não está em conformidade</v>
+        <v>Nome da tag</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>Critical validation error</v>
+        <v>ID</v>
       </c>
       <c r="B419" t="str">
-        <v>Erro de validação crítico</v>
+        <v>ID</v>
       </c>
       <c r="C419" t="str">
-        <v>Erro de validação crítico</v>
+        <v>ID</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>Unknown validation status</v>
+        <v>Offset</v>
       </c>
       <c r="B420" t="str">
-        <v>Estado de validação desconhecido</v>
+        <v>Deslocamento</v>
       </c>
       <c r="C420" t="str">
-        <v>Status de validação desconhecido</v>
+        <v>Deslocamento</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>Critical — shown for inspection only</v>
+        <v>Size</v>
       </c>
       <c r="B421" t="str">
-        <v>Crítico — apresentado apenas para inspeção</v>
+        <v>Tamanho</v>
       </c>
       <c r="C421" t="str">
-        <v>Crítico — exibido apenas para inspeção</v>
+        <v>Tamanho</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>No warnings or errors found.</v>
+        <v>Pad</v>
       </c>
       <c r="B422" t="str">
-        <v>Sem avisos nem erros encontrados.</v>
+        <v>Preenchimento</v>
       </c>
       <c r="C422" t="str">
-        <v>Nenhum aviso ou erro encontrado.</v>
+        <v>Preenchimento</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>Valid</v>
+        <v>Bytes changed since load</v>
       </c>
       <c r="B423" t="str">
-        <v>Válido</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
       <c r="C423" t="str">
-        <v>Válido</v>
+        <v>Bytes alterados desde o carregamento</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>Warning</v>
+        <v>Type</v>
       </c>
       <c r="B424" t="str">
-        <v>Aviso</v>
+        <v>Tipo</v>
       </c>
       <c r="C424" t="str">
-        <v>Aviso</v>
+        <v>Tipo</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>Error</v>
+        <v>Array of {type}</v>
       </c>
       <c r="B425" t="str">
-        <v>Erro</v>
+        <v>Vetor de {type}</v>
       </c>
       <c r="C425" t="str">
-        <v>Erro</v>
+        <v>Array de {type}</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>Unknown</v>
+        <v>(No content)</v>
       </c>
       <c r="B426" t="str">
-        <v>Desconhecido</v>
+        <v>(Sem conteúdo)</v>
       </c>
       <c r="C426" t="str">
-        <v>Desconhecido</v>
+        <v>(Sem conteúdo)</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>Pass</v>
+        <v>bytes</v>
       </c>
       <c r="B427" t="str">
-        <v>Aprovado</v>
+        <v>bytes</v>
       </c>
       <c r="C427" t="str">
-        <v>Aprovado</v>
+        <v>bytes</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>Fail</v>
+        <v>Loading full description…</v>
       </c>
       <c r="B428" t="str">
-        <v>Reprovado</v>
+        <v>A carregar descrição completa…</v>
       </c>
       <c r="C428" t="str">
-        <v>Reprovado</v>
+        <v>Carregando descrição completa…</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>View in context</v>
+        <v>Could not load full description:</v>
       </c>
       <c r="B429" t="str">
-        <v>Ver no contexto</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
       <c r="C429" t="str">
-        <v>Ver no contexto</v>
+        <v>Não foi possível carregar a descrição completa:</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>Validation detail</v>
+        <v>This profile could not be fully parsed and must not be applied. The header and tag directory below are shown for inspection only.</v>
       </c>
       <c r="B430" t="str">
-        <v>Detalhe de validação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de etiquetas abaixo são apresentados apenas para inspeção.</v>
       </c>
       <c r="C430" t="str">
-        <v>Detalhe de validação</v>
+        <v>Este perfil não pôde ser totalmente analisado e não deve ser aplicado. O cabeçalho e o diretório de tags abaixo são exibidos apenas para inspeção.</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>Triggered by</v>
+        <v>Tag contents unavailable — the profile could not be fully parsed.</v>
       </c>
       <c r="B431" t="str">
-        <v>Acionado por</v>
+        <v>Conteúdo da etiqueta indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
       <c r="C431" t="str">
-        <v>Acionado por</v>
+        <v>Conteúdo da tag indisponível — o perfil não pôde ser totalmente analisado.</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>Field</v>
+        <v>No validation output</v>
       </c>
       <c r="B432" t="str">
-        <v>Campo</v>
+        <v>Sem saída de validação</v>
       </c>
       <c r="C432" t="str">
-        <v>Campo</v>
+        <v>Sem saída de validação</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>Current value</v>
+        <v>Profile is valid</v>
       </c>
       <c r="B433" t="str">
-        <v>Valor atual</v>
+        <v>O perfil é válido</v>
       </c>
       <c r="C433" t="str">
-        <v>Valor atual</v>
+        <v>O perfil é válido</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>Required: 0</v>
+        <v>Profile has warning(s)</v>
       </c>
       <c r="B434" t="str">
-        <v>Obrigatório: 0</v>
+        <v>O perfil tem avisos</v>
       </c>
       <c r="C434" t="str">
-        <v>Obrigatório: 0</v>
+        <v>O perfil tem avisos</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>Expected: {value}</v>
+        <v>Profile is non-compliant</v>
       </c>
       <c r="B435" t="str">
-        <v>Esperado: {value}</v>
+        <v>O perfil não é conforme</v>
       </c>
       <c r="C435" t="str">
-        <v>Esperado: {value}</v>
+        <v>O perfil não está em conformidade</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>Invalid</v>
+        <v>Critical validation error</v>
       </c>
       <c r="B436" t="str">
-        <v>Inválido</v>
+        <v>Erro de validação crítico</v>
       </c>
       <c r="C436" t="str">
-        <v>Inválido</v>
+        <v>Erro de validação crítico</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>This finding couldn't be tied to a specific field.</v>
+        <v>Unknown validation status</v>
       </c>
       <c r="B437" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Estado de validação desconhecido</v>
       </c>
       <c r="C437" t="str">
-        <v>Não foi possível associar este resultado a um campo específico.</v>
+        <v>Status de validação desconhecido</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>Close</v>
+        <v>Critical — shown for inspection only</v>
       </c>
       <c r="B438" t="str">
-        <v>Fechar</v>
+        <v>Crítico — apresentado apenas para inspeção</v>
       </c>
       <c r="C438" t="str">
-        <v>Fechar</v>
+        <v>Crítico — exibido apenas para inspeção</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>Loading XML editor…</v>
+        <v>No warnings or errors found.</v>
       </c>
       <c r="B439" t="str">
-        <v>A carregar o editor XML…</v>
+        <v>Sem avisos nem erros encontrados.</v>
       </c>
       <c r="C439" t="str">
-        <v>Carregando editor XML…</v>
+        <v>Nenhum aviso ou erro encontrado.</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>Loading JSON editor…</v>
+        <v>Valid</v>
       </c>
       <c r="B440" t="str">
-        <v>A carregar o editor JSON…</v>
+        <v>Válido</v>
       </c>
       <c r="C440" t="str">
-        <v>Carregando editor JSON…</v>
+        <v>Válido</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Warning</v>
       </c>
       <c r="B441" t="str">
-        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Aviso</v>
       </c>
       <c r="C441" t="str">
-        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Aviso</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+        <v>Error</v>
       </c>
       <c r="B442" t="str">
-        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+        <v>Erro</v>
       </c>
       <c r="C442" t="str">
-        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+        <v>Erro</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>● unsaved XML edits</v>
+        <v>Unknown</v>
       </c>
       <c r="B443" t="str">
-        <v>● edições XML por guardar</v>
+        <v>Desconhecido</v>
       </c>
       <c r="C443" t="str">
-        <v>● edições XML não salvas</v>
+        <v>Desconhecido</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>● unsaved JSON edits</v>
+        <v>Pass</v>
       </c>
       <c r="B444" t="str">
-        <v>● edições JSON por guardar</v>
+        <v>Aprovado</v>
       </c>
       <c r="C444" t="str">
-        <v>● edições JSON não salvas</v>
+        <v>Aprovado</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+        <v>Fail</v>
       </c>
       <c r="B445" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Reprovado</v>
       </c>
       <c r="C445" t="str">
-        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+        <v>Reprovado</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+        <v>View in context</v>
       </c>
       <c r="B446" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Ver no contexto</v>
       </c>
       <c r="C446" t="str">
-        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+        <v>Ver no contexto</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>indent</v>
+        <v>Validation detail</v>
       </c>
       <c r="B447" t="str">
-        <v>indentação</v>
+        <v>Detalhe de validação</v>
       </c>
       <c r="C447" t="str">
-        <v>indentação</v>
+        <v>Detalhe de validação</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>sort keys</v>
+        <v>Triggered by</v>
       </c>
       <c r="B448" t="str">
-        <v>ordenar chaves</v>
+        <v>Acionado por</v>
       </c>
       <c r="C448" t="str">
-        <v>ordenar chaves</v>
+        <v>Acionado por</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="str">
+        <v>Field</v>
+      </c>
+      <c r="B449" t="str">
+        <v>Campo</v>
+      </c>
+      <c r="C449" t="str">
+        <v>Campo</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>Current value</v>
+      </c>
+      <c r="B450" t="str">
+        <v>Valor atual</v>
+      </c>
+      <c r="C450" t="str">
+        <v>Valor atual</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>Required: 0</v>
+      </c>
+      <c r="B451" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+      <c r="C451" t="str">
+        <v>Obrigatório: 0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>Expected: {value}</v>
+      </c>
+      <c r="B452" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+      <c r="C452" t="str">
+        <v>Esperado: {value}</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>Invalid</v>
+      </c>
+      <c r="B453" t="str">
+        <v>Inválido</v>
+      </c>
+      <c r="C453" t="str">
+        <v>Inválido</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>This finding couldn't be tied to a specific field.</v>
+      </c>
+      <c r="B454" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+      <c r="C454" t="str">
+        <v>Não foi possível associar este resultado a um campo específico.</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>Close</v>
+      </c>
+      <c r="B455" t="str">
+        <v>Fechar</v>
+      </c>
+      <c r="C455" t="str">
+        <v>Fechar</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>Loading XML editor…</v>
+      </c>
+      <c r="B456" t="str">
+        <v>A carregar o editor XML…</v>
+      </c>
+      <c r="C456" t="str">
+        <v>Carregando editor XML…</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
+        <v>Loading JSON editor…</v>
+      </c>
+      <c r="B457" t="str">
+        <v>A carregar o editor JSON…</v>
+      </c>
+      <c r="C457" t="str">
+        <v>Carregando editor JSON…</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>You have unsaved XML edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B458" t="str">
+        <v>Tem edições XML por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C458" t="str">
+        <v>Você tem edições XML não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>You have unsaved JSON edits. Overwrite them with a fresh conversion from the ICC profile?</v>
+      </c>
+      <c r="B459" t="str">
+        <v>Tem edições JSON por guardar. Substituir por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+      <c r="C459" t="str">
+        <v>Você tem edições JSON não salvas. Substituí-las por uma nova conversão a partir do perfil ICC?</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>● unsaved XML edits</v>
+      </c>
+      <c r="B460" t="str">
+        <v>● edições XML por guardar</v>
+      </c>
+      <c r="C460" t="str">
+        <v>● edições XML não salvas</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>● unsaved JSON edits</v>
+      </c>
+      <c r="B461" t="str">
+        <v>● edições JSON por guardar</v>
+      </c>
+      <c r="C461" t="str">
+        <v>● edições JSON não salvas</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>Click &lt;em&gt;Convert to XML&lt;/em&gt; to generate an editable XML representation of this profile. The XML is produced by the same IccLibXML code path used by the upstream &lt;code&gt;IccToXml&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B462" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+      <c r="C462" t="str">
+        <v>Clique em &lt;em&gt;Converter para XML&lt;/em&gt; para gerar uma representação XML editável deste perfil. O XML é produzido pelo mesmo caminho de código IccLibXML usado pela ferramenta &lt;code&gt;IccToXml&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
+        <v>Click &lt;em&gt;Convert to JSON&lt;/em&gt; to generate an editable JSON representation of this profile. The JSON is produced by the same IccLibJSON code path used by the upstream &lt;code&gt;IccToJson&lt;/code&gt; tool.</v>
+      </c>
+      <c r="B463" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+      <c r="C463" t="str">
+        <v>Clique em &lt;em&gt;Converter para JSON&lt;/em&gt; para gerar uma representação JSON editável deste perfil. O JSON é produzido pelo mesmo caminho de código IccLibJSON usado pela ferramenta &lt;code&gt;IccToJson&lt;/code&gt;.</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>indent</v>
+      </c>
+      <c r="B464" t="str">
+        <v>indentação</v>
+      </c>
+      <c r="C464" t="str">
+        <v>indentação</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
+        <v>sort keys</v>
+      </c>
+      <c r="B465" t="str">
+        <v>ordenar chaves</v>
+      </c>
+      <c r="C465" t="str">
+        <v>ordenar chaves</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
         <v>Profile written from edits, but re-validation failed:</v>
       </c>
-      <c r="B449" t="str">
+      <c r="B466" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
-      <c r="C449" t="str">
+      <c r="C466" t="str">
         <v>Perfil gravado a partir das edições, mas a revalidação falhou:</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C449"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C466"/>
   </ignoredErrors>
 </worksheet>
 </file>